--- a/Permanents-Vacataires-ELT2-2026-2027.xlsx
+++ b/Permanents-Vacataires-ELT2-2026-2027.xlsx
@@ -394,7 +394,7 @@
     <t>ahmassoum@yahoo.fr</t>
   </si>
   <si>
-    <t>MILOUA</t>
+    <t>MILOUA FARID</t>
   </si>
   <si>
     <t>milouafarid@gmail.com</t>
@@ -3300,7 +3300,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="26" ht="31.5" spans="1:7">
+    <row r="26" ht="31.5" hidden="1" spans="1:7">
       <c r="A26" s="24">
         <v>25</v>
       </c>
@@ -3549,7 +3549,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="37" ht="15.75" hidden="1" spans="1:7">
+    <row r="37" ht="15.75" spans="1:7">
       <c r="A37" s="24">
         <v>36</v>
       </c>
@@ -9608,9 +9608,9 @@
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G127" etc:filterBottomFollowUsedRange="0">
     <filterColumn colId="1">
-      <customFilters>
-        <customFilter operator="equal" val="FELLAH MOHAMMED KARIM"/>
-      </customFilters>
+      <filters>
+        <filter val="MILOUA"/>
+      </filters>
     </filterColumn>
     <extLst/>
   </autoFilter>

--- a/Permanents-Vacataires-ELT2-2026-2027.xlsx
+++ b/Permanents-Vacataires-ELT2-2026-2027.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="733" uniqueCount="463">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="733" uniqueCount="466">
   <si>
     <t>N°</t>
   </si>
@@ -55,7 +55,7 @@
     <t>N°/TEL</t>
   </si>
   <si>
-    <t>ABID</t>
+    <t>ABID MOHAMED</t>
   </si>
   <si>
     <t>MOHAMED</t>
@@ -73,7 +73,7 @@
     <t>RAS</t>
   </si>
   <si>
-    <t>AKSA</t>
+    <t>AKSA WESSIM</t>
   </si>
   <si>
     <t>WESSIM</t>
@@ -85,7 +85,7 @@
     <t>Corrigé</t>
   </si>
   <si>
-    <t>ARDJOUN</t>
+    <t>ARDJOUN SID AHMED</t>
   </si>
   <si>
     <t>SID AHMED</t>
@@ -94,7 +94,7 @@
     <t>ardjoun.s.e.m@gmail.com</t>
   </si>
   <si>
-    <t>AYAD</t>
+    <t>AYAD ABDELGHANI</t>
   </si>
   <si>
     <t>ABDELGHANI</t>
@@ -103,7 +103,7 @@
     <t>ayad_abdelghani@yahoo.fr</t>
   </si>
   <si>
-    <t>AZAIZ</t>
+    <t>AZAIZ AHMED</t>
   </si>
   <si>
     <t>AHMED</t>
@@ -112,7 +112,7 @@
     <t>ahazaiz2011@yahoo.fr</t>
   </si>
   <si>
-    <t>BADIS</t>
+    <t>BADIS KARIMA</t>
   </si>
   <si>
     <t>KARIMA</t>
@@ -130,7 +130,7 @@
     <t>0560337902</t>
   </si>
   <si>
-    <t>BAHLIL</t>
+    <t>BAHLIL MOUNIR</t>
   </si>
   <si>
     <t>MOUNIR</t>
@@ -142,7 +142,7 @@
     <t>0672447184</t>
   </si>
   <si>
-    <t>BECHEKIR</t>
+    <t>BECHEKIR SEYFEDDINE</t>
   </si>
   <si>
     <t>SEYFEDDINE</t>
@@ -154,7 +154,7 @@
     <t>seyfeddine.electrotechnique@gmail.com</t>
   </si>
   <si>
-    <t>BEDDAD</t>
+    <t>BEDDAD BOUCIF</t>
   </si>
   <si>
     <t>BOUCIF</t>
@@ -166,7 +166,7 @@
     <t>0665458282</t>
   </si>
   <si>
-    <t>BELLEBNA</t>
+    <t>BELLEBNA YASSINE</t>
   </si>
   <si>
     <t>YASSINE</t>
@@ -175,7 +175,7 @@
     <t>fgevdpg@gmail.com</t>
   </si>
   <si>
-    <t>BENAISSA</t>
+    <t>BENAISSA ABDELKADER</t>
   </si>
   <si>
     <t>ABDELKADER</t>
@@ -184,7 +184,7 @@
     <t>aek_benaissa@yahoo.fr</t>
   </si>
   <si>
-    <t>BERRAHAL</t>
+    <t>BERRAHAL BEL ABBES</t>
   </si>
   <si>
     <t>BEL ABBES</t>
@@ -193,7 +193,7 @@
     <t>dept.eln@gmail.com</t>
   </si>
   <si>
-    <t>BENBELLIL</t>
+    <t>BENBELLIL NADJAT</t>
   </si>
   <si>
     <t>NADJAT</t>
@@ -202,7 +202,7 @@
     <t xml:space="preserve">nn.nn.phy.chi@gmail.com </t>
   </si>
   <si>
-    <t>BENDAOUD</t>
+    <t>BENDAOUD ABDELBER</t>
   </si>
   <si>
     <t>ABDELBER</t>
@@ -211,7 +211,7 @@
     <t>babdelber22@yahoo.fr</t>
   </si>
   <si>
-    <t>BENDIMERAD</t>
+    <t>BENDIMERAD SALAH EDDINE</t>
   </si>
   <si>
     <t>SALAH EDDINE</t>
@@ -220,7 +220,7 @@
     <t>s_bendimerad@yahoo.fr</t>
   </si>
   <si>
-    <t>BENGRIT</t>
+    <t>BENGRIT MALIKA</t>
   </si>
   <si>
     <t>MALIKA</t>
@@ -232,7 +232,7 @@
     <t>malikabengrit@gmail.com</t>
   </si>
   <si>
-    <t>BENHAMIDA</t>
+    <t>BENHAMIDA FARID</t>
   </si>
   <si>
     <t>FARID</t>
@@ -241,7 +241,7 @@
     <t>farid.benhamida@yahoo.fr</t>
   </si>
   <si>
-    <t>BENKHALLOUK</t>
+    <t>BENKHALLOUK KADDOUR</t>
   </si>
   <si>
     <t>KADDOUR</t>
@@ -250,7 +250,7 @@
     <t>benkh_ka@yahoo.fr</t>
   </si>
   <si>
-    <t>BENTAALLAH</t>
+    <t>BENTAALLAH ABDERRAHIM</t>
   </si>
   <si>
     <t>ABDERRAHIM</t>
@@ -259,7 +259,7 @@
     <t>bentaallah65@yahoo.fr</t>
   </si>
   <si>
-    <t>BERMAKI</t>
+    <t>BERMAKI HAMZA</t>
   </si>
   <si>
     <t>HAMZA</t>
@@ -268,7 +268,7 @@
     <t>bermaki.hamza@gmail.com</t>
   </si>
   <si>
-    <t>BOUKHOULDA</t>
+    <t>BOUKHOULDA FODIL</t>
   </si>
   <si>
     <t>FODIL</t>
@@ -277,7 +277,7 @@
     <t>boukhoulda.fodil@yahoo.fr</t>
   </si>
   <si>
-    <t>BOUNOUA</t>
+    <t>BOUNOUA HOURIA</t>
   </si>
   <si>
     <t>HOURIA</t>
@@ -286,7 +286,7 @@
     <t>hsemmach@yahoo.fr</t>
   </si>
   <si>
-    <t>DJERIRI</t>
+    <t>DJERIRI YOUCEF</t>
   </si>
   <si>
     <t>YOUCEF</t>
@@ -295,7 +295,7 @@
     <t>djeriri_youcef@yahoo.fr</t>
   </si>
   <si>
-    <t>DRIEF</t>
+    <t>DRIEF FAIZA</t>
   </si>
   <si>
     <t>FAIZA</t>
@@ -313,7 +313,7 @@
     <t>mkfellah@gmail.com</t>
   </si>
   <si>
-    <t>GHAZEL</t>
+    <t>GHAZEL FATIHA</t>
   </si>
   <si>
     <t>FATIHA</t>
@@ -322,7 +322,7 @@
     <t>nour73_fac@yahoo.fr</t>
   </si>
   <si>
-    <t>HADJERI</t>
+    <t>HADJERI SAMIR</t>
   </si>
   <si>
     <t>SAMIR</t>
@@ -331,7 +331,7 @@
     <t>shadjeri2@yahoo.fr</t>
   </si>
   <si>
-    <t>HANAFI</t>
+    <t>HANAFI SALAH</t>
   </si>
   <si>
     <t>SALAH</t>
@@ -340,7 +340,7 @@
     <t xml:space="preserve">sal_hanafi@outlook.com </t>
   </si>
   <si>
-    <t>HASSANI</t>
+    <t>HASSANI NAIMA</t>
   </si>
   <si>
     <t>NAIMA</t>
@@ -349,7 +349,7 @@
     <t>naimahassani69@yahoo.fr</t>
   </si>
   <si>
-    <t>JBILOU</t>
+    <t>JBILOU MOKHTARIA</t>
   </si>
   <si>
     <t>MOKHTARIA</t>
@@ -358,13 +358,13 @@
     <t>harmel71@yahoo.fr</t>
   </si>
   <si>
-    <t>KHATIR</t>
+    <t>KHATIR MOHAMED</t>
   </si>
   <si>
     <t xml:space="preserve">med_khatir@yahoo.fr </t>
   </si>
   <si>
-    <t>LALEDJ</t>
+    <t>LALEDJ NADJET</t>
   </si>
   <si>
     <t>NADJET</t>
@@ -373,7 +373,7 @@
     <t>nadjet_69@hotmail.fr</t>
   </si>
   <si>
-    <t>M.BRAHAMI</t>
+    <t>M.BRAHAMI MOSTEFA</t>
   </si>
   <si>
     <t>MOSTEFA</t>
@@ -382,13 +382,13 @@
     <t>mbrahami@yahoo.com</t>
   </si>
   <si>
-    <t>MAAMMAR</t>
+    <t>MAAMMAR MOHAMED</t>
   </si>
   <si>
     <t>mohamed.maammar@gmail.com</t>
   </si>
   <si>
-    <t>MASSOUM</t>
+    <t>MASSOUM AHMED</t>
   </si>
   <si>
     <t>ahmassoum@yahoo.fr</t>
@@ -400,7 +400,7 @@
     <t>milouafarid@gmail.com</t>
   </si>
   <si>
-    <t>MILOUDI</t>
+    <t>MILOUDI HOUCINE</t>
   </si>
   <si>
     <t>HOUCINE</t>
@@ -409,7 +409,7 @@
     <t>el.houcine@yahoo.fr</t>
   </si>
   <si>
-    <t>MIMOUNI</t>
+    <t>MIMOUNI CHAHINEZ</t>
   </si>
   <si>
     <t>CHAHINEZ</t>
@@ -421,7 +421,7 @@
     <t>0558193860</t>
   </si>
   <si>
-    <t>MN.BRAHAMI</t>
+    <t>MN.BRAHAMI NADJIB</t>
   </si>
   <si>
     <t>NADJIB</t>
@@ -430,7 +430,7 @@
     <t>nadjbrahami@gmail.com</t>
   </si>
   <si>
-    <t>NACERI</t>
+    <t>NACERI ABDELLATIF</t>
   </si>
   <si>
     <t>ABDELLATIF</t>
@@ -439,7 +439,7 @@
     <t>abdnaceri@yahoo.fr</t>
   </si>
   <si>
-    <t>NASSOUR</t>
+    <t>NASSOUR KAMEL</t>
   </si>
   <si>
     <t>KAMEL</t>
@@ -448,7 +448,7 @@
     <t>nass_ka@yahoo.fr</t>
   </si>
   <si>
-    <t>NEMMICH</t>
+    <t>NEMMICH SAID</t>
   </si>
   <si>
     <t>SAID</t>
@@ -457,7 +457,7 @@
     <t>nemmichsaid@gmail.com</t>
   </si>
   <si>
-    <t>OUKLI</t>
+    <t>OUKLI MIMOUNA</t>
   </si>
   <si>
     <t>MIMOUNA</t>
@@ -466,7 +466,7 @@
     <t>mounaoukli@yahoo.fr</t>
   </si>
   <si>
-    <t>RAMI</t>
+    <t>RAMI ABDELKADER</t>
   </si>
   <si>
     <t>abc_rim20052003@yahoo.fr</t>
@@ -475,7 +475,7 @@
     <t>A revoir !!!!</t>
   </si>
   <si>
-    <t>REZOUG</t>
+    <t>REZOUG MOHAMMED</t>
   </si>
   <si>
     <t>MOHAMMED</t>
@@ -484,7 +484,7 @@
     <t>rezoug.med@gmail.com</t>
   </si>
   <si>
-    <t>SAHALI</t>
+    <t>SAHALI YAMINA</t>
   </si>
   <si>
     <t>YAMINA</t>
@@ -493,7 +493,7 @@
     <t>ya_sahali@yahoo.fr</t>
   </si>
   <si>
-    <t>SEMMAH</t>
+    <t>SEMMAH ABDELHAFID</t>
   </si>
   <si>
     <t>ABDELHAFID</t>
@@ -502,7 +502,7 @@
     <t>hafid.semmah@yahoo.fr</t>
   </si>
   <si>
-    <t>TABET DERRAZ</t>
+    <t>TABET DERRAZ HIND</t>
   </si>
   <si>
     <t>HIND</t>
@@ -511,7 +511,7 @@
     <t>htabet05@yahoo.fr</t>
   </si>
   <si>
-    <t>TILMATINE</t>
+    <t>TILMATINE AMAR</t>
   </si>
   <si>
     <t>AMAR</t>
@@ -520,7 +520,7 @@
     <t>atilmatine@gmail.com</t>
   </si>
   <si>
-    <t>TOUHAMI</t>
+    <t>TOUHAMI SEDDIK</t>
   </si>
   <si>
     <t>SEDDIK</t>
@@ -529,13 +529,13 @@
     <t>seddik.touhami@gmail.com</t>
   </si>
   <si>
-    <t>ZEBLAH</t>
+    <t>ZEBLAH ABDELKADER</t>
   </si>
   <si>
     <t>azeblah@yahoo.fr</t>
   </si>
   <si>
-    <t>ZENASNI</t>
+    <t>ZENASNI MERIEM</t>
   </si>
   <si>
     <t>MERIEM</t>
@@ -547,580 +547,586 @@
     <t>0552037098</t>
   </si>
   <si>
+    <t>ZIDI SID AHMED</t>
+  </si>
+  <si>
+    <t>sbzidi@yahoo.fr</t>
+  </si>
+  <si>
+    <t>ABBAS MOHAMED</t>
+  </si>
+  <si>
+    <t>Vacataire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Doctorant (Master) </t>
+  </si>
+  <si>
+    <t>abbasmohammed.com@gmail.com</t>
+  </si>
+  <si>
+    <t>0696562379</t>
+  </si>
+  <si>
+    <t>ABDELI MAMA</t>
+  </si>
+  <si>
+    <t>MAMA</t>
+  </si>
+  <si>
+    <t>abdelli.mama@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05 52 96 89 21 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACHARA </t>
+  </si>
+  <si>
+    <t>ARAB ABDELMADJID</t>
+  </si>
+  <si>
+    <t>ABDELMADJID</t>
+  </si>
+  <si>
+    <t>Doctorat</t>
+  </si>
+  <si>
+    <t>arab4abdelmadjid@gmail.com</t>
+  </si>
+  <si>
+    <t>06 57 28 84 81</t>
+  </si>
+  <si>
+    <t>AREZKI MOUFOK</t>
+  </si>
+  <si>
+    <t>MOUFOK</t>
+  </si>
+  <si>
+    <t>Master</t>
+  </si>
+  <si>
+    <t>Mouffok.arezki22@gmail.com </t>
+  </si>
+  <si>
+    <t>06 97 05 81 64</t>
+  </si>
+  <si>
+    <t>BENCELLA SARRA</t>
+  </si>
+  <si>
+    <t>SARRA</t>
+  </si>
+  <si>
+    <t>sarrabencella@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07 94 25 37 34 </t>
+  </si>
+  <si>
+    <t>BENDIDA MOHAMED</t>
+  </si>
+  <si>
+    <t>bendida65@gmail.com</t>
+  </si>
+  <si>
+    <t>05 50 59 52 24</t>
+  </si>
+  <si>
+    <t>BELHABRI RIHAB</t>
+  </si>
+  <si>
+    <t>RIHAB</t>
+  </si>
+  <si>
+    <t>ri123hab@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05 54 40 75 58 </t>
+  </si>
+  <si>
+    <t>BELHALLOUCHE LAKHDAR</t>
+  </si>
+  <si>
+    <t>LAKHDAR</t>
+  </si>
+  <si>
+    <t>lakhdar_belhallouche@hotmail.fr</t>
+  </si>
+  <si>
+    <t>06 96 0582 37</t>
+  </si>
+  <si>
+    <t>BENSALEM RITEDJ INES</t>
+  </si>
+  <si>
+    <t>RITEDJ INES</t>
+  </si>
+  <si>
+    <t>rawnakritedj@gmail.com</t>
+  </si>
+  <si>
+    <t>07 91 88 64 96</t>
+  </si>
+  <si>
+    <t>BENSALEM ABDELHAMID</t>
+  </si>
+  <si>
+    <t>ABDELHAMID</t>
+  </si>
+  <si>
+    <t>bensalemabdelhamid7@gmail.com</t>
+  </si>
+  <si>
+    <t>0550114832</t>
+  </si>
+  <si>
+    <t>BETTACHE ABDERRAHMANE</t>
+  </si>
+  <si>
+    <t>ABDERRAHMANE</t>
+  </si>
+  <si>
+    <t>abderrahmanbettache@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">066939 21 49 </t>
+  </si>
+  <si>
+    <t>BOUBEKEUR HALIMA</t>
+  </si>
+  <si>
+    <t>HALIMA</t>
+  </si>
+  <si>
+    <t>boubekeur97sba@gmail.com</t>
+  </si>
+  <si>
+    <t>06 74 50 65 01</t>
+  </si>
+  <si>
+    <t>BOUDALI AHMED</t>
+  </si>
+  <si>
+    <t>ahmedboudali32@gmail.com</t>
+  </si>
+  <si>
+    <t>0656855101</t>
+  </si>
+  <si>
+    <t>BOUKHARI SOUMIA</t>
+  </si>
+  <si>
+    <t>SOUMIA</t>
+  </si>
+  <si>
+    <t>boukharisoumiafarah@gmail.com</t>
+  </si>
+  <si>
+    <t>06 96 05 82 37</t>
+  </si>
+  <si>
+    <t>BOULARAF AICHA</t>
+  </si>
+  <si>
+    <t>AICHA</t>
+  </si>
+  <si>
+    <t>douaaboularaf@gmail.com</t>
+  </si>
+  <si>
+    <t>0799747080</t>
+  </si>
+  <si>
+    <t>BOURAHLA CHAHRAZED</t>
+  </si>
+  <si>
+    <t>CHAHRAZED</t>
+  </si>
+  <si>
+    <t>bourahla.phys@gmail.com</t>
+  </si>
+  <si>
+    <t>0781893264</t>
+  </si>
+  <si>
+    <t>CHABANE CHAOUCHE ABDALLAH</t>
+  </si>
+  <si>
+    <t>ABDALLAH</t>
+  </si>
+  <si>
+    <t>chaouche.abdallah@gmail.com</t>
+  </si>
+  <si>
+    <t>0664457108</t>
+  </si>
+  <si>
+    <t>DJELLOULI YOUNES</t>
+  </si>
+  <si>
+    <t>YOUNES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">djellouli08younes08@gmail.com </t>
+  </si>
+  <si>
+    <t>0673948096</t>
+  </si>
+  <si>
+    <t>DJEZIRI SOUMIA</t>
+  </si>
+  <si>
+    <t>somiadjeziri22@gmail.com</t>
+  </si>
+  <si>
+    <t>0540920164</t>
+  </si>
+  <si>
+    <t>DRICI LAMIA</t>
+  </si>
+  <si>
+    <t>LAMIA</t>
+  </si>
+  <si>
+    <t>Lamia_du22@hotmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06 97 35 08 88 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DROUNI Wassila Abir </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wassila Abir </t>
+  </si>
+  <si>
+    <t>Wassila.drouni@gmail.com</t>
+  </si>
+  <si>
+    <t>05 51 24 38 19</t>
+  </si>
+  <si>
+    <t>El MESTARI WAHIBA</t>
+  </si>
+  <si>
+    <t>WAHIBA</t>
+  </si>
+  <si>
+    <t>wahibaelmestarii@gmail.com</t>
+  </si>
+  <si>
+    <t>0556130770</t>
+  </si>
+  <si>
+    <t>ELGHODASSE ABDEL MADJID</t>
+  </si>
+  <si>
+    <t>ABDEL MADJID</t>
+  </si>
+  <si>
+    <t>elghodasseabdelmadjid@gmail.com</t>
+  </si>
+  <si>
+    <t>05 41 77 21 68</t>
+  </si>
+  <si>
+    <t>FETHI.M FETHI</t>
+  </si>
+  <si>
+    <t>FETHI</t>
+  </si>
+  <si>
+    <t>fethi22miloua@gmail.com</t>
+  </si>
+  <si>
+    <t>GHALEM ABDELHAK</t>
+  </si>
+  <si>
+    <t>ABDELHAK</t>
+  </si>
+  <si>
+    <t>ghalem.abdelhak@yahoo.com</t>
+  </si>
+  <si>
+    <t>0675437370</t>
+  </si>
+  <si>
+    <t>HADER ABDERRAHMANE</t>
+  </si>
+  <si>
+    <t>aer.hader91@gmail.com</t>
+  </si>
+  <si>
+    <t>05 41 00 44 75</t>
+  </si>
+  <si>
+    <t>BENHARAT ABDELHADI</t>
+  </si>
+  <si>
+    <t>ABDELHADI</t>
+  </si>
+  <si>
+    <t>Hadi.bnh00@gmail.com</t>
+  </si>
+  <si>
+    <t>HADJI AHMED</t>
+  </si>
+  <si>
+    <t>ahmed.hadji22@yahoo.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06 98 14 23 47 </t>
+  </si>
+  <si>
+    <t>HAMMAR MEHDI</t>
+  </si>
+  <si>
+    <t>MEHDI</t>
+  </si>
+  <si>
+    <t>protoboy9999@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06 69 33 46 70 </t>
+  </si>
+  <si>
+    <t>HARMEL MOHAMED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harmel.mohamed22@hotmail.com </t>
+  </si>
+  <si>
+    <t>KHELLAF KADDA</t>
+  </si>
+  <si>
+    <t>KADDA</t>
+  </si>
+  <si>
+    <t>khellafkadda1234@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06 65 72 17 23 </t>
+  </si>
+  <si>
+    <t>LAHCEN AZDDINE</t>
+  </si>
+  <si>
+    <t>AZDDINE</t>
+  </si>
+  <si>
+    <t>azddinelahcene@gmail.com</t>
+  </si>
+  <si>
+    <t>LATRECHE MOKHTAR</t>
+  </si>
+  <si>
+    <t>MOKHTAR</t>
+  </si>
+  <si>
+    <t>m_latreche@yahoo.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07 75 89 45 05 </t>
+  </si>
+  <si>
+    <t>LOUSDAD AYMEN</t>
+  </si>
+  <si>
+    <t>AYMEN</t>
+  </si>
+  <si>
+    <t>lousdadaymen.aziz@gmail.com</t>
+  </si>
+  <si>
+    <t>07 94 94 48 94</t>
+  </si>
+  <si>
+    <t>MAHIDDINE Abderrahim</t>
+  </si>
+  <si>
+    <t>Abderrahim</t>
+  </si>
+  <si>
+    <t>ma2006ne_86@yahoo.fr</t>
+  </si>
+  <si>
+    <t>0657058282</t>
+  </si>
+  <si>
+    <t>MAHKOUKA ZAZA</t>
+  </si>
+  <si>
+    <t>ZAZA</t>
+  </si>
+  <si>
+    <t>mahkouka.zaza@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0778 36 07 76 </t>
+  </si>
+  <si>
+    <t>MANSOURI ABDERRAZAK</t>
+  </si>
+  <si>
+    <t>ABDERRAZAK</t>
+  </si>
+  <si>
+    <t>abderazakmahdi22@gmail.com</t>
+  </si>
+  <si>
+    <t>0696417435</t>
+  </si>
+  <si>
+    <t>MECHETTEM KHALIDA</t>
+  </si>
+  <si>
+    <t>KHALIDA</t>
+  </si>
+  <si>
+    <t>Doctorante (Master)</t>
+  </si>
+  <si>
+    <t>khalidamet4@gmail.com</t>
+  </si>
+  <si>
+    <t>0550651046</t>
+  </si>
+  <si>
+    <t>MEKHALEF SOUMIA</t>
+  </si>
+  <si>
+    <t>mekhalefleila@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05 59 03 18 24 </t>
+  </si>
+  <si>
+    <t>MERADJAH IBRAHIM</t>
+  </si>
+  <si>
+    <t>IBRAHIM</t>
+  </si>
+  <si>
+    <t>ibrahimmeradjah72@gmail.com</t>
+  </si>
+  <si>
+    <t>0663114536</t>
+  </si>
+  <si>
+    <t>MESLEM MEHADJIA</t>
+  </si>
+  <si>
+    <t>MEHADJIA</t>
+  </si>
+  <si>
+    <t>mehadjiameslem@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06 97 01 34 39 </t>
+  </si>
+  <si>
+    <t>MOULAY MILOUD</t>
+  </si>
+  <si>
+    <t>MILOUD</t>
+  </si>
+  <si>
+    <t>Doctorant (Magister)</t>
+  </si>
+  <si>
+    <t>mmiloud@yahoo.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05 42 85 61 91 </t>
+  </si>
+  <si>
+    <t>MIR KHELIFA</t>
+  </si>
+  <si>
+    <t>KHELIFA</t>
+  </si>
+  <si>
+    <t>khelifa-mir@outlook.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06 69 59 78 39 </t>
+  </si>
+  <si>
+    <t>MOKEDDEM AMINA</t>
+  </si>
+  <si>
+    <t>AMINA</t>
+  </si>
+  <si>
+    <t>mokeddem.amina2222@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06 56 42 87 15 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Non Défini </t>
+  </si>
+  <si>
+    <t>REDJALA MAJDA</t>
+  </si>
+  <si>
+    <t>MAJDA</t>
+  </si>
+  <si>
+    <t>majdaredjala1492@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05 53 64 47 91 </t>
+  </si>
+  <si>
+    <t>SENOUCI HAYAT</t>
+  </si>
+  <si>
+    <t>HAYAT</t>
+  </si>
+  <si>
+    <t>senoucihayat11@gmail.com</t>
+  </si>
+  <si>
+    <t>ZAREB Mohammed Amine</t>
+  </si>
+  <si>
+    <t>Mohammed Amine</t>
+  </si>
+  <si>
+    <t>zarebmohammedamine@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0674 68 05 35 </t>
+  </si>
+  <si>
+    <t>ZIANI DJAMEL</t>
+  </si>
+  <si>
+    <t>DJAMEL</t>
+  </si>
+  <si>
+    <t>djamel71ziani@gmail.com</t>
+  </si>
+  <si>
+    <t>05 61 11 10 02</t>
+  </si>
+  <si>
+    <t>LARBI ZIDI</t>
+  </si>
+  <si>
     <t>ZIDI</t>
   </si>
   <si>
-    <t>sbzidi@yahoo.fr</t>
-  </si>
-  <si>
-    <t>ABBAS</t>
-  </si>
-  <si>
-    <t>Vacataire</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Doctorant (Master) </t>
-  </si>
-  <si>
-    <t>abbasmohammed.com@gmail.com</t>
-  </si>
-  <si>
-    <t>0696562379</t>
-  </si>
-  <si>
-    <t>ABDELI</t>
-  </si>
-  <si>
-    <t>MAMA</t>
-  </si>
-  <si>
-    <t>abdelli.mama@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">05 52 96 89 21 </t>
-  </si>
-  <si>
-    <t>ACHARA</t>
-  </si>
-  <si>
-    <t>ARAB</t>
-  </si>
-  <si>
-    <t>ABDELMADJID</t>
-  </si>
-  <si>
-    <t>Doctorat</t>
-  </si>
-  <si>
-    <t>arab4abdelmadjid@gmail.com</t>
-  </si>
-  <si>
-    <t>06 57 28 84 81</t>
-  </si>
-  <si>
-    <t>AREZKI</t>
-  </si>
-  <si>
-    <t>MOUFOK</t>
-  </si>
-  <si>
-    <t>Master</t>
-  </si>
-  <si>
-    <t>Mouffok.arezki22@gmail.com </t>
-  </si>
-  <si>
-    <t>06 97 05 81 64</t>
-  </si>
-  <si>
-    <t>BENCELLA</t>
-  </si>
-  <si>
-    <t>SARRA</t>
-  </si>
-  <si>
-    <t>sarrabencella@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">07 94 25 37 34 </t>
-  </si>
-  <si>
-    <t>BENDIDA</t>
-  </si>
-  <si>
-    <t>bendida65@gmail.com</t>
-  </si>
-  <si>
-    <t>05 50 59 52 24</t>
-  </si>
-  <si>
-    <t>BELHABRI</t>
-  </si>
-  <si>
-    <t>RIHAB</t>
-  </si>
-  <si>
-    <t>ri123hab@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">05 54 40 75 58 </t>
-  </si>
-  <si>
-    <t>BELHALLOUCHE</t>
-  </si>
-  <si>
-    <t>LAKHDAR</t>
-  </si>
-  <si>
-    <t>lakhdar_belhallouche@hotmail.fr</t>
-  </si>
-  <si>
-    <t>06 96 0582 37</t>
-  </si>
-  <si>
-    <t>BENSALEM</t>
-  </si>
-  <si>
-    <t>RITEDJ INES</t>
-  </si>
-  <si>
-    <t>rawnakritedj@gmail.com</t>
-  </si>
-  <si>
-    <t>07 91 88 64 96</t>
-  </si>
-  <si>
-    <t>ABDELHAMID</t>
-  </si>
-  <si>
-    <t>bensalemabdelhamid7@gmail.com</t>
-  </si>
-  <si>
-    <t>0550114832</t>
-  </si>
-  <si>
-    <t>BETTACHE</t>
-  </si>
-  <si>
-    <t>ABDERRAHMANE</t>
-  </si>
-  <si>
-    <t>abderrahmanbettache@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">066939 21 49 </t>
-  </si>
-  <si>
-    <t>BOUBEKEUR</t>
-  </si>
-  <si>
-    <t>HALIMA</t>
-  </si>
-  <si>
-    <t>boubekeur97sba@gmail.com</t>
-  </si>
-  <si>
-    <t>06 74 50 65 01</t>
-  </si>
-  <si>
-    <t>BOUDALI</t>
-  </si>
-  <si>
-    <t>ahmedboudali32@gmail.com</t>
-  </si>
-  <si>
-    <t>0656855101</t>
-  </si>
-  <si>
-    <t>BOUKHARI</t>
-  </si>
-  <si>
-    <t>SOUMIA</t>
-  </si>
-  <si>
-    <t>boukharisoumiafarah@gmail.com</t>
-  </si>
-  <si>
-    <t>06 96 05 82 37</t>
-  </si>
-  <si>
-    <t>BOULARAF</t>
-  </si>
-  <si>
-    <t>AICHA</t>
-  </si>
-  <si>
-    <t>douaaboularaf@gmail.com</t>
-  </si>
-  <si>
-    <t>0799747080</t>
-  </si>
-  <si>
-    <t>BOURAHLA</t>
-  </si>
-  <si>
-    <t>CHAHRAZED</t>
-  </si>
-  <si>
-    <t>bourahla.phys@gmail.com</t>
-  </si>
-  <si>
-    <t>0781893264</t>
-  </si>
-  <si>
-    <t>CHABANE CHAOUCHE</t>
-  </si>
-  <si>
-    <t>ABDALLAH</t>
-  </si>
-  <si>
-    <t>chaouche.abdallah@gmail.com</t>
-  </si>
-  <si>
-    <t>0664457108</t>
-  </si>
-  <si>
-    <t>DJELLOULI</t>
-  </si>
-  <si>
-    <t>YOUNES</t>
-  </si>
-  <si>
-    <t xml:space="preserve">djellouli08younes08@gmail.com </t>
-  </si>
-  <si>
-    <t>0673948096</t>
-  </si>
-  <si>
-    <t>DJEZIRI</t>
-  </si>
-  <si>
-    <t>somiadjeziri22@gmail.com</t>
-  </si>
-  <si>
-    <t>0540920164</t>
-  </si>
-  <si>
-    <t>DRICI</t>
-  </si>
-  <si>
-    <t>LAMIA</t>
-  </si>
-  <si>
-    <t>Lamia_du22@hotmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">06 97 35 08 88 </t>
-  </si>
-  <si>
-    <t>DROUNI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wassila Abir </t>
-  </si>
-  <si>
-    <t>Wassila.drouni@gmail.com</t>
-  </si>
-  <si>
-    <t>05 51 24 38 19</t>
-  </si>
-  <si>
-    <t>El MESTARI</t>
-  </si>
-  <si>
-    <t>WAHIBA</t>
-  </si>
-  <si>
-    <t>wahibaelmestarii@gmail.com</t>
-  </si>
-  <si>
-    <t>0556130770</t>
-  </si>
-  <si>
-    <t>ELGHODASSE</t>
-  </si>
-  <si>
-    <t>ABDEL MADJID</t>
-  </si>
-  <si>
-    <t>elghodasseabdelmadjid@gmail.com</t>
-  </si>
-  <si>
-    <t>05 41 77 21 68</t>
-  </si>
-  <si>
-    <t>FETHI.M</t>
-  </si>
-  <si>
-    <t>FETHI</t>
-  </si>
-  <si>
-    <t>fethi22miloua@gmail.com</t>
-  </si>
-  <si>
-    <t>GHALEM</t>
-  </si>
-  <si>
-    <t>ABDELHAK</t>
-  </si>
-  <si>
-    <t>ghalem.abdelhak@yahoo.com</t>
-  </si>
-  <si>
-    <t>0675437370</t>
-  </si>
-  <si>
-    <t>HADER</t>
-  </si>
-  <si>
-    <t>aer.hader91@gmail.com</t>
-  </si>
-  <si>
-    <t>05 41 00 44 75</t>
-  </si>
-  <si>
-    <t>BENHARAT</t>
-  </si>
-  <si>
-    <t>ABDELHADI</t>
-  </si>
-  <si>
-    <t>Hadi.bnh00@gmail.com</t>
-  </si>
-  <si>
-    <t>HADJI</t>
-  </si>
-  <si>
-    <t>ahmed.hadji22@yahoo.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">06 98 14 23 47 </t>
-  </si>
-  <si>
-    <t>HAMMAR</t>
-  </si>
-  <si>
-    <t>MEHDI</t>
-  </si>
-  <si>
-    <t>protoboy9999@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">06 69 33 46 70 </t>
-  </si>
-  <si>
-    <t>HARMEL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harmel.mohamed22@hotmail.com </t>
-  </si>
-  <si>
-    <t>KHELLAF</t>
-  </si>
-  <si>
-    <t>KADDA</t>
-  </si>
-  <si>
-    <t>khellafkadda1234@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">06 65 72 17 23 </t>
-  </si>
-  <si>
-    <t>LAHCEN</t>
-  </si>
-  <si>
-    <t>AZDDINE</t>
-  </si>
-  <si>
-    <t>azddinelahcene@gmail.com</t>
-  </si>
-  <si>
-    <t>LATRECHE</t>
-  </si>
-  <si>
-    <t>MOKHTAR</t>
-  </si>
-  <si>
-    <t>m_latreche@yahoo.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">07 75 89 45 05 </t>
-  </si>
-  <si>
-    <t>LOUSDAD</t>
-  </si>
-  <si>
-    <t>AYMEN</t>
-  </si>
-  <si>
-    <t>lousdadaymen.aziz@gmail.com</t>
-  </si>
-  <si>
-    <t>07 94 94 48 94</t>
-  </si>
-  <si>
-    <t>MAHIDDINE</t>
-  </si>
-  <si>
-    <t>Abderrahim</t>
-  </si>
-  <si>
-    <t>ma2006ne_86@yahoo.fr</t>
-  </si>
-  <si>
-    <t>0657058282</t>
-  </si>
-  <si>
-    <t>MAHKOUKA</t>
-  </si>
-  <si>
-    <t>ZAZA</t>
-  </si>
-  <si>
-    <t>mahkouka.zaza@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0778 36 07 76 </t>
-  </si>
-  <si>
-    <t>MANSOURI</t>
-  </si>
-  <si>
-    <t>ABDERRAZAK</t>
-  </si>
-  <si>
-    <t>abderazakmahdi22@gmail.com</t>
-  </si>
-  <si>
-    <t>0696417435</t>
-  </si>
-  <si>
-    <t>MECHETTEM</t>
-  </si>
-  <si>
-    <t>KHALIDA</t>
-  </si>
-  <si>
-    <t>Doctorante (Master)</t>
-  </si>
-  <si>
-    <t>khalidamet4@gmail.com</t>
-  </si>
-  <si>
-    <t>0550651046</t>
-  </si>
-  <si>
-    <t>MEKHALEF</t>
-  </si>
-  <si>
-    <t>mekhalefleila@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">05 59 03 18 24 </t>
-  </si>
-  <si>
-    <t>MERADJAH</t>
-  </si>
-  <si>
-    <t>IBRAHIM</t>
-  </si>
-  <si>
-    <t>ibrahimmeradjah72@gmail.com</t>
-  </si>
-  <si>
-    <t>0663114536</t>
-  </si>
-  <si>
-    <t>MESLEM</t>
-  </si>
-  <si>
-    <t>MEHADJIA</t>
-  </si>
-  <si>
-    <t>mehadjiameslem@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">06 97 01 34 39 </t>
-  </si>
-  <si>
-    <t>MOULAY</t>
-  </si>
-  <si>
-    <t>MILOUD</t>
-  </si>
-  <si>
-    <t>Doctorant (Magister)</t>
-  </si>
-  <si>
-    <t>mmiloud@yahoo.fr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">05 42 85 61 91 </t>
-  </si>
-  <si>
-    <t>MIR</t>
-  </si>
-  <si>
-    <t>KHELIFA</t>
-  </si>
-  <si>
-    <t>khelifa-mir@outlook.fr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">06 69 59 78 39 </t>
-  </si>
-  <si>
-    <t>MOKEDDEM</t>
-  </si>
-  <si>
-    <t>AMINA</t>
-  </si>
-  <si>
-    <t>mokeddem.amina2222@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">06 56 42 87 15 </t>
-  </si>
-  <si>
-    <t>Non Défini</t>
-  </si>
-  <si>
-    <t>REDJALA</t>
-  </si>
-  <si>
-    <t>MAJDA</t>
-  </si>
-  <si>
-    <t>majdaredjala1492@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">05 53 64 47 91 </t>
-  </si>
-  <si>
-    <t>SENOUCI</t>
-  </si>
-  <si>
-    <t>HAYAT</t>
-  </si>
-  <si>
-    <t>senoucihayat11@gmail.com</t>
-  </si>
-  <si>
-    <t>ZAREB</t>
-  </si>
-  <si>
-    <t>Mohammed Amine</t>
-  </si>
-  <si>
-    <t>zarebmohammedamine@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0674 68 05 35 </t>
-  </si>
-  <si>
-    <t>ZIANI</t>
-  </si>
-  <si>
-    <t>DJAMEL</t>
-  </si>
-  <si>
-    <t>djamel71ziani@gmail.com</t>
-  </si>
-  <si>
-    <t>05 61 11 10 02</t>
-  </si>
-  <si>
-    <t>LARBI</t>
-  </si>
-  <si>
     <t>larbi.zidi6@gmail.com</t>
   </si>
   <si>
     <t>07 92 12 03 38</t>
   </si>
   <si>
-    <t>BERROUNA</t>
+    <t>BERROUNA HENEN</t>
   </si>
   <si>
     <t>HENEN</t>
@@ -1132,7 +1138,7 @@
     <t>0671745806</t>
   </si>
   <si>
-    <t xml:space="preserve">MOUILAH </t>
+    <t>MOUILAH  KHEIRA</t>
   </si>
   <si>
     <t>KHEIRA</t>
@@ -1144,7 +1150,7 @@
     <t>mouilahka4614@gmail.com</t>
   </si>
   <si>
-    <t>ABED</t>
+    <t>ABED ZOULIKHA</t>
   </si>
   <si>
     <t>ZOULIKHA</t>
@@ -1153,7 +1159,7 @@
     <t>zoulikhaabed3@gmail.com</t>
   </si>
   <si>
-    <t>AISSANI</t>
+    <t>AISSANI ALI</t>
   </si>
   <si>
     <t>ALI</t>
@@ -1162,7 +1168,7 @@
     <t>aliaissani97@gmail.com</t>
   </si>
   <si>
-    <t>AZZA</t>
+    <t>AZZA ROMAISSA FATIMA ZOHRA</t>
   </si>
   <si>
     <t>ROMAISSA FATIMA ZOHRA</t>
@@ -1171,13 +1177,13 @@
     <t>azzafatimazohraromaissa.l3@gmail.com</t>
   </si>
   <si>
-    <t>BELABED</t>
+    <t>BELABED MERIEM</t>
   </si>
   <si>
     <t>meriembelabed5@gmail.com</t>
   </si>
   <si>
-    <t>BENKABOU</t>
+    <t>BENKABOU MOHAMED EL HABIB</t>
   </si>
   <si>
     <t>MOHAMED EL HABIB</t>
@@ -1186,7 +1192,7 @@
     <t>bkbhbb22@gmail.com</t>
   </si>
   <si>
-    <t>BENMASOUD</t>
+    <t>BENMASOUD LEILA</t>
   </si>
   <si>
     <t>LEILA</t>
@@ -1195,10 +1201,13 @@
     <t>l.benmessaoud@yahoo.fr</t>
   </si>
   <si>
+    <t>BERROUNA HANANE</t>
+  </si>
+  <si>
     <t>HANANE</t>
   </si>
   <si>
-    <t>CHIKHI</t>
+    <t>CHIKHI NAWEL</t>
   </si>
   <si>
     <t>NAWEL</t>
@@ -1207,7 +1216,7 @@
     <t>chikhi nawel75@yahoo.fr</t>
   </si>
   <si>
-    <t>DELLOUM</t>
+    <t>DELLOUM AMIRA</t>
   </si>
   <si>
     <t>AMIRA</t>
@@ -1216,7 +1225,7 @@
     <t>amiradelloum28@gmail.com</t>
   </si>
   <si>
-    <t>FENTAZY</t>
+    <t>FENTAZY BELKISSE</t>
   </si>
   <si>
     <t>BELKISSE</t>
@@ -1225,7 +1234,7 @@
     <t>fantazibelkisse.13@gmail.com</t>
   </si>
   <si>
-    <t>FEZAZI</t>
+    <t>FEZAZI KHADIDJA</t>
   </si>
   <si>
     <t>KHADIDJA</t>
@@ -1234,7 +1243,7 @@
     <t>khadidjafezazi90@gmail</t>
   </si>
   <si>
-    <t>KADA ZAIR</t>
+    <t>KADA ZAIR IKRAM</t>
   </si>
   <si>
     <t>IKRAM</t>
@@ -1243,7 +1252,7 @@
     <t>ikram.kadazair@gmail.com</t>
   </si>
   <si>
-    <t>KADRI</t>
+    <t>KADRI RANIA</t>
   </si>
   <si>
     <t>RANIA</t>
@@ -1252,7 +1261,7 @@
     <t>kadrirania51@gmail.com</t>
   </si>
   <si>
-    <t>LAYATI</t>
+    <t>LAYATI TAYEB MEHDI</t>
   </si>
   <si>
     <t>TAYEB MEHDI</t>
@@ -1261,7 +1270,7 @@
     <t>layatimedi@gmail.com</t>
   </si>
   <si>
-    <t>NEFAHA</t>
+    <t>NEFAHA ABOUBAKR</t>
   </si>
   <si>
     <t>ABOUBAKR</t>
@@ -1270,13 +1279,13 @@
     <t>Boba1620@hotmail.com</t>
   </si>
   <si>
-    <t>SACI</t>
+    <t>SACI HAMZA</t>
   </si>
   <si>
     <t>sacihamza40@gmail.com</t>
   </si>
   <si>
-    <t>TURKI</t>
+    <t>TURKI BILAL MEROUANE</t>
   </si>
   <si>
     <t>BILAL MEROUANE</t>
@@ -1285,7 +1294,7 @@
     <t>turkibilal22@gmail.com</t>
   </si>
   <si>
-    <t>RAIS</t>
+    <t>RAIS ABDELMAJID</t>
   </si>
   <si>
     <t>ABDELMAJID</t>
@@ -1294,7 +1303,7 @@
     <t>amrais@yahoo.com</t>
   </si>
   <si>
-    <t>REGUIG</t>
+    <t>REGUIG ABDELDJALIL</t>
   </si>
   <si>
     <t>ABDELDJALIL</t>
@@ -1303,7 +1312,7 @@
     <t>abdeldjalil.reguig@outlook.com</t>
   </si>
   <si>
-    <t>ZERDANI</t>
+    <t>ZERDANI MOHAMMED</t>
   </si>
   <si>
     <t>medzerdani@gmail.com</t>
@@ -1433,7 +1442,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="31">
+  <fonts count="30">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1485,12 +1494,6 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
-      <name val="Cambria"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF31333F"/>
       <name val="Cambria"/>
       <charset val="134"/>
     </font>
@@ -2072,11 +2075,14 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2085,122 +2091,119 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2280,13 +2283,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2301,10 +2298,7 @@
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="6" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2313,13 +2307,10 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2328,13 +2319,13 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="6" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="6" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2346,20 +2337,23 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
@@ -2869,7 +2863,7 @@
       <c r="A7" s="24">
         <v>6</v>
       </c>
-      <c r="B7" s="29" t="s">
+      <c r="B7" s="25" t="s">
         <v>26</v>
       </c>
       <c r="C7" s="25" t="s">
@@ -2884,7 +2878,7 @@
       <c r="F7" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="G7" s="57" t="s">
+      <c r="G7" s="54" t="s">
         <v>31</v>
       </c>
     </row>
@@ -2892,7 +2886,7 @@
       <c r="A8" s="24">
         <v>7</v>
       </c>
-      <c r="B8" s="29" t="s">
+      <c r="B8" s="25" t="s">
         <v>32</v>
       </c>
       <c r="C8" s="25" t="s">
@@ -2907,7 +2901,7 @@
       <c r="F8" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="G8" s="57" t="s">
+      <c r="G8" s="54" t="s">
         <v>35</v>
       </c>
     </row>
@@ -2938,22 +2932,22 @@
       <c r="A10" s="24">
         <v>9</v>
       </c>
-      <c r="B10" s="31" t="s">
+      <c r="B10" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="C10" s="32" t="s">
+      <c r="C10" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="D10" s="33" t="s">
+      <c r="D10" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="E10" s="34" t="s">
+      <c r="E10" s="32" t="s">
         <v>38</v>
       </c>
-      <c r="F10" s="35" t="s">
+      <c r="F10" s="33" t="s">
         <v>42</v>
       </c>
-      <c r="G10" s="57" t="s">
+      <c r="G10" s="54" t="s">
         <v>43</v>
       </c>
     </row>
@@ -2973,7 +2967,7 @@
       <c r="E11" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="F11" s="36" t="s">
+      <c r="F11" s="34" t="s">
         <v>46</v>
       </c>
       <c r="G11" s="28" t="s">
@@ -3070,7 +3064,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" ht="15.75" hidden="1" spans="1:7">
+    <row r="16" ht="31.5" hidden="1" spans="1:7">
       <c r="A16" s="24">
         <v>15</v>
       </c>
@@ -3143,7 +3137,7 @@
       <c r="A19" s="24">
         <v>18</v>
       </c>
-      <c r="B19" s="37" t="s">
+      <c r="B19" s="25" t="s">
         <v>69</v>
       </c>
       <c r="C19" s="28" t="s">
@@ -3152,17 +3146,17 @@
       <c r="D19" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="E19" s="38" t="s">
+      <c r="E19" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="F19" s="35" t="s">
+      <c r="F19" s="33" t="s">
         <v>71</v>
       </c>
       <c r="G19" s="28" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="20" ht="15.75" hidden="1" spans="1:7">
+    <row r="20" ht="31.5" hidden="1" spans="1:7">
       <c r="A20" s="24">
         <v>19</v>
       </c>
@@ -3293,14 +3287,14 @@
       <c r="E25" s="26" t="s">
         <v>38</v>
       </c>
-      <c r="F25" s="35" t="s">
+      <c r="F25" s="33" t="s">
         <v>89</v>
       </c>
       <c r="G25" s="28" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="26" ht="31.5" hidden="1" spans="1:7">
+    <row r="26" ht="47.25" spans="1:7">
       <c r="A26" s="24">
         <v>25</v>
       </c>
@@ -3549,7 +3543,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="37" ht="15.75" spans="1:7">
+    <row r="37" ht="15.75" hidden="1" spans="1:7">
       <c r="A37" s="24">
         <v>36</v>
       </c>
@@ -3599,7 +3593,7 @@
       <c r="A39" s="24">
         <v>38</v>
       </c>
-      <c r="B39" s="29" t="s">
+      <c r="B39" s="25" t="s">
         <v>125</v>
       </c>
       <c r="C39" s="25" t="s">
@@ -3614,7 +3608,7 @@
       <c r="F39" s="27" t="s">
         <v>127</v>
       </c>
-      <c r="G39" s="57" t="s">
+      <c r="G39" s="54" t="s">
         <v>128</v>
       </c>
     </row>
@@ -3921,7 +3915,7 @@
       <c r="A53" s="24">
         <v>52</v>
       </c>
-      <c r="B53" s="29" t="s">
+      <c r="B53" s="25" t="s">
         <v>167</v>
       </c>
       <c r="C53" s="25" t="s">
@@ -3936,7 +3930,7 @@
       <c r="F53" s="27" t="s">
         <v>169</v>
       </c>
-      <c r="G53" s="57" t="s">
+      <c r="G53" s="54" t="s">
         <v>170</v>
       </c>
     </row>
@@ -3967,22 +3961,22 @@
       <c r="A55" s="24">
         <v>54</v>
       </c>
-      <c r="B55" s="29" t="s">
+      <c r="B55" s="25" t="s">
         <v>173</v>
       </c>
-      <c r="C55" s="39" t="s">
+      <c r="C55" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="D55" s="33" t="s">
+      <c r="D55" s="31" t="s">
         <v>174</v>
       </c>
       <c r="E55" s="26" t="s">
         <v>175</v>
       </c>
-      <c r="F55" s="35" t="s">
+      <c r="F55" s="33" t="s">
         <v>176</v>
       </c>
-      <c r="G55" s="57" t="s">
+      <c r="G55" s="54" t="s">
         <v>177</v>
       </c>
     </row>
@@ -3990,16 +3984,16 @@
       <c r="A56" s="24">
         <v>55</v>
       </c>
-      <c r="B56" s="39" t="s">
+      <c r="B56" s="25" t="s">
         <v>178</v>
       </c>
-      <c r="C56" s="39" t="s">
+      <c r="C56" s="36" t="s">
         <v>179</v>
       </c>
-      <c r="D56" s="33" t="s">
+      <c r="D56" s="31" t="s">
         <v>174</v>
       </c>
-      <c r="E56" s="40"/>
+      <c r="E56" s="37"/>
       <c r="F56" s="27" t="s">
         <v>180</v>
       </c>
@@ -4011,34 +4005,34 @@
       <c r="A57" s="24">
         <v>56</v>
       </c>
-      <c r="B57" s="41" t="s">
+      <c r="B57" s="25" t="s">
         <v>182</v>
       </c>
-      <c r="C57" s="32"/>
-      <c r="D57" s="33" t="s">
+      <c r="C57" s="30"/>
+      <c r="D57" s="31" t="s">
         <v>174</v>
       </c>
-      <c r="E57" s="34"/>
-      <c r="F57" s="32"/>
+      <c r="E57" s="32"/>
+      <c r="F57" s="30"/>
       <c r="G57" s="28"/>
     </row>
     <row r="58" ht="15.75" hidden="1" spans="1:7">
       <c r="A58" s="24">
         <v>57</v>
       </c>
-      <c r="B58" s="39" t="s">
+      <c r="B58" s="25" t="s">
         <v>183</v>
       </c>
-      <c r="C58" s="39" t="s">
+      <c r="C58" s="36" t="s">
         <v>184</v>
       </c>
-      <c r="D58" s="33" t="s">
+      <c r="D58" s="31" t="s">
         <v>174</v>
       </c>
-      <c r="E58" s="33" t="s">
+      <c r="E58" s="31" t="s">
         <v>185</v>
       </c>
-      <c r="F58" s="35" t="s">
+      <c r="F58" s="33" t="s">
         <v>186</v>
       </c>
       <c r="G58" s="28" t="s">
@@ -4049,19 +4043,19 @@
       <c r="A59" s="24">
         <v>58</v>
       </c>
-      <c r="B59" s="39" t="s">
+      <c r="B59" s="25" t="s">
         <v>188</v>
       </c>
-      <c r="C59" s="39" t="s">
+      <c r="C59" s="36" t="s">
         <v>189</v>
       </c>
-      <c r="D59" s="33" t="s">
+      <c r="D59" s="31" t="s">
         <v>174</v>
       </c>
-      <c r="E59" s="33" t="s">
+      <c r="E59" s="31" t="s">
         <v>190</v>
       </c>
-      <c r="F59" s="35" t="s">
+      <c r="F59" s="33" t="s">
         <v>191</v>
       </c>
       <c r="G59" s="28" t="s">
@@ -4084,7 +4078,7 @@
       <c r="E60" s="26" t="s">
         <v>190</v>
       </c>
-      <c r="F60" s="35" t="s">
+      <c r="F60" s="33" t="s">
         <v>195</v>
       </c>
       <c r="G60" s="28" t="s">
@@ -4104,8 +4098,8 @@
       <c r="D61" s="26" t="s">
         <v>174</v>
       </c>
-      <c r="E61" s="42"/>
-      <c r="F61" s="35" t="s">
+      <c r="E61" s="38"/>
+      <c r="F61" s="33" t="s">
         <v>198</v>
       </c>
       <c r="G61" s="28" t="s">
@@ -4116,38 +4110,38 @@
       <c r="A62" s="24">
         <v>61</v>
       </c>
-      <c r="B62" s="43" t="s">
+      <c r="B62" s="25" t="s">
         <v>200</v>
       </c>
-      <c r="C62" s="43" t="s">
+      <c r="C62" s="39" t="s">
         <v>201</v>
       </c>
-      <c r="D62" s="44" t="s">
+      <c r="D62" s="40" t="s">
         <v>174</v>
       </c>
-      <c r="E62" s="45"/>
-      <c r="F62" s="35" t="s">
+      <c r="E62" s="41"/>
+      <c r="F62" s="33" t="s">
         <v>202</v>
       </c>
-      <c r="G62" s="46" t="s">
+      <c r="G62" s="42" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="63" ht="15.75" hidden="1" spans="1:7">
+    <row r="63" ht="31.5" hidden="1" spans="1:7">
       <c r="A63" s="24">
         <v>62</v>
       </c>
-      <c r="B63" s="41" t="s">
+      <c r="B63" s="25" t="s">
         <v>204</v>
       </c>
-      <c r="C63" s="32" t="s">
+      <c r="C63" s="30" t="s">
         <v>205</v>
       </c>
-      <c r="D63" s="33" t="s">
+      <c r="D63" s="31" t="s">
         <v>174</v>
       </c>
-      <c r="E63" s="34"/>
-      <c r="F63" s="47" t="s">
+      <c r="E63" s="32"/>
+      <c r="F63" s="43" t="s">
         <v>206</v>
       </c>
       <c r="G63" s="28" t="s">
@@ -4167,8 +4161,8 @@
       <c r="D64" s="26" t="s">
         <v>174</v>
       </c>
-      <c r="E64" s="42"/>
-      <c r="F64" s="35" t="s">
+      <c r="E64" s="38"/>
+      <c r="F64" s="33" t="s">
         <v>210</v>
       </c>
       <c r="G64" s="28" t="s">
@@ -4179,44 +4173,44 @@
       <c r="A65" s="24">
         <v>64</v>
       </c>
-      <c r="B65" s="29" t="s">
-        <v>208</v>
-      </c>
-      <c r="C65" s="48" t="s">
+      <c r="B65" s="25" t="s">
         <v>212</v>
       </c>
-      <c r="D65" s="49" t="s">
+      <c r="C65" s="44" t="s">
+        <v>213</v>
+      </c>
+      <c r="D65" s="45" t="s">
         <v>174</v>
       </c>
-      <c r="E65" s="49" t="s">
+      <c r="E65" s="45" t="s">
         <v>185</v>
       </c>
-      <c r="F65" s="50" t="s">
-        <v>213</v>
-      </c>
-      <c r="G65" s="57" t="s">
+      <c r="F65" s="46" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="66" ht="15.75" hidden="1" spans="1:7">
+      <c r="G65" s="54" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="66" ht="31.5" hidden="1" spans="1:7">
       <c r="A66" s="24">
         <v>65</v>
       </c>
-      <c r="B66" s="37" t="s">
-        <v>215</v>
+      <c r="B66" s="25" t="s">
+        <v>216</v>
       </c>
       <c r="C66" s="28" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D66" s="26" t="s">
         <v>174</v>
       </c>
-      <c r="E66" s="38"/>
-      <c r="F66" s="35" t="s">
-        <v>217</v>
+      <c r="E66" s="35"/>
+      <c r="F66" s="33" t="s">
+        <v>218</v>
       </c>
       <c r="G66" s="28" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="67" ht="15.75" hidden="1" spans="1:7">
@@ -4224,28 +4218,28 @@
         <v>66</v>
       </c>
       <c r="B67" s="25" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C67" s="25" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D67" s="26" t="s">
         <v>174</v>
       </c>
-      <c r="E67" s="42"/>
-      <c r="F67" s="51" t="s">
-        <v>221</v>
+      <c r="E67" s="38"/>
+      <c r="F67" s="47" t="s">
+        <v>222</v>
       </c>
       <c r="G67" s="28" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="68" ht="15.75" hidden="1" spans="1:7">
       <c r="A68" s="24">
         <v>67</v>
       </c>
-      <c r="B68" s="37" t="s">
-        <v>223</v>
+      <c r="B68" s="25" t="s">
+        <v>224</v>
       </c>
       <c r="C68" s="28" t="s">
         <v>24</v>
@@ -4253,12 +4247,12 @@
       <c r="D68" s="26" t="s">
         <v>174</v>
       </c>
-      <c r="E68" s="38"/>
-      <c r="F68" s="36" t="s">
-        <v>224</v>
-      </c>
-      <c r="G68" s="58" t="s">
+      <c r="E68" s="35"/>
+      <c r="F68" s="34" t="s">
         <v>225</v>
+      </c>
+      <c r="G68" s="55" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="69" ht="15.75" hidden="1" spans="1:7">
@@ -4266,10 +4260,10 @@
         <v>68</v>
       </c>
       <c r="B69" s="25" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C69" s="25" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D69" s="26" t="s">
         <v>174</v>
@@ -4277,74 +4271,74 @@
       <c r="E69" s="26" t="s">
         <v>185</v>
       </c>
-      <c r="F69" s="35" t="s">
-        <v>228</v>
+      <c r="F69" s="33" t="s">
+        <v>229</v>
       </c>
       <c r="G69" s="28" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="70" ht="15.75" hidden="1" spans="1:7">
       <c r="A70" s="24">
         <v>69</v>
       </c>
-      <c r="B70" s="29" t="s">
-        <v>230</v>
+      <c r="B70" s="25" t="s">
+        <v>231</v>
       </c>
       <c r="C70" s="25" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D70" s="26" t="s">
         <v>174</v>
       </c>
       <c r="E70" s="26"/>
-      <c r="F70" s="35" t="s">
-        <v>232</v>
-      </c>
-      <c r="G70" s="57" t="s">
+      <c r="F70" s="33" t="s">
         <v>233</v>
+      </c>
+      <c r="G70" s="54" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="71" ht="15.75" hidden="1" spans="1:7">
       <c r="A71" s="24">
         <v>70</v>
       </c>
-      <c r="B71" s="31" t="s">
-        <v>234</v>
+      <c r="B71" s="25" t="s">
+        <v>235</v>
       </c>
       <c r="C71" s="28" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D71" s="26" t="s">
         <v>174</v>
       </c>
       <c r="E71" s="26"/>
-      <c r="F71" s="35" t="s">
-        <v>236</v>
-      </c>
-      <c r="G71" s="57" t="s">
+      <c r="F71" s="33" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="72" ht="15.75" hidden="1" spans="1:7">
+      <c r="G71" s="54" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="72" ht="31.5" hidden="1" spans="1:7">
       <c r="A72" s="24">
         <v>71</v>
       </c>
-      <c r="B72" s="31" t="s">
-        <v>238</v>
-      </c>
-      <c r="C72" s="32" t="s">
+      <c r="B72" s="25" t="s">
         <v>239</v>
       </c>
-      <c r="D72" s="33" t="s">
+      <c r="C72" s="30" t="s">
+        <v>240</v>
+      </c>
+      <c r="D72" s="31" t="s">
         <v>174</v>
       </c>
       <c r="E72" s="26"/>
-      <c r="F72" s="47" t="s">
-        <v>240</v>
-      </c>
-      <c r="G72" s="57" t="s">
+      <c r="F72" s="43" t="s">
         <v>241</v>
+      </c>
+      <c r="G72" s="54" t="s">
+        <v>242</v>
       </c>
     </row>
     <row r="73" ht="15.75" hidden="1" spans="1:7">
@@ -4352,31 +4346,31 @@
         <v>72</v>
       </c>
       <c r="B73" s="25" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C73" s="25" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D73" s="26" t="s">
         <v>174</v>
       </c>
       <c r="E73" s="26"/>
       <c r="F73" s="27" t="s">
-        <v>244</v>
-      </c>
-      <c r="G73" s="57" t="s">
         <v>245</v>
+      </c>
+      <c r="G73" s="54" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="74" ht="15.75" hidden="1" spans="1:7">
       <c r="A74" s="24">
         <v>73</v>
       </c>
-      <c r="B74" s="29" t="s">
-        <v>246</v>
+      <c r="B74" s="25" t="s">
+        <v>247</v>
       </c>
       <c r="C74" s="25" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D74" s="26" t="s">
         <v>174</v>
@@ -4385,10 +4379,10 @@
         <v>185</v>
       </c>
       <c r="F74" s="27" t="s">
-        <v>247</v>
-      </c>
-      <c r="G74" s="57" t="s">
         <v>248</v>
+      </c>
+      <c r="G74" s="54" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="75" ht="15.75" hidden="1" spans="1:7">
@@ -4396,20 +4390,20 @@
         <v>74</v>
       </c>
       <c r="B75" s="25" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C75" s="25" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D75" s="26" t="s">
         <v>174</v>
       </c>
       <c r="E75" s="26"/>
-      <c r="F75" s="35" t="s">
-        <v>251</v>
+      <c r="F75" s="33" t="s">
+        <v>252</v>
       </c>
       <c r="G75" s="28" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="76" ht="15.75" hidden="1" spans="1:7">
@@ -4417,10 +4411,10 @@
         <v>75</v>
       </c>
       <c r="B76" s="25" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C76" s="25" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D76" s="26" t="s">
         <v>174</v>
@@ -4428,43 +4422,43 @@
       <c r="E76" s="26" t="s">
         <v>185</v>
       </c>
-      <c r="F76" s="35" t="s">
-        <v>255</v>
+      <c r="F76" s="33" t="s">
+        <v>256</v>
       </c>
       <c r="G76" s="28" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="77" ht="15.75" hidden="1" spans="1:7">
       <c r="A77" s="24">
         <v>76</v>
       </c>
-      <c r="B77" s="29" t="s">
-        <v>257</v>
+      <c r="B77" s="25" t="s">
+        <v>258</v>
       </c>
       <c r="C77" s="25" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D77" s="26" t="s">
         <v>174</v>
       </c>
       <c r="E77" s="26"/>
-      <c r="F77" s="35" t="s">
-        <v>259</v>
-      </c>
-      <c r="G77" s="57" t="s">
+      <c r="F77" s="33" t="s">
         <v>260</v>
       </c>
-    </row>
-    <row r="78" ht="15.75" hidden="1" spans="1:7">
+      <c r="G77" s="54" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="78" ht="31.5" hidden="1" spans="1:7">
       <c r="A78" s="24">
         <v>77</v>
       </c>
       <c r="B78" s="25" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C78" s="25" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D78" s="26" t="s">
         <v>174</v>
@@ -4472,11 +4466,11 @@
       <c r="E78" s="26" t="s">
         <v>175</v>
       </c>
-      <c r="F78" s="35" t="s">
-        <v>263</v>
+      <c r="F78" s="33" t="s">
+        <v>264</v>
       </c>
       <c r="G78" s="28" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="79" ht="15.75" hidden="1" spans="1:7">
@@ -4484,17 +4478,17 @@
         <v>78</v>
       </c>
       <c r="B79" s="25" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C79" s="25" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D79" s="26" t="s">
         <v>174</v>
       </c>
       <c r="E79" s="26"/>
-      <c r="F79" s="35" t="s">
-        <v>267</v>
+      <c r="F79" s="33" t="s">
+        <v>268</v>
       </c>
       <c r="G79" s="28"/>
     </row>
@@ -4502,11 +4496,11 @@
       <c r="A80" s="24">
         <v>79</v>
       </c>
-      <c r="B80" s="29" t="s">
-        <v>268</v>
+      <c r="B80" s="25" t="s">
+        <v>269</v>
       </c>
       <c r="C80" s="25" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D80" s="26" t="s">
         <v>174</v>
@@ -4514,11 +4508,11 @@
       <c r="E80" s="26" t="s">
         <v>175</v>
       </c>
-      <c r="F80" s="35" t="s">
-        <v>270</v>
-      </c>
-      <c r="G80" s="57" t="s">
+      <c r="F80" s="33" t="s">
         <v>271</v>
+      </c>
+      <c r="G80" s="54" t="s">
+        <v>272</v>
       </c>
     </row>
     <row r="81" ht="15.75" hidden="1" spans="1:7">
@@ -4526,10 +4520,10 @@
         <v>80</v>
       </c>
       <c r="B81" s="25" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C81" s="25" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D81" s="26" t="s">
         <v>174</v>
@@ -4537,22 +4531,22 @@
       <c r="E81" s="26" t="s">
         <v>185</v>
       </c>
-      <c r="F81" s="35" t="s">
-        <v>273</v>
+      <c r="F81" s="33" t="s">
+        <v>274</v>
       </c>
       <c r="G81" s="28" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="82" ht="15.75" hidden="1" spans="1:7">
       <c r="A82" s="24">
         <v>81</v>
       </c>
-      <c r="B82" s="37" t="s">
-        <v>275</v>
+      <c r="B82" s="25" t="s">
+        <v>276</v>
       </c>
       <c r="C82" s="28" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D82" s="26" t="s">
         <v>174</v>
@@ -4560,8 +4554,8 @@
       <c r="E82" s="26" t="s">
         <v>190</v>
       </c>
-      <c r="F82" s="35" t="s">
-        <v>277</v>
+      <c r="F82" s="33" t="s">
+        <v>278</v>
       </c>
       <c r="G82" s="28"/>
     </row>
@@ -4569,8 +4563,8 @@
       <c r="A83" s="24">
         <v>82</v>
       </c>
-      <c r="B83" s="37" t="s">
-        <v>278</v>
+      <c r="B83" s="25" t="s">
+        <v>279</v>
       </c>
       <c r="C83" s="28" t="s">
         <v>24</v>
@@ -4579,11 +4573,11 @@
         <v>174</v>
       </c>
       <c r="E83" s="26"/>
-      <c r="F83" s="36" t="s">
-        <v>279</v>
+      <c r="F83" s="34" t="s">
+        <v>280</v>
       </c>
       <c r="G83" s="28" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="84" ht="15.75" hidden="1" spans="1:7">
@@ -4591,10 +4585,10 @@
         <v>83</v>
       </c>
       <c r="B84" s="25" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C84" s="25" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D84" s="26" t="s">
         <v>174</v>
@@ -4602,19 +4596,19 @@
       <c r="E84" s="26" t="s">
         <v>175</v>
       </c>
-      <c r="F84" s="35" t="s">
-        <v>283</v>
+      <c r="F84" s="33" t="s">
+        <v>284</v>
       </c>
       <c r="G84" s="28" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="85" ht="15.75" hidden="1" spans="1:7">
       <c r="A85" s="24">
         <v>84</v>
       </c>
-      <c r="B85" s="37" t="s">
-        <v>285</v>
+      <c r="B85" s="25" t="s">
+        <v>286</v>
       </c>
       <c r="C85" s="28" t="s">
         <v>8</v>
@@ -4622,9 +4616,9 @@
       <c r="D85" s="26" t="s">
         <v>174</v>
       </c>
-      <c r="E85" s="38"/>
-      <c r="F85" s="35" t="s">
-        <v>286</v>
+      <c r="E85" s="35"/>
+      <c r="F85" s="33" t="s">
+        <v>287</v>
       </c>
       <c r="G85" s="28"/>
     </row>
@@ -4633,40 +4627,40 @@
         <v>85</v>
       </c>
       <c r="B86" s="25" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C86" s="25" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D86" s="26" t="s">
         <v>174</v>
       </c>
-      <c r="E86" s="38" t="s">
+      <c r="E86" s="35" t="s">
         <v>190</v>
       </c>
-      <c r="F86" s="52" t="s">
-        <v>289</v>
+      <c r="F86" s="48" t="s">
+        <v>290</v>
       </c>
       <c r="G86" s="28" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="87" ht="15.75" hidden="1" spans="1:7">
       <c r="A87" s="24">
         <v>86</v>
       </c>
-      <c r="B87" s="41" t="s">
-        <v>291</v>
-      </c>
-      <c r="C87" s="32" t="s">
+      <c r="B87" s="25" t="s">
         <v>292</v>
       </c>
-      <c r="D87" s="33" t="s">
+      <c r="C87" s="30" t="s">
+        <v>293</v>
+      </c>
+      <c r="D87" s="31" t="s">
         <v>174</v>
       </c>
-      <c r="E87" s="38"/>
-      <c r="F87" s="35" t="s">
-        <v>293</v>
+      <c r="E87" s="35"/>
+      <c r="F87" s="33" t="s">
+        <v>294</v>
       </c>
       <c r="G87" s="28" t="s">
         <v>16</v>
@@ -4677,20 +4671,20 @@
         <v>87</v>
       </c>
       <c r="B88" s="25" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C88" s="25" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D88" s="26" t="s">
         <v>174</v>
       </c>
-      <c r="E88" s="38"/>
-      <c r="F88" s="35" t="s">
-        <v>296</v>
+      <c r="E88" s="35"/>
+      <c r="F88" s="33" t="s">
+        <v>297</v>
       </c>
       <c r="G88" s="28" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="89" ht="15.75" hidden="1" spans="1:7">
@@ -4698,41 +4692,41 @@
         <v>88</v>
       </c>
       <c r="B89" s="25" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C89" s="25" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D89" s="26" t="s">
         <v>174</v>
       </c>
-      <c r="E89" s="42"/>
-      <c r="F89" s="35" t="s">
-        <v>300</v>
+      <c r="E89" s="38"/>
+      <c r="F89" s="33" t="s">
+        <v>301</v>
       </c>
       <c r="G89" s="28" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="90" ht="15.75" hidden="1" spans="1:7">
       <c r="A90" s="24">
         <v>89</v>
       </c>
-      <c r="B90" s="31" t="s">
-        <v>302</v>
+      <c r="B90" s="25" t="s">
+        <v>303</v>
       </c>
       <c r="C90" s="25" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D90" s="26" t="s">
         <v>174</v>
       </c>
       <c r="E90" s="26"/>
-      <c r="F90" s="35" t="s">
-        <v>304</v>
-      </c>
-      <c r="G90" s="57" t="s">
+      <c r="F90" s="33" t="s">
         <v>305</v>
+      </c>
+      <c r="G90" s="54" t="s">
+        <v>306</v>
       </c>
     </row>
     <row r="91" ht="15.75" hidden="1" spans="1:7">
@@ -4740,10 +4734,10 @@
         <v>90</v>
       </c>
       <c r="B91" s="25" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C91" s="25" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D91" s="26" t="s">
         <v>174</v>
@@ -4751,55 +4745,55 @@
       <c r="E91" s="26" t="s">
         <v>190</v>
       </c>
-      <c r="F91" s="35" t="s">
-        <v>308</v>
+      <c r="F91" s="33" t="s">
+        <v>309</v>
       </c>
       <c r="G91" s="28" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="92" ht="15.75" hidden="1" spans="1:7">
       <c r="A92" s="24">
         <v>91</v>
       </c>
-      <c r="B92" s="29" t="s">
-        <v>310</v>
+      <c r="B92" s="25" t="s">
+        <v>311</v>
       </c>
       <c r="C92" s="25" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D92" s="26" t="s">
         <v>174</v>
       </c>
       <c r="E92" s="26"/>
-      <c r="F92" s="35" t="s">
-        <v>312</v>
-      </c>
-      <c r="G92" s="57" t="s">
+      <c r="F92" s="33" t="s">
         <v>313</v>
+      </c>
+      <c r="G92" s="54" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="93" ht="15.75" hidden="1" spans="1:7">
       <c r="A93" s="24">
         <v>92</v>
       </c>
-      <c r="B93" s="29" t="s">
-        <v>314</v>
+      <c r="B93" s="25" t="s">
+        <v>315</v>
       </c>
       <c r="C93" s="25" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D93" s="26" t="s">
         <v>174</v>
       </c>
       <c r="E93" s="26" t="s">
-        <v>316</v>
-      </c>
-      <c r="F93" s="35" t="s">
         <v>317</v>
       </c>
-      <c r="G93" s="57" t="s">
+      <c r="F93" s="33" t="s">
         <v>318</v>
+      </c>
+      <c r="G93" s="54" t="s">
+        <v>319</v>
       </c>
     </row>
     <row r="94" ht="15.75" hidden="1" spans="1:7">
@@ -4807,31 +4801,31 @@
         <v>93</v>
       </c>
       <c r="B94" s="25" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C94" s="25" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D94" s="26" t="s">
         <v>174</v>
       </c>
       <c r="E94" s="26"/>
-      <c r="F94" s="35" t="s">
-        <v>320</v>
+      <c r="F94" s="33" t="s">
+        <v>321</v>
       </c>
       <c r="G94" s="28" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="95" ht="15.75" hidden="1" spans="1:7">
       <c r="A95" s="24">
         <v>94</v>
       </c>
-      <c r="B95" s="29" t="s">
-        <v>322</v>
+      <c r="B95" s="25" t="s">
+        <v>323</v>
       </c>
       <c r="C95" s="25" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D95" s="26" t="s">
         <v>174</v>
@@ -4839,11 +4833,11 @@
       <c r="E95" s="26" t="s">
         <v>185</v>
       </c>
-      <c r="F95" s="52" t="s">
-        <v>324</v>
-      </c>
-      <c r="G95" s="57" t="s">
+      <c r="F95" s="48" t="s">
         <v>325</v>
+      </c>
+      <c r="G95" s="54" t="s">
+        <v>326</v>
       </c>
     </row>
     <row r="96" ht="15.75" hidden="1" spans="1:7">
@@ -4851,54 +4845,54 @@
         <v>95</v>
       </c>
       <c r="B96" s="25" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C96" s="25" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D96" s="26" t="s">
         <v>174</v>
       </c>
       <c r="E96" s="26"/>
-      <c r="F96" s="35" t="s">
-        <v>328</v>
+      <c r="F96" s="33" t="s">
+        <v>329</v>
       </c>
       <c r="G96" s="28" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="97" ht="31.5" hidden="1" spans="1:7">
       <c r="A97" s="24">
         <v>96</v>
       </c>
-      <c r="B97" s="41" t="s">
-        <v>330</v>
-      </c>
-      <c r="C97" s="32" t="s">
+      <c r="B97" s="25" t="s">
         <v>331</v>
       </c>
-      <c r="D97" s="33" t="s">
+      <c r="C97" s="30" t="s">
+        <v>332</v>
+      </c>
+      <c r="D97" s="31" t="s">
         <v>174</v>
       </c>
       <c r="E97" s="26" t="s">
-        <v>332</v>
-      </c>
-      <c r="F97" s="35" t="s">
         <v>333</v>
       </c>
+      <c r="F97" s="33" t="s">
+        <v>334</v>
+      </c>
       <c r="G97" s="28" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="98" ht="15.75" hidden="1" spans="1:7">
       <c r="A98" s="24">
         <v>97</v>
       </c>
-      <c r="B98" s="29" t="s">
-        <v>335</v>
+      <c r="B98" s="25" t="s">
+        <v>336</v>
       </c>
       <c r="C98" s="25" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D98" s="26" t="s">
         <v>174</v>
@@ -4906,11 +4900,11 @@
       <c r="E98" s="26" t="s">
         <v>190</v>
       </c>
-      <c r="F98" s="35" t="s">
-        <v>337</v>
+      <c r="F98" s="33" t="s">
+        <v>338</v>
       </c>
       <c r="G98" s="28" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="99" ht="15.75" hidden="1" spans="1:7">
@@ -4918,10 +4912,10 @@
         <v>98</v>
       </c>
       <c r="B99" s="25" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C99" s="25" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D99" s="26" t="s">
         <v>174</v>
@@ -4929,11 +4923,11 @@
       <c r="E99" s="26" t="s">
         <v>185</v>
       </c>
-      <c r="F99" s="35" t="s">
-        <v>341</v>
+      <c r="F99" s="33" t="s">
+        <v>342</v>
       </c>
       <c r="G99" s="28" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="100" ht="15.75" hidden="1" spans="1:7">
@@ -4941,14 +4935,14 @@
         <v>99</v>
       </c>
       <c r="B100" s="25" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C100" s="25"/>
       <c r="D100" s="26" t="s">
         <v>174</v>
       </c>
       <c r="E100" s="26"/>
-      <c r="F100" s="35"/>
+      <c r="F100" s="33"/>
       <c r="G100" s="28"/>
     </row>
     <row r="101" ht="15.75" hidden="1" spans="1:7">
@@ -4956,38 +4950,38 @@
         <v>100</v>
       </c>
       <c r="B101" s="25" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C101" s="25" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D101" s="26" t="s">
         <v>174</v>
       </c>
-      <c r="E101" s="42"/>
+      <c r="E101" s="38"/>
       <c r="F101" s="27" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="G101" s="28" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="102" ht="15.75" hidden="1" spans="1:7">
       <c r="A102" s="24">
         <v>101</v>
       </c>
-      <c r="B102" s="37" t="s">
-        <v>348</v>
+      <c r="B102" s="25" t="s">
+        <v>349</v>
       </c>
       <c r="C102" s="28" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D102" s="26" t="s">
         <v>174</v>
       </c>
-      <c r="E102" s="38"/>
+      <c r="E102" s="35"/>
       <c r="F102" s="27" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="G102" s="28"/>
     </row>
@@ -4996,31 +4990,31 @@
         <v>102</v>
       </c>
       <c r="B103" s="25" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C103" s="25" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D103" s="26" t="s">
         <v>174</v>
       </c>
-      <c r="E103" s="42"/>
-      <c r="F103" s="35" t="s">
-        <v>353</v>
+      <c r="E103" s="38"/>
+      <c r="F103" s="33" t="s">
+        <v>354</v>
       </c>
       <c r="G103" s="28" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="104" ht="15.75" hidden="1" spans="1:7">
       <c r="A104" s="24">
         <v>103</v>
       </c>
-      <c r="B104" s="29" t="s">
-        <v>355</v>
+      <c r="B104" s="25" t="s">
+        <v>356</v>
       </c>
       <c r="C104" s="25" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D104" s="26" t="s">
         <v>174</v>
@@ -5028,11 +5022,11 @@
       <c r="E104" s="26" t="s">
         <v>185</v>
       </c>
-      <c r="F104" s="35" t="s">
-        <v>357</v>
+      <c r="F104" s="33" t="s">
+        <v>358</v>
       </c>
       <c r="G104" s="28" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="105" ht="15.75" hidden="1" spans="1:7">
@@ -5040,20 +5034,20 @@
         <v>104</v>
       </c>
       <c r="B105" s="25" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C105" s="25" t="s">
-        <v>171</v>
+        <v>361</v>
       </c>
       <c r="D105" s="26" t="s">
         <v>174</v>
       </c>
-      <c r="E105" s="42"/>
-      <c r="F105" s="35" t="s">
-        <v>360</v>
+      <c r="E105" s="38"/>
+      <c r="F105" s="33" t="s">
+        <v>362</v>
       </c>
       <c r="G105" s="28" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="106" ht="15.75" hidden="1" spans="1:7">
@@ -5061,10 +5055,10 @@
         <v>105</v>
       </c>
       <c r="B106" s="25" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C106" s="25" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="D106" s="26" t="s">
         <v>174</v>
@@ -5072,11 +5066,11 @@
       <c r="E106" s="26" t="s">
         <v>190</v>
       </c>
-      <c r="F106" s="35" t="s">
-        <v>364</v>
-      </c>
-      <c r="G106" s="58" t="s">
-        <v>365</v>
+      <c r="F106" s="33" t="s">
+        <v>366</v>
+      </c>
+      <c r="G106" s="55" t="s">
+        <v>367</v>
       </c>
     </row>
     <row r="107" ht="15.75" hidden="1" spans="1:7">
@@ -5084,370 +5078,370 @@
         <v>106</v>
       </c>
       <c r="B107" s="25" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="C107" s="25" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="D107" s="26" t="s">
         <v>174</v>
       </c>
       <c r="E107" s="26" t="s">
-        <v>368</v>
-      </c>
-      <c r="F107" s="35" t="s">
-        <v>369</v>
+        <v>370</v>
+      </c>
+      <c r="F107" s="33" t="s">
+        <v>371</v>
       </c>
       <c r="G107" s="28"/>
     </row>
     <row r="108" ht="15.75" hidden="1" spans="1:7">
       <c r="A108" s="24"/>
-      <c r="B108" s="29" t="s">
-        <v>370</v>
-      </c>
-      <c r="C108" s="29" t="s">
-        <v>371</v>
-      </c>
-      <c r="D108" s="53" t="s">
+      <c r="B108" s="25" t="s">
+        <v>372</v>
+      </c>
+      <c r="C108" s="49" t="s">
+        <v>373</v>
+      </c>
+      <c r="D108" s="50" t="s">
         <v>174</v>
       </c>
-      <c r="E108" s="54"/>
-      <c r="F108" s="55" t="s">
-        <v>372</v>
-      </c>
-      <c r="G108" s="30"/>
+      <c r="E108" s="51"/>
+      <c r="F108" s="52" t="s">
+        <v>374</v>
+      </c>
+      <c r="G108" s="29"/>
     </row>
     <row r="109" ht="15.75" hidden="1" spans="1:7">
       <c r="A109" s="24"/>
-      <c r="B109" s="29" t="s">
-        <v>373</v>
-      </c>
-      <c r="C109" s="29" t="s">
-        <v>374</v>
-      </c>
-      <c r="D109" s="53" t="s">
+      <c r="B109" s="25" t="s">
+        <v>375</v>
+      </c>
+      <c r="C109" s="49" t="s">
+        <v>376</v>
+      </c>
+      <c r="D109" s="50" t="s">
         <v>174</v>
       </c>
-      <c r="E109" s="54"/>
-      <c r="F109" s="55" t="s">
-        <v>375</v>
-      </c>
-      <c r="G109" s="30"/>
-    </row>
-    <row r="110" ht="15.75" hidden="1" spans="1:7">
+      <c r="E109" s="51"/>
+      <c r="F109" s="52" t="s">
+        <v>377</v>
+      </c>
+      <c r="G109" s="29"/>
+    </row>
+    <row r="110" ht="31.5" hidden="1" spans="1:7">
       <c r="A110" s="24"/>
-      <c r="B110" s="29" t="s">
-        <v>376</v>
-      </c>
-      <c r="C110" s="29" t="s">
-        <v>377</v>
-      </c>
-      <c r="D110" s="53" t="s">
+      <c r="B110" s="25" t="s">
+        <v>378</v>
+      </c>
+      <c r="C110" s="49" t="s">
+        <v>379</v>
+      </c>
+      <c r="D110" s="50" t="s">
         <v>174</v>
       </c>
-      <c r="E110" s="54"/>
-      <c r="F110" s="55" t="s">
-        <v>378</v>
-      </c>
-      <c r="G110" s="30"/>
+      <c r="E110" s="51"/>
+      <c r="F110" s="52" t="s">
+        <v>380</v>
+      </c>
+      <c r="G110" s="29"/>
     </row>
     <row r="111" ht="15.75" hidden="1" spans="1:7">
       <c r="A111" s="24"/>
-      <c r="B111" s="29" t="s">
-        <v>379</v>
-      </c>
-      <c r="C111" s="29" t="s">
+      <c r="B111" s="25" t="s">
+        <v>381</v>
+      </c>
+      <c r="C111" s="49" t="s">
         <v>168</v>
       </c>
-      <c r="D111" s="53" t="s">
+      <c r="D111" s="50" t="s">
         <v>174</v>
       </c>
-      <c r="E111" s="54"/>
-      <c r="F111" s="55" t="s">
-        <v>380</v>
-      </c>
-      <c r="G111" s="30"/>
-    </row>
-    <row r="112" ht="15.75" hidden="1" spans="1:7">
+      <c r="E111" s="51"/>
+      <c r="F111" s="52" t="s">
+        <v>382</v>
+      </c>
+      <c r="G111" s="29"/>
+    </row>
+    <row r="112" ht="31.5" hidden="1" spans="1:7">
       <c r="A112" s="24"/>
-      <c r="B112" s="29" t="s">
-        <v>381</v>
-      </c>
-      <c r="C112" s="29" t="s">
-        <v>382</v>
-      </c>
-      <c r="D112" s="53" t="s">
+      <c r="B112" s="25" t="s">
+        <v>383</v>
+      </c>
+      <c r="C112" s="49" t="s">
+        <v>384</v>
+      </c>
+      <c r="D112" s="50" t="s">
         <v>174</v>
       </c>
-      <c r="E112" s="54"/>
-      <c r="F112" s="55" t="s">
-        <v>383</v>
-      </c>
-      <c r="G112" s="30"/>
+      <c r="E112" s="51"/>
+      <c r="F112" s="52" t="s">
+        <v>385</v>
+      </c>
+      <c r="G112" s="29"/>
     </row>
     <row r="113" ht="15.75" hidden="1" spans="1:7">
       <c r="A113" s="24"/>
-      <c r="B113" s="29" t="s">
-        <v>384</v>
-      </c>
-      <c r="C113" s="29" t="s">
-        <v>385</v>
-      </c>
-      <c r="D113" s="53" t="s">
+      <c r="B113" s="25" t="s">
+        <v>386</v>
+      </c>
+      <c r="C113" s="49" t="s">
+        <v>387</v>
+      </c>
+      <c r="D113" s="50" t="s">
         <v>174</v>
       </c>
-      <c r="E113" s="54"/>
-      <c r="F113" s="55" t="s">
-        <v>386</v>
-      </c>
-      <c r="G113" s="30"/>
+      <c r="E113" s="51"/>
+      <c r="F113" s="52" t="s">
+        <v>388</v>
+      </c>
+      <c r="G113" s="29"/>
     </row>
     <row r="114" ht="15.75" hidden="1" spans="1:7">
       <c r="A114" s="24"/>
-      <c r="B114" s="29" t="s">
-        <v>362</v>
-      </c>
-      <c r="C114" s="29" t="s">
-        <v>387</v>
-      </c>
-      <c r="D114" s="53" t="s">
+      <c r="B114" s="25" t="s">
+        <v>389</v>
+      </c>
+      <c r="C114" s="49" t="s">
+        <v>390</v>
+      </c>
+      <c r="D114" s="50" t="s">
         <v>174</v>
       </c>
-      <c r="E114" s="54"/>
-      <c r="F114" s="55" t="s">
-        <v>364</v>
-      </c>
-      <c r="G114" s="30"/>
+      <c r="E114" s="51"/>
+      <c r="F114" s="52" t="s">
+        <v>366</v>
+      </c>
+      <c r="G114" s="29"/>
     </row>
     <row r="115" s="15" customFormat="1" ht="15.75" hidden="1" spans="1:7">
       <c r="A115" s="24"/>
-      <c r="B115" s="29" t="s">
-        <v>388</v>
-      </c>
-      <c r="C115" s="29" t="s">
-        <v>389</v>
-      </c>
-      <c r="D115" s="53" t="s">
+      <c r="B115" s="25" t="s">
+        <v>391</v>
+      </c>
+      <c r="C115" s="49" t="s">
+        <v>392</v>
+      </c>
+      <c r="D115" s="50" t="s">
         <v>174</v>
       </c>
-      <c r="E115" s="54"/>
-      <c r="F115" s="55" t="s">
-        <v>390</v>
-      </c>
-      <c r="G115" s="30"/>
+      <c r="E115" s="51"/>
+      <c r="F115" s="52" t="s">
+        <v>393</v>
+      </c>
+      <c r="G115" s="29"/>
     </row>
     <row r="116" ht="15.75" hidden="1" spans="1:7">
       <c r="A116" s="24"/>
-      <c r="B116" s="29" t="s">
-        <v>391</v>
-      </c>
-      <c r="C116" s="29" t="s">
-        <v>392</v>
-      </c>
-      <c r="D116" s="53" t="s">
+      <c r="B116" s="25" t="s">
+        <v>394</v>
+      </c>
+      <c r="C116" s="49" t="s">
+        <v>395</v>
+      </c>
+      <c r="D116" s="50" t="s">
         <v>174</v>
       </c>
-      <c r="E116" s="53" t="s">
+      <c r="E116" s="50" t="s">
         <v>190</v>
       </c>
-      <c r="F116" s="55" t="s">
-        <v>393</v>
-      </c>
-      <c r="G116" s="30"/>
+      <c r="F116" s="52" t="s">
+        <v>396</v>
+      </c>
+      <c r="G116" s="29"/>
     </row>
     <row r="117" ht="15.75" hidden="1" spans="1:7">
       <c r="A117" s="24"/>
-      <c r="B117" s="29" t="s">
-        <v>394</v>
-      </c>
-      <c r="C117" s="29" t="s">
-        <v>395</v>
-      </c>
-      <c r="D117" s="53" t="s">
+      <c r="B117" s="25" t="s">
+        <v>397</v>
+      </c>
+      <c r="C117" s="49" t="s">
+        <v>398</v>
+      </c>
+      <c r="D117" s="50" t="s">
         <v>174</v>
       </c>
-      <c r="E117" s="54"/>
-      <c r="F117" s="55" t="s">
-        <v>396</v>
-      </c>
-      <c r="G117" s="30"/>
+      <c r="E117" s="51"/>
+      <c r="F117" s="52" t="s">
+        <v>399</v>
+      </c>
+      <c r="G117" s="29"/>
     </row>
     <row r="118" ht="15.75" hidden="1" spans="1:7">
       <c r="A118" s="24"/>
-      <c r="B118" s="29" t="s">
-        <v>397</v>
-      </c>
-      <c r="C118" s="29" t="s">
-        <v>398</v>
-      </c>
-      <c r="D118" s="53" t="s">
+      <c r="B118" s="25" t="s">
+        <v>400</v>
+      </c>
+      <c r="C118" s="49" t="s">
+        <v>401</v>
+      </c>
+      <c r="D118" s="50" t="s">
         <v>174</v>
       </c>
-      <c r="E118" s="54"/>
-      <c r="F118" s="55" t="s">
-        <v>399</v>
-      </c>
-      <c r="G118" s="30"/>
+      <c r="E118" s="51"/>
+      <c r="F118" s="52" t="s">
+        <v>402</v>
+      </c>
+      <c r="G118" s="29"/>
     </row>
     <row r="119" ht="15.75" hidden="1" spans="1:7">
       <c r="A119" s="24"/>
-      <c r="B119" s="29" t="s">
-        <v>400</v>
-      </c>
-      <c r="C119" s="29" t="s">
-        <v>401</v>
-      </c>
-      <c r="D119" s="53" t="s">
+      <c r="B119" s="25" t="s">
+        <v>403</v>
+      </c>
+      <c r="C119" s="49" t="s">
+        <v>404</v>
+      </c>
+      <c r="D119" s="50" t="s">
         <v>174</v>
       </c>
-      <c r="E119" s="54"/>
-      <c r="F119" s="55" t="s">
-        <v>402</v>
-      </c>
-      <c r="G119" s="30"/>
+      <c r="E119" s="51"/>
+      <c r="F119" s="52" t="s">
+        <v>405</v>
+      </c>
+      <c r="G119" s="29"/>
     </row>
     <row r="120" ht="15.75" hidden="1" spans="1:7">
       <c r="A120" s="24"/>
-      <c r="B120" s="29" t="s">
-        <v>403</v>
-      </c>
-      <c r="C120" s="29" t="s">
-        <v>404</v>
-      </c>
-      <c r="D120" s="53" t="s">
+      <c r="B120" s="25" t="s">
+        <v>406</v>
+      </c>
+      <c r="C120" s="49" t="s">
+        <v>407</v>
+      </c>
+      <c r="D120" s="50" t="s">
         <v>174</v>
       </c>
-      <c r="E120" s="54"/>
-      <c r="F120" s="55" t="s">
-        <v>405</v>
-      </c>
-      <c r="G120" s="30"/>
+      <c r="E120" s="51"/>
+      <c r="F120" s="52" t="s">
+        <v>408</v>
+      </c>
+      <c r="G120" s="29"/>
     </row>
     <row r="121" ht="15.75" hidden="1" spans="1:7">
       <c r="A121" s="24"/>
-      <c r="B121" s="29" t="s">
-        <v>406</v>
-      </c>
-      <c r="C121" s="29" t="s">
-        <v>407</v>
-      </c>
-      <c r="D121" s="53" t="s">
+      <c r="B121" s="25" t="s">
+        <v>409</v>
+      </c>
+      <c r="C121" s="49" t="s">
+        <v>410</v>
+      </c>
+      <c r="D121" s="50" t="s">
         <v>174</v>
       </c>
-      <c r="E121" s="54"/>
-      <c r="F121" s="55" t="s">
-        <v>408</v>
-      </c>
-      <c r="G121" s="30"/>
+      <c r="E121" s="51"/>
+      <c r="F121" s="52" t="s">
+        <v>411</v>
+      </c>
+      <c r="G121" s="29"/>
     </row>
     <row r="122" ht="15.75" hidden="1" spans="1:7">
       <c r="A122" s="24"/>
-      <c r="B122" s="29" t="s">
-        <v>409</v>
-      </c>
-      <c r="C122" s="29" t="s">
-        <v>410</v>
-      </c>
-      <c r="D122" s="53" t="s">
+      <c r="B122" s="25" t="s">
+        <v>412</v>
+      </c>
+      <c r="C122" s="49" t="s">
+        <v>413</v>
+      </c>
+      <c r="D122" s="50" t="s">
         <v>174</v>
       </c>
-      <c r="E122" s="54"/>
-      <c r="F122" s="55" t="s">
-        <v>411</v>
-      </c>
-      <c r="G122" s="30"/>
+      <c r="E122" s="51"/>
+      <c r="F122" s="52" t="s">
+        <v>414</v>
+      </c>
+      <c r="G122" s="29"/>
     </row>
     <row r="123" ht="15.75" hidden="1" spans="1:7">
       <c r="A123" s="24"/>
-      <c r="B123" s="29" t="s">
-        <v>412</v>
-      </c>
-      <c r="C123" s="29" t="s">
+      <c r="B123" s="25" t="s">
+        <v>415</v>
+      </c>
+      <c r="C123" s="49" t="s">
         <v>76</v>
       </c>
-      <c r="D123" s="53" t="s">
+      <c r="D123" s="50" t="s">
         <v>174</v>
       </c>
-      <c r="E123" s="54"/>
-      <c r="F123" s="55" t="s">
-        <v>413</v>
-      </c>
-      <c r="G123" s="56" t="s">
+      <c r="E123" s="51"/>
+      <c r="F123" s="52" t="s">
+        <v>416</v>
+      </c>
+      <c r="G123" s="53" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="124" ht="15.75" hidden="1" spans="1:7">
       <c r="A124" s="24"/>
-      <c r="B124" s="29" t="s">
-        <v>414</v>
-      </c>
-      <c r="C124" s="29" t="s">
-        <v>415</v>
-      </c>
-      <c r="D124" s="53" t="s">
+      <c r="B124" s="25" t="s">
+        <v>417</v>
+      </c>
+      <c r="C124" s="49" t="s">
+        <v>418</v>
+      </c>
+      <c r="D124" s="50" t="s">
         <v>174</v>
       </c>
-      <c r="E124" s="54"/>
-      <c r="F124" s="55" t="s">
-        <v>416</v>
-      </c>
-      <c r="G124" s="30"/>
+      <c r="E124" s="51"/>
+      <c r="F124" s="52" t="s">
+        <v>419</v>
+      </c>
+      <c r="G124" s="29"/>
     </row>
     <row r="125" ht="15.75" hidden="1" spans="1:7">
       <c r="A125" s="24"/>
-      <c r="B125" s="29" t="s">
-        <v>417</v>
-      </c>
-      <c r="C125" s="29" t="s">
-        <v>418</v>
-      </c>
-      <c r="D125" s="53"/>
-      <c r="E125" s="53" t="s">
+      <c r="B125" s="25" t="s">
+        <v>420</v>
+      </c>
+      <c r="C125" s="49" t="s">
+        <v>421</v>
+      </c>
+      <c r="D125" s="50"/>
+      <c r="E125" s="50" t="s">
         <v>10</v>
       </c>
-      <c r="F125" s="55" t="s">
-        <v>419</v>
-      </c>
-      <c r="G125" s="30"/>
+      <c r="F125" s="52" t="s">
+        <v>422</v>
+      </c>
+      <c r="G125" s="29"/>
     </row>
     <row r="126" ht="15.75" hidden="1" spans="1:7">
       <c r="A126" s="24"/>
-      <c r="B126" s="29" t="s">
-        <v>420</v>
-      </c>
-      <c r="C126" s="29" t="s">
-        <v>421</v>
-      </c>
-      <c r="D126" s="53"/>
-      <c r="E126" s="53" t="s">
+      <c r="B126" s="25" t="s">
+        <v>423</v>
+      </c>
+      <c r="C126" s="49" t="s">
+        <v>424</v>
+      </c>
+      <c r="D126" s="50"/>
+      <c r="E126" s="50" t="s">
         <v>38</v>
       </c>
-      <c r="F126" s="55" t="s">
-        <v>422</v>
-      </c>
-      <c r="G126" s="30"/>
+      <c r="F126" s="52" t="s">
+        <v>425</v>
+      </c>
+      <c r="G126" s="29"/>
     </row>
     <row r="127" ht="15.75" hidden="1" spans="1:7">
       <c r="A127" s="24"/>
-      <c r="B127" s="29" t="s">
-        <v>423</v>
-      </c>
-      <c r="C127" s="29" t="s">
+      <c r="B127" s="25" t="s">
+        <v>426</v>
+      </c>
+      <c r="C127" s="49" t="s">
         <v>148</v>
       </c>
-      <c r="D127" s="53" t="s">
+      <c r="D127" s="50" t="s">
         <v>174</v>
       </c>
-      <c r="E127" s="54"/>
-      <c r="F127" s="55" t="s">
-        <v>424</v>
-      </c>
-      <c r="G127" s="30"/>
+      <c r="E127" s="51"/>
+      <c r="F127" s="52" t="s">
+        <v>427</v>
+      </c>
+      <c r="G127" s="29"/>
     </row>
     <row r="128" spans="1:7">
       <c r="A128" s="19"/>
       <c r="D128" s="17"/>
-      <c r="F128" s="51"/>
+      <c r="F128" s="47"/>
     </row>
     <row r="129" spans="1:4">
       <c r="A129" s="19"/>
@@ -9609,7 +9603,7 @@
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G127" etc:filterBottomFollowUsedRange="0">
     <filterColumn colId="1">
       <filters>
-        <filter val="MILOUA"/>
+        <filter val="FELLAH MOHAMMED KARIM MOHAMMED KARIM"/>
       </filters>
     </filterColumn>
     <extLst/>
@@ -9677,202 +9671,202 @@
   <sheetData>
     <row r="1" ht="15.75" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="2" ht="15.75" spans="1:4">
       <c r="A2" s="4" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="3" ht="15.75" spans="1:4">
       <c r="A3" s="8"/>
       <c r="B3" s="5" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="4" ht="15.75" spans="1:4">
       <c r="A4" s="8"/>
       <c r="B4" s="5" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="5" ht="15.75" spans="1:4">
       <c r="A5" s="8"/>
       <c r="B5" s="5" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="6" ht="15.75" spans="1:4">
       <c r="A6" s="8"/>
       <c r="B6" s="5" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
     </row>
     <row r="7" ht="15.75" spans="1:4">
       <c r="A7" s="9" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="8" ht="15.75" spans="1:4">
       <c r="A8" s="8"/>
       <c r="B8" s="10" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="9" ht="15.75" spans="1:4">
       <c r="A9" s="11" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
     </row>
     <row r="10" ht="15.75" spans="1:4">
       <c r="A10" s="8"/>
       <c r="B10" s="13" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="11" ht="15.75" spans="1:4">
       <c r="A11" s="8"/>
       <c r="B11" s="13" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="12" ht="15.75" spans="1:4">
       <c r="A12" s="8"/>
       <c r="B12" s="13" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="13" ht="15.75" spans="1:4">
       <c r="A13" s="8"/>
       <c r="B13" s="13" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="14" ht="15.75" spans="1:4">
       <c r="A14" s="8"/>
       <c r="B14" s="13" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
     </row>
     <row r="15" ht="15.75" spans="1:4">
       <c r="A15" s="8"/>
       <c r="B15" s="13" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="16" ht="15.75" spans="1:4">
       <c r="A16" s="8"/>
       <c r="B16" s="13" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
     </row>
     <row r="656" ht="15.75"/>

--- a/Permanents-Vacataires-ELT2-2026-2027.xlsx
+++ b/Permanents-Vacataires-ELT2-2026-2027.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="733" uniqueCount="466">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="738" uniqueCount="363">
   <si>
     <t>N°</t>
   </si>
@@ -58,7 +58,7 @@
     <t>ABID MOHAMED</t>
   </si>
   <si>
-    <t>MOHAMED</t>
+    <t>-</t>
   </si>
   <si>
     <t>Permanent</t>
@@ -76,9 +76,6 @@
     <t>AKSA WESSIM</t>
   </si>
   <si>
-    <t>WESSIM</t>
-  </si>
-  <si>
     <t>aksa86wessim@gmail.com</t>
   </si>
   <si>
@@ -88,36 +85,24 @@
     <t>ARDJOUN SID AHMED</t>
   </si>
   <si>
-    <t>SID AHMED</t>
-  </si>
-  <si>
     <t>ardjoun.s.e.m@gmail.com</t>
   </si>
   <si>
     <t>AYAD ABDELGHANI</t>
   </si>
   <si>
-    <t>ABDELGHANI</t>
-  </si>
-  <si>
     <t>ayad_abdelghani@yahoo.fr</t>
   </si>
   <si>
     <t>AZAIZ AHMED</t>
   </si>
   <si>
-    <t>AHMED</t>
-  </si>
-  <si>
     <t>ahazaiz2011@yahoo.fr</t>
   </si>
   <si>
     <t>BADIS KARIMA</t>
   </si>
   <si>
-    <t>KARIMA</t>
-  </si>
-  <si>
     <t>Permanente</t>
   </si>
   <si>
@@ -133,9 +118,6 @@
     <t>BAHLIL MOUNIR</t>
   </si>
   <si>
-    <t>MOUNIR</t>
-  </si>
-  <si>
     <t>bahlilmounir@yahoo.fr</t>
   </si>
   <si>
@@ -145,9 +127,6 @@
     <t>BECHEKIR SEYFEDDINE</t>
   </si>
   <si>
-    <t>SEYFEDDINE</t>
-  </si>
-  <si>
     <t>MCA</t>
   </si>
   <si>
@@ -157,9 +136,6 @@
     <t>BEDDAD BOUCIF</t>
   </si>
   <si>
-    <t>BOUCIF</t>
-  </si>
-  <si>
     <t>beddadboucif@gmail.com</t>
   </si>
   <si>
@@ -169,63 +145,42 @@
     <t>BELLEBNA YASSINE</t>
   </si>
   <si>
-    <t>YASSINE</t>
-  </si>
-  <si>
     <t>fgevdpg@gmail.com</t>
   </si>
   <si>
     <t>BENAISSA ABDELKADER</t>
   </si>
   <si>
-    <t>ABDELKADER</t>
-  </si>
-  <si>
     <t>aek_benaissa@yahoo.fr</t>
   </si>
   <si>
     <t>BERRAHAL BEL ABBES</t>
   </si>
   <si>
-    <t>BEL ABBES</t>
-  </si>
-  <si>
     <t>dept.eln@gmail.com</t>
   </si>
   <si>
     <t>BENBELLIL NADJAT</t>
   </si>
   <si>
-    <t>NADJAT</t>
-  </si>
-  <si>
     <t xml:space="preserve">nn.nn.phy.chi@gmail.com </t>
   </si>
   <si>
     <t>BENDAOUD ABDELBER</t>
   </si>
   <si>
-    <t>ABDELBER</t>
-  </si>
-  <si>
     <t>babdelber22@yahoo.fr</t>
   </si>
   <si>
     <t>BENDIMERAD SALAH EDDINE</t>
   </si>
   <si>
-    <t>SALAH EDDINE</t>
-  </si>
-  <si>
     <t>s_bendimerad@yahoo.fr</t>
   </si>
   <si>
     <t>BENGRIT MALIKA</t>
   </si>
   <si>
-    <t>MALIKA</t>
-  </si>
-  <si>
     <t>MAA</t>
   </si>
   <si>
@@ -235,126 +190,84 @@
     <t>BENHAMIDA FARID</t>
   </si>
   <si>
-    <t>FARID</t>
-  </si>
-  <si>
     <t>farid.benhamida@yahoo.fr</t>
   </si>
   <si>
     <t>BENKHALLOUK KADDOUR</t>
   </si>
   <si>
-    <t>KADDOUR</t>
-  </si>
-  <si>
     <t>benkh_ka@yahoo.fr</t>
   </si>
   <si>
     <t>BENTAALLAH ABDERRAHIM</t>
   </si>
   <si>
-    <t>ABDERRAHIM</t>
-  </si>
-  <si>
     <t>bentaallah65@yahoo.fr</t>
   </si>
   <si>
     <t>BERMAKI HAMZA</t>
   </si>
   <si>
-    <t>HAMZA</t>
-  </si>
-  <si>
     <t>bermaki.hamza@gmail.com</t>
   </si>
   <si>
     <t>BOUKHOULDA FODIL</t>
   </si>
   <si>
-    <t>FODIL</t>
-  </si>
-  <si>
     <t>boukhoulda.fodil@yahoo.fr</t>
   </si>
   <si>
     <t>BOUNOUA HOURIA</t>
   </si>
   <si>
-    <t>HOURIA</t>
-  </si>
-  <si>
     <t>hsemmach@yahoo.fr</t>
   </si>
   <si>
     <t>DJERIRI YOUCEF</t>
   </si>
   <si>
-    <t>YOUCEF</t>
-  </si>
-  <si>
     <t>djeriri_youcef@yahoo.fr</t>
   </si>
   <si>
     <t>DRIEF FAIZA</t>
   </si>
   <si>
-    <t>FAIZA</t>
-  </si>
-  <si>
     <t xml:space="preserve">drieff4@gmail.com </t>
   </si>
   <si>
     <t>FELLAH MOHAMMED KARIM</t>
   </si>
   <si>
-    <t>MOHAMMED KARIM</t>
-  </si>
-  <si>
     <t>mkfellah@gmail.com</t>
   </si>
   <si>
     <t>GHAZEL FATIHA</t>
   </si>
   <si>
-    <t>FATIHA</t>
-  </si>
-  <si>
     <t>nour73_fac@yahoo.fr</t>
   </si>
   <si>
     <t>HADJERI SAMIR</t>
   </si>
   <si>
-    <t>SAMIR</t>
-  </si>
-  <si>
     <t>shadjeri2@yahoo.fr</t>
   </si>
   <si>
     <t>HANAFI SALAH</t>
   </si>
   <si>
-    <t>SALAH</t>
-  </si>
-  <si>
     <t xml:space="preserve">sal_hanafi@outlook.com </t>
   </si>
   <si>
     <t>HASSANI NAIMA</t>
   </si>
   <si>
-    <t>NAIMA</t>
-  </si>
-  <si>
     <t>naimahassani69@yahoo.fr</t>
   </si>
   <si>
     <t>JBILOU MOKHTARIA</t>
   </si>
   <si>
-    <t>MOKHTARIA</t>
-  </si>
-  <si>
     <t>harmel71@yahoo.fr</t>
   </si>
   <si>
@@ -367,18 +280,12 @@
     <t>LALEDJ NADJET</t>
   </si>
   <si>
-    <t>NADJET</t>
-  </si>
-  <si>
     <t>nadjet_69@hotmail.fr</t>
   </si>
   <si>
     <t>M.BRAHAMI MOSTEFA</t>
   </si>
   <si>
-    <t>MOSTEFA</t>
-  </si>
-  <si>
     <t>mbrahami@yahoo.com</t>
   </si>
   <si>
@@ -403,18 +310,12 @@
     <t>MILOUDI HOUCINE</t>
   </si>
   <si>
-    <t>HOUCINE</t>
-  </si>
-  <si>
     <t>el.houcine@yahoo.fr</t>
   </si>
   <si>
     <t>MIMOUNI CHAHINEZ</t>
   </si>
   <si>
-    <t>CHAHINEZ</t>
-  </si>
-  <si>
     <t xml:space="preserve">mimounichahinez@gmail.com </t>
   </si>
   <si>
@@ -424,45 +325,30 @@
     <t>MN.BRAHAMI NADJIB</t>
   </si>
   <si>
-    <t>NADJIB</t>
-  </si>
-  <si>
     <t>nadjbrahami@gmail.com</t>
   </si>
   <si>
     <t>NACERI ABDELLATIF</t>
   </si>
   <si>
-    <t>ABDELLATIF</t>
-  </si>
-  <si>
     <t>abdnaceri@yahoo.fr</t>
   </si>
   <si>
     <t>NASSOUR KAMEL</t>
   </si>
   <si>
-    <t>KAMEL</t>
-  </si>
-  <si>
     <t>nass_ka@yahoo.fr</t>
   </si>
   <si>
     <t>NEMMICH SAID</t>
   </si>
   <si>
-    <t>SAID</t>
-  </si>
-  <si>
     <t>nemmichsaid@gmail.com</t>
   </si>
   <si>
     <t>OUKLI MIMOUNA</t>
   </si>
   <si>
-    <t>MIMOUNA</t>
-  </si>
-  <si>
     <t>mounaoukli@yahoo.fr</t>
   </si>
   <si>
@@ -478,54 +364,36 @@
     <t>REZOUG MOHAMMED</t>
   </si>
   <si>
-    <t>MOHAMMED</t>
-  </si>
-  <si>
     <t>rezoug.med@gmail.com</t>
   </si>
   <si>
     <t>SAHALI YAMINA</t>
   </si>
   <si>
-    <t>YAMINA</t>
-  </si>
-  <si>
     <t>ya_sahali@yahoo.fr</t>
   </si>
   <si>
     <t>SEMMAH ABDELHAFID</t>
   </si>
   <si>
-    <t>ABDELHAFID</t>
-  </si>
-  <si>
     <t>hafid.semmah@yahoo.fr</t>
   </si>
   <si>
     <t>TABET DERRAZ HIND</t>
   </si>
   <si>
-    <t>HIND</t>
-  </si>
-  <si>
     <t>htabet05@yahoo.fr</t>
   </si>
   <si>
     <t>TILMATINE AMAR</t>
   </si>
   <si>
-    <t>AMAR</t>
-  </si>
-  <si>
     <t>atilmatine@gmail.com</t>
   </si>
   <si>
     <t>TOUHAMI SEDDIK</t>
   </si>
   <si>
-    <t>SEDDIK</t>
-  </si>
-  <si>
     <t>seddik.touhami@gmail.com</t>
   </si>
   <si>
@@ -538,9 +406,6 @@
     <t>ZENASNI MERIEM</t>
   </si>
   <si>
-    <t>MERIEM</t>
-  </si>
-  <si>
     <t>zenasnimeriem29@gmail.com</t>
   </si>
   <si>
@@ -571,9 +436,6 @@
     <t>ABDELI MAMA</t>
   </si>
   <si>
-    <t>MAMA</t>
-  </si>
-  <si>
     <t>abdelli.mama@gmail.com</t>
   </si>
   <si>
@@ -586,9 +448,6 @@
     <t>ARAB ABDELMADJID</t>
   </si>
   <si>
-    <t>ABDELMADJID</t>
-  </si>
-  <si>
     <t>Doctorat</t>
   </si>
   <si>
@@ -601,9 +460,6 @@
     <t>AREZKI MOUFOK</t>
   </si>
   <si>
-    <t>MOUFOK</t>
-  </si>
-  <si>
     <t>Master</t>
   </si>
   <si>
@@ -616,9 +472,6 @@
     <t>BENCELLA SARRA</t>
   </si>
   <si>
-    <t>SARRA</t>
-  </si>
-  <si>
     <t>sarrabencella@gmail.com</t>
   </si>
   <si>
@@ -637,9 +490,6 @@
     <t>BELHABRI RIHAB</t>
   </si>
   <si>
-    <t>RIHAB</t>
-  </si>
-  <si>
     <t>ri123hab@gmail.com</t>
   </si>
   <si>
@@ -649,9 +499,6 @@
     <t>BELHALLOUCHE LAKHDAR</t>
   </si>
   <si>
-    <t>LAKHDAR</t>
-  </si>
-  <si>
     <t>lakhdar_belhallouche@hotmail.fr</t>
   </si>
   <si>
@@ -661,9 +508,6 @@
     <t>BENSALEM RITEDJ INES</t>
   </si>
   <si>
-    <t>RITEDJ INES</t>
-  </si>
-  <si>
     <t>rawnakritedj@gmail.com</t>
   </si>
   <si>
@@ -673,9 +517,6 @@
     <t>BENSALEM ABDELHAMID</t>
   </si>
   <si>
-    <t>ABDELHAMID</t>
-  </si>
-  <si>
     <t>bensalemabdelhamid7@gmail.com</t>
   </si>
   <si>
@@ -685,9 +526,6 @@
     <t>BETTACHE ABDERRAHMANE</t>
   </si>
   <si>
-    <t>ABDERRAHMANE</t>
-  </si>
-  <si>
     <t>abderrahmanbettache@gmail.com</t>
   </si>
   <si>
@@ -697,9 +535,6 @@
     <t>BOUBEKEUR HALIMA</t>
   </si>
   <si>
-    <t>HALIMA</t>
-  </si>
-  <si>
     <t>boubekeur97sba@gmail.com</t>
   </si>
   <si>
@@ -718,9 +553,6 @@
     <t>BOUKHARI SOUMIA</t>
   </si>
   <si>
-    <t>SOUMIA</t>
-  </si>
-  <si>
     <t>boukharisoumiafarah@gmail.com</t>
   </si>
   <si>
@@ -730,9 +562,6 @@
     <t>BOULARAF AICHA</t>
   </si>
   <si>
-    <t>AICHA</t>
-  </si>
-  <si>
     <t>douaaboularaf@gmail.com</t>
   </si>
   <si>
@@ -742,9 +571,6 @@
     <t>BOURAHLA CHAHRAZED</t>
   </si>
   <si>
-    <t>CHAHRAZED</t>
-  </si>
-  <si>
     <t>bourahla.phys@gmail.com</t>
   </si>
   <si>
@@ -754,9 +580,6 @@
     <t>CHABANE CHAOUCHE ABDALLAH</t>
   </si>
   <si>
-    <t>ABDALLAH</t>
-  </si>
-  <si>
     <t>chaouche.abdallah@gmail.com</t>
   </si>
   <si>
@@ -766,9 +589,6 @@
     <t>DJELLOULI YOUNES</t>
   </si>
   <si>
-    <t>YOUNES</t>
-  </si>
-  <si>
     <t xml:space="preserve">djellouli08younes08@gmail.com </t>
   </si>
   <si>
@@ -787,9 +607,6 @@
     <t>DRICI LAMIA</t>
   </si>
   <si>
-    <t>LAMIA</t>
-  </si>
-  <si>
     <t>Lamia_du22@hotmail.com</t>
   </si>
   <si>
@@ -799,9 +616,6 @@
     <t xml:space="preserve">DROUNI Wassila Abir </t>
   </si>
   <si>
-    <t xml:space="preserve">Wassila Abir </t>
-  </si>
-  <si>
     <t>Wassila.drouni@gmail.com</t>
   </si>
   <si>
@@ -811,9 +625,6 @@
     <t>El MESTARI WAHIBA</t>
   </si>
   <si>
-    <t>WAHIBA</t>
-  </si>
-  <si>
     <t>wahibaelmestarii@gmail.com</t>
   </si>
   <si>
@@ -823,19 +634,13 @@
     <t>ELGHODASSE ABDEL MADJID</t>
   </si>
   <si>
-    <t>ABDEL MADJID</t>
-  </si>
-  <si>
     <t>elghodasseabdelmadjid@gmail.com</t>
   </si>
   <si>
     <t>05 41 77 21 68</t>
   </si>
   <si>
-    <t>FETHI.M FETHI</t>
-  </si>
-  <si>
-    <t>FETHI</t>
+    <t>MILOUA FATHI</t>
   </si>
   <si>
     <t>fethi22miloua@gmail.com</t>
@@ -844,9 +649,6 @@
     <t>GHALEM ABDELHAK</t>
   </si>
   <si>
-    <t>ABDELHAK</t>
-  </si>
-  <si>
     <t>ghalem.abdelhak@yahoo.com</t>
   </si>
   <si>
@@ -865,9 +667,6 @@
     <t>BENHARAT ABDELHADI</t>
   </si>
   <si>
-    <t>ABDELHADI</t>
-  </si>
-  <si>
     <t>Hadi.bnh00@gmail.com</t>
   </si>
   <si>
@@ -883,9 +682,6 @@
     <t>HAMMAR MEHDI</t>
   </si>
   <si>
-    <t>MEHDI</t>
-  </si>
-  <si>
     <t>protoboy9999@gmail.com</t>
   </si>
   <si>
@@ -901,9 +697,6 @@
     <t>KHELLAF KADDA</t>
   </si>
   <si>
-    <t>KADDA</t>
-  </si>
-  <si>
     <t>khellafkadda1234@gmail.com</t>
   </si>
   <si>
@@ -913,18 +706,12 @@
     <t>LAHCEN AZDDINE</t>
   </si>
   <si>
-    <t>AZDDINE</t>
-  </si>
-  <si>
     <t>azddinelahcene@gmail.com</t>
   </si>
   <si>
     <t>LATRECHE MOKHTAR</t>
   </si>
   <si>
-    <t>MOKHTAR</t>
-  </si>
-  <si>
     <t>m_latreche@yahoo.com</t>
   </si>
   <si>
@@ -934,9 +721,6 @@
     <t>LOUSDAD AYMEN</t>
   </si>
   <si>
-    <t>AYMEN</t>
-  </si>
-  <si>
     <t>lousdadaymen.aziz@gmail.com</t>
   </si>
   <si>
@@ -946,9 +730,6 @@
     <t>MAHIDDINE Abderrahim</t>
   </si>
   <si>
-    <t>Abderrahim</t>
-  </si>
-  <si>
     <t>ma2006ne_86@yahoo.fr</t>
   </si>
   <si>
@@ -958,9 +739,6 @@
     <t>MAHKOUKA ZAZA</t>
   </si>
   <si>
-    <t>ZAZA</t>
-  </si>
-  <si>
     <t>mahkouka.zaza@gmail.com</t>
   </si>
   <si>
@@ -970,9 +748,6 @@
     <t>MANSOURI ABDERRAZAK</t>
   </si>
   <si>
-    <t>ABDERRAZAK</t>
-  </si>
-  <si>
     <t>abderazakmahdi22@gmail.com</t>
   </si>
   <si>
@@ -982,9 +757,6 @@
     <t>MECHETTEM KHALIDA</t>
   </si>
   <si>
-    <t>KHALIDA</t>
-  </si>
-  <si>
     <t>Doctorante (Master)</t>
   </si>
   <si>
@@ -1006,9 +778,6 @@
     <t>MERADJAH IBRAHIM</t>
   </si>
   <si>
-    <t>IBRAHIM</t>
-  </si>
-  <si>
     <t>ibrahimmeradjah72@gmail.com</t>
   </si>
   <si>
@@ -1018,9 +787,6 @@
     <t>MESLEM MEHADJIA</t>
   </si>
   <si>
-    <t>MEHADJIA</t>
-  </si>
-  <si>
     <t>mehadjiameslem@gmail.com</t>
   </si>
   <si>
@@ -1030,9 +796,6 @@
     <t>MOULAY MILOUD</t>
   </si>
   <si>
-    <t>MILOUD</t>
-  </si>
-  <si>
     <t>Doctorant (Magister)</t>
   </si>
   <si>
@@ -1045,9 +808,6 @@
     <t>MIR KHELIFA</t>
   </si>
   <si>
-    <t>KHELIFA</t>
-  </si>
-  <si>
     <t>khelifa-mir@outlook.fr</t>
   </si>
   <si>
@@ -1057,9 +817,6 @@
     <t>MOKEDDEM AMINA</t>
   </si>
   <si>
-    <t>AMINA</t>
-  </si>
-  <si>
     <t>mokeddem.amina2222@gmail.com</t>
   </si>
   <si>
@@ -1072,9 +829,6 @@
     <t>REDJALA MAJDA</t>
   </si>
   <si>
-    <t>MAJDA</t>
-  </si>
-  <si>
     <t>majdaredjala1492@gmail.com</t>
   </si>
   <si>
@@ -1084,18 +838,12 @@
     <t>SENOUCI HAYAT</t>
   </si>
   <si>
-    <t>HAYAT</t>
-  </si>
-  <si>
     <t>senoucihayat11@gmail.com</t>
   </si>
   <si>
     <t>ZAREB Mohammed Amine</t>
   </si>
   <si>
-    <t>Mohammed Amine</t>
-  </si>
-  <si>
     <t>zarebmohammedamine@gmail.com</t>
   </si>
   <si>
@@ -1105,9 +853,6 @@
     <t>ZIANI DJAMEL</t>
   </si>
   <si>
-    <t>DJAMEL</t>
-  </si>
-  <si>
     <t>djamel71ziani@gmail.com</t>
   </si>
   <si>
@@ -1117,9 +862,6 @@
     <t>LARBI ZIDI</t>
   </si>
   <si>
-    <t>ZIDI</t>
-  </si>
-  <si>
     <t>larbi.zidi6@gmail.com</t>
   </si>
   <si>
@@ -1129,9 +871,6 @@
     <t>BERROUNA HENEN</t>
   </si>
   <si>
-    <t>HENEN</t>
-  </si>
-  <si>
     <t>berhenen@yahoo.fr</t>
   </si>
   <si>
@@ -1141,9 +880,6 @@
     <t>MOUILAH  KHEIRA</t>
   </si>
   <si>
-    <t>KHEIRA</t>
-  </si>
-  <si>
     <t>Ingénieur</t>
   </si>
   <si>
@@ -1153,27 +889,18 @@
     <t>ABED ZOULIKHA</t>
   </si>
   <si>
-    <t>ZOULIKHA</t>
-  </si>
-  <si>
     <t>zoulikhaabed3@gmail.com</t>
   </si>
   <si>
     <t>AISSANI ALI</t>
   </si>
   <si>
-    <t>ALI</t>
-  </si>
-  <si>
     <t>aliaissani97@gmail.com</t>
   </si>
   <si>
     <t>AZZA ROMAISSA FATIMA ZOHRA</t>
   </si>
   <si>
-    <t>ROMAISSA FATIMA ZOHRA</t>
-  </si>
-  <si>
     <t>azzafatimazohraromaissa.l3@gmail.com</t>
   </si>
   <si>
@@ -1186,96 +913,63 @@
     <t>BENKABOU MOHAMED EL HABIB</t>
   </si>
   <si>
-    <t>MOHAMED EL HABIB</t>
-  </si>
-  <si>
     <t>bkbhbb22@gmail.com</t>
   </si>
   <si>
     <t>BENMASOUD LEILA</t>
   </si>
   <si>
-    <t>LEILA</t>
-  </si>
-  <si>
     <t>l.benmessaoud@yahoo.fr</t>
   </si>
   <si>
     <t>BERROUNA HANANE</t>
   </si>
   <si>
-    <t>HANANE</t>
-  </si>
-  <si>
     <t>CHIKHI NAWEL</t>
   </si>
   <si>
-    <t>NAWEL</t>
-  </si>
-  <si>
     <t>chikhi nawel75@yahoo.fr</t>
   </si>
   <si>
     <t>DELLOUM AMIRA</t>
   </si>
   <si>
-    <t>AMIRA</t>
-  </si>
-  <si>
     <t>amiradelloum28@gmail.com</t>
   </si>
   <si>
     <t>FENTAZY BELKISSE</t>
   </si>
   <si>
-    <t>BELKISSE</t>
-  </si>
-  <si>
     <t>fantazibelkisse.13@gmail.com</t>
   </si>
   <si>
     <t>FEZAZI KHADIDJA</t>
   </si>
   <si>
-    <t>KHADIDJA</t>
-  </si>
-  <si>
     <t>khadidjafezazi90@gmail</t>
   </si>
   <si>
     <t>KADA ZAIR IKRAM</t>
   </si>
   <si>
-    <t>IKRAM</t>
-  </si>
-  <si>
     <t>ikram.kadazair@gmail.com</t>
   </si>
   <si>
     <t>KADRI RANIA</t>
   </si>
   <si>
-    <t>RANIA</t>
-  </si>
-  <si>
     <t>kadrirania51@gmail.com</t>
   </si>
   <si>
     <t>LAYATI TAYEB MEHDI</t>
   </si>
   <si>
-    <t>TAYEB MEHDI</t>
-  </si>
-  <si>
     <t>layatimedi@gmail.com</t>
   </si>
   <si>
     <t>NEFAHA ABOUBAKR</t>
   </si>
   <si>
-    <t>ABOUBAKR</t>
-  </si>
-  <si>
     <t>Boba1620@hotmail.com</t>
   </si>
   <si>
@@ -1288,16 +982,13 @@
     <t>TURKI BILAL MEROUANE</t>
   </si>
   <si>
-    <t>BILAL MEROUANE</t>
-  </si>
-  <si>
     <t>turkibilal22@gmail.com</t>
   </si>
   <si>
     <t>RAIS ABDELMAJID</t>
   </si>
   <si>
-    <t>ABDELMAJID</t>
+    <t>Retraité</t>
   </si>
   <si>
     <t>amrais@yahoo.com</t>
@@ -1306,7 +997,7 @@
     <t>REGUIG ABDELDJALIL</t>
   </si>
   <si>
-    <t>ABDELDJALIL</t>
+    <t>Mise en disponibilité</t>
   </si>
   <si>
     <t>abdeldjalil.reguig@outlook.com</t>
@@ -2203,7 +1894,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2286,9 +1977,6 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2304,17 +1992,14 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2329,9 +2014,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2340,9 +2022,6 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2707,7 +2386,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr filterMode="1" codeName="Sheet1"/>
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:G1167"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.25" outlineLevelCol="6"/>
   <cols>
@@ -2744,7 +2423,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" ht="15.75" hidden="1" spans="1:7">
+    <row r="2" ht="15.75" spans="1:7">
       <c r="A2" s="24">
         <v>1</v>
       </c>
@@ -2767,7 +2446,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" ht="15.75" hidden="1" spans="1:7">
+    <row r="3" ht="15.75" spans="1:7">
       <c r="A3" s="24">
         <v>2</v>
       </c>
@@ -2775,7 +2454,7 @@
         <v>13</v>
       </c>
       <c r="C3" s="25" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D3" s="26" t="s">
         <v>9</v>
@@ -2784,21 +2463,21 @@
         <v>10</v>
       </c>
       <c r="F3" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="28" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" ht="15.75" hidden="1" spans="1:7">
+    </row>
+    <row r="4" ht="15.75" spans="1:7">
       <c r="A4" s="24">
         <v>3</v>
       </c>
       <c r="B4" s="25" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C4" s="25" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="D4" s="26" t="s">
         <v>9</v>
@@ -2807,21 +2486,21 @@
         <v>10</v>
       </c>
       <c r="F4" s="27" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G4" s="28" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="5" ht="15.75" hidden="1" spans="1:7">
+    <row r="5" ht="15.75" spans="1:7">
       <c r="A5" s="24">
         <v>4</v>
       </c>
       <c r="B5" s="25" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C5" s="25" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="D5" s="26" t="s">
         <v>9</v>
@@ -2830,21 +2509,21 @@
         <v>10</v>
       </c>
       <c r="F5" s="27" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G5" s="28" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="6" ht="15.75" hidden="1" spans="1:7">
+    <row r="6" ht="15.75" spans="1:7">
       <c r="A6" s="24">
         <v>5</v>
       </c>
       <c r="B6" s="25" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C6" s="25" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="D6" s="26" t="s">
         <v>9</v>
@@ -2853,44 +2532,44 @@
         <v>10</v>
       </c>
       <c r="F6" s="27" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G6" s="28" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="7" ht="15.75" hidden="1" spans="1:7">
+    <row r="7" ht="15.75" spans="1:7">
       <c r="A7" s="24">
         <v>6</v>
       </c>
       <c r="B7" s="25" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="F7" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="G7" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="C7" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="D7" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="E7" s="26" t="s">
-        <v>29</v>
-      </c>
-      <c r="F7" s="27" t="s">
-        <v>30</v>
-      </c>
-      <c r="G7" s="54" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="8" ht="15.75" hidden="1" spans="1:7">
+    </row>
+    <row r="8" ht="15.75" spans="1:7">
       <c r="A8" s="24">
         <v>7</v>
       </c>
       <c r="B8" s="25" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C8" s="25" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="D8" s="26" t="s">
         <v>9</v>
@@ -2899,67 +2578,67 @@
         <v>10</v>
       </c>
       <c r="F8" s="27" t="s">
-        <v>34</v>
-      </c>
-      <c r="G8" s="54" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="9" ht="15.75" hidden="1" spans="1:7">
+        <v>28</v>
+      </c>
+      <c r="G8" s="50" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" ht="15.75" spans="1:7">
       <c r="A9" s="24">
         <v>8</v>
       </c>
       <c r="B9" s="25" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C9" s="25" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="D9" s="26" t="s">
         <v>9</v>
       </c>
       <c r="E9" s="26" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="F9" s="27" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="G9" s="28" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="10" ht="15.75" hidden="1" spans="1:7">
+    <row r="10" ht="15.75" spans="1:7">
       <c r="A10" s="24">
         <v>9</v>
       </c>
       <c r="B10" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="C10" s="30" t="s">
-        <v>41</v>
-      </c>
-      <c r="D10" s="31" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="E10" s="32" t="s">
-        <v>38</v>
-      </c>
-      <c r="F10" s="33" t="s">
-        <v>42</v>
-      </c>
-      <c r="G10" s="54" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="11" ht="15.75" hidden="1" spans="1:7">
+      <c r="E10" s="31" t="s">
+        <v>31</v>
+      </c>
+      <c r="F10" s="32" t="s">
+        <v>34</v>
+      </c>
+      <c r="G10" s="50" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" ht="15.75" spans="1:7">
       <c r="A11" s="24">
         <v>10</v>
       </c>
       <c r="B11" s="25" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="C11" s="25" t="s">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="D11" s="26" t="s">
         <v>9</v>
@@ -2967,22 +2646,22 @@
       <c r="E11" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="F11" s="34" t="s">
-        <v>46</v>
+      <c r="F11" s="33" t="s">
+        <v>37</v>
       </c>
       <c r="G11" s="28" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="12" ht="15.75" hidden="1" spans="1:7">
+    <row r="12" ht="15.75" spans="1:7">
       <c r="A12" s="24">
         <v>11</v>
       </c>
       <c r="B12" s="25" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="C12" s="25" t="s">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="D12" s="26" t="s">
         <v>9</v>
@@ -2991,21 +2670,21 @@
         <v>10</v>
       </c>
       <c r="F12" s="27" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="G12" s="28" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="13" ht="15.75" hidden="1" spans="1:7">
+    <row r="13" ht="15.75" spans="1:7">
       <c r="A13" s="24">
         <v>12</v>
       </c>
       <c r="B13" s="25" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="C13" s="25" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="D13" s="26" t="s">
         <v>9</v>
@@ -3014,42 +2693,42 @@
         <v>10</v>
       </c>
       <c r="F13" s="27" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="G13" s="28"/>
     </row>
-    <row r="14" ht="15.75" hidden="1" spans="1:7">
+    <row r="14" ht="15.75" spans="1:7">
       <c r="A14" s="24">
         <v>13</v>
       </c>
       <c r="B14" s="25" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="C14" s="25" t="s">
-        <v>54</v>
+        <v>8</v>
       </c>
       <c r="D14" s="26" t="s">
         <v>9</v>
       </c>
       <c r="E14" s="26" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="F14" s="27" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="G14" s="28" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="15" ht="15.75" hidden="1" spans="1:7">
+    <row r="15" ht="15.75" spans="1:7">
       <c r="A15" s="24">
         <v>14</v>
       </c>
       <c r="B15" s="25" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="C15" s="25" t="s">
-        <v>57</v>
+        <v>8</v>
       </c>
       <c r="D15" s="26" t="s">
         <v>9</v>
@@ -3058,67 +2737,67 @@
         <v>10</v>
       </c>
       <c r="F15" s="27" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="G15" s="28" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="16" ht="31.5" hidden="1" spans="1:7">
+    <row r="16" ht="31.5" spans="1:7">
       <c r="A16" s="24">
         <v>15</v>
       </c>
       <c r="B16" s="25" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="C16" s="25" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="D16" s="26" t="s">
         <v>9</v>
       </c>
       <c r="E16" s="26" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="F16" s="27" t="s">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="G16" s="28" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="17" ht="15.75" hidden="1" spans="1:7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" ht="15.75" spans="1:7">
       <c r="A17" s="24">
         <v>16</v>
       </c>
       <c r="B17" s="25" t="s">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="C17" s="25" t="s">
-        <v>63</v>
+        <v>8</v>
       </c>
       <c r="D17" s="26" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="E17" s="26" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="F17" s="27" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="G17" s="28" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" ht="15.75" hidden="1" spans="1:7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" ht="15.75" spans="1:7">
       <c r="A18" s="24">
         <v>17</v>
       </c>
       <c r="B18" s="25" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="C18" s="25" t="s">
-        <v>67</v>
+        <v>8</v>
       </c>
       <c r="D18" s="26" t="s">
         <v>9</v>
@@ -3127,44 +2806,44 @@
         <v>10</v>
       </c>
       <c r="F18" s="27" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="G18" s="28" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="19" ht="15.75" hidden="1" spans="1:7">
+    <row r="19" ht="15.75" spans="1:7">
       <c r="A19" s="24">
         <v>18</v>
       </c>
       <c r="B19" s="25" t="s">
-        <v>69</v>
-      </c>
-      <c r="C19" s="28" t="s">
-        <v>70</v>
+        <v>53</v>
+      </c>
+      <c r="C19" s="25" t="s">
+        <v>8</v>
       </c>
       <c r="D19" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="E19" s="35" t="s">
-        <v>64</v>
-      </c>
-      <c r="F19" s="33" t="s">
-        <v>71</v>
+      <c r="E19" s="34" t="s">
+        <v>49</v>
+      </c>
+      <c r="F19" s="32" t="s">
+        <v>54</v>
       </c>
       <c r="G19" s="28" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="20" ht="31.5" hidden="1" spans="1:7">
+    <row r="20" ht="31.5" spans="1:7">
       <c r="A20" s="24">
         <v>19</v>
       </c>
       <c r="B20" s="25" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="C20" s="25" t="s">
-        <v>73</v>
+        <v>8</v>
       </c>
       <c r="D20" s="26" t="s">
         <v>9</v>
@@ -3173,44 +2852,44 @@
         <v>10</v>
       </c>
       <c r="F20" s="27" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="G20" s="28" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="21" ht="15.75" hidden="1" spans="1:7">
+    <row r="21" ht="15.75" spans="1:7">
       <c r="A21" s="24">
         <v>20</v>
       </c>
       <c r="B21" s="25" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="C21" s="25" t="s">
-        <v>76</v>
+        <v>8</v>
       </c>
       <c r="D21" s="26" t="s">
         <v>9</v>
       </c>
       <c r="E21" s="26" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="F21" s="27" t="s">
-        <v>77</v>
+        <v>58</v>
       </c>
       <c r="G21" s="28" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="22" ht="15.75" hidden="1" spans="1:7">
+    <row r="22" ht="15.75" spans="1:7">
       <c r="A22" s="24">
         <v>21</v>
       </c>
       <c r="B22" s="25" t="s">
-        <v>78</v>
+        <v>59</v>
       </c>
       <c r="C22" s="25" t="s">
-        <v>79</v>
+        <v>8</v>
       </c>
       <c r="D22" s="26" t="s">
         <v>9</v>
@@ -3219,90 +2898,90 @@
         <v>10</v>
       </c>
       <c r="F22" s="27" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="G22" s="28" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="23" ht="15.75" hidden="1" spans="1:7">
+    <row r="23" ht="15.75" spans="1:7">
       <c r="A23" s="24">
         <v>22</v>
       </c>
       <c r="B23" s="25" t="s">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="C23" s="25" t="s">
-        <v>82</v>
+        <v>8</v>
       </c>
       <c r="D23" s="26" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="E23" s="26" t="s">
         <v>10</v>
       </c>
       <c r="F23" s="27" t="s">
-        <v>83</v>
+        <v>62</v>
       </c>
       <c r="G23" s="28" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="24" ht="15.75" hidden="1" spans="1:7">
+    <row r="24" ht="15.75" spans="1:7">
       <c r="A24" s="24">
         <v>23</v>
       </c>
       <c r="B24" s="25" t="s">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="C24" s="25" t="s">
-        <v>85</v>
+        <v>8</v>
       </c>
       <c r="D24" s="26" t="s">
         <v>9</v>
       </c>
       <c r="E24" s="26" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="F24" s="27" t="s">
-        <v>86</v>
+        <v>64</v>
       </c>
       <c r="G24" s="28" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="25" ht="15.75" hidden="1" spans="1:7">
+    <row r="25" ht="15.75" spans="1:7">
       <c r="A25" s="24">
         <v>24</v>
       </c>
       <c r="B25" s="25" t="s">
-        <v>87</v>
+        <v>65</v>
       </c>
       <c r="C25" s="25" t="s">
-        <v>88</v>
+        <v>8</v>
       </c>
       <c r="D25" s="26" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="E25" s="26" t="s">
-        <v>38</v>
-      </c>
-      <c r="F25" s="33" t="s">
-        <v>89</v>
+        <v>31</v>
+      </c>
+      <c r="F25" s="32" t="s">
+        <v>66</v>
       </c>
       <c r="G25" s="28" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="26" ht="47.25" spans="1:7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" ht="31.5" spans="1:7">
       <c r="A26" s="24">
         <v>25</v>
       </c>
       <c r="B26" s="25" t="s">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="C26" s="25" t="s">
-        <v>91</v>
+        <v>8</v>
       </c>
       <c r="D26" s="26" t="s">
         <v>9</v>
@@ -3311,42 +2990,42 @@
         <v>10</v>
       </c>
       <c r="F26" s="27" t="s">
-        <v>92</v>
+        <v>68</v>
       </c>
       <c r="G26" s="28" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="27" ht="15.75" hidden="1" spans="1:7">
+    <row r="27" ht="15.75" spans="1:7">
       <c r="A27" s="24">
         <v>26</v>
       </c>
       <c r="B27" s="25" t="s">
-        <v>93</v>
+        <v>69</v>
       </c>
       <c r="C27" s="25" t="s">
-        <v>94</v>
+        <v>8</v>
       </c>
       <c r="D27" s="26" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="E27" s="26" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="F27" s="27" t="s">
-        <v>95</v>
+        <v>70</v>
       </c>
       <c r="G27" s="28"/>
     </row>
-    <row r="28" ht="15.75" hidden="1" spans="1:7">
+    <row r="28" ht="15.75" spans="1:7">
       <c r="A28" s="24">
         <v>27</v>
       </c>
       <c r="B28" s="25" t="s">
-        <v>96</v>
+        <v>71</v>
       </c>
       <c r="C28" s="25" t="s">
-        <v>97</v>
+        <v>8</v>
       </c>
       <c r="D28" s="26" t="s">
         <v>9</v>
@@ -3355,87 +3034,87 @@
         <v>10</v>
       </c>
       <c r="F28" s="27" t="s">
-        <v>98</v>
+        <v>72</v>
       </c>
       <c r="G28" s="28" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="29" ht="15.75" hidden="1" spans="1:7">
+    <row r="29" ht="15.75" spans="1:7">
       <c r="A29" s="24">
         <v>28</v>
       </c>
       <c r="B29" s="25" t="s">
-        <v>99</v>
+        <v>73</v>
       </c>
       <c r="C29" s="25" t="s">
-        <v>100</v>
+        <v>8</v>
       </c>
       <c r="D29" s="26" t="s">
         <v>9</v>
       </c>
       <c r="E29" s="26" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="F29" s="27" t="s">
-        <v>101</v>
+        <v>74</v>
       </c>
       <c r="G29" s="28" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="30" ht="15.75" hidden="1" spans="1:7">
+    <row r="30" ht="15.75" spans="1:7">
       <c r="A30" s="24">
         <v>29</v>
       </c>
       <c r="B30" s="25" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="C30" s="25" t="s">
-        <v>103</v>
+        <v>8</v>
       </c>
       <c r="D30" s="26" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="E30" s="26" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="F30" s="27" t="s">
-        <v>104</v>
+        <v>76</v>
       </c>
       <c r="G30" s="28" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="31" ht="15.75" hidden="1" spans="1:7">
+    <row r="31" ht="15.75" spans="1:7">
       <c r="A31" s="24">
         <v>30</v>
       </c>
       <c r="B31" s="25" t="s">
-        <v>105</v>
+        <v>77</v>
       </c>
       <c r="C31" s="25" t="s">
-        <v>106</v>
+        <v>8</v>
       </c>
       <c r="D31" s="26" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="E31" s="26" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="F31" s="27" t="s">
-        <v>107</v>
+        <v>78</v>
       </c>
       <c r="G31" s="28" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="32" ht="15.75" hidden="1" spans="1:7">
+    <row r="32" ht="15.75" spans="1:7">
       <c r="A32" s="24">
         <v>31</v>
       </c>
       <c r="B32" s="25" t="s">
-        <v>108</v>
+        <v>79</v>
       </c>
       <c r="C32" s="25" t="s">
         <v>8</v>
@@ -3447,42 +3126,42 @@
         <v>10</v>
       </c>
       <c r="F32" s="27" t="s">
-        <v>109</v>
+        <v>80</v>
       </c>
       <c r="G32" s="28"/>
     </row>
-    <row r="33" ht="15.75" hidden="1" spans="1:7">
+    <row r="33" ht="15.75" spans="1:7">
       <c r="A33" s="24">
         <v>32</v>
       </c>
       <c r="B33" s="25" t="s">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="C33" s="25" t="s">
-        <v>111</v>
+        <v>8</v>
       </c>
       <c r="D33" s="26" t="s">
         <v>9</v>
       </c>
       <c r="E33" s="26" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="F33" s="27" t="s">
-        <v>112</v>
+        <v>82</v>
       </c>
       <c r="G33" s="28" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="34" ht="15.75" hidden="1" spans="1:7">
+    <row r="34" ht="15.75" spans="1:7">
       <c r="A34" s="24">
         <v>33</v>
       </c>
       <c r="B34" s="25" t="s">
-        <v>113</v>
+        <v>83</v>
       </c>
       <c r="C34" s="25" t="s">
-        <v>114</v>
+        <v>8</v>
       </c>
       <c r="D34" s="26" t="s">
         <v>9</v>
@@ -3491,18 +3170,18 @@
         <v>10</v>
       </c>
       <c r="F34" s="27" t="s">
-        <v>115</v>
+        <v>84</v>
       </c>
       <c r="G34" s="28" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="35" ht="15.75" hidden="1" spans="1:7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="35" ht="15.75" spans="1:7">
       <c r="A35" s="24">
         <v>34</v>
       </c>
       <c r="B35" s="25" t="s">
-        <v>116</v>
+        <v>85</v>
       </c>
       <c r="C35" s="25" t="s">
         <v>8</v>
@@ -3511,24 +3190,24 @@
         <v>9</v>
       </c>
       <c r="E35" s="26" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="F35" s="27" t="s">
-        <v>117</v>
+        <v>86</v>
       </c>
       <c r="G35" s="28" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="36" ht="15.75" hidden="1" spans="1:7">
+    <row r="36" ht="15.75" spans="1:7">
       <c r="A36" s="24">
         <v>35</v>
       </c>
       <c r="B36" s="25" t="s">
-        <v>118</v>
+        <v>87</v>
       </c>
       <c r="C36" s="25" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="D36" s="26" t="s">
         <v>9</v>
@@ -3537,21 +3216,21 @@
         <v>10</v>
       </c>
       <c r="F36" s="27" t="s">
-        <v>119</v>
+        <v>88</v>
       </c>
       <c r="G36" s="28" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="37" ht="15.75" hidden="1" spans="1:7">
+    <row r="37" ht="15.75" spans="1:7">
       <c r="A37" s="24">
         <v>36</v>
       </c>
       <c r="B37" s="25" t="s">
-        <v>120</v>
+        <v>89</v>
       </c>
       <c r="C37" s="25" t="s">
-        <v>67</v>
+        <v>8</v>
       </c>
       <c r="D37" s="26" t="s">
         <v>9</v>
@@ -3560,21 +3239,21 @@
         <v>10</v>
       </c>
       <c r="F37" s="27" t="s">
-        <v>121</v>
+        <v>90</v>
       </c>
       <c r="G37" s="28" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="38" ht="15.75" hidden="1" spans="1:7">
+    <row r="38" ht="15.75" spans="1:7">
       <c r="A38" s="24">
         <v>37</v>
       </c>
       <c r="B38" s="25" t="s">
-        <v>122</v>
+        <v>91</v>
       </c>
       <c r="C38" s="25" t="s">
-        <v>123</v>
+        <v>8</v>
       </c>
       <c r="D38" s="26" t="s">
         <v>9</v>
@@ -3583,67 +3262,67 @@
         <v>10</v>
       </c>
       <c r="F38" s="27" t="s">
-        <v>124</v>
+        <v>92</v>
       </c>
       <c r="G38" s="28" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="39" ht="15.75" hidden="1" spans="1:7">
+    <row r="39" ht="15.75" spans="1:7">
       <c r="A39" s="24">
         <v>38</v>
       </c>
       <c r="B39" s="25" t="s">
-        <v>125</v>
+        <v>93</v>
       </c>
       <c r="C39" s="25" t="s">
-        <v>126</v>
+        <v>8</v>
       </c>
       <c r="D39" s="26" t="s">
         <v>9</v>
       </c>
       <c r="E39" s="26" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="F39" s="27" t="s">
-        <v>127</v>
-      </c>
-      <c r="G39" s="54" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="40" ht="15.75" hidden="1" spans="1:7">
+        <v>94</v>
+      </c>
+      <c r="G39" s="50" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="40" ht="15.75" spans="1:7">
       <c r="A40" s="24">
         <v>39</v>
       </c>
       <c r="B40" s="25" t="s">
-        <v>129</v>
+        <v>96</v>
       </c>
       <c r="C40" s="25" t="s">
-        <v>130</v>
+        <v>8</v>
       </c>
       <c r="D40" s="26" t="s">
         <v>9</v>
       </c>
       <c r="E40" s="26" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="F40" s="27" t="s">
-        <v>131</v>
+        <v>97</v>
       </c>
       <c r="G40" s="28" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="41" ht="15.75" hidden="1" spans="1:7">
+    <row r="41" ht="15.75" spans="1:7">
       <c r="A41" s="24">
         <v>40</v>
       </c>
       <c r="B41" s="25" t="s">
-        <v>132</v>
+        <v>98</v>
       </c>
       <c r="C41" s="25" t="s">
-        <v>133</v>
+        <v>8</v>
       </c>
       <c r="D41" s="26" t="s">
         <v>9</v>
@@ -3652,21 +3331,21 @@
         <v>10</v>
       </c>
       <c r="F41" s="27" t="s">
-        <v>134</v>
+        <v>99</v>
       </c>
       <c r="G41" s="28" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="42" ht="15.75" hidden="1" spans="1:7">
+    <row r="42" ht="15.75" spans="1:7">
       <c r="A42" s="24">
         <v>41</v>
       </c>
       <c r="B42" s="25" t="s">
-        <v>135</v>
+        <v>100</v>
       </c>
       <c r="C42" s="25" t="s">
-        <v>136</v>
+        <v>8</v>
       </c>
       <c r="D42" s="26" t="s">
         <v>9</v>
@@ -3675,21 +3354,21 @@
         <v>10</v>
       </c>
       <c r="F42" s="27" t="s">
-        <v>137</v>
+        <v>101</v>
       </c>
       <c r="G42" s="28" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="43" ht="15.75" hidden="1" spans="1:7">
+    <row r="43" ht="15.75" spans="1:7">
       <c r="A43" s="24">
         <v>42</v>
       </c>
       <c r="B43" s="25" t="s">
-        <v>138</v>
+        <v>102</v>
       </c>
       <c r="C43" s="25" t="s">
-        <v>139</v>
+        <v>8</v>
       </c>
       <c r="D43" s="26" t="s">
         <v>9</v>
@@ -3698,44 +3377,44 @@
         <v>10</v>
       </c>
       <c r="F43" s="27" t="s">
-        <v>140</v>
+        <v>103</v>
       </c>
       <c r="G43" s="28" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="44" ht="15.75" hidden="1" spans="1:7">
+    <row r="44" ht="15.75" spans="1:7">
       <c r="A44" s="24">
         <v>43</v>
       </c>
       <c r="B44" s="25" t="s">
-        <v>141</v>
+        <v>104</v>
       </c>
       <c r="C44" s="25" t="s">
-        <v>142</v>
+        <v>8</v>
       </c>
       <c r="D44" s="26" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="E44" s="26" t="s">
         <v>10</v>
       </c>
       <c r="F44" s="27" t="s">
-        <v>143</v>
+        <v>105</v>
       </c>
       <c r="G44" s="28" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="45" ht="15.75" hidden="1" spans="1:7">
+    <row r="45" ht="15.75" spans="1:7">
       <c r="A45" s="24">
         <v>44</v>
       </c>
       <c r="B45" s="25" t="s">
-        <v>144</v>
+        <v>106</v>
       </c>
       <c r="C45" s="25" t="s">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="D45" s="26" t="s">
         <v>9</v>
@@ -3744,21 +3423,21 @@
         <v>10</v>
       </c>
       <c r="F45" s="27" t="s">
-        <v>145</v>
+        <v>107</v>
       </c>
       <c r="G45" s="28" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="46" ht="15.75" hidden="1" spans="1:7">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="46" ht="15.75" spans="1:7">
       <c r="A46" s="24">
         <v>45</v>
       </c>
       <c r="B46" s="25" t="s">
-        <v>147</v>
+        <v>109</v>
       </c>
       <c r="C46" s="25" t="s">
-        <v>148</v>
+        <v>8</v>
       </c>
       <c r="D46" s="26" t="s">
         <v>9</v>
@@ -3767,44 +3446,44 @@
         <v>10</v>
       </c>
       <c r="F46" s="27" t="s">
-        <v>149</v>
+        <v>110</v>
       </c>
       <c r="G46" s="28" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="47" ht="15.75" hidden="1" spans="1:7">
+    <row r="47" ht="15.75" spans="1:7">
       <c r="A47" s="24">
         <v>46</v>
       </c>
       <c r="B47" s="25" t="s">
-        <v>150</v>
+        <v>111</v>
       </c>
       <c r="C47" s="25" t="s">
-        <v>151</v>
+        <v>8</v>
       </c>
       <c r="D47" s="26" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="E47" s="26" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="F47" s="27" t="s">
-        <v>152</v>
+        <v>112</v>
       </c>
       <c r="G47" s="28" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="48" ht="15.75" hidden="1" spans="1:7">
+    <row r="48" ht="15.75" spans="1:7">
       <c r="A48" s="24">
         <v>47</v>
       </c>
       <c r="B48" s="25" t="s">
-        <v>153</v>
+        <v>113</v>
       </c>
       <c r="C48" s="25" t="s">
-        <v>154</v>
+        <v>8</v>
       </c>
       <c r="D48" s="26" t="s">
         <v>9</v>
@@ -3813,44 +3492,44 @@
         <v>10</v>
       </c>
       <c r="F48" s="27" t="s">
-        <v>155</v>
+        <v>114</v>
       </c>
       <c r="G48" s="28" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="49" ht="15.75" hidden="1" spans="1:7">
+    <row r="49" ht="15.75" spans="1:7">
       <c r="A49" s="24">
         <v>48</v>
       </c>
       <c r="B49" s="25" t="s">
-        <v>156</v>
+        <v>115</v>
       </c>
       <c r="C49" s="25" t="s">
-        <v>157</v>
+        <v>8</v>
       </c>
       <c r="D49" s="26" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="E49" s="26" t="s">
         <v>10</v>
       </c>
       <c r="F49" s="27" t="s">
-        <v>158</v>
+        <v>116</v>
       </c>
       <c r="G49" s="28" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="50" ht="15.75" hidden="1" spans="1:7">
+    <row r="50" ht="15.75" spans="1:7">
       <c r="A50" s="24">
         <v>49</v>
       </c>
       <c r="B50" s="25" t="s">
-        <v>159</v>
+        <v>117</v>
       </c>
       <c r="C50" s="25" t="s">
-        <v>160</v>
+        <v>8</v>
       </c>
       <c r="D50" s="26" t="s">
         <v>9</v>
@@ -3859,44 +3538,44 @@
         <v>10</v>
       </c>
       <c r="F50" s="27" t="s">
-        <v>161</v>
+        <v>118</v>
       </c>
       <c r="G50" s="28" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="51" ht="15.75" hidden="1" spans="1:7">
+    <row r="51" ht="15.75" spans="1:7">
       <c r="A51" s="24">
         <v>50</v>
       </c>
       <c r="B51" s="25" t="s">
-        <v>162</v>
+        <v>119</v>
       </c>
       <c r="C51" s="25" t="s">
-        <v>163</v>
+        <v>8</v>
       </c>
       <c r="D51" s="26" t="s">
         <v>9</v>
       </c>
       <c r="E51" s="26" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="F51" s="27" t="s">
-        <v>164</v>
+        <v>120</v>
       </c>
       <c r="G51" s="28" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="52" ht="15.75" hidden="1" spans="1:7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="52" ht="15.75" spans="1:7">
       <c r="A52" s="24">
         <v>51</v>
       </c>
       <c r="B52" s="25" t="s">
-        <v>165</v>
+        <v>121</v>
       </c>
       <c r="C52" s="25" t="s">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="D52" s="26" t="s">
         <v>9</v>
@@ -3905,44 +3584,44 @@
         <v>10</v>
       </c>
       <c r="F52" s="27" t="s">
-        <v>166</v>
+        <v>122</v>
       </c>
       <c r="G52" s="28" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="53" ht="15.75" hidden="1" spans="1:7">
+    <row r="53" ht="15.75" spans="1:7">
       <c r="A53" s="24">
         <v>52</v>
       </c>
       <c r="B53" s="25" t="s">
-        <v>167</v>
+        <v>123</v>
       </c>
       <c r="C53" s="25" t="s">
-        <v>168</v>
+        <v>8</v>
       </c>
       <c r="D53" s="26" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="E53" s="26" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="F53" s="27" t="s">
-        <v>169</v>
-      </c>
-      <c r="G53" s="54" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="54" ht="15.75" hidden="1" spans="1:7">
+        <v>124</v>
+      </c>
+      <c r="G53" s="50" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="54" ht="15.75" spans="1:7">
       <c r="A54" s="24">
         <v>53</v>
       </c>
       <c r="B54" s="25" t="s">
-        <v>171</v>
+        <v>126</v>
       </c>
       <c r="C54" s="25" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="D54" s="26" t="s">
         <v>9</v>
@@ -3951,1497 +3630,1507 @@
         <v>10</v>
       </c>
       <c r="F54" s="27" t="s">
-        <v>172</v>
+        <v>127</v>
       </c>
       <c r="G54" s="28" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="55" ht="15.75" hidden="1" spans="1:7">
+    <row r="55" ht="15.75" spans="1:7">
       <c r="A55" s="24">
         <v>54</v>
       </c>
       <c r="B55" s="25" t="s">
-        <v>173</v>
-      </c>
-      <c r="C55" s="36" t="s">
-        <v>8</v>
-      </c>
-      <c r="D55" s="31" t="s">
-        <v>174</v>
+        <v>128</v>
+      </c>
+      <c r="C55" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D55" s="30" t="s">
+        <v>129</v>
       </c>
       <c r="E55" s="26" t="s">
-        <v>175</v>
-      </c>
-      <c r="F55" s="33" t="s">
-        <v>176</v>
-      </c>
-      <c r="G55" s="54" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="56" ht="15.75" hidden="1" spans="1:7">
+        <v>130</v>
+      </c>
+      <c r="F55" s="32" t="s">
+        <v>131</v>
+      </c>
+      <c r="G55" s="50" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="56" ht="15.75" spans="1:7">
       <c r="A56" s="24">
         <v>55</v>
       </c>
       <c r="B56" s="25" t="s">
-        <v>178</v>
-      </c>
-      <c r="C56" s="36" t="s">
-        <v>179</v>
-      </c>
-      <c r="D56" s="31" t="s">
-        <v>174</v>
-      </c>
-      <c r="E56" s="37"/>
+        <v>133</v>
+      </c>
+      <c r="C56" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D56" s="30" t="s">
+        <v>129</v>
+      </c>
+      <c r="E56" s="35"/>
       <c r="F56" s="27" t="s">
-        <v>180</v>
+        <v>134</v>
       </c>
       <c r="G56" s="28" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="57" ht="15.75" hidden="1" spans="1:7">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="57" ht="15.75" spans="1:7">
       <c r="A57" s="24">
         <v>56</v>
       </c>
       <c r="B57" s="25" t="s">
-        <v>182</v>
-      </c>
-      <c r="C57" s="30"/>
-      <c r="D57" s="31" t="s">
-        <v>174</v>
-      </c>
-      <c r="E57" s="32"/>
-      <c r="F57" s="30"/>
+        <v>136</v>
+      </c>
+      <c r="C57" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D57" s="30" t="s">
+        <v>129</v>
+      </c>
+      <c r="E57" s="31"/>
+      <c r="F57" s="36"/>
       <c r="G57" s="28"/>
     </row>
-    <row r="58" ht="15.75" hidden="1" spans="1:7">
+    <row r="58" ht="15.75" spans="1:7">
       <c r="A58" s="24">
         <v>57</v>
       </c>
       <c r="B58" s="25" t="s">
-        <v>183</v>
-      </c>
-      <c r="C58" s="36" t="s">
-        <v>184</v>
-      </c>
-      <c r="D58" s="31" t="s">
-        <v>174</v>
-      </c>
-      <c r="E58" s="31" t="s">
-        <v>185</v>
-      </c>
-      <c r="F58" s="33" t="s">
-        <v>186</v>
+        <v>137</v>
+      </c>
+      <c r="C58" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D58" s="30" t="s">
+        <v>129</v>
+      </c>
+      <c r="E58" s="30" t="s">
+        <v>138</v>
+      </c>
+      <c r="F58" s="32" t="s">
+        <v>139</v>
       </c>
       <c r="G58" s="28" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="59" ht="15.75" hidden="1" spans="1:7">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="59" ht="15.75" spans="1:7">
       <c r="A59" s="24">
         <v>58</v>
       </c>
       <c r="B59" s="25" t="s">
-        <v>188</v>
-      </c>
-      <c r="C59" s="36" t="s">
-        <v>189</v>
-      </c>
-      <c r="D59" s="31" t="s">
-        <v>174</v>
-      </c>
-      <c r="E59" s="31" t="s">
-        <v>190</v>
-      </c>
-      <c r="F59" s="33" t="s">
-        <v>191</v>
+        <v>141</v>
+      </c>
+      <c r="C59" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D59" s="30" t="s">
+        <v>129</v>
+      </c>
+      <c r="E59" s="30" t="s">
+        <v>142</v>
+      </c>
+      <c r="F59" s="32" t="s">
+        <v>143</v>
       </c>
       <c r="G59" s="28" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="60" ht="15.75" hidden="1" spans="1:7">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="60" ht="15.75" spans="1:7">
       <c r="A60" s="24">
         <v>59</v>
       </c>
       <c r="B60" s="25" t="s">
-        <v>193</v>
+        <v>145</v>
       </c>
       <c r="C60" s="25" t="s">
-        <v>194</v>
+        <v>8</v>
       </c>
       <c r="D60" s="26" t="s">
-        <v>174</v>
+        <v>129</v>
       </c>
       <c r="E60" s="26" t="s">
-        <v>190</v>
-      </c>
-      <c r="F60" s="33" t="s">
-        <v>195</v>
+        <v>142</v>
+      </c>
+      <c r="F60" s="32" t="s">
+        <v>146</v>
       </c>
       <c r="G60" s="28" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="61" ht="15.75" hidden="1" spans="1:7">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="61" ht="15.75" spans="1:7">
       <c r="A61" s="24">
         <v>60</v>
       </c>
       <c r="B61" s="25" t="s">
-        <v>197</v>
+        <v>148</v>
       </c>
       <c r="C61" s="25" t="s">
         <v>8</v>
       </c>
       <c r="D61" s="26" t="s">
-        <v>174</v>
-      </c>
-      <c r="E61" s="38"/>
-      <c r="F61" s="33" t="s">
-        <v>198</v>
+        <v>129</v>
+      </c>
+      <c r="E61" s="37" t="s">
+        <v>138</v>
+      </c>
+      <c r="F61" s="32" t="s">
+        <v>149</v>
       </c>
       <c r="G61" s="28" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="62" ht="15.75" hidden="1" spans="1:7">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="62" ht="15.75" spans="1:7">
       <c r="A62" s="24">
         <v>61</v>
       </c>
       <c r="B62" s="25" t="s">
-        <v>200</v>
-      </c>
-      <c r="C62" s="39" t="s">
-        <v>201</v>
-      </c>
-      <c r="D62" s="40" t="s">
-        <v>174</v>
-      </c>
-      <c r="E62" s="41"/>
-      <c r="F62" s="33" t="s">
-        <v>202</v>
-      </c>
-      <c r="G62" s="42" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="63" ht="31.5" hidden="1" spans="1:7">
+        <v>151</v>
+      </c>
+      <c r="C62" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D62" s="38" t="s">
+        <v>129</v>
+      </c>
+      <c r="E62" s="39"/>
+      <c r="F62" s="32" t="s">
+        <v>152</v>
+      </c>
+      <c r="G62" s="40" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="63" ht="31.5" spans="1:7">
       <c r="A63" s="24">
         <v>62</v>
       </c>
       <c r="B63" s="25" t="s">
-        <v>204</v>
-      </c>
-      <c r="C63" s="30" t="s">
-        <v>205</v>
-      </c>
-      <c r="D63" s="31" t="s">
-        <v>174</v>
-      </c>
-      <c r="E63" s="32"/>
-      <c r="F63" s="43" t="s">
-        <v>206</v>
+        <v>154</v>
+      </c>
+      <c r="C63" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D63" s="30" t="s">
+        <v>129</v>
+      </c>
+      <c r="E63" s="31"/>
+      <c r="F63" s="41" t="s">
+        <v>155</v>
       </c>
       <c r="G63" s="28" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="64" ht="15.75" hidden="1" spans="1:7">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="64" ht="15.75" spans="1:7">
       <c r="A64" s="24">
         <v>63</v>
       </c>
       <c r="B64" s="25" t="s">
-        <v>208</v>
+        <v>157</v>
       </c>
       <c r="C64" s="25" t="s">
-        <v>209</v>
+        <v>8</v>
       </c>
       <c r="D64" s="26" t="s">
-        <v>174</v>
-      </c>
-      <c r="E64" s="38"/>
-      <c r="F64" s="33" t="s">
-        <v>210</v>
+        <v>129</v>
+      </c>
+      <c r="E64" s="37"/>
+      <c r="F64" s="32" t="s">
+        <v>158</v>
       </c>
       <c r="G64" s="28" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="65" ht="15.75" hidden="1" spans="1:7">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="65" ht="15.75" spans="1:7">
       <c r="A65" s="24">
         <v>64</v>
       </c>
       <c r="B65" s="25" t="s">
-        <v>212</v>
-      </c>
-      <c r="C65" s="44" t="s">
-        <v>213</v>
-      </c>
-      <c r="D65" s="45" t="s">
-        <v>174</v>
-      </c>
-      <c r="E65" s="45" t="s">
-        <v>185</v>
-      </c>
-      <c r="F65" s="46" t="s">
-        <v>214</v>
-      </c>
-      <c r="G65" s="54" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="66" ht="31.5" hidden="1" spans="1:7">
+        <v>160</v>
+      </c>
+      <c r="C65" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D65" s="42" t="s">
+        <v>129</v>
+      </c>
+      <c r="E65" s="42" t="s">
+        <v>138</v>
+      </c>
+      <c r="F65" s="43" t="s">
+        <v>161</v>
+      </c>
+      <c r="G65" s="50" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="66" ht="31.5" spans="1:7">
       <c r="A66" s="24">
         <v>65</v>
       </c>
       <c r="B66" s="25" t="s">
-        <v>216</v>
-      </c>
-      <c r="C66" s="28" t="s">
-        <v>217</v>
+        <v>163</v>
+      </c>
+      <c r="C66" s="25" t="s">
+        <v>8</v>
       </c>
       <c r="D66" s="26" t="s">
-        <v>174</v>
-      </c>
-      <c r="E66" s="35"/>
-      <c r="F66" s="33" t="s">
-        <v>218</v>
+        <v>129</v>
+      </c>
+      <c r="E66" s="34"/>
+      <c r="F66" s="32" t="s">
+        <v>164</v>
       </c>
       <c r="G66" s="28" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="67" ht="15.75" hidden="1" spans="1:7">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="67" ht="15.75" spans="1:7">
       <c r="A67" s="24">
         <v>66</v>
       </c>
       <c r="B67" s="25" t="s">
-        <v>220</v>
+        <v>166</v>
       </c>
       <c r="C67" s="25" t="s">
-        <v>221</v>
+        <v>8</v>
       </c>
       <c r="D67" s="26" t="s">
-        <v>174</v>
-      </c>
-      <c r="E67" s="38"/>
-      <c r="F67" s="47" t="s">
-        <v>222</v>
+        <v>129</v>
+      </c>
+      <c r="E67" s="37"/>
+      <c r="F67" s="44" t="s">
+        <v>167</v>
       </c>
       <c r="G67" s="28" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="68" ht="15.75" hidden="1" spans="1:7">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="68" ht="15.75" spans="1:7">
       <c r="A68" s="24">
         <v>67</v>
       </c>
       <c r="B68" s="25" t="s">
-        <v>224</v>
-      </c>
-      <c r="C68" s="28" t="s">
-        <v>24</v>
+        <v>169</v>
+      </c>
+      <c r="C68" s="25" t="s">
+        <v>8</v>
       </c>
       <c r="D68" s="26" t="s">
-        <v>174</v>
-      </c>
-      <c r="E68" s="35"/>
-      <c r="F68" s="34" t="s">
-        <v>225</v>
-      </c>
-      <c r="G68" s="55" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="69" ht="15.75" hidden="1" spans="1:7">
+        <v>129</v>
+      </c>
+      <c r="E68" s="34"/>
+      <c r="F68" s="33" t="s">
+        <v>170</v>
+      </c>
+      <c r="G68" s="51" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="69" ht="15.75" spans="1:7">
       <c r="A69" s="24">
         <v>68</v>
       </c>
       <c r="B69" s="25" t="s">
-        <v>227</v>
+        <v>172</v>
       </c>
       <c r="C69" s="25" t="s">
-        <v>228</v>
+        <v>8</v>
       </c>
       <c r="D69" s="26" t="s">
+        <v>129</v>
+      </c>
+      <c r="E69" s="26" t="s">
+        <v>138</v>
+      </c>
+      <c r="F69" s="32" t="s">
+        <v>173</v>
+      </c>
+      <c r="G69" s="28" t="s">
         <v>174</v>
       </c>
-      <c r="E69" s="26" t="s">
-        <v>185</v>
-      </c>
-      <c r="F69" s="33" t="s">
-        <v>229</v>
-      </c>
-      <c r="G69" s="28" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="70" ht="15.75" hidden="1" spans="1:7">
+    </row>
+    <row r="70" ht="15.75" spans="1:7">
       <c r="A70" s="24">
         <v>69</v>
       </c>
       <c r="B70" s="25" t="s">
-        <v>231</v>
+        <v>175</v>
       </c>
       <c r="C70" s="25" t="s">
-        <v>232</v>
+        <v>8</v>
       </c>
       <c r="D70" s="26" t="s">
-        <v>174</v>
+        <v>129</v>
       </c>
       <c r="E70" s="26"/>
-      <c r="F70" s="33" t="s">
-        <v>233</v>
-      </c>
-      <c r="G70" s="54" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="71" ht="15.75" hidden="1" spans="1:7">
+      <c r="F70" s="32" t="s">
+        <v>176</v>
+      </c>
+      <c r="G70" s="50" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="71" ht="15.75" spans="1:7">
       <c r="A71" s="24">
         <v>70</v>
       </c>
       <c r="B71" s="25" t="s">
-        <v>235</v>
-      </c>
-      <c r="C71" s="28" t="s">
-        <v>236</v>
+        <v>178</v>
+      </c>
+      <c r="C71" s="25" t="s">
+        <v>8</v>
       </c>
       <c r="D71" s="26" t="s">
-        <v>174</v>
+        <v>129</v>
       </c>
       <c r="E71" s="26"/>
-      <c r="F71" s="33" t="s">
-        <v>237</v>
-      </c>
-      <c r="G71" s="54" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="72" ht="31.5" hidden="1" spans="1:7">
+      <c r="F71" s="32" t="s">
+        <v>179</v>
+      </c>
+      <c r="G71" s="50" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="72" ht="31.5" spans="1:7">
       <c r="A72" s="24">
         <v>71</v>
       </c>
       <c r="B72" s="25" t="s">
-        <v>239</v>
-      </c>
-      <c r="C72" s="30" t="s">
-        <v>240</v>
-      </c>
-      <c r="D72" s="31" t="s">
-        <v>174</v>
+        <v>181</v>
+      </c>
+      <c r="C72" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D72" s="30" t="s">
+        <v>129</v>
       </c>
       <c r="E72" s="26"/>
-      <c r="F72" s="43" t="s">
-        <v>241</v>
-      </c>
-      <c r="G72" s="54" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="73" ht="15.75" hidden="1" spans="1:7">
+      <c r="F72" s="41" t="s">
+        <v>182</v>
+      </c>
+      <c r="G72" s="50" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="73" ht="15.75" spans="1:7">
       <c r="A73" s="24">
         <v>72</v>
       </c>
       <c r="B73" s="25" t="s">
-        <v>243</v>
+        <v>184</v>
       </c>
       <c r="C73" s="25" t="s">
-        <v>244</v>
+        <v>8</v>
       </c>
       <c r="D73" s="26" t="s">
-        <v>174</v>
+        <v>129</v>
       </c>
       <c r="E73" s="26"/>
       <c r="F73" s="27" t="s">
-        <v>245</v>
-      </c>
-      <c r="G73" s="54" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="74" ht="15.75" hidden="1" spans="1:7">
+        <v>185</v>
+      </c>
+      <c r="G73" s="50" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="74" ht="15.75" spans="1:7">
       <c r="A74" s="24">
         <v>73</v>
       </c>
       <c r="B74" s="25" t="s">
-        <v>247</v>
+        <v>187</v>
       </c>
       <c r="C74" s="25" t="s">
-        <v>228</v>
+        <v>8</v>
       </c>
       <c r="D74" s="26" t="s">
-        <v>174</v>
+        <v>129</v>
       </c>
       <c r="E74" s="26" t="s">
-        <v>185</v>
+        <v>138</v>
       </c>
       <c r="F74" s="27" t="s">
-        <v>248</v>
-      </c>
-      <c r="G74" s="54" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="75" ht="15.75" hidden="1" spans="1:7">
+        <v>188</v>
+      </c>
+      <c r="G74" s="50" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="75" ht="15.75" spans="1:7">
       <c r="A75" s="24">
         <v>74</v>
       </c>
       <c r="B75" s="25" t="s">
-        <v>250</v>
+        <v>190</v>
       </c>
       <c r="C75" s="25" t="s">
-        <v>251</v>
+        <v>8</v>
       </c>
       <c r="D75" s="26" t="s">
-        <v>174</v>
+        <v>129</v>
       </c>
       <c r="E75" s="26"/>
-      <c r="F75" s="33" t="s">
-        <v>252</v>
+      <c r="F75" s="32" t="s">
+        <v>191</v>
       </c>
       <c r="G75" s="28" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="76" ht="15.75" hidden="1" spans="1:7">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="76" ht="15.75" spans="1:7">
       <c r="A76" s="24">
         <v>75</v>
       </c>
       <c r="B76" s="25" t="s">
-        <v>254</v>
+        <v>193</v>
       </c>
       <c r="C76" s="25" t="s">
-        <v>255</v>
+        <v>8</v>
       </c>
       <c r="D76" s="26" t="s">
-        <v>174</v>
+        <v>129</v>
       </c>
       <c r="E76" s="26" t="s">
-        <v>185</v>
-      </c>
-      <c r="F76" s="33" t="s">
-        <v>256</v>
+        <v>138</v>
+      </c>
+      <c r="F76" s="32" t="s">
+        <v>194</v>
       </c>
       <c r="G76" s="28" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="77" ht="15.75" hidden="1" spans="1:7">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="77" ht="15.75" spans="1:7">
       <c r="A77" s="24">
         <v>76</v>
       </c>
       <c r="B77" s="25" t="s">
-        <v>258</v>
+        <v>196</v>
       </c>
       <c r="C77" s="25" t="s">
-        <v>259</v>
+        <v>8</v>
       </c>
       <c r="D77" s="26" t="s">
-        <v>174</v>
+        <v>129</v>
       </c>
       <c r="E77" s="26"/>
-      <c r="F77" s="33" t="s">
-        <v>260</v>
-      </c>
-      <c r="G77" s="54" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="78" ht="31.5" hidden="1" spans="1:7">
+      <c r="F77" s="32" t="s">
+        <v>197</v>
+      </c>
+      <c r="G77" s="50" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="78" ht="31.5" spans="1:7">
       <c r="A78" s="24">
         <v>77</v>
       </c>
       <c r="B78" s="25" t="s">
-        <v>262</v>
+        <v>199</v>
       </c>
       <c r="C78" s="25" t="s">
-        <v>263</v>
+        <v>8</v>
       </c>
       <c r="D78" s="26" t="s">
-        <v>174</v>
+        <v>129</v>
       </c>
       <c r="E78" s="26" t="s">
-        <v>175</v>
-      </c>
-      <c r="F78" s="33" t="s">
-        <v>264</v>
+        <v>130</v>
+      </c>
+      <c r="F78" s="32" t="s">
+        <v>200</v>
       </c>
       <c r="G78" s="28" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="79" ht="15.75" hidden="1" spans="1:7">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="79" ht="15.75" spans="1:7">
       <c r="A79" s="24">
         <v>78</v>
       </c>
       <c r="B79" s="25" t="s">
-        <v>266</v>
+        <v>202</v>
       </c>
       <c r="C79" s="25" t="s">
-        <v>267</v>
+        <v>8</v>
       </c>
       <c r="D79" s="26" t="s">
-        <v>174</v>
+        <v>129</v>
       </c>
       <c r="E79" s="26"/>
-      <c r="F79" s="33" t="s">
-        <v>268</v>
+      <c r="F79" s="32" t="s">
+        <v>203</v>
       </c>
       <c r="G79" s="28"/>
     </row>
-    <row r="80" ht="15.75" hidden="1" spans="1:7">
+    <row r="80" ht="15.75" spans="1:7">
       <c r="A80" s="24">
         <v>79</v>
       </c>
       <c r="B80" s="25" t="s">
-        <v>269</v>
+        <v>204</v>
       </c>
       <c r="C80" s="25" t="s">
-        <v>270</v>
+        <v>8</v>
       </c>
       <c r="D80" s="26" t="s">
-        <v>174</v>
+        <v>129</v>
       </c>
       <c r="E80" s="26" t="s">
-        <v>175</v>
-      </c>
-      <c r="F80" s="33" t="s">
-        <v>271</v>
-      </c>
-      <c r="G80" s="54" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="81" ht="15.75" hidden="1" spans="1:7">
+        <v>130</v>
+      </c>
+      <c r="F80" s="32" t="s">
+        <v>205</v>
+      </c>
+      <c r="G80" s="50" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="81" ht="15.75" spans="1:7">
       <c r="A81" s="24">
         <v>80</v>
       </c>
       <c r="B81" s="25" t="s">
-        <v>273</v>
+        <v>207</v>
       </c>
       <c r="C81" s="25" t="s">
-        <v>217</v>
+        <v>8</v>
       </c>
       <c r="D81" s="26" t="s">
-        <v>174</v>
+        <v>129</v>
       </c>
       <c r="E81" s="26" t="s">
-        <v>185</v>
-      </c>
-      <c r="F81" s="33" t="s">
-        <v>274</v>
+        <v>138</v>
+      </c>
+      <c r="F81" s="32" t="s">
+        <v>208</v>
       </c>
       <c r="G81" s="28" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="82" ht="15.75" hidden="1" spans="1:7">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="82" ht="15.75" spans="1:7">
       <c r="A82" s="24">
         <v>81</v>
       </c>
       <c r="B82" s="25" t="s">
-        <v>276</v>
-      </c>
-      <c r="C82" s="28" t="s">
-        <v>277</v>
+        <v>210</v>
+      </c>
+      <c r="C82" s="25" t="s">
+        <v>8</v>
       </c>
       <c r="D82" s="26" t="s">
-        <v>174</v>
+        <v>129</v>
       </c>
       <c r="E82" s="26" t="s">
-        <v>190</v>
-      </c>
-      <c r="F82" s="33" t="s">
-        <v>278</v>
+        <v>142</v>
+      </c>
+      <c r="F82" s="32" t="s">
+        <v>211</v>
       </c>
       <c r="G82" s="28"/>
     </row>
-    <row r="83" ht="15.75" hidden="1" spans="1:7">
+    <row r="83" ht="15.75" spans="1:7">
       <c r="A83" s="24">
         <v>82</v>
       </c>
       <c r="B83" s="25" t="s">
-        <v>279</v>
-      </c>
-      <c r="C83" s="28" t="s">
-        <v>24</v>
+        <v>212</v>
+      </c>
+      <c r="C83" s="25" t="s">
+        <v>8</v>
       </c>
       <c r="D83" s="26" t="s">
-        <v>174</v>
+        <v>129</v>
       </c>
       <c r="E83" s="26"/>
-      <c r="F83" s="34" t="s">
-        <v>280</v>
+      <c r="F83" s="33" t="s">
+        <v>213</v>
       </c>
       <c r="G83" s="28" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="84" ht="15.75" hidden="1" spans="1:7">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="84" ht="15.75" spans="1:7">
       <c r="A84" s="24">
         <v>83</v>
       </c>
       <c r="B84" s="25" t="s">
-        <v>282</v>
+        <v>215</v>
       </c>
       <c r="C84" s="25" t="s">
-        <v>283</v>
+        <v>8</v>
       </c>
       <c r="D84" s="26" t="s">
-        <v>174</v>
+        <v>129</v>
       </c>
       <c r="E84" s="26" t="s">
-        <v>175</v>
-      </c>
-      <c r="F84" s="33" t="s">
-        <v>284</v>
+        <v>130</v>
+      </c>
+      <c r="F84" s="32" t="s">
+        <v>216</v>
       </c>
       <c r="G84" s="28" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="85" ht="15.75" hidden="1" spans="1:7">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="85" ht="15.75" spans="1:7">
       <c r="A85" s="24">
         <v>84</v>
       </c>
       <c r="B85" s="25" t="s">
-        <v>286</v>
-      </c>
-      <c r="C85" s="28" t="s">
+        <v>218</v>
+      </c>
+      <c r="C85" s="25" t="s">
         <v>8</v>
       </c>
       <c r="D85" s="26" t="s">
-        <v>174</v>
-      </c>
-      <c r="E85" s="35"/>
-      <c r="F85" s="33" t="s">
-        <v>287</v>
+        <v>129</v>
+      </c>
+      <c r="E85" s="34"/>
+      <c r="F85" s="32" t="s">
+        <v>219</v>
       </c>
       <c r="G85" s="28"/>
     </row>
-    <row r="86" ht="15.75" hidden="1" spans="1:7">
+    <row r="86" ht="15.75" spans="1:7">
       <c r="A86" s="24">
         <v>85</v>
       </c>
       <c r="B86" s="25" t="s">
-        <v>288</v>
+        <v>220</v>
       </c>
       <c r="C86" s="25" t="s">
-        <v>289</v>
+        <v>8</v>
       </c>
       <c r="D86" s="26" t="s">
-        <v>174</v>
-      </c>
-      <c r="E86" s="35" t="s">
-        <v>190</v>
-      </c>
-      <c r="F86" s="48" t="s">
-        <v>290</v>
+        <v>129</v>
+      </c>
+      <c r="E86" s="34" t="s">
+        <v>142</v>
+      </c>
+      <c r="F86" s="45" t="s">
+        <v>221</v>
       </c>
       <c r="G86" s="28" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="87" ht="15.75" hidden="1" spans="1:7">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="87" ht="15.75" spans="1:7">
       <c r="A87" s="24">
         <v>86</v>
       </c>
       <c r="B87" s="25" t="s">
-        <v>292</v>
-      </c>
-      <c r="C87" s="30" t="s">
-        <v>293</v>
-      </c>
-      <c r="D87" s="31" t="s">
-        <v>174</v>
-      </c>
-      <c r="E87" s="35"/>
-      <c r="F87" s="33" t="s">
-        <v>294</v>
+        <v>223</v>
+      </c>
+      <c r="C87" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D87" s="30" t="s">
+        <v>129</v>
+      </c>
+      <c r="E87" s="34"/>
+      <c r="F87" s="32" t="s">
+        <v>224</v>
       </c>
       <c r="G87" s="28" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="88" ht="15.75" hidden="1" spans="1:7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="88" ht="15.75" spans="1:7">
       <c r="A88" s="24">
         <v>87</v>
       </c>
       <c r="B88" s="25" t="s">
-        <v>295</v>
+        <v>225</v>
       </c>
       <c r="C88" s="25" t="s">
-        <v>296</v>
+        <v>8</v>
       </c>
       <c r="D88" s="26" t="s">
-        <v>174</v>
-      </c>
-      <c r="E88" s="35"/>
-      <c r="F88" s="33" t="s">
-        <v>297</v>
+        <v>129</v>
+      </c>
+      <c r="E88" s="34"/>
+      <c r="F88" s="32" t="s">
+        <v>226</v>
       </c>
       <c r="G88" s="28" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="89" ht="15.75" hidden="1" spans="1:7">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="89" ht="15.75" spans="1:7">
       <c r="A89" s="24">
         <v>88</v>
       </c>
       <c r="B89" s="25" t="s">
-        <v>299</v>
+        <v>228</v>
       </c>
       <c r="C89" s="25" t="s">
-        <v>300</v>
+        <v>8</v>
       </c>
       <c r="D89" s="26" t="s">
-        <v>174</v>
-      </c>
-      <c r="E89" s="38"/>
-      <c r="F89" s="33" t="s">
-        <v>301</v>
+        <v>129</v>
+      </c>
+      <c r="E89" s="37"/>
+      <c r="F89" s="32" t="s">
+        <v>229</v>
       </c>
       <c r="G89" s="28" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="90" ht="15.75" hidden="1" spans="1:7">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="90" ht="15.75" spans="1:7">
       <c r="A90" s="24">
         <v>89</v>
       </c>
       <c r="B90" s="25" t="s">
-        <v>303</v>
+        <v>231</v>
       </c>
       <c r="C90" s="25" t="s">
-        <v>304</v>
+        <v>8</v>
       </c>
       <c r="D90" s="26" t="s">
-        <v>174</v>
+        <v>129</v>
       </c>
       <c r="E90" s="26"/>
-      <c r="F90" s="33" t="s">
-        <v>305</v>
-      </c>
-      <c r="G90" s="54" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="91" ht="15.75" hidden="1" spans="1:7">
+      <c r="F90" s="32" t="s">
+        <v>232</v>
+      </c>
+      <c r="G90" s="50" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="91" ht="15.75" spans="1:7">
       <c r="A91" s="24">
         <v>90</v>
       </c>
       <c r="B91" s="25" t="s">
-        <v>307</v>
+        <v>234</v>
       </c>
       <c r="C91" s="25" t="s">
-        <v>308</v>
+        <v>8</v>
       </c>
       <c r="D91" s="26" t="s">
-        <v>174</v>
+        <v>129</v>
       </c>
       <c r="E91" s="26" t="s">
-        <v>190</v>
-      </c>
-      <c r="F91" s="33" t="s">
-        <v>309</v>
+        <v>142</v>
+      </c>
+      <c r="F91" s="32" t="s">
+        <v>235</v>
       </c>
       <c r="G91" s="28" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="92" ht="15.75" hidden="1" spans="1:7">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="92" ht="15.75" spans="1:7">
       <c r="A92" s="24">
         <v>91</v>
       </c>
       <c r="B92" s="25" t="s">
-        <v>311</v>
+        <v>237</v>
       </c>
       <c r="C92" s="25" t="s">
-        <v>312</v>
+        <v>8</v>
       </c>
       <c r="D92" s="26" t="s">
-        <v>174</v>
+        <v>129</v>
       </c>
       <c r="E92" s="26"/>
-      <c r="F92" s="33" t="s">
-        <v>313</v>
-      </c>
-      <c r="G92" s="54" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="93" ht="15.75" hidden="1" spans="1:7">
+      <c r="F92" s="32" t="s">
+        <v>238</v>
+      </c>
+      <c r="G92" s="50" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="93" ht="15.75" spans="1:7">
       <c r="A93" s="24">
         <v>92</v>
       </c>
       <c r="B93" s="25" t="s">
-        <v>315</v>
+        <v>240</v>
       </c>
       <c r="C93" s="25" t="s">
-        <v>316</v>
+        <v>8</v>
       </c>
       <c r="D93" s="26" t="s">
-        <v>174</v>
+        <v>129</v>
       </c>
       <c r="E93" s="26" t="s">
-        <v>317</v>
-      </c>
-      <c r="F93" s="33" t="s">
-        <v>318</v>
-      </c>
-      <c r="G93" s="54" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="94" ht="15.75" hidden="1" spans="1:7">
+        <v>241</v>
+      </c>
+      <c r="F93" s="32" t="s">
+        <v>242</v>
+      </c>
+      <c r="G93" s="50" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="94" ht="15.75" spans="1:7">
       <c r="A94" s="24">
         <v>93</v>
       </c>
       <c r="B94" s="25" t="s">
-        <v>320</v>
+        <v>244</v>
       </c>
       <c r="C94" s="25" t="s">
-        <v>228</v>
+        <v>8</v>
       </c>
       <c r="D94" s="26" t="s">
-        <v>174</v>
+        <v>129</v>
       </c>
       <c r="E94" s="26"/>
-      <c r="F94" s="33" t="s">
-        <v>321</v>
+      <c r="F94" s="32" t="s">
+        <v>245</v>
       </c>
       <c r="G94" s="28" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="95" ht="15.75" hidden="1" spans="1:7">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="95" ht="15.75" spans="1:7">
       <c r="A95" s="24">
         <v>94</v>
       </c>
       <c r="B95" s="25" t="s">
-        <v>323</v>
+        <v>247</v>
       </c>
       <c r="C95" s="25" t="s">
-        <v>324</v>
+        <v>8</v>
       </c>
       <c r="D95" s="26" t="s">
-        <v>174</v>
+        <v>129</v>
       </c>
       <c r="E95" s="26" t="s">
-        <v>185</v>
-      </c>
-      <c r="F95" s="48" t="s">
-        <v>325</v>
-      </c>
-      <c r="G95" s="54" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="96" ht="15.75" hidden="1" spans="1:7">
+        <v>138</v>
+      </c>
+      <c r="F95" s="45" t="s">
+        <v>248</v>
+      </c>
+      <c r="G95" s="50" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="96" ht="15.75" spans="1:7">
       <c r="A96" s="24">
         <v>95</v>
       </c>
       <c r="B96" s="25" t="s">
-        <v>327</v>
+        <v>250</v>
       </c>
       <c r="C96" s="25" t="s">
-        <v>328</v>
+        <v>8</v>
       </c>
       <c r="D96" s="26" t="s">
-        <v>174</v>
+        <v>129</v>
       </c>
       <c r="E96" s="26"/>
-      <c r="F96" s="33" t="s">
-        <v>329</v>
+      <c r="F96" s="32" t="s">
+        <v>251</v>
       </c>
       <c r="G96" s="28" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="97" ht="31.5" hidden="1" spans="1:7">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="97" ht="31.5" spans="1:7">
       <c r="A97" s="24">
         <v>96</v>
       </c>
       <c r="B97" s="25" t="s">
-        <v>331</v>
-      </c>
-      <c r="C97" s="30" t="s">
-        <v>332</v>
-      </c>
-      <c r="D97" s="31" t="s">
-        <v>174</v>
+        <v>253</v>
+      </c>
+      <c r="C97" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D97" s="30" t="s">
+        <v>129</v>
       </c>
       <c r="E97" s="26" t="s">
-        <v>333</v>
-      </c>
-      <c r="F97" s="33" t="s">
-        <v>334</v>
+        <v>254</v>
+      </c>
+      <c r="F97" s="32" t="s">
+        <v>255</v>
       </c>
       <c r="G97" s="28" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="98" ht="15.75" hidden="1" spans="1:7">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="98" ht="15.75" spans="1:7">
       <c r="A98" s="24">
         <v>97</v>
       </c>
       <c r="B98" s="25" t="s">
-        <v>336</v>
+        <v>257</v>
       </c>
       <c r="C98" s="25" t="s">
-        <v>337</v>
+        <v>8</v>
       </c>
       <c r="D98" s="26" t="s">
-        <v>174</v>
+        <v>129</v>
       </c>
       <c r="E98" s="26" t="s">
-        <v>190</v>
-      </c>
-      <c r="F98" s="33" t="s">
-        <v>338</v>
+        <v>142</v>
+      </c>
+      <c r="F98" s="32" t="s">
+        <v>258</v>
       </c>
       <c r="G98" s="28" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="99" ht="15.75" hidden="1" spans="1:7">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="99" ht="15.75" spans="1:7">
       <c r="A99" s="24">
         <v>98</v>
       </c>
       <c r="B99" s="25" t="s">
-        <v>340</v>
+        <v>260</v>
       </c>
       <c r="C99" s="25" t="s">
-        <v>341</v>
+        <v>8</v>
       </c>
       <c r="D99" s="26" t="s">
-        <v>174</v>
+        <v>129</v>
       </c>
       <c r="E99" s="26" t="s">
-        <v>185</v>
-      </c>
-      <c r="F99" s="33" t="s">
-        <v>342</v>
+        <v>138</v>
+      </c>
+      <c r="F99" s="32" t="s">
+        <v>261</v>
       </c>
       <c r="G99" s="28" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="100" ht="15.75" hidden="1" spans="1:7">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="100" ht="15.75" spans="1:7">
       <c r="A100" s="24">
         <v>99</v>
       </c>
       <c r="B100" s="25" t="s">
-        <v>344</v>
-      </c>
-      <c r="C100" s="25"/>
+        <v>263</v>
+      </c>
+      <c r="C100" s="25" t="s">
+        <v>8</v>
+      </c>
       <c r="D100" s="26" t="s">
-        <v>174</v>
+        <v>129</v>
       </c>
       <c r="E100" s="26"/>
-      <c r="F100" s="33"/>
+      <c r="F100" s="32"/>
       <c r="G100" s="28"/>
     </row>
-    <row r="101" ht="15.75" hidden="1" spans="1:7">
+    <row r="101" ht="15.75" spans="1:7">
       <c r="A101" s="24">
         <v>100</v>
       </c>
       <c r="B101" s="25" t="s">
-        <v>345</v>
+        <v>264</v>
       </c>
       <c r="C101" s="25" t="s">
-        <v>346</v>
+        <v>8</v>
       </c>
       <c r="D101" s="26" t="s">
-        <v>174</v>
-      </c>
-      <c r="E101" s="38"/>
+        <v>129</v>
+      </c>
+      <c r="E101" s="37"/>
       <c r="F101" s="27" t="s">
-        <v>347</v>
+        <v>265</v>
       </c>
       <c r="G101" s="28" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="102" ht="15.75" hidden="1" spans="1:7">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="102" ht="15.75" spans="1:7">
       <c r="A102" s="24">
         <v>101</v>
       </c>
       <c r="B102" s="25" t="s">
-        <v>349</v>
-      </c>
-      <c r="C102" s="28" t="s">
-        <v>350</v>
+        <v>267</v>
+      </c>
+      <c r="C102" s="25" t="s">
+        <v>8</v>
       </c>
       <c r="D102" s="26" t="s">
-        <v>174</v>
-      </c>
-      <c r="E102" s="35"/>
+        <v>129</v>
+      </c>
+      <c r="E102" s="34"/>
       <c r="F102" s="27" t="s">
-        <v>351</v>
+        <v>268</v>
       </c>
       <c r="G102" s="28"/>
     </row>
-    <row r="103" ht="15.75" hidden="1" spans="1:7">
+    <row r="103" ht="15.75" spans="1:7">
       <c r="A103" s="24">
         <v>102</v>
       </c>
       <c r="B103" s="25" t="s">
-        <v>352</v>
+        <v>269</v>
       </c>
       <c r="C103" s="25" t="s">
-        <v>353</v>
+        <v>8</v>
       </c>
       <c r="D103" s="26" t="s">
-        <v>174</v>
-      </c>
-      <c r="E103" s="38"/>
-      <c r="F103" s="33" t="s">
-        <v>354</v>
+        <v>129</v>
+      </c>
+      <c r="E103" s="37"/>
+      <c r="F103" s="32" t="s">
+        <v>270</v>
       </c>
       <c r="G103" s="28" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="104" ht="15.75" hidden="1" spans="1:7">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="104" ht="15.75" spans="1:7">
       <c r="A104" s="24">
         <v>103</v>
       </c>
       <c r="B104" s="25" t="s">
-        <v>356</v>
+        <v>272</v>
       </c>
       <c r="C104" s="25" t="s">
-        <v>357</v>
+        <v>8</v>
       </c>
       <c r="D104" s="26" t="s">
-        <v>174</v>
+        <v>129</v>
       </c>
       <c r="E104" s="26" t="s">
-        <v>185</v>
-      </c>
-      <c r="F104" s="33" t="s">
-        <v>358</v>
+        <v>138</v>
+      </c>
+      <c r="F104" s="32" t="s">
+        <v>273</v>
       </c>
       <c r="G104" s="28" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="105" ht="15.75" hidden="1" spans="1:7">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="105" ht="15.75" spans="1:7">
       <c r="A105" s="24">
         <v>104</v>
       </c>
       <c r="B105" s="25" t="s">
-        <v>360</v>
+        <v>275</v>
       </c>
       <c r="C105" s="25" t="s">
-        <v>361</v>
+        <v>8</v>
       </c>
       <c r="D105" s="26" t="s">
-        <v>174</v>
-      </c>
-      <c r="E105" s="38"/>
-      <c r="F105" s="33" t="s">
-        <v>362</v>
+        <v>129</v>
+      </c>
+      <c r="E105" s="37"/>
+      <c r="F105" s="32" t="s">
+        <v>276</v>
       </c>
       <c r="G105" s="28" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="106" ht="15.75" hidden="1" spans="1:7">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="106" ht="15.75" spans="1:7">
       <c r="A106" s="24">
         <v>105</v>
       </c>
       <c r="B106" s="25" t="s">
-        <v>364</v>
+        <v>278</v>
       </c>
       <c r="C106" s="25" t="s">
-        <v>365</v>
+        <v>8</v>
       </c>
       <c r="D106" s="26" t="s">
-        <v>174</v>
+        <v>129</v>
       </c>
       <c r="E106" s="26" t="s">
-        <v>190</v>
-      </c>
-      <c r="F106" s="33" t="s">
-        <v>366</v>
-      </c>
-      <c r="G106" s="55" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="107" ht="15.75" hidden="1" spans="1:7">
+        <v>142</v>
+      </c>
+      <c r="F106" s="32" t="s">
+        <v>279</v>
+      </c>
+      <c r="G106" s="51" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="107" ht="15.75" spans="1:7">
       <c r="A107" s="24">
         <v>106</v>
       </c>
       <c r="B107" s="25" t="s">
-        <v>368</v>
+        <v>281</v>
       </c>
       <c r="C107" s="25" t="s">
-        <v>369</v>
+        <v>8</v>
       </c>
       <c r="D107" s="26" t="s">
-        <v>174</v>
+        <v>129</v>
       </c>
       <c r="E107" s="26" t="s">
-        <v>370</v>
-      </c>
-      <c r="F107" s="33" t="s">
-        <v>371</v>
+        <v>282</v>
+      </c>
+      <c r="F107" s="32" t="s">
+        <v>283</v>
       </c>
       <c r="G107" s="28"/>
     </row>
-    <row r="108" ht="15.75" hidden="1" spans="1:7">
+    <row r="108" ht="15.75" spans="1:7">
       <c r="A108" s="24"/>
       <c r="B108" s="25" t="s">
-        <v>372</v>
-      </c>
-      <c r="C108" s="49" t="s">
-        <v>373</v>
-      </c>
-      <c r="D108" s="50" t="s">
-        <v>174</v>
-      </c>
-      <c r="E108" s="51"/>
-      <c r="F108" s="52" t="s">
-        <v>374</v>
+        <v>284</v>
+      </c>
+      <c r="C108" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D108" s="46" t="s">
+        <v>129</v>
+      </c>
+      <c r="E108" s="47"/>
+      <c r="F108" s="48" t="s">
+        <v>285</v>
       </c>
       <c r="G108" s="29"/>
     </row>
-    <row r="109" ht="15.75" hidden="1" spans="1:7">
+    <row r="109" ht="15.75" spans="1:7">
       <c r="A109" s="24"/>
       <c r="B109" s="25" t="s">
-        <v>375</v>
-      </c>
-      <c r="C109" s="49" t="s">
-        <v>376</v>
-      </c>
-      <c r="D109" s="50" t="s">
-        <v>174</v>
-      </c>
-      <c r="E109" s="51"/>
-      <c r="F109" s="52" t="s">
-        <v>377</v>
+        <v>286</v>
+      </c>
+      <c r="C109" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D109" s="46" t="s">
+        <v>129</v>
+      </c>
+      <c r="E109" s="47"/>
+      <c r="F109" s="48" t="s">
+        <v>287</v>
       </c>
       <c r="G109" s="29"/>
     </row>
-    <row r="110" ht="31.5" hidden="1" spans="1:7">
+    <row r="110" ht="31.5" spans="1:7">
       <c r="A110" s="24"/>
       <c r="B110" s="25" t="s">
-        <v>378</v>
-      </c>
-      <c r="C110" s="49" t="s">
-        <v>379</v>
-      </c>
-      <c r="D110" s="50" t="s">
-        <v>174</v>
-      </c>
-      <c r="E110" s="51"/>
-      <c r="F110" s="52" t="s">
-        <v>380</v>
+        <v>288</v>
+      </c>
+      <c r="C110" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D110" s="46" t="s">
+        <v>129</v>
+      </c>
+      <c r="E110" s="47"/>
+      <c r="F110" s="48" t="s">
+        <v>289</v>
       </c>
       <c r="G110" s="29"/>
     </row>
-    <row r="111" ht="15.75" hidden="1" spans="1:7">
+    <row r="111" ht="15.75" spans="1:7">
       <c r="A111" s="24"/>
       <c r="B111" s="25" t="s">
-        <v>381</v>
-      </c>
-      <c r="C111" s="49" t="s">
-        <v>168</v>
-      </c>
-      <c r="D111" s="50" t="s">
-        <v>174</v>
-      </c>
-      <c r="E111" s="51"/>
-      <c r="F111" s="52" t="s">
-        <v>382</v>
+        <v>290</v>
+      </c>
+      <c r="C111" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D111" s="46" t="s">
+        <v>129</v>
+      </c>
+      <c r="E111" s="47"/>
+      <c r="F111" s="48" t="s">
+        <v>291</v>
       </c>
       <c r="G111" s="29"/>
     </row>
-    <row r="112" ht="31.5" hidden="1" spans="1:7">
+    <row r="112" ht="31.5" spans="1:7">
       <c r="A112" s="24"/>
       <c r="B112" s="25" t="s">
-        <v>383</v>
-      </c>
-      <c r="C112" s="49" t="s">
-        <v>384</v>
-      </c>
-      <c r="D112" s="50" t="s">
-        <v>174</v>
-      </c>
-      <c r="E112" s="51"/>
-      <c r="F112" s="52" t="s">
-        <v>385</v>
+        <v>292</v>
+      </c>
+      <c r="C112" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D112" s="46" t="s">
+        <v>129</v>
+      </c>
+      <c r="E112" s="47"/>
+      <c r="F112" s="48" t="s">
+        <v>293</v>
       </c>
       <c r="G112" s="29"/>
     </row>
-    <row r="113" ht="15.75" hidden="1" spans="1:7">
+    <row r="113" ht="15.75" spans="1:7">
       <c r="A113" s="24"/>
       <c r="B113" s="25" t="s">
-        <v>386</v>
-      </c>
-      <c r="C113" s="49" t="s">
-        <v>387</v>
-      </c>
-      <c r="D113" s="50" t="s">
-        <v>174</v>
-      </c>
-      <c r="E113" s="51"/>
-      <c r="F113" s="52" t="s">
-        <v>388</v>
+        <v>294</v>
+      </c>
+      <c r="C113" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D113" s="46" t="s">
+        <v>129</v>
+      </c>
+      <c r="E113" s="47"/>
+      <c r="F113" s="48" t="s">
+        <v>295</v>
       </c>
       <c r="G113" s="29"/>
     </row>
-    <row r="114" ht="15.75" hidden="1" spans="1:7">
+    <row r="114" ht="15.75" spans="1:7">
       <c r="A114" s="24"/>
       <c r="B114" s="25" t="s">
-        <v>389</v>
-      </c>
-      <c r="C114" s="49" t="s">
-        <v>390</v>
-      </c>
-      <c r="D114" s="50" t="s">
-        <v>174</v>
-      </c>
-      <c r="E114" s="51"/>
-      <c r="F114" s="52" t="s">
-        <v>366</v>
+        <v>296</v>
+      </c>
+      <c r="C114" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D114" s="46" t="s">
+        <v>129</v>
+      </c>
+      <c r="E114" s="47"/>
+      <c r="F114" s="48" t="s">
+        <v>279</v>
       </c>
       <c r="G114" s="29"/>
     </row>
-    <row r="115" s="15" customFormat="1" ht="15.75" hidden="1" spans="1:7">
+    <row r="115" s="15" customFormat="1" ht="15.75" spans="1:7">
       <c r="A115" s="24"/>
       <c r="B115" s="25" t="s">
-        <v>391</v>
-      </c>
-      <c r="C115" s="49" t="s">
-        <v>392</v>
-      </c>
-      <c r="D115" s="50" t="s">
-        <v>174</v>
-      </c>
-      <c r="E115" s="51"/>
-      <c r="F115" s="52" t="s">
-        <v>393</v>
+        <v>297</v>
+      </c>
+      <c r="C115" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D115" s="46" t="s">
+        <v>129</v>
+      </c>
+      <c r="E115" s="47"/>
+      <c r="F115" s="48" t="s">
+        <v>298</v>
       </c>
       <c r="G115" s="29"/>
     </row>
-    <row r="116" ht="15.75" hidden="1" spans="1:7">
+    <row r="116" ht="15.75" spans="1:7">
       <c r="A116" s="24"/>
       <c r="B116" s="25" t="s">
-        <v>394</v>
-      </c>
-      <c r="C116" s="49" t="s">
-        <v>395</v>
-      </c>
-      <c r="D116" s="50" t="s">
-        <v>174</v>
-      </c>
-      <c r="E116" s="50" t="s">
-        <v>190</v>
-      </c>
-      <c r="F116" s="52" t="s">
-        <v>396</v>
+        <v>299</v>
+      </c>
+      <c r="C116" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D116" s="46" t="s">
+        <v>129</v>
+      </c>
+      <c r="E116" s="46" t="s">
+        <v>142</v>
+      </c>
+      <c r="F116" s="48" t="s">
+        <v>300</v>
       </c>
       <c r="G116" s="29"/>
     </row>
-    <row r="117" ht="15.75" hidden="1" spans="1:7">
+    <row r="117" ht="15.75" spans="1:7">
       <c r="A117" s="24"/>
       <c r="B117" s="25" t="s">
-        <v>397</v>
-      </c>
-      <c r="C117" s="49" t="s">
-        <v>398</v>
-      </c>
-      <c r="D117" s="50" t="s">
-        <v>174</v>
-      </c>
-      <c r="E117" s="51"/>
-      <c r="F117" s="52" t="s">
-        <v>399</v>
+        <v>301</v>
+      </c>
+      <c r="C117" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D117" s="46" t="s">
+        <v>129</v>
+      </c>
+      <c r="E117" s="47"/>
+      <c r="F117" s="48" t="s">
+        <v>302</v>
       </c>
       <c r="G117" s="29"/>
     </row>
-    <row r="118" ht="15.75" hidden="1" spans="1:7">
+    <row r="118" ht="15.75" spans="1:7">
       <c r="A118" s="24"/>
       <c r="B118" s="25" t="s">
-        <v>400</v>
-      </c>
-      <c r="C118" s="49" t="s">
-        <v>401</v>
-      </c>
-      <c r="D118" s="50" t="s">
-        <v>174</v>
-      </c>
-      <c r="E118" s="51"/>
-      <c r="F118" s="52" t="s">
-        <v>402</v>
+        <v>303</v>
+      </c>
+      <c r="C118" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D118" s="46" t="s">
+        <v>129</v>
+      </c>
+      <c r="E118" s="47"/>
+      <c r="F118" s="48" t="s">
+        <v>304</v>
       </c>
       <c r="G118" s="29"/>
     </row>
-    <row r="119" ht="15.75" hidden="1" spans="1:7">
+    <row r="119" ht="15.75" spans="1:7">
       <c r="A119" s="24"/>
       <c r="B119" s="25" t="s">
-        <v>403</v>
-      </c>
-      <c r="C119" s="49" t="s">
-        <v>404</v>
-      </c>
-      <c r="D119" s="50" t="s">
-        <v>174</v>
-      </c>
-      <c r="E119" s="51"/>
-      <c r="F119" s="52" t="s">
-        <v>405</v>
+        <v>305</v>
+      </c>
+      <c r="C119" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D119" s="46" t="s">
+        <v>129</v>
+      </c>
+      <c r="E119" s="47"/>
+      <c r="F119" s="48" t="s">
+        <v>306</v>
       </c>
       <c r="G119" s="29"/>
     </row>
-    <row r="120" ht="15.75" hidden="1" spans="1:7">
+    <row r="120" ht="15.75" spans="1:7">
       <c r="A120" s="24"/>
       <c r="B120" s="25" t="s">
-        <v>406</v>
-      </c>
-      <c r="C120" s="49" t="s">
-        <v>407</v>
-      </c>
-      <c r="D120" s="50" t="s">
-        <v>174</v>
-      </c>
-      <c r="E120" s="51"/>
-      <c r="F120" s="52" t="s">
-        <v>408</v>
+        <v>307</v>
+      </c>
+      <c r="C120" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D120" s="46" t="s">
+        <v>129</v>
+      </c>
+      <c r="E120" s="47"/>
+      <c r="F120" s="48" t="s">
+        <v>308</v>
       </c>
       <c r="G120" s="29"/>
     </row>
-    <row r="121" ht="15.75" hidden="1" spans="1:7">
+    <row r="121" ht="15.75" spans="1:7">
       <c r="A121" s="24"/>
       <c r="B121" s="25" t="s">
-        <v>409</v>
-      </c>
-      <c r="C121" s="49" t="s">
-        <v>410</v>
-      </c>
-      <c r="D121" s="50" t="s">
-        <v>174</v>
-      </c>
-      <c r="E121" s="51"/>
-      <c r="F121" s="52" t="s">
-        <v>411</v>
+        <v>309</v>
+      </c>
+      <c r="C121" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D121" s="46" t="s">
+        <v>129</v>
+      </c>
+      <c r="E121" s="47"/>
+      <c r="F121" s="48" t="s">
+        <v>310</v>
       </c>
       <c r="G121" s="29"/>
     </row>
-    <row r="122" ht="15.75" hidden="1" spans="1:7">
+    <row r="122" ht="15.75" spans="1:7">
       <c r="A122" s="24"/>
       <c r="B122" s="25" t="s">
-        <v>412</v>
-      </c>
-      <c r="C122" s="49" t="s">
-        <v>413</v>
-      </c>
-      <c r="D122" s="50" t="s">
-        <v>174</v>
-      </c>
-      <c r="E122" s="51"/>
-      <c r="F122" s="52" t="s">
-        <v>414</v>
+        <v>311</v>
+      </c>
+      <c r="C122" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D122" s="46" t="s">
+        <v>129</v>
+      </c>
+      <c r="E122" s="47"/>
+      <c r="F122" s="48" t="s">
+        <v>312</v>
       </c>
       <c r="G122" s="29"/>
     </row>
-    <row r="123" ht="15.75" hidden="1" spans="1:7">
+    <row r="123" ht="15.75" spans="1:7">
       <c r="A123" s="24"/>
       <c r="B123" s="25" t="s">
-        <v>415</v>
-      </c>
-      <c r="C123" s="49" t="s">
-        <v>76</v>
-      </c>
-      <c r="D123" s="50" t="s">
-        <v>174</v>
-      </c>
-      <c r="E123" s="51"/>
-      <c r="F123" s="52" t="s">
-        <v>416</v>
-      </c>
-      <c r="G123" s="53" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="124" ht="15.75" hidden="1" spans="1:7">
+        <v>313</v>
+      </c>
+      <c r="C123" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D123" s="46" t="s">
+        <v>129</v>
+      </c>
+      <c r="E123" s="47"/>
+      <c r="F123" s="48" t="s">
+        <v>314</v>
+      </c>
+      <c r="G123" s="49" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="124" ht="15.75" spans="1:7">
       <c r="A124" s="24"/>
       <c r="B124" s="25" t="s">
-        <v>417</v>
-      </c>
-      <c r="C124" s="49" t="s">
-        <v>418</v>
-      </c>
-      <c r="D124" s="50" t="s">
-        <v>174</v>
-      </c>
-      <c r="E124" s="51"/>
-      <c r="F124" s="52" t="s">
-        <v>419</v>
+        <v>315</v>
+      </c>
+      <c r="C124" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D124" s="46" t="s">
+        <v>129</v>
+      </c>
+      <c r="E124" s="47"/>
+      <c r="F124" s="48" t="s">
+        <v>316</v>
       </c>
       <c r="G124" s="29"/>
     </row>
-    <row r="125" ht="15.75" hidden="1" spans="1:7">
+    <row r="125" ht="15.75" spans="1:7">
       <c r="A125" s="24"/>
       <c r="B125" s="25" t="s">
-        <v>420</v>
-      </c>
-      <c r="C125" s="49" t="s">
-        <v>421</v>
-      </c>
-      <c r="D125" s="50"/>
-      <c r="E125" s="50" t="s">
+        <v>317</v>
+      </c>
+      <c r="C125" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D125" s="46" t="s">
+        <v>318</v>
+      </c>
+      <c r="E125" s="46" t="s">
         <v>10</v>
       </c>
-      <c r="F125" s="52" t="s">
-        <v>422</v>
+      <c r="F125" s="48" t="s">
+        <v>319</v>
       </c>
       <c r="G125" s="29"/>
     </row>
-    <row r="126" ht="15.75" hidden="1" spans="1:7">
+    <row r="126" ht="31.5" spans="1:7">
       <c r="A126" s="24"/>
       <c r="B126" s="25" t="s">
-        <v>423</v>
-      </c>
-      <c r="C126" s="49" t="s">
-        <v>424</v>
-      </c>
-      <c r="D126" s="50"/>
-      <c r="E126" s="50" t="s">
-        <v>38</v>
-      </c>
-      <c r="F126" s="52" t="s">
-        <v>425</v>
+        <v>320</v>
+      </c>
+      <c r="C126" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D126" s="46" t="s">
+        <v>321</v>
+      </c>
+      <c r="E126" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="F126" s="48" t="s">
+        <v>322</v>
       </c>
       <c r="G126" s="29"/>
     </row>
-    <row r="127" ht="15.75" hidden="1" spans="1:7">
+    <row r="127" ht="15.75" spans="1:7">
       <c r="A127" s="24"/>
       <c r="B127" s="25" t="s">
-        <v>426</v>
-      </c>
-      <c r="C127" s="49" t="s">
-        <v>148</v>
-      </c>
-      <c r="D127" s="50" t="s">
-        <v>174</v>
-      </c>
-      <c r="E127" s="51"/>
-      <c r="F127" s="52" t="s">
-        <v>427</v>
+        <v>323</v>
+      </c>
+      <c r="C127" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D127" s="46" t="s">
+        <v>129</v>
+      </c>
+      <c r="E127" s="47"/>
+      <c r="F127" s="48" t="s">
+        <v>324</v>
       </c>
       <c r="G127" s="29"/>
     </row>
     <row r="128" spans="1:7">
       <c r="A128" s="19"/>
       <c r="D128" s="17"/>
-      <c r="F128" s="47"/>
+      <c r="F128" s="44"/>
     </row>
     <row r="129" spans="1:4">
       <c r="A129" s="19"/>
@@ -9601,11 +9290,6 @@
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G127" etc:filterBottomFollowUsedRange="0">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="FELLAH MOHAMMED KARIM MOHAMMED KARIM"/>
-      </filters>
-    </filterColumn>
     <extLst/>
   </autoFilter>
   <hyperlinks>
@@ -9671,202 +9355,202 @@
   <sheetData>
     <row r="1" ht="15.75" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>428</v>
+        <v>325</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>429</v>
+        <v>326</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>430</v>
+        <v>327</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>431</v>
+        <v>328</v>
       </c>
     </row>
     <row r="2" ht="15.75" spans="1:4">
       <c r="A2" s="4" t="s">
-        <v>432</v>
+        <v>329</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>433</v>
+        <v>330</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>434</v>
+        <v>331</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>435</v>
+        <v>332</v>
       </c>
     </row>
     <row r="3" ht="15.75" spans="1:4">
       <c r="A3" s="8"/>
       <c r="B3" s="5" t="s">
-        <v>436</v>
+        <v>333</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>437</v>
+        <v>334</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>438</v>
+        <v>335</v>
       </c>
     </row>
     <row r="4" ht="15.75" spans="1:4">
       <c r="A4" s="8"/>
       <c r="B4" s="5" t="s">
-        <v>439</v>
+        <v>336</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>440</v>
+        <v>337</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>441</v>
+        <v>338</v>
       </c>
     </row>
     <row r="5" ht="15.75" spans="1:4">
       <c r="A5" s="8"/>
       <c r="B5" s="5" t="s">
-        <v>442</v>
+        <v>339</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>440</v>
+        <v>337</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>443</v>
+        <v>340</v>
       </c>
     </row>
     <row r="6" ht="15.75" spans="1:4">
       <c r="A6" s="8"/>
       <c r="B6" s="5" t="s">
-        <v>444</v>
+        <v>341</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>437</v>
+        <v>334</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>445</v>
+        <v>342</v>
       </c>
     </row>
     <row r="7" ht="15.75" spans="1:4">
       <c r="A7" s="9" t="s">
-        <v>446</v>
+        <v>343</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>447</v>
+        <v>344</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>437</v>
+        <v>334</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>448</v>
+        <v>345</v>
       </c>
     </row>
     <row r="8" ht="15.75" spans="1:4">
       <c r="A8" s="8"/>
       <c r="B8" s="10" t="s">
-        <v>449</v>
+        <v>346</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>440</v>
+        <v>337</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>448</v>
+        <v>345</v>
       </c>
     </row>
     <row r="9" ht="15.75" spans="1:4">
       <c r="A9" s="11" t="s">
-        <v>450</v>
+        <v>347</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>451</v>
+        <v>348</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>434</v>
+        <v>331</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>452</v>
+        <v>349</v>
       </c>
     </row>
     <row r="10" ht="15.75" spans="1:4">
       <c r="A10" s="8"/>
       <c r="B10" s="13" t="s">
-        <v>453</v>
+        <v>350</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>437</v>
+        <v>334</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>454</v>
+        <v>351</v>
       </c>
     </row>
     <row r="11" ht="15.75" spans="1:4">
       <c r="A11" s="8"/>
       <c r="B11" s="13" t="s">
-        <v>455</v>
+        <v>352</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>440</v>
+        <v>337</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>456</v>
+        <v>353</v>
       </c>
     </row>
     <row r="12" ht="15.75" spans="1:4">
       <c r="A12" s="8"/>
       <c r="B12" s="13" t="s">
-        <v>457</v>
+        <v>354</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>440</v>
+        <v>337</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>438</v>
+        <v>335</v>
       </c>
     </row>
     <row r="13" ht="15.75" spans="1:4">
       <c r="A13" s="8"/>
       <c r="B13" s="13" t="s">
-        <v>458</v>
+        <v>355</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>440</v>
+        <v>337</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>459</v>
+        <v>356</v>
       </c>
     </row>
     <row r="14" ht="15.75" spans="1:4">
       <c r="A14" s="8"/>
       <c r="B14" s="13" t="s">
-        <v>460</v>
+        <v>357</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>440</v>
+        <v>337</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>461</v>
+        <v>358</v>
       </c>
     </row>
     <row r="15" ht="15.75" spans="1:4">
       <c r="A15" s="8"/>
       <c r="B15" s="13" t="s">
-        <v>462</v>
+        <v>359</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>440</v>
+        <v>337</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>463</v>
+        <v>360</v>
       </c>
     </row>
     <row r="16" ht="15.75" spans="1:4">
       <c r="A16" s="8"/>
       <c r="B16" s="13" t="s">
-        <v>464</v>
+        <v>361</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>440</v>
+        <v>337</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>465</v>
+        <v>362</v>
       </c>
     </row>
     <row r="656" ht="15.75"/>

--- a/Permanents-Vacataires-ELT2-2026-2027.xlsx
+++ b/Permanents-Vacataires-ELT2-2026-2027.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Répartiion pour Examen" sheetId="8" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Permanents-Vacataires'!$A$1:$G$127</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Permanents-Vacataires'!$A$1:$G$128</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Répartiion pour Examen'!$A$1:$D$16</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="738" uniqueCount="363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="748" uniqueCount="368">
   <si>
     <t>N°</t>
   </si>
@@ -1007,6 +1007,21 @@
   </si>
   <si>
     <t>medzerdani@gmail.com</t>
+  </si>
+  <si>
+    <t>KADA KLOUCHA OMAR</t>
+  </si>
+  <si>
+    <t>Permenant Associé</t>
+  </si>
+  <si>
+    <t>klomar05@yahoo.fr</t>
+  </si>
+  <si>
+    <t>SAIDI KHEIREDDINE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">saidi_kheiro@yahoo.fr </t>
   </si>
   <si>
     <t>CYCLE</t>
@@ -5127,72 +5142,101 @@
       </c>
       <c r="G127" s="29"/>
     </row>
-    <row r="128" spans="1:7">
-      <c r="A128" s="19"/>
-      <c r="D128" s="17"/>
-      <c r="F128" s="44"/>
-    </row>
-    <row r="129" spans="1:4">
-      <c r="A129" s="19"/>
-      <c r="D129" s="17"/>
-    </row>
-    <row r="130" spans="1:4">
+    <row r="128" ht="31.5" spans="1:7">
+      <c r="A128" s="24"/>
+      <c r="B128" s="25" t="s">
+        <v>325</v>
+      </c>
+      <c r="C128" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D128" s="46" t="s">
+        <v>326</v>
+      </c>
+      <c r="E128" s="47" t="s">
+        <v>31</v>
+      </c>
+      <c r="F128" s="48" t="s">
+        <v>327</v>
+      </c>
+      <c r="G128" s="29"/>
+    </row>
+    <row r="129" ht="31.5" spans="1:7">
+      <c r="A129" s="24"/>
+      <c r="B129" s="25" t="s">
+        <v>328</v>
+      </c>
+      <c r="C129" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D129" s="46" t="s">
+        <v>326</v>
+      </c>
+      <c r="E129" s="47" t="s">
+        <v>31</v>
+      </c>
+      <c r="F129" s="48" t="s">
+        <v>329</v>
+      </c>
+      <c r="G129" s="29"/>
+    </row>
+    <row r="130" spans="1:7">
       <c r="A130" s="19"/>
       <c r="D130" s="17"/>
     </row>
-    <row r="131" spans="1:4">
+    <row r="131" spans="1:7">
       <c r="A131" s="19"/>
       <c r="D131" s="17"/>
     </row>
-    <row r="132" spans="1:4">
+    <row r="132" spans="1:7">
       <c r="A132" s="19"/>
       <c r="D132" s="17"/>
     </row>
-    <row r="133" spans="1:4">
+    <row r="133" spans="1:7">
       <c r="A133" s="19"/>
       <c r="D133" s="17"/>
     </row>
-    <row r="134" spans="1:4">
+    <row r="134" spans="1:7">
       <c r="A134" s="19"/>
       <c r="D134" s="17"/>
     </row>
-    <row r="135" spans="1:4">
+    <row r="135" spans="1:7">
       <c r="A135" s="19"/>
       <c r="D135" s="17"/>
     </row>
-    <row r="136" spans="1:4">
+    <row r="136" spans="1:7">
       <c r="A136" s="19"/>
       <c r="D136" s="17"/>
     </row>
-    <row r="137" spans="1:4">
+    <row r="137" spans="1:7">
       <c r="A137" s="19"/>
       <c r="D137" s="17"/>
     </row>
-    <row r="138" spans="1:4">
+    <row r="138" spans="1:7">
       <c r="A138" s="19"/>
       <c r="D138" s="17"/>
     </row>
-    <row r="139" spans="1:4">
+    <row r="139" spans="1:7">
       <c r="A139" s="19"/>
       <c r="D139" s="17"/>
     </row>
-    <row r="140" spans="1:4">
+    <row r="140" spans="1:7">
       <c r="A140" s="19"/>
       <c r="D140" s="17"/>
     </row>
-    <row r="141" spans="1:4">
+    <row r="141" spans="1:7">
       <c r="A141" s="19"/>
       <c r="D141" s="17"/>
     </row>
-    <row r="142" spans="1:4">
+    <row r="142" spans="1:7">
       <c r="A142" s="19"/>
       <c r="D142" s="17"/>
     </row>
-    <row r="143" spans="1:4">
+    <row r="143" spans="1:7">
       <c r="A143" s="19"/>
       <c r="D143" s="17"/>
     </row>
-    <row r="144" spans="1:4">
+    <row r="144" spans="1:7">
       <c r="A144" s="19"/>
       <c r="D144" s="17"/>
     </row>
@@ -9289,7 +9333,7 @@
       <c r="D1167" s="17"/>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G127" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G128" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <hyperlinks>
@@ -9355,202 +9399,202 @@
   <sheetData>
     <row r="1" ht="15.75" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
     </row>
     <row r="2" ht="15.75" spans="1:4">
       <c r="A2" s="4" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
     </row>
     <row r="3" ht="15.75" spans="1:4">
       <c r="A3" s="8"/>
       <c r="B3" s="5" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
     </row>
     <row r="4" ht="15.75" spans="1:4">
       <c r="A4" s="8"/>
       <c r="B4" s="5" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
     </row>
     <row r="5" ht="15.75" spans="1:4">
       <c r="A5" s="8"/>
       <c r="B5" s="5" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="6" ht="15.75" spans="1:4">
       <c r="A6" s="8"/>
       <c r="B6" s="5" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
     </row>
     <row r="7" ht="15.75" spans="1:4">
       <c r="A7" s="9" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
     </row>
     <row r="8" ht="15.75" spans="1:4">
       <c r="A8" s="8"/>
       <c r="B8" s="10" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
     </row>
     <row r="9" ht="15.75" spans="1:4">
       <c r="A9" s="11" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
     </row>
     <row r="10" ht="15.75" spans="1:4">
       <c r="A10" s="8"/>
       <c r="B10" s="13" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
     </row>
     <row r="11" ht="15.75" spans="1:4">
       <c r="A11" s="8"/>
       <c r="B11" s="13" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
     </row>
     <row r="12" ht="15.75" spans="1:4">
       <c r="A12" s="8"/>
       <c r="B12" s="13" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
     </row>
     <row r="13" ht="15.75" spans="1:4">
       <c r="A13" s="8"/>
       <c r="B13" s="13" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
     </row>
     <row r="14" ht="15.75" spans="1:4">
       <c r="A14" s="8"/>
       <c r="B14" s="13" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
     </row>
     <row r="15" ht="15.75" spans="1:4">
       <c r="A15" s="8"/>
       <c r="B15" s="13" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
     </row>
     <row r="16" ht="15.75" spans="1:4">
       <c r="A16" s="8"/>
       <c r="B16" s="13" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
     </row>
     <row r="656" ht="15.75"/>

--- a/Permanents-Vacataires-ELT2-2026-2027.xlsx
+++ b/Permanents-Vacataires-ELT2-2026-2027.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Répartiion pour Examen" sheetId="8" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Permanents-Vacataires'!$A$1:$G$128</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Permanents-Vacataires'!$A$1:$G$129</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Répartiion pour Examen'!$A$1:$D$16</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="748" uniqueCount="368">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="702" uniqueCount="366">
   <si>
     <t>N°</t>
   </si>
@@ -70,18 +70,12 @@
     <t>irecom_abid@yahoo.fr</t>
   </si>
   <si>
-    <t>RAS</t>
-  </si>
-  <si>
     <t>AKSA WESSIM</t>
   </si>
   <si>
     <t>aksa86wessim@gmail.com</t>
   </si>
   <si>
-    <t>Corrigé</t>
-  </si>
-  <si>
     <t>ARDJOUN SID AHMED</t>
   </si>
   <si>
@@ -274,7 +268,7 @@
     <t>KHATIR MOHAMED</t>
   </si>
   <si>
-    <t xml:space="preserve">med_khatir@yahoo.fr </t>
+    <t>khatir.mohamed1977@gmail.com</t>
   </si>
   <si>
     <t>LALEDJ NADJET</t>
@@ -307,6 +301,9 @@
     <t>milouafarid@gmail.com</t>
   </si>
   <si>
+    <t>0657011874</t>
+  </si>
+  <si>
     <t>MILOUDI HOUCINE</t>
   </si>
   <si>
@@ -356,9 +353,6 @@
   </si>
   <si>
     <t>abc_rim20052003@yahoo.fr</t>
-  </si>
-  <si>
-    <t>A revoir !!!!</t>
   </si>
   <si>
     <t>REZOUG MOHAMMED</t>
@@ -2457,16 +2451,14 @@
       <c r="F2" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="28" t="s">
-        <v>12</v>
-      </c>
+      <c r="G2" s="28"/>
     </row>
     <row r="3" ht="15.75" spans="1:7">
       <c r="A3" s="24">
         <v>2</v>
       </c>
       <c r="B3" s="25" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C3" s="25" t="s">
         <v>8</v>
@@ -2478,18 +2470,16 @@
         <v>10</v>
       </c>
       <c r="F3" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3" s="28" t="s">
-        <v>15</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="G3" s="28"/>
     </row>
     <row r="4" ht="15.75" spans="1:7">
       <c r="A4" s="24">
         <v>3</v>
       </c>
       <c r="B4" s="25" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C4" s="25" t="s">
         <v>8</v>
@@ -2501,18 +2491,16 @@
         <v>10</v>
       </c>
       <c r="F4" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="G4" s="28" t="s">
-        <v>12</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="G4" s="28"/>
     </row>
     <row r="5" ht="15.75" spans="1:7">
       <c r="A5" s="24">
         <v>4</v>
       </c>
       <c r="B5" s="25" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C5" s="25" t="s">
         <v>8</v>
@@ -2524,18 +2512,16 @@
         <v>10</v>
       </c>
       <c r="F5" s="27" t="s">
-        <v>19</v>
-      </c>
-      <c r="G5" s="28" t="s">
-        <v>12</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="G5" s="28"/>
     </row>
     <row r="6" ht="15.75" spans="1:7">
       <c r="A6" s="24">
         <v>5</v>
       </c>
       <c r="B6" s="25" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C6" s="25" t="s">
         <v>8</v>
@@ -2547,33 +2533,31 @@
         <v>10</v>
       </c>
       <c r="F6" s="27" t="s">
-        <v>21</v>
-      </c>
-      <c r="G6" s="28" t="s">
-        <v>12</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="G6" s="28"/>
     </row>
     <row r="7" ht="15.75" spans="1:7">
       <c r="A7" s="24">
         <v>6</v>
       </c>
       <c r="B7" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="C7" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D7" s="26" t="s">
+      <c r="F7" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="E7" s="26" t="s">
+      <c r="G7" s="50" t="s">
         <v>24</v>
-      </c>
-      <c r="F7" s="27" t="s">
-        <v>25</v>
-      </c>
-      <c r="G7" s="50" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="8" ht="15.75" spans="1:7">
@@ -2581,7 +2565,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="25" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C8" s="25" t="s">
         <v>8</v>
@@ -2593,10 +2577,10 @@
         <v>10</v>
       </c>
       <c r="F8" s="27" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G8" s="50" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9" ht="15.75" spans="1:7">
@@ -2604,7 +2588,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="25" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C9" s="25" t="s">
         <v>8</v>
@@ -2613,21 +2597,19 @@
         <v>9</v>
       </c>
       <c r="E9" s="26" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F9" s="27" t="s">
-        <v>32</v>
-      </c>
-      <c r="G9" s="28" t="s">
-        <v>12</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="G9" s="28"/>
     </row>
     <row r="10" ht="15.75" spans="1:7">
       <c r="A10" s="24">
         <v>9</v>
       </c>
       <c r="B10" s="25" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C10" s="25" t="s">
         <v>8</v>
@@ -2636,13 +2618,13 @@
         <v>9</v>
       </c>
       <c r="E10" s="31" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F10" s="32" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G10" s="50" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" ht="15.75" spans="1:7">
@@ -2650,7 +2632,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="25" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C11" s="25" t="s">
         <v>8</v>
@@ -2662,18 +2644,16 @@
         <v>10</v>
       </c>
       <c r="F11" s="33" t="s">
-        <v>37</v>
-      </c>
-      <c r="G11" s="28" t="s">
-        <v>12</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="G11" s="28"/>
     </row>
     <row r="12" ht="15.75" spans="1:7">
       <c r="A12" s="24">
         <v>11</v>
       </c>
       <c r="B12" s="25" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C12" s="25" t="s">
         <v>8</v>
@@ -2685,18 +2665,16 @@
         <v>10</v>
       </c>
       <c r="F12" s="27" t="s">
-        <v>39</v>
-      </c>
-      <c r="G12" s="28" t="s">
-        <v>12</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="G12" s="28"/>
     </row>
     <row r="13" ht="15.75" spans="1:7">
       <c r="A13" s="24">
         <v>12</v>
       </c>
       <c r="B13" s="25" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C13" s="25" t="s">
         <v>8</v>
@@ -2708,7 +2686,7 @@
         <v>10</v>
       </c>
       <c r="F13" s="27" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G13" s="28"/>
     </row>
@@ -2717,7 +2695,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="25" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C14" s="25" t="s">
         <v>8</v>
@@ -2726,21 +2704,19 @@
         <v>9</v>
       </c>
       <c r="E14" s="26" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F14" s="27" t="s">
-        <v>43</v>
-      </c>
-      <c r="G14" s="28" t="s">
-        <v>12</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="G14" s="28"/>
     </row>
     <row r="15" ht="15.75" spans="1:7">
       <c r="A15" s="24">
         <v>14</v>
       </c>
       <c r="B15" s="25" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C15" s="25" t="s">
         <v>8</v>
@@ -2752,18 +2728,16 @@
         <v>10</v>
       </c>
       <c r="F15" s="27" t="s">
-        <v>45</v>
-      </c>
-      <c r="G15" s="28" t="s">
-        <v>12</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="G15" s="28"/>
     </row>
     <row r="16" ht="31.5" spans="1:7">
       <c r="A16" s="24">
         <v>15</v>
       </c>
       <c r="B16" s="25" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C16" s="25" t="s">
         <v>8</v>
@@ -2772,44 +2746,40 @@
         <v>9</v>
       </c>
       <c r="E16" s="26" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F16" s="27" t="s">
-        <v>47</v>
-      </c>
-      <c r="G16" s="28" t="s">
-        <v>15</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="G16" s="28"/>
     </row>
     <row r="17" ht="15.75" spans="1:7">
       <c r="A17" s="24">
         <v>16</v>
       </c>
       <c r="B17" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="C17" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="E17" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="F17" s="27" t="s">
         <v>48</v>
       </c>
-      <c r="C17" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D17" s="26" t="s">
-        <v>23</v>
-      </c>
-      <c r="E17" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="F17" s="27" t="s">
-        <v>50</v>
-      </c>
-      <c r="G17" s="28" t="s">
-        <v>15</v>
-      </c>
+      <c r="G17" s="28"/>
     </row>
     <row r="18" ht="15.75" spans="1:7">
       <c r="A18" s="24">
         <v>17</v>
       </c>
       <c r="B18" s="25" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C18" s="25" t="s">
         <v>8</v>
@@ -2821,18 +2791,16 @@
         <v>10</v>
       </c>
       <c r="F18" s="27" t="s">
-        <v>52</v>
-      </c>
-      <c r="G18" s="28" t="s">
-        <v>12</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="G18" s="28"/>
     </row>
     <row r="19" ht="15.75" spans="1:7">
       <c r="A19" s="24">
         <v>18</v>
       </c>
       <c r="B19" s="25" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C19" s="25" t="s">
         <v>8</v>
@@ -2841,21 +2809,19 @@
         <v>9</v>
       </c>
       <c r="E19" s="34" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F19" s="32" t="s">
-        <v>54</v>
-      </c>
-      <c r="G19" s="28" t="s">
-        <v>12</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="G19" s="28"/>
     </row>
     <row r="20" ht="31.5" spans="1:7">
       <c r="A20" s="24">
         <v>19</v>
       </c>
       <c r="B20" s="25" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C20" s="25" t="s">
         <v>8</v>
@@ -2867,18 +2833,16 @@
         <v>10</v>
       </c>
       <c r="F20" s="27" t="s">
-        <v>56</v>
-      </c>
-      <c r="G20" s="28" t="s">
-        <v>12</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="G20" s="28"/>
     </row>
     <row r="21" ht="15.75" spans="1:7">
       <c r="A21" s="24">
         <v>20</v>
       </c>
       <c r="B21" s="25" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C21" s="25" t="s">
         <v>8</v>
@@ -2887,21 +2851,19 @@
         <v>9</v>
       </c>
       <c r="E21" s="26" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F21" s="27" t="s">
-        <v>58</v>
-      </c>
-      <c r="G21" s="28" t="s">
-        <v>12</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="G21" s="28"/>
     </row>
     <row r="22" ht="15.75" spans="1:7">
       <c r="A22" s="24">
         <v>21</v>
       </c>
       <c r="B22" s="25" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C22" s="25" t="s">
         <v>8</v>
@@ -2913,41 +2875,37 @@
         <v>10</v>
       </c>
       <c r="F22" s="27" t="s">
-        <v>60</v>
-      </c>
-      <c r="G22" s="28" t="s">
-        <v>12</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="G22" s="28"/>
     </row>
     <row r="23" ht="15.75" spans="1:7">
       <c r="A23" s="24">
         <v>22</v>
       </c>
       <c r="B23" s="25" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C23" s="25" t="s">
         <v>8</v>
       </c>
       <c r="D23" s="26" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E23" s="26" t="s">
         <v>10</v>
       </c>
       <c r="F23" s="27" t="s">
-        <v>62</v>
-      </c>
-      <c r="G23" s="28" t="s">
-        <v>12</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="G23" s="28"/>
     </row>
     <row r="24" ht="15.75" spans="1:7">
       <c r="A24" s="24">
         <v>23</v>
       </c>
       <c r="B24" s="25" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C24" s="25" t="s">
         <v>8</v>
@@ -2956,44 +2914,40 @@
         <v>9</v>
       </c>
       <c r="E24" s="26" t="s">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="F24" s="27" t="s">
-        <v>64</v>
-      </c>
-      <c r="G24" s="28" t="s">
-        <v>12</v>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="G24" s="28"/>
     </row>
     <row r="25" ht="15.75" spans="1:7">
       <c r="A25" s="24">
         <v>24</v>
       </c>
       <c r="B25" s="25" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C25" s="25" t="s">
         <v>8</v>
       </c>
       <c r="D25" s="26" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E25" s="26" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F25" s="32" t="s">
-        <v>66</v>
-      </c>
-      <c r="G25" s="28" t="s">
-        <v>15</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="G25" s="28"/>
     </row>
     <row r="26" ht="31.5" spans="1:7">
       <c r="A26" s="24">
         <v>25</v>
       </c>
       <c r="B26" s="25" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C26" s="25" t="s">
         <v>8</v>
@@ -3005,30 +2959,28 @@
         <v>10</v>
       </c>
       <c r="F26" s="27" t="s">
-        <v>68</v>
-      </c>
-      <c r="G26" s="28" t="s">
-        <v>12</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="G26" s="28"/>
     </row>
     <row r="27" ht="15.75" spans="1:7">
       <c r="A27" s="24">
         <v>26</v>
       </c>
       <c r="B27" s="25" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C27" s="25" t="s">
         <v>8</v>
       </c>
       <c r="D27" s="26" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E27" s="26" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F27" s="27" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G27" s="28"/>
     </row>
@@ -3037,7 +2989,7 @@
         <v>27</v>
       </c>
       <c r="B28" s="25" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C28" s="25" t="s">
         <v>8</v>
@@ -3049,18 +3001,16 @@
         <v>10</v>
       </c>
       <c r="F28" s="27" t="s">
-        <v>72</v>
-      </c>
-      <c r="G28" s="28" t="s">
-        <v>12</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="G28" s="28"/>
     </row>
     <row r="29" ht="15.75" spans="1:7">
       <c r="A29" s="24">
         <v>28</v>
       </c>
       <c r="B29" s="25" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C29" s="25" t="s">
         <v>8</v>
@@ -3069,67 +3019,61 @@
         <v>9</v>
       </c>
       <c r="E29" s="26" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F29" s="27" t="s">
-        <v>74</v>
-      </c>
-      <c r="G29" s="28" t="s">
-        <v>12</v>
-      </c>
+        <v>72</v>
+      </c>
+      <c r="G29" s="28"/>
     </row>
     <row r="30" ht="15.75" spans="1:7">
       <c r="A30" s="24">
         <v>29</v>
       </c>
       <c r="B30" s="25" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C30" s="25" t="s">
         <v>8</v>
       </c>
       <c r="D30" s="26" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E30" s="26" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F30" s="27" t="s">
-        <v>76</v>
-      </c>
-      <c r="G30" s="28" t="s">
-        <v>12</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="G30" s="28"/>
     </row>
     <row r="31" ht="15.75" spans="1:7">
       <c r="A31" s="24">
         <v>30</v>
       </c>
       <c r="B31" s="25" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C31" s="25" t="s">
         <v>8</v>
       </c>
       <c r="D31" s="26" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E31" s="26" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F31" s="27" t="s">
-        <v>78</v>
-      </c>
-      <c r="G31" s="28" t="s">
-        <v>12</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="G31" s="28"/>
     </row>
     <row r="32" ht="15.75" spans="1:7">
       <c r="A32" s="24">
         <v>31</v>
       </c>
       <c r="B32" s="25" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C32" s="25" t="s">
         <v>8</v>
@@ -3140,8 +3084,8 @@
       <c r="E32" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="F32" s="27" t="s">
-        <v>80</v>
+      <c r="F32" s="33" t="s">
+        <v>78</v>
       </c>
       <c r="G32" s="28"/>
     </row>
@@ -3150,7 +3094,7 @@
         <v>32</v>
       </c>
       <c r="B33" s="25" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C33" s="25" t="s">
         <v>8</v>
@@ -3159,21 +3103,19 @@
         <v>9</v>
       </c>
       <c r="E33" s="26" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F33" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="G33" s="28" t="s">
-        <v>12</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="G33" s="28"/>
     </row>
     <row r="34" ht="15.75" spans="1:7">
       <c r="A34" s="24">
         <v>33</v>
       </c>
       <c r="B34" s="25" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C34" s="25" t="s">
         <v>8</v>
@@ -3185,18 +3127,16 @@
         <v>10</v>
       </c>
       <c r="F34" s="27" t="s">
-        <v>84</v>
-      </c>
-      <c r="G34" s="28" t="s">
-        <v>15</v>
-      </c>
+        <v>82</v>
+      </c>
+      <c r="G34" s="28"/>
     </row>
     <row r="35" ht="15.75" spans="1:7">
       <c r="A35" s="24">
         <v>34</v>
       </c>
       <c r="B35" s="25" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C35" s="25" t="s">
         <v>8</v>
@@ -3205,21 +3145,19 @@
         <v>9</v>
       </c>
       <c r="E35" s="26" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F35" s="27" t="s">
-        <v>86</v>
-      </c>
-      <c r="G35" s="28" t="s">
-        <v>12</v>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="G35" s="28"/>
     </row>
     <row r="36" ht="15.75" spans="1:7">
       <c r="A36" s="24">
         <v>35</v>
       </c>
       <c r="B36" s="25" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C36" s="25" t="s">
         <v>8</v>
@@ -3231,18 +3169,16 @@
         <v>10</v>
       </c>
       <c r="F36" s="27" t="s">
-        <v>88</v>
-      </c>
-      <c r="G36" s="28" t="s">
-        <v>12</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="G36" s="28"/>
     </row>
     <row r="37" ht="15.75" spans="1:7">
       <c r="A37" s="24">
         <v>36</v>
       </c>
       <c r="B37" s="25" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C37" s="25" t="s">
         <v>8</v>
@@ -3254,10 +3190,10 @@
         <v>10</v>
       </c>
       <c r="F37" s="27" t="s">
-        <v>90</v>
-      </c>
-      <c r="G37" s="28" t="s">
-        <v>12</v>
+        <v>88</v>
+      </c>
+      <c r="G37" s="51" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="38" ht="15.75" spans="1:7">
@@ -3265,7 +3201,7 @@
         <v>37</v>
       </c>
       <c r="B38" s="25" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C38" s="25" t="s">
         <v>8</v>
@@ -3277,18 +3213,16 @@
         <v>10</v>
       </c>
       <c r="F38" s="27" t="s">
-        <v>92</v>
-      </c>
-      <c r="G38" s="28" t="s">
-        <v>12</v>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="G38" s="28"/>
     </row>
     <row r="39" ht="15.75" spans="1:7">
       <c r="A39" s="24">
         <v>38</v>
       </c>
       <c r="B39" s="25" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C39" s="25" t="s">
         <v>8</v>
@@ -3297,13 +3231,13 @@
         <v>9</v>
       </c>
       <c r="E39" s="26" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F39" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="G39" s="50" t="s">
         <v>94</v>
-      </c>
-      <c r="G39" s="50" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="40" ht="15.75" spans="1:7">
@@ -3311,7 +3245,7 @@
         <v>39</v>
       </c>
       <c r="B40" s="25" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C40" s="25" t="s">
         <v>8</v>
@@ -3320,21 +3254,19 @@
         <v>9</v>
       </c>
       <c r="E40" s="26" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F40" s="27" t="s">
-        <v>97</v>
-      </c>
-      <c r="G40" s="28" t="s">
-        <v>12</v>
-      </c>
+        <v>96</v>
+      </c>
+      <c r="G40" s="28"/>
     </row>
     <row r="41" ht="15.75" spans="1:7">
       <c r="A41" s="24">
         <v>40</v>
       </c>
       <c r="B41" s="25" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C41" s="25" t="s">
         <v>8</v>
@@ -3346,18 +3278,16 @@
         <v>10</v>
       </c>
       <c r="F41" s="27" t="s">
-        <v>99</v>
-      </c>
-      <c r="G41" s="28" t="s">
-        <v>12</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="G41" s="28"/>
     </row>
     <row r="42" ht="15.75" spans="1:7">
       <c r="A42" s="24">
         <v>41</v>
       </c>
       <c r="B42" s="25" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C42" s="25" t="s">
         <v>8</v>
@@ -3369,18 +3299,16 @@
         <v>10</v>
       </c>
       <c r="F42" s="27" t="s">
-        <v>101</v>
-      </c>
-      <c r="G42" s="28" t="s">
-        <v>12</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="G42" s="28"/>
     </row>
     <row r="43" ht="15.75" spans="1:7">
       <c r="A43" s="24">
         <v>42</v>
       </c>
       <c r="B43" s="25" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C43" s="25" t="s">
         <v>8</v>
@@ -3392,41 +3320,37 @@
         <v>10</v>
       </c>
       <c r="F43" s="27" t="s">
-        <v>103</v>
-      </c>
-      <c r="G43" s="28" t="s">
-        <v>12</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="G43" s="28"/>
     </row>
     <row r="44" ht="15.75" spans="1:7">
       <c r="A44" s="24">
         <v>43</v>
       </c>
       <c r="B44" s="25" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C44" s="25" t="s">
         <v>8</v>
       </c>
       <c r="D44" s="26" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E44" s="26" t="s">
         <v>10</v>
       </c>
       <c r="F44" s="27" t="s">
-        <v>105</v>
-      </c>
-      <c r="G44" s="28" t="s">
-        <v>12</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="G44" s="28"/>
     </row>
     <row r="45" ht="15.75" spans="1:7">
       <c r="A45" s="24">
         <v>44</v>
       </c>
       <c r="B45" s="25" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C45" s="25" t="s">
         <v>8</v>
@@ -3438,18 +3362,16 @@
         <v>10</v>
       </c>
       <c r="F45" s="27" t="s">
-        <v>107</v>
-      </c>
-      <c r="G45" s="28" t="s">
-        <v>108</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="G45" s="28"/>
     </row>
     <row r="46" ht="15.75" spans="1:7">
       <c r="A46" s="24">
         <v>45</v>
       </c>
       <c r="B46" s="25" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C46" s="25" t="s">
         <v>8</v>
@@ -3461,41 +3383,37 @@
         <v>10</v>
       </c>
       <c r="F46" s="27" t="s">
-        <v>110</v>
-      </c>
-      <c r="G46" s="28" t="s">
-        <v>12</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="G46" s="28"/>
     </row>
     <row r="47" ht="15.75" spans="1:7">
       <c r="A47" s="24">
         <v>46</v>
       </c>
       <c r="B47" s="25" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C47" s="25" t="s">
         <v>8</v>
       </c>
       <c r="D47" s="26" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E47" s="26" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F47" s="27" t="s">
-        <v>112</v>
-      </c>
-      <c r="G47" s="28" t="s">
-        <v>12</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="G47" s="28"/>
     </row>
     <row r="48" ht="15.75" spans="1:7">
       <c r="A48" s="24">
         <v>47</v>
       </c>
       <c r="B48" s="25" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C48" s="25" t="s">
         <v>8</v>
@@ -3507,41 +3425,37 @@
         <v>10</v>
       </c>
       <c r="F48" s="27" t="s">
-        <v>114</v>
-      </c>
-      <c r="G48" s="28" t="s">
-        <v>12</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="G48" s="28"/>
     </row>
     <row r="49" ht="15.75" spans="1:7">
       <c r="A49" s="24">
         <v>48</v>
       </c>
       <c r="B49" s="25" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C49" s="25" t="s">
         <v>8</v>
       </c>
       <c r="D49" s="26" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E49" s="26" t="s">
         <v>10</v>
       </c>
       <c r="F49" s="27" t="s">
-        <v>116</v>
-      </c>
-      <c r="G49" s="28" t="s">
-        <v>12</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="G49" s="28"/>
     </row>
     <row r="50" ht="15.75" spans="1:7">
       <c r="A50" s="24">
         <v>49</v>
       </c>
       <c r="B50" s="25" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C50" s="25" t="s">
         <v>8</v>
@@ -3553,18 +3467,16 @@
         <v>10</v>
       </c>
       <c r="F50" s="27" t="s">
-        <v>118</v>
-      </c>
-      <c r="G50" s="28" t="s">
-        <v>12</v>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="G50" s="28"/>
     </row>
     <row r="51" ht="15.75" spans="1:7">
       <c r="A51" s="24">
         <v>50</v>
       </c>
       <c r="B51" s="25" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C51" s="25" t="s">
         <v>8</v>
@@ -3573,21 +3485,19 @@
         <v>9</v>
       </c>
       <c r="E51" s="26" t="s">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="F51" s="27" t="s">
-        <v>120</v>
-      </c>
-      <c r="G51" s="28" t="s">
-        <v>15</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="G51" s="28"/>
     </row>
     <row r="52" ht="15.75" spans="1:7">
       <c r="A52" s="24">
         <v>51</v>
       </c>
       <c r="B52" s="25" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C52" s="25" t="s">
         <v>8</v>
@@ -3599,33 +3509,31 @@
         <v>10</v>
       </c>
       <c r="F52" s="27" t="s">
-        <v>122</v>
-      </c>
-      <c r="G52" s="28" t="s">
-        <v>12</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="G52" s="28"/>
     </row>
     <row r="53" ht="15.75" spans="1:7">
       <c r="A53" s="24">
         <v>52</v>
       </c>
       <c r="B53" s="25" t="s">
+        <v>121</v>
+      </c>
+      <c r="C53" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D53" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="E53" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="F53" s="27" t="s">
+        <v>122</v>
+      </c>
+      <c r="G53" s="50" t="s">
         <v>123</v>
-      </c>
-      <c r="C53" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D53" s="26" t="s">
-        <v>23</v>
-      </c>
-      <c r="E53" s="26" t="s">
-        <v>31</v>
-      </c>
-      <c r="F53" s="27" t="s">
-        <v>124</v>
-      </c>
-      <c r="G53" s="50" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="54" ht="15.75" spans="1:7">
@@ -3633,7 +3541,7 @@
         <v>53</v>
       </c>
       <c r="B54" s="25" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C54" s="25" t="s">
         <v>8</v>
@@ -3645,33 +3553,31 @@
         <v>10</v>
       </c>
       <c r="F54" s="27" t="s">
-        <v>127</v>
-      </c>
-      <c r="G54" s="28" t="s">
-        <v>12</v>
-      </c>
+        <v>125</v>
+      </c>
+      <c r="G54" s="28"/>
     </row>
     <row r="55" ht="15.75" spans="1:7">
       <c r="A55" s="24">
         <v>54</v>
       </c>
       <c r="B55" s="25" t="s">
+        <v>126</v>
+      </c>
+      <c r="C55" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D55" s="30" t="s">
+        <v>127</v>
+      </c>
+      <c r="E55" s="26" t="s">
         <v>128</v>
       </c>
-      <c r="C55" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D55" s="30" t="s">
+      <c r="F55" s="32" t="s">
         <v>129</v>
       </c>
-      <c r="E55" s="26" t="s">
+      <c r="G55" s="50" t="s">
         <v>130</v>
-      </c>
-      <c r="F55" s="32" t="s">
-        <v>131</v>
-      </c>
-      <c r="G55" s="50" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="56" ht="15.75" spans="1:7">
@@ -3679,20 +3585,20 @@
         <v>55</v>
       </c>
       <c r="B56" s="25" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C56" s="25" t="s">
         <v>8</v>
       </c>
       <c r="D56" s="30" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E56" s="35"/>
       <c r="F56" s="27" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="G56" s="28" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="57" ht="15.75" spans="1:7">
@@ -3700,13 +3606,13 @@
         <v>56</v>
       </c>
       <c r="B57" s="25" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C57" s="25" t="s">
         <v>8</v>
       </c>
       <c r="D57" s="30" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E57" s="31"/>
       <c r="F57" s="36"/>
@@ -3717,22 +3623,22 @@
         <v>57</v>
       </c>
       <c r="B58" s="25" t="s">
+        <v>135</v>
+      </c>
+      <c r="C58" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D58" s="30" t="s">
+        <v>127</v>
+      </c>
+      <c r="E58" s="30" t="s">
+        <v>136</v>
+      </c>
+      <c r="F58" s="32" t="s">
         <v>137</v>
       </c>
-      <c r="C58" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D58" s="30" t="s">
-        <v>129</v>
-      </c>
-      <c r="E58" s="30" t="s">
+      <c r="G58" s="28" t="s">
         <v>138</v>
-      </c>
-      <c r="F58" s="32" t="s">
-        <v>139</v>
-      </c>
-      <c r="G58" s="28" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="59" ht="15.75" spans="1:7">
@@ -3740,22 +3646,22 @@
         <v>58</v>
       </c>
       <c r="B59" s="25" t="s">
+        <v>139</v>
+      </c>
+      <c r="C59" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D59" s="30" t="s">
+        <v>127</v>
+      </c>
+      <c r="E59" s="30" t="s">
+        <v>140</v>
+      </c>
+      <c r="F59" s="32" t="s">
         <v>141</v>
       </c>
-      <c r="C59" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D59" s="30" t="s">
-        <v>129</v>
-      </c>
-      <c r="E59" s="30" t="s">
+      <c r="G59" s="28" t="s">
         <v>142</v>
-      </c>
-      <c r="F59" s="32" t="s">
-        <v>143</v>
-      </c>
-      <c r="G59" s="28" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="60" ht="15.75" spans="1:7">
@@ -3763,22 +3669,22 @@
         <v>59</v>
       </c>
       <c r="B60" s="25" t="s">
+        <v>143</v>
+      </c>
+      <c r="C60" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D60" s="26" t="s">
+        <v>127</v>
+      </c>
+      <c r="E60" s="26" t="s">
+        <v>140</v>
+      </c>
+      <c r="F60" s="32" t="s">
+        <v>144</v>
+      </c>
+      <c r="G60" s="28" t="s">
         <v>145</v>
-      </c>
-      <c r="C60" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D60" s="26" t="s">
-        <v>129</v>
-      </c>
-      <c r="E60" s="26" t="s">
-        <v>142</v>
-      </c>
-      <c r="F60" s="32" t="s">
-        <v>146</v>
-      </c>
-      <c r="G60" s="28" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="61" ht="15.75" spans="1:7">
@@ -3786,22 +3692,22 @@
         <v>60</v>
       </c>
       <c r="B61" s="25" t="s">
+        <v>146</v>
+      </c>
+      <c r="C61" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D61" s="26" t="s">
+        <v>127</v>
+      </c>
+      <c r="E61" s="37" t="s">
+        <v>136</v>
+      </c>
+      <c r="F61" s="32" t="s">
+        <v>147</v>
+      </c>
+      <c r="G61" s="28" t="s">
         <v>148</v>
-      </c>
-      <c r="C61" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D61" s="26" t="s">
-        <v>129</v>
-      </c>
-      <c r="E61" s="37" t="s">
-        <v>138</v>
-      </c>
-      <c r="F61" s="32" t="s">
-        <v>149</v>
-      </c>
-      <c r="G61" s="28" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="62" ht="15.75" spans="1:7">
@@ -3809,20 +3715,20 @@
         <v>61</v>
       </c>
       <c r="B62" s="25" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C62" s="25" t="s">
         <v>8</v>
       </c>
       <c r="D62" s="38" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E62" s="39"/>
       <c r="F62" s="32" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="G62" s="40" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="63" ht="31.5" spans="1:7">
@@ -3830,20 +3736,20 @@
         <v>62</v>
       </c>
       <c r="B63" s="25" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C63" s="25" t="s">
         <v>8</v>
       </c>
       <c r="D63" s="30" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E63" s="31"/>
       <c r="F63" s="41" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="G63" s="28" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="64" ht="15.75" spans="1:7">
@@ -3851,20 +3757,20 @@
         <v>63</v>
       </c>
       <c r="B64" s="25" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C64" s="25" t="s">
         <v>8</v>
       </c>
       <c r="D64" s="26" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E64" s="37"/>
       <c r="F64" s="32" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="G64" s="28" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="65" ht="15.75" spans="1:7">
@@ -3872,22 +3778,22 @@
         <v>64</v>
       </c>
       <c r="B65" s="25" t="s">
+        <v>158</v>
+      </c>
+      <c r="C65" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D65" s="42" t="s">
+        <v>127</v>
+      </c>
+      <c r="E65" s="42" t="s">
+        <v>136</v>
+      </c>
+      <c r="F65" s="43" t="s">
+        <v>159</v>
+      </c>
+      <c r="G65" s="50" t="s">
         <v>160</v>
-      </c>
-      <c r="C65" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D65" s="42" t="s">
-        <v>129</v>
-      </c>
-      <c r="E65" s="42" t="s">
-        <v>138</v>
-      </c>
-      <c r="F65" s="43" t="s">
-        <v>161</v>
-      </c>
-      <c r="G65" s="50" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="66" ht="31.5" spans="1:7">
@@ -3895,20 +3801,20 @@
         <v>65</v>
       </c>
       <c r="B66" s="25" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C66" s="25" t="s">
         <v>8</v>
       </c>
       <c r="D66" s="26" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E66" s="34"/>
       <c r="F66" s="32" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="G66" s="28" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="67" ht="15.75" spans="1:7">
@@ -3916,20 +3822,20 @@
         <v>66</v>
       </c>
       <c r="B67" s="25" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C67" s="25" t="s">
         <v>8</v>
       </c>
       <c r="D67" s="26" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E67" s="37"/>
       <c r="F67" s="44" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="G67" s="28" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="68" ht="15.75" spans="1:7">
@@ -3937,20 +3843,20 @@
         <v>67</v>
       </c>
       <c r="B68" s="25" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C68" s="25" t="s">
         <v>8</v>
       </c>
       <c r="D68" s="26" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E68" s="34"/>
       <c r="F68" s="33" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="G68" s="51" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="69" ht="15.75" spans="1:7">
@@ -3958,22 +3864,22 @@
         <v>68</v>
       </c>
       <c r="B69" s="25" t="s">
+        <v>170</v>
+      </c>
+      <c r="C69" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D69" s="26" t="s">
+        <v>127</v>
+      </c>
+      <c r="E69" s="26" t="s">
+        <v>136</v>
+      </c>
+      <c r="F69" s="32" t="s">
+        <v>171</v>
+      </c>
+      <c r="G69" s="28" t="s">
         <v>172</v>
-      </c>
-      <c r="C69" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D69" s="26" t="s">
-        <v>129</v>
-      </c>
-      <c r="E69" s="26" t="s">
-        <v>138</v>
-      </c>
-      <c r="F69" s="32" t="s">
-        <v>173</v>
-      </c>
-      <c r="G69" s="28" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="70" ht="15.75" spans="1:7">
@@ -3981,20 +3887,20 @@
         <v>69</v>
       </c>
       <c r="B70" s="25" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C70" s="25" t="s">
         <v>8</v>
       </c>
       <c r="D70" s="26" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E70" s="26"/>
       <c r="F70" s="32" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="G70" s="50" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="71" ht="15.75" spans="1:7">
@@ -4002,20 +3908,20 @@
         <v>70</v>
       </c>
       <c r="B71" s="25" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C71" s="25" t="s">
         <v>8</v>
       </c>
       <c r="D71" s="26" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E71" s="26"/>
       <c r="F71" s="32" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="G71" s="50" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="72" ht="31.5" spans="1:7">
@@ -4023,20 +3929,20 @@
         <v>71</v>
       </c>
       <c r="B72" s="25" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C72" s="25" t="s">
         <v>8</v>
       </c>
       <c r="D72" s="30" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E72" s="26"/>
       <c r="F72" s="41" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="G72" s="50" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="73" ht="15.75" spans="1:7">
@@ -4044,20 +3950,20 @@
         <v>72</v>
       </c>
       <c r="B73" s="25" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C73" s="25" t="s">
         <v>8</v>
       </c>
       <c r="D73" s="26" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E73" s="26"/>
       <c r="F73" s="27" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="G73" s="50" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="74" ht="15.75" spans="1:7">
@@ -4065,22 +3971,22 @@
         <v>73</v>
       </c>
       <c r="B74" s="25" t="s">
+        <v>185</v>
+      </c>
+      <c r="C74" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D74" s="26" t="s">
+        <v>127</v>
+      </c>
+      <c r="E74" s="26" t="s">
+        <v>136</v>
+      </c>
+      <c r="F74" s="27" t="s">
+        <v>186</v>
+      </c>
+      <c r="G74" s="50" t="s">
         <v>187</v>
-      </c>
-      <c r="C74" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D74" s="26" t="s">
-        <v>129</v>
-      </c>
-      <c r="E74" s="26" t="s">
-        <v>138</v>
-      </c>
-      <c r="F74" s="27" t="s">
-        <v>188</v>
-      </c>
-      <c r="G74" s="50" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="75" ht="15.75" spans="1:7">
@@ -4088,20 +3994,20 @@
         <v>74</v>
       </c>
       <c r="B75" s="25" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C75" s="25" t="s">
         <v>8</v>
       </c>
       <c r="D75" s="26" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E75" s="26"/>
       <c r="F75" s="32" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="G75" s="28" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="76" ht="15.75" spans="1:7">
@@ -4109,22 +4015,22 @@
         <v>75</v>
       </c>
       <c r="B76" s="25" t="s">
+        <v>191</v>
+      </c>
+      <c r="C76" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D76" s="26" t="s">
+        <v>127</v>
+      </c>
+      <c r="E76" s="26" t="s">
+        <v>136</v>
+      </c>
+      <c r="F76" s="32" t="s">
+        <v>192</v>
+      </c>
+      <c r="G76" s="28" t="s">
         <v>193</v>
-      </c>
-      <c r="C76" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D76" s="26" t="s">
-        <v>129</v>
-      </c>
-      <c r="E76" s="26" t="s">
-        <v>138</v>
-      </c>
-      <c r="F76" s="32" t="s">
-        <v>194</v>
-      </c>
-      <c r="G76" s="28" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="77" ht="15.75" spans="1:7">
@@ -4132,20 +4038,20 @@
         <v>76</v>
       </c>
       <c r="B77" s="25" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C77" s="25" t="s">
         <v>8</v>
       </c>
       <c r="D77" s="26" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E77" s="26"/>
       <c r="F77" s="32" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="G77" s="50" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="78" ht="31.5" spans="1:7">
@@ -4153,22 +4059,22 @@
         <v>77</v>
       </c>
       <c r="B78" s="25" t="s">
+        <v>197</v>
+      </c>
+      <c r="C78" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D78" s="26" t="s">
+        <v>127</v>
+      </c>
+      <c r="E78" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="F78" s="32" t="s">
+        <v>198</v>
+      </c>
+      <c r="G78" s="28" t="s">
         <v>199</v>
-      </c>
-      <c r="C78" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D78" s="26" t="s">
-        <v>129</v>
-      </c>
-      <c r="E78" s="26" t="s">
-        <v>130</v>
-      </c>
-      <c r="F78" s="32" t="s">
-        <v>200</v>
-      </c>
-      <c r="G78" s="28" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="79" ht="15.75" spans="1:7">
@@ -4176,17 +4082,17 @@
         <v>78</v>
       </c>
       <c r="B79" s="25" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C79" s="25" t="s">
         <v>8</v>
       </c>
       <c r="D79" s="26" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E79" s="26"/>
       <c r="F79" s="32" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="G79" s="28"/>
     </row>
@@ -4195,22 +4101,22 @@
         <v>79</v>
       </c>
       <c r="B80" s="25" t="s">
+        <v>202</v>
+      </c>
+      <c r="C80" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D80" s="26" t="s">
+        <v>127</v>
+      </c>
+      <c r="E80" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="F80" s="32" t="s">
+        <v>203</v>
+      </c>
+      <c r="G80" s="50" t="s">
         <v>204</v>
-      </c>
-      <c r="C80" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D80" s="26" t="s">
-        <v>129</v>
-      </c>
-      <c r="E80" s="26" t="s">
-        <v>130</v>
-      </c>
-      <c r="F80" s="32" t="s">
-        <v>205</v>
-      </c>
-      <c r="G80" s="50" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="81" ht="15.75" spans="1:7">
@@ -4218,22 +4124,22 @@
         <v>80</v>
       </c>
       <c r="B81" s="25" t="s">
+        <v>205</v>
+      </c>
+      <c r="C81" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D81" s="26" t="s">
+        <v>127</v>
+      </c>
+      <c r="E81" s="26" t="s">
+        <v>136</v>
+      </c>
+      <c r="F81" s="32" t="s">
+        <v>206</v>
+      </c>
+      <c r="G81" s="28" t="s">
         <v>207</v>
-      </c>
-      <c r="C81" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D81" s="26" t="s">
-        <v>129</v>
-      </c>
-      <c r="E81" s="26" t="s">
-        <v>138</v>
-      </c>
-      <c r="F81" s="32" t="s">
-        <v>208</v>
-      </c>
-      <c r="G81" s="28" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="82" ht="15.75" spans="1:7">
@@ -4241,19 +4147,19 @@
         <v>81</v>
       </c>
       <c r="B82" s="25" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C82" s="25" t="s">
         <v>8</v>
       </c>
       <c r="D82" s="26" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E82" s="26" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="F82" s="32" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="G82" s="28"/>
     </row>
@@ -4262,20 +4168,20 @@
         <v>82</v>
       </c>
       <c r="B83" s="25" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C83" s="25" t="s">
         <v>8</v>
       </c>
       <c r="D83" s="26" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E83" s="26"/>
       <c r="F83" s="33" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="G83" s="28" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="84" ht="15.75" spans="1:7">
@@ -4283,22 +4189,22 @@
         <v>83</v>
       </c>
       <c r="B84" s="25" t="s">
+        <v>213</v>
+      </c>
+      <c r="C84" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D84" s="26" t="s">
+        <v>127</v>
+      </c>
+      <c r="E84" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="F84" s="32" t="s">
+        <v>214</v>
+      </c>
+      <c r="G84" s="28" t="s">
         <v>215</v>
-      </c>
-      <c r="C84" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D84" s="26" t="s">
-        <v>129</v>
-      </c>
-      <c r="E84" s="26" t="s">
-        <v>130</v>
-      </c>
-      <c r="F84" s="32" t="s">
-        <v>216</v>
-      </c>
-      <c r="G84" s="28" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="85" ht="15.75" spans="1:7">
@@ -4306,17 +4212,17 @@
         <v>84</v>
       </c>
       <c r="B85" s="25" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C85" s="25" t="s">
         <v>8</v>
       </c>
       <c r="D85" s="26" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E85" s="34"/>
       <c r="F85" s="32" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="G85" s="28"/>
     </row>
@@ -4325,22 +4231,22 @@
         <v>85</v>
       </c>
       <c r="B86" s="25" t="s">
+        <v>218</v>
+      </c>
+      <c r="C86" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D86" s="26" t="s">
+        <v>127</v>
+      </c>
+      <c r="E86" s="34" t="s">
+        <v>140</v>
+      </c>
+      <c r="F86" s="45" t="s">
+        <v>219</v>
+      </c>
+      <c r="G86" s="28" t="s">
         <v>220</v>
-      </c>
-      <c r="C86" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D86" s="26" t="s">
-        <v>129</v>
-      </c>
-      <c r="E86" s="34" t="s">
-        <v>142</v>
-      </c>
-      <c r="F86" s="45" t="s">
-        <v>221</v>
-      </c>
-      <c r="G86" s="28" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="87" ht="15.75" spans="1:7">
@@ -4348,41 +4254,39 @@
         <v>86</v>
       </c>
       <c r="B87" s="25" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C87" s="25" t="s">
         <v>8</v>
       </c>
       <c r="D87" s="30" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E87" s="34"/>
       <c r="F87" s="32" t="s">
-        <v>224</v>
-      </c>
-      <c r="G87" s="28" t="s">
-        <v>15</v>
-      </c>
+        <v>222</v>
+      </c>
+      <c r="G87" s="28"/>
     </row>
     <row r="88" ht="15.75" spans="1:7">
       <c r="A88" s="24">
         <v>87</v>
       </c>
       <c r="B88" s="25" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C88" s="25" t="s">
         <v>8</v>
       </c>
       <c r="D88" s="26" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E88" s="34"/>
       <c r="F88" s="32" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G88" s="28" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="89" ht="15.75" spans="1:7">
@@ -4390,20 +4294,20 @@
         <v>88</v>
       </c>
       <c r="B89" s="25" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C89" s="25" t="s">
         <v>8</v>
       </c>
       <c r="D89" s="26" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E89" s="37"/>
       <c r="F89" s="32" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="G89" s="28" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="90" ht="15.75" spans="1:7">
@@ -4411,20 +4315,20 @@
         <v>89</v>
       </c>
       <c r="B90" s="25" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C90" s="25" t="s">
         <v>8</v>
       </c>
       <c r="D90" s="26" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E90" s="26"/>
       <c r="F90" s="32" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="G90" s="50" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="91" ht="15.75" spans="1:7">
@@ -4432,22 +4336,22 @@
         <v>90</v>
       </c>
       <c r="B91" s="25" t="s">
+        <v>232</v>
+      </c>
+      <c r="C91" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D91" s="26" t="s">
+        <v>127</v>
+      </c>
+      <c r="E91" s="26" t="s">
+        <v>140</v>
+      </c>
+      <c r="F91" s="32" t="s">
+        <v>233</v>
+      </c>
+      <c r="G91" s="28" t="s">
         <v>234</v>
-      </c>
-      <c r="C91" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D91" s="26" t="s">
-        <v>129</v>
-      </c>
-      <c r="E91" s="26" t="s">
-        <v>142</v>
-      </c>
-      <c r="F91" s="32" t="s">
-        <v>235</v>
-      </c>
-      <c r="G91" s="28" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="92" ht="15.75" spans="1:7">
@@ -4455,20 +4359,20 @@
         <v>91</v>
       </c>
       <c r="B92" s="25" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C92" s="25" t="s">
         <v>8</v>
       </c>
       <c r="D92" s="26" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E92" s="26"/>
       <c r="F92" s="32" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="G92" s="50" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="93" ht="15.75" spans="1:7">
@@ -4476,22 +4380,22 @@
         <v>92</v>
       </c>
       <c r="B93" s="25" t="s">
+        <v>238</v>
+      </c>
+      <c r="C93" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D93" s="26" t="s">
+        <v>127</v>
+      </c>
+      <c r="E93" s="26" t="s">
+        <v>239</v>
+      </c>
+      <c r="F93" s="32" t="s">
         <v>240</v>
       </c>
-      <c r="C93" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D93" s="26" t="s">
-        <v>129</v>
-      </c>
-      <c r="E93" s="26" t="s">
+      <c r="G93" s="50" t="s">
         <v>241</v>
-      </c>
-      <c r="F93" s="32" t="s">
-        <v>242</v>
-      </c>
-      <c r="G93" s="50" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="94" ht="15.75" spans="1:7">
@@ -4499,20 +4403,20 @@
         <v>93</v>
       </c>
       <c r="B94" s="25" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C94" s="25" t="s">
         <v>8</v>
       </c>
       <c r="D94" s="26" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E94" s="26"/>
       <c r="F94" s="32" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="G94" s="28" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="95" ht="15.75" spans="1:7">
@@ -4520,22 +4424,22 @@
         <v>94</v>
       </c>
       <c r="B95" s="25" t="s">
+        <v>245</v>
+      </c>
+      <c r="C95" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D95" s="26" t="s">
+        <v>127</v>
+      </c>
+      <c r="E95" s="26" t="s">
+        <v>136</v>
+      </c>
+      <c r="F95" s="45" t="s">
+        <v>246</v>
+      </c>
+      <c r="G95" s="50" t="s">
         <v>247</v>
-      </c>
-      <c r="C95" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D95" s="26" t="s">
-        <v>129</v>
-      </c>
-      <c r="E95" s="26" t="s">
-        <v>138</v>
-      </c>
-      <c r="F95" s="45" t="s">
-        <v>248</v>
-      </c>
-      <c r="G95" s="50" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="96" ht="15.75" spans="1:7">
@@ -4543,20 +4447,20 @@
         <v>95</v>
       </c>
       <c r="B96" s="25" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C96" s="25" t="s">
         <v>8</v>
       </c>
       <c r="D96" s="26" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E96" s="26"/>
       <c r="F96" s="32" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="G96" s="28" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="97" ht="31.5" spans="1:7">
@@ -4564,22 +4468,22 @@
         <v>96</v>
       </c>
       <c r="B97" s="25" t="s">
+        <v>251</v>
+      </c>
+      <c r="C97" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D97" s="30" t="s">
+        <v>127</v>
+      </c>
+      <c r="E97" s="26" t="s">
+        <v>252</v>
+      </c>
+      <c r="F97" s="32" t="s">
         <v>253</v>
       </c>
-      <c r="C97" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D97" s="30" t="s">
-        <v>129</v>
-      </c>
-      <c r="E97" s="26" t="s">
+      <c r="G97" s="28" t="s">
         <v>254</v>
-      </c>
-      <c r="F97" s="32" t="s">
-        <v>255</v>
-      </c>
-      <c r="G97" s="28" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="98" ht="15.75" spans="1:7">
@@ -4587,22 +4491,22 @@
         <v>97</v>
       </c>
       <c r="B98" s="25" t="s">
+        <v>255</v>
+      </c>
+      <c r="C98" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D98" s="26" t="s">
+        <v>127</v>
+      </c>
+      <c r="E98" s="26" t="s">
+        <v>140</v>
+      </c>
+      <c r="F98" s="32" t="s">
+        <v>256</v>
+      </c>
+      <c r="G98" s="28" t="s">
         <v>257</v>
-      </c>
-      <c r="C98" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D98" s="26" t="s">
-        <v>129</v>
-      </c>
-      <c r="E98" s="26" t="s">
-        <v>142</v>
-      </c>
-      <c r="F98" s="32" t="s">
-        <v>258</v>
-      </c>
-      <c r="G98" s="28" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="99" ht="15.75" spans="1:7">
@@ -4610,22 +4514,22 @@
         <v>98</v>
       </c>
       <c r="B99" s="25" t="s">
+        <v>258</v>
+      </c>
+      <c r="C99" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D99" s="26" t="s">
+        <v>127</v>
+      </c>
+      <c r="E99" s="26" t="s">
+        <v>136</v>
+      </c>
+      <c r="F99" s="32" t="s">
+        <v>259</v>
+      </c>
+      <c r="G99" s="28" t="s">
         <v>260</v>
-      </c>
-      <c r="C99" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D99" s="26" t="s">
-        <v>129</v>
-      </c>
-      <c r="E99" s="26" t="s">
-        <v>138</v>
-      </c>
-      <c r="F99" s="32" t="s">
-        <v>261</v>
-      </c>
-      <c r="G99" s="28" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="100" ht="15.75" spans="1:7">
@@ -4633,13 +4537,13 @@
         <v>99</v>
       </c>
       <c r="B100" s="25" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C100" s="25" t="s">
         <v>8</v>
       </c>
       <c r="D100" s="26" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E100" s="26"/>
       <c r="F100" s="32"/>
@@ -4650,20 +4554,20 @@
         <v>100</v>
       </c>
       <c r="B101" s="25" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C101" s="25" t="s">
         <v>8</v>
       </c>
       <c r="D101" s="26" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E101" s="37"/>
       <c r="F101" s="27" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="G101" s="28" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="102" ht="15.75" spans="1:7">
@@ -4671,17 +4575,17 @@
         <v>101</v>
       </c>
       <c r="B102" s="25" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C102" s="25" t="s">
         <v>8</v>
       </c>
       <c r="D102" s="26" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E102" s="34"/>
       <c r="F102" s="27" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="G102" s="28"/>
     </row>
@@ -4690,20 +4594,20 @@
         <v>102</v>
       </c>
       <c r="B103" s="25" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C103" s="25" t="s">
         <v>8</v>
       </c>
       <c r="D103" s="26" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E103" s="37"/>
       <c r="F103" s="32" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="G103" s="28" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="104" ht="15.75" spans="1:7">
@@ -4711,22 +4615,22 @@
         <v>103</v>
       </c>
       <c r="B104" s="25" t="s">
+        <v>270</v>
+      </c>
+      <c r="C104" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D104" s="26" t="s">
+        <v>127</v>
+      </c>
+      <c r="E104" s="26" t="s">
+        <v>136</v>
+      </c>
+      <c r="F104" s="32" t="s">
+        <v>271</v>
+      </c>
+      <c r="G104" s="28" t="s">
         <v>272</v>
-      </c>
-      <c r="C104" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D104" s="26" t="s">
-        <v>129</v>
-      </c>
-      <c r="E104" s="26" t="s">
-        <v>138</v>
-      </c>
-      <c r="F104" s="32" t="s">
-        <v>273</v>
-      </c>
-      <c r="G104" s="28" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="105" ht="15.75" spans="1:7">
@@ -4734,20 +4638,20 @@
         <v>104</v>
       </c>
       <c r="B105" s="25" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C105" s="25" t="s">
         <v>8</v>
       </c>
       <c r="D105" s="26" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E105" s="37"/>
       <c r="F105" s="32" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="G105" s="28" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="106" ht="15.75" spans="1:7">
@@ -4755,22 +4659,22 @@
         <v>105</v>
       </c>
       <c r="B106" s="25" t="s">
+        <v>276</v>
+      </c>
+      <c r="C106" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D106" s="26" t="s">
+        <v>127</v>
+      </c>
+      <c r="E106" s="26" t="s">
+        <v>140</v>
+      </c>
+      <c r="F106" s="32" t="s">
+        <v>277</v>
+      </c>
+      <c r="G106" s="51" t="s">
         <v>278</v>
-      </c>
-      <c r="C106" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D106" s="26" t="s">
-        <v>129</v>
-      </c>
-      <c r="E106" s="26" t="s">
-        <v>142</v>
-      </c>
-      <c r="F106" s="32" t="s">
-        <v>279</v>
-      </c>
-      <c r="G106" s="51" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="107" ht="15.75" spans="1:7">
@@ -4778,405 +4682,447 @@
         <v>106</v>
       </c>
       <c r="B107" s="25" t="s">
+        <v>279</v>
+      </c>
+      <c r="C107" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D107" s="26" t="s">
+        <v>127</v>
+      </c>
+      <c r="E107" s="26" t="s">
+        <v>280</v>
+      </c>
+      <c r="F107" s="32" t="s">
         <v>281</v>
       </c>
-      <c r="C107" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D107" s="26" t="s">
-        <v>129</v>
-      </c>
-      <c r="E107" s="26" t="s">
+      <c r="G107" s="28"/>
+    </row>
+    <row r="108" ht="15.75" spans="1:7">
+      <c r="A108" s="24">
+        <v>107</v>
+      </c>
+      <c r="B108" s="25" t="s">
         <v>282</v>
       </c>
-      <c r="F107" s="32" t="s">
-        <v>283</v>
-      </c>
-      <c r="G107" s="28"/>
-    </row>
-    <row r="108" ht="15.75" spans="1:7">
-      <c r="A108" s="24"/>
-      <c r="B108" s="25" t="s">
-        <v>284</v>
-      </c>
       <c r="C108" s="25" t="s">
         <v>8</v>
       </c>
       <c r="D108" s="46" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E108" s="47"/>
       <c r="F108" s="48" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G108" s="29"/>
     </row>
     <row r="109" ht="15.75" spans="1:7">
-      <c r="A109" s="24"/>
+      <c r="A109" s="24">
+        <v>108</v>
+      </c>
       <c r="B109" s="25" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C109" s="25" t="s">
         <v>8</v>
       </c>
       <c r="D109" s="46" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E109" s="47"/>
       <c r="F109" s="48" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="G109" s="29"/>
     </row>
     <row r="110" ht="31.5" spans="1:7">
-      <c r="A110" s="24"/>
+      <c r="A110" s="24">
+        <v>109</v>
+      </c>
       <c r="B110" s="25" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C110" s="25" t="s">
         <v>8</v>
       </c>
       <c r="D110" s="46" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E110" s="47"/>
       <c r="F110" s="48" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="G110" s="29"/>
     </row>
     <row r="111" ht="15.75" spans="1:7">
-      <c r="A111" s="24"/>
+      <c r="A111" s="24">
+        <v>110</v>
+      </c>
       <c r="B111" s="25" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C111" s="25" t="s">
         <v>8</v>
       </c>
       <c r="D111" s="46" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E111" s="47"/>
       <c r="F111" s="48" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="G111" s="29"/>
     </row>
     <row r="112" ht="31.5" spans="1:7">
-      <c r="A112" s="24"/>
+      <c r="A112" s="24">
+        <v>111</v>
+      </c>
       <c r="B112" s="25" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C112" s="25" t="s">
         <v>8</v>
       </c>
       <c r="D112" s="46" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E112" s="47"/>
       <c r="F112" s="48" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="G112" s="29"/>
     </row>
     <row r="113" ht="15.75" spans="1:7">
-      <c r="A113" s="24"/>
+      <c r="A113" s="24">
+        <v>112</v>
+      </c>
       <c r="B113" s="25" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C113" s="25" t="s">
         <v>8</v>
       </c>
       <c r="D113" s="46" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E113" s="47"/>
       <c r="F113" s="48" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="G113" s="29"/>
     </row>
     <row r="114" ht="15.75" spans="1:7">
-      <c r="A114" s="24"/>
+      <c r="A114" s="24">
+        <v>113</v>
+      </c>
       <c r="B114" s="25" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C114" s="25" t="s">
         <v>8</v>
       </c>
       <c r="D114" s="46" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E114" s="47"/>
       <c r="F114" s="48" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="G114" s="29"/>
     </row>
     <row r="115" s="15" customFormat="1" ht="15.75" spans="1:7">
-      <c r="A115" s="24"/>
+      <c r="A115" s="24">
+        <v>114</v>
+      </c>
       <c r="B115" s="25" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C115" s="25" t="s">
         <v>8</v>
       </c>
       <c r="D115" s="46" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E115" s="47"/>
       <c r="F115" s="48" t="s">
+        <v>296</v>
+      </c>
+      <c r="G115" s="29"/>
+    </row>
+    <row r="116" ht="15.75" spans="1:7">
+      <c r="A116" s="24">
+        <v>115</v>
+      </c>
+      <c r="B116" s="25" t="s">
+        <v>297</v>
+      </c>
+      <c r="C116" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D116" s="46" t="s">
+        <v>127</v>
+      </c>
+      <c r="E116" s="46" t="s">
+        <v>140</v>
+      </c>
+      <c r="F116" s="48" t="s">
         <v>298</v>
       </c>
-      <c r="G115" s="29"/>
-    </row>
-    <row r="116" ht="15.75" spans="1:7">
-      <c r="A116" s="24"/>
-      <c r="B116" s="25" t="s">
+      <c r="G116" s="29"/>
+    </row>
+    <row r="117" ht="15.75" spans="1:7">
+      <c r="A117" s="24">
+        <v>116</v>
+      </c>
+      <c r="B117" s="25" t="s">
         <v>299</v>
       </c>
-      <c r="C116" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D116" s="46" t="s">
-        <v>129</v>
-      </c>
-      <c r="E116" s="46" t="s">
-        <v>142</v>
-      </c>
-      <c r="F116" s="48" t="s">
-        <v>300</v>
-      </c>
-      <c r="G116" s="29"/>
-    </row>
-    <row r="117" ht="15.75" spans="1:7">
-      <c r="A117" s="24"/>
-      <c r="B117" s="25" t="s">
-        <v>301</v>
-      </c>
       <c r="C117" s="25" t="s">
         <v>8</v>
       </c>
       <c r="D117" s="46" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E117" s="47"/>
       <c r="F117" s="48" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="G117" s="29"/>
     </row>
     <row r="118" ht="15.75" spans="1:7">
-      <c r="A118" s="24"/>
+      <c r="A118" s="24">
+        <v>117</v>
+      </c>
       <c r="B118" s="25" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C118" s="25" t="s">
         <v>8</v>
       </c>
       <c r="D118" s="46" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E118" s="47"/>
       <c r="F118" s="48" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="G118" s="29"/>
     </row>
     <row r="119" ht="15.75" spans="1:7">
-      <c r="A119" s="24"/>
+      <c r="A119" s="24">
+        <v>118</v>
+      </c>
       <c r="B119" s="25" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C119" s="25" t="s">
         <v>8</v>
       </c>
       <c r="D119" s="46" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E119" s="47"/>
       <c r="F119" s="48" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="G119" s="29"/>
     </row>
     <row r="120" ht="15.75" spans="1:7">
-      <c r="A120" s="24"/>
+      <c r="A120" s="24">
+        <v>119</v>
+      </c>
       <c r="B120" s="25" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C120" s="25" t="s">
         <v>8</v>
       </c>
       <c r="D120" s="46" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E120" s="47"/>
       <c r="F120" s="48" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="G120" s="29"/>
     </row>
     <row r="121" ht="15.75" spans="1:7">
-      <c r="A121" s="24"/>
+      <c r="A121" s="24">
+        <v>120</v>
+      </c>
       <c r="B121" s="25" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C121" s="25" t="s">
         <v>8</v>
       </c>
       <c r="D121" s="46" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E121" s="47"/>
       <c r="F121" s="48" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="G121" s="29"/>
     </row>
     <row r="122" ht="15.75" spans="1:7">
-      <c r="A122" s="24"/>
+      <c r="A122" s="24">
+        <v>121</v>
+      </c>
       <c r="B122" s="25" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C122" s="25" t="s">
         <v>8</v>
       </c>
       <c r="D122" s="46" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E122" s="47"/>
       <c r="F122" s="48" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="G122" s="29"/>
     </row>
     <row r="123" ht="15.75" spans="1:7">
-      <c r="A123" s="24"/>
+      <c r="A123" s="24">
+        <v>122</v>
+      </c>
       <c r="B123" s="25" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C123" s="25" t="s">
         <v>8</v>
       </c>
       <c r="D123" s="46" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E123" s="47"/>
       <c r="F123" s="48" t="s">
-        <v>314</v>
-      </c>
-      <c r="G123" s="49" t="s">
-        <v>108</v>
-      </c>
+        <v>312</v>
+      </c>
+      <c r="G123" s="49"/>
     </row>
     <row r="124" ht="15.75" spans="1:7">
-      <c r="A124" s="24"/>
+      <c r="A124" s="24">
+        <v>123</v>
+      </c>
       <c r="B124" s="25" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C124" s="25" t="s">
         <v>8</v>
       </c>
       <c r="D124" s="46" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E124" s="47"/>
       <c r="F124" s="48" t="s">
+        <v>314</v>
+      </c>
+      <c r="G124" s="29"/>
+    </row>
+    <row r="125" ht="15.75" spans="1:7">
+      <c r="A125" s="24">
+        <v>124</v>
+      </c>
+      <c r="B125" s="25" t="s">
+        <v>315</v>
+      </c>
+      <c r="C125" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D125" s="46" t="s">
         <v>316</v>
-      </c>
-      <c r="G124" s="29"/>
-    </row>
-    <row r="125" ht="15.75" spans="1:7">
-      <c r="A125" s="24"/>
-      <c r="B125" s="25" t="s">
-        <v>317</v>
-      </c>
-      <c r="C125" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D125" s="46" t="s">
-        <v>318</v>
       </c>
       <c r="E125" s="46" t="s">
         <v>10</v>
       </c>
       <c r="F125" s="48" t="s">
+        <v>317</v>
+      </c>
+      <c r="G125" s="29"/>
+    </row>
+    <row r="126" ht="31.5" spans="1:7">
+      <c r="A126" s="24">
+        <v>125</v>
+      </c>
+      <c r="B126" s="25" t="s">
+        <v>318</v>
+      </c>
+      <c r="C126" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D126" s="46" t="s">
         <v>319</v>
       </c>
-      <c r="G125" s="29"/>
-    </row>
-    <row r="126" ht="31.5" spans="1:7">
-      <c r="A126" s="24"/>
-      <c r="B126" s="25" t="s">
+      <c r="E126" s="46" t="s">
+        <v>29</v>
+      </c>
+      <c r="F126" s="48" t="s">
         <v>320</v>
       </c>
-      <c r="C126" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D126" s="46" t="s">
+      <c r="G126" s="29"/>
+    </row>
+    <row r="127" ht="15.75" spans="1:7">
+      <c r="A127" s="24">
+        <v>126</v>
+      </c>
+      <c r="B127" s="25" t="s">
         <v>321</v>
       </c>
-      <c r="E126" s="46" t="s">
-        <v>31</v>
-      </c>
-      <c r="F126" s="48" t="s">
-        <v>322</v>
-      </c>
-      <c r="G126" s="29"/>
-    </row>
-    <row r="127" ht="15.75" spans="1:7">
-      <c r="A127" s="24"/>
-      <c r="B127" s="25" t="s">
-        <v>323</v>
-      </c>
       <c r="C127" s="25" t="s">
         <v>8</v>
       </c>
       <c r="D127" s="46" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E127" s="47"/>
       <c r="F127" s="48" t="s">
+        <v>322</v>
+      </c>
+      <c r="G127" s="29"/>
+    </row>
+    <row r="128" ht="31.5" spans="1:7">
+      <c r="A128" s="24">
+        <v>127</v>
+      </c>
+      <c r="B128" s="25" t="s">
+        <v>323</v>
+      </c>
+      <c r="C128" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D128" s="46" t="s">
         <v>324</v>
       </c>
-      <c r="G127" s="29"/>
-    </row>
-    <row r="128" ht="31.5" spans="1:7">
-      <c r="A128" s="24"/>
-      <c r="B128" s="25" t="s">
+      <c r="E128" s="47" t="s">
+        <v>29</v>
+      </c>
+      <c r="F128" s="48" t="s">
         <v>325</v>
       </c>
-      <c r="C128" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D128" s="46" t="s">
+      <c r="G128" s="29"/>
+    </row>
+    <row r="129" ht="31.5" spans="1:7">
+      <c r="A129" s="24">
+        <v>128</v>
+      </c>
+      <c r="B129" s="25" t="s">
         <v>326</v>
       </c>
-      <c r="E128" s="47" t="s">
-        <v>31</v>
-      </c>
-      <c r="F128" s="48" t="s">
+      <c r="C129" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D129" s="46" t="s">
+        <v>324</v>
+      </c>
+      <c r="E129" s="47" t="s">
+        <v>29</v>
+      </c>
+      <c r="F129" s="48" t="s">
         <v>327</v>
-      </c>
-      <c r="G128" s="29"/>
-    </row>
-    <row r="129" ht="31.5" spans="1:7">
-      <c r="A129" s="24"/>
-      <c r="B129" s="25" t="s">
-        <v>328</v>
-      </c>
-      <c r="C129" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D129" s="46" t="s">
-        <v>326</v>
-      </c>
-      <c r="E129" s="47" t="s">
-        <v>31</v>
-      </c>
-      <c r="F129" s="48" t="s">
-        <v>329</v>
       </c>
       <c r="G129" s="29"/>
     </row>
@@ -9333,7 +9279,7 @@
       <c r="D1167" s="17"/>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G128" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G129" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <hyperlinks>
@@ -9377,6 +9323,7 @@
     <hyperlink ref="F63" r:id="rId38" display="lakhdar_belhallouche@hotmail.fr"/>
     <hyperlink ref="F83" r:id="rId39" display="ahmed.hadji22@yahoo.com"/>
     <hyperlink ref="F106" r:id="rId40" display="berhenen@yahoo.fr"/>
+    <hyperlink ref="F32" r:id="rId41" display="khatir.mohamed1977@gmail.com"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
@@ -9399,202 +9346,202 @@
   <sheetData>
     <row r="1" ht="15.75" spans="1:4">
       <c r="A1" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>331</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>332</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>333</v>
       </c>
     </row>
     <row r="2" ht="15.75" spans="1:4">
       <c r="A2" s="4" t="s">
+        <v>332</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="C2" s="6" t="s">
         <v>334</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="D2" s="7" t="s">
         <v>335</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>336</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>337</v>
       </c>
     </row>
     <row r="3" ht="15.75" spans="1:4">
       <c r="A3" s="8"/>
       <c r="B3" s="5" t="s">
+        <v>336</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>337</v>
+      </c>
+      <c r="D3" s="7" t="s">
         <v>338</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>339</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>340</v>
       </c>
     </row>
     <row r="4" ht="15.75" spans="1:4">
       <c r="A4" s="8"/>
       <c r="B4" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>340</v>
+      </c>
+      <c r="D4" s="7" t="s">
         <v>341</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>342</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>343</v>
       </c>
     </row>
     <row r="5" ht="15.75" spans="1:4">
       <c r="A5" s="8"/>
       <c r="B5" s="5" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
     </row>
     <row r="6" ht="15.75" spans="1:4">
       <c r="A6" s="8"/>
       <c r="B6" s="5" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="7" ht="15.75" spans="1:4">
       <c r="A7" s="9" t="s">
+        <v>346</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>347</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>337</v>
+      </c>
+      <c r="D7" s="7" t="s">
         <v>348</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>349</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>339</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="8" ht="15.75" spans="1:4">
       <c r="A8" s="8"/>
       <c r="B8" s="10" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="9" ht="15.75" spans="1:4">
       <c r="A9" s="11" t="s">
+        <v>350</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="D9" s="7" t="s">
         <v>352</v>
-      </c>
-      <c r="B9" s="12" t="s">
-        <v>353</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>336</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>354</v>
       </c>
     </row>
     <row r="10" ht="15.75" spans="1:4">
       <c r="A10" s="8"/>
       <c r="B10" s="13" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="11" ht="15.75" spans="1:4">
       <c r="A11" s="8"/>
       <c r="B11" s="13" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
     </row>
     <row r="12" ht="15.75" spans="1:4">
       <c r="A12" s="8"/>
       <c r="B12" s="13" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="13" ht="15.75" spans="1:4">
       <c r="A13" s="8"/>
       <c r="B13" s="13" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="14" ht="15.75" spans="1:4">
       <c r="A14" s="8"/>
       <c r="B14" s="13" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="15" ht="15.75" spans="1:4">
       <c r="A15" s="8"/>
       <c r="B15" s="13" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="16" ht="15.75" spans="1:4">
       <c r="A16" s="8"/>
       <c r="B16" s="13" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="656" ht="15.75"/>

--- a/Permanents-Vacataires-ELT2-2026-2027.xlsx
+++ b/Permanents-Vacataires-ELT2-2026-2027.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="702" uniqueCount="366">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="708" uniqueCount="369">
   <si>
     <t>N°</t>
   </si>
@@ -1016,6 +1016,15 @@
   </si>
   <si>
     <t xml:space="preserve">saidi_kheiro@yahoo.fr </t>
+  </si>
+  <si>
+    <t>ABBOU MAJDA</t>
+  </si>
+  <si>
+    <t>milouaf@yahoo.fr</t>
+  </si>
+  <si>
+    <t>0556831346</t>
   </si>
   <si>
     <t>CYCLE</t>
@@ -1194,16 +1203,16 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
-      <name val="Cambria"/>
+      <name val="Calibri"/>
       <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
       <color theme="10"/>
-      <name val="Calibri"/>
+      <name val="Cambria"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
@@ -1775,7 +1784,7 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -1947,18 +1956,12 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1969,18 +1972,18 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="6" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1992,14 +1995,14 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="6" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="6" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2019,17 +2022,17 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="6" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="6" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2038,11 +2041,17 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="6" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment vertical="center"/>
@@ -2402,158 +2411,158 @@
     <col min="1" max="1" width="7" style="16" customWidth="1"/>
     <col min="2" max="2" width="27.2857142857143" style="17" customWidth="1"/>
     <col min="3" max="3" width="29.7142857142857" style="17" customWidth="1"/>
-    <col min="4" max="4" width="19.1428571428571" style="18" customWidth="1"/>
-    <col min="5" max="5" width="21.552380952381" style="18" customWidth="1"/>
+    <col min="4" max="4" width="19.1428571428571" style="16" customWidth="1"/>
+    <col min="5" max="5" width="21.552380952381" style="16" customWidth="1"/>
     <col min="6" max="6" width="38.8571428571429" style="17" customWidth="1"/>
     <col min="7" max="7" width="18.2857142857143" style="17" customWidth="1"/>
-    <col min="8" max="16384" width="11" style="19"/>
+    <col min="8" max="16384" width="11" style="18"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" spans="1:7">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="21" t="s">
+      <c r="B1" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="21" t="s">
+      <c r="C1" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="21" t="s">
+      <c r="D1" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="22" t="s">
+      <c r="E1" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="23" t="s">
+      <c r="F1" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="23" t="s">
+      <c r="G1" s="21" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" ht="15.75" spans="1:7">
-      <c r="A2" s="24">
+      <c r="A2" s="22">
         <v>1</v>
       </c>
-      <c r="B2" s="25" t="s">
+      <c r="B2" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="26" t="s">
+      <c r="C2" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="26" t="s">
+      <c r="E2" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="27" t="s">
+      <c r="F2" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="28"/>
+      <c r="G2" s="25"/>
     </row>
     <row r="3" ht="15.75" spans="1:7">
-      <c r="A3" s="24">
+      <c r="A3" s="22">
         <v>2</v>
       </c>
-      <c r="B3" s="25" t="s">
+      <c r="B3" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="26" t="s">
+      <c r="C3" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="26" t="s">
+      <c r="E3" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="27" t="s">
+      <c r="F3" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="28"/>
+      <c r="G3" s="25"/>
     </row>
     <row r="4" ht="15.75" spans="1:7">
-      <c r="A4" s="24">
+      <c r="A4" s="22">
         <v>3</v>
       </c>
-      <c r="B4" s="25" t="s">
+      <c r="B4" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="26" t="s">
+      <c r="C4" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="26" t="s">
+      <c r="E4" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="27" t="s">
+      <c r="F4" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="G4" s="28"/>
+      <c r="G4" s="25"/>
     </row>
     <row r="5" ht="15.75" spans="1:7">
-      <c r="A5" s="24">
+      <c r="A5" s="22">
         <v>4</v>
       </c>
-      <c r="B5" s="25" t="s">
+      <c r="B5" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" s="26" t="s">
+      <c r="C5" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="26" t="s">
+      <c r="E5" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="27" t="s">
+      <c r="F5" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="G5" s="28"/>
+      <c r="G5" s="25"/>
     </row>
     <row r="6" ht="15.75" spans="1:7">
-      <c r="A6" s="24">
+      <c r="A6" s="22">
         <v>5</v>
       </c>
-      <c r="B6" s="25" t="s">
+      <c r="B6" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" s="26" t="s">
+      <c r="C6" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="E6" s="26" t="s">
+      <c r="E6" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="F6" s="27" t="s">
+      <c r="F6" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="G6" s="28"/>
+      <c r="G6" s="25"/>
     </row>
     <row r="7" ht="15.75" spans="1:7">
-      <c r="A7" s="24">
+      <c r="A7" s="22">
         <v>6</v>
       </c>
-      <c r="B7" s="25" t="s">
+      <c r="B7" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D7" s="26" t="s">
+      <c r="C7" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="E7" s="26" t="s">
+      <c r="E7" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="F7" s="27" t="s">
+      <c r="F7" s="24" t="s">
         <v>23</v>
       </c>
       <c r="G7" s="50" t="s">
@@ -2561,22 +2570,22 @@
       </c>
     </row>
     <row r="8" ht="15.75" spans="1:7">
-      <c r="A8" s="24">
+      <c r="A8" s="22">
         <v>7</v>
       </c>
-      <c r="B8" s="25" t="s">
+      <c r="B8" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D8" s="26" t="s">
+      <c r="C8" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="26" t="s">
+      <c r="E8" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="F8" s="27" t="s">
+      <c r="F8" s="24" t="s">
         <v>26</v>
       </c>
       <c r="G8" s="50" t="s">
@@ -2584,43 +2593,43 @@
       </c>
     </row>
     <row r="9" ht="15.75" spans="1:7">
-      <c r="A9" s="24">
-        <v>8</v>
-      </c>
-      <c r="B9" s="25" t="s">
+      <c r="A9" s="22">
+        <v>8</v>
+      </c>
+      <c r="B9" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="C9" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D9" s="26" t="s">
+      <c r="C9" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="E9" s="26" t="s">
+      <c r="E9" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="F9" s="27" t="s">
+      <c r="F9" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="G9" s="28"/>
+      <c r="G9" s="25"/>
     </row>
     <row r="10" ht="15.75" spans="1:7">
-      <c r="A10" s="24">
+      <c r="A10" s="22">
         <v>9</v>
       </c>
-      <c r="B10" s="25" t="s">
+      <c r="B10" s="23" t="s">
         <v>31</v>
       </c>
-      <c r="C10" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D10" s="30" t="s">
+      <c r="C10" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="E10" s="31" t="s">
+      <c r="E10" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="F10" s="32" t="s">
+      <c r="F10" s="30" t="s">
         <v>32</v>
       </c>
       <c r="G10" s="50" t="s">
@@ -2628,568 +2637,568 @@
       </c>
     </row>
     <row r="11" ht="15.75" spans="1:7">
-      <c r="A11" s="24">
+      <c r="A11" s="22">
         <v>10</v>
       </c>
-      <c r="B11" s="25" t="s">
+      <c r="B11" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="C11" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D11" s="26" t="s">
+      <c r="C11" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="E11" s="26" t="s">
+      <c r="E11" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="F11" s="33" t="s">
+      <c r="F11" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="G11" s="28"/>
+      <c r="G11" s="25"/>
     </row>
     <row r="12" ht="15.75" spans="1:7">
-      <c r="A12" s="24">
+      <c r="A12" s="22">
         <v>11</v>
       </c>
-      <c r="B12" s="25" t="s">
+      <c r="B12" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="C12" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D12" s="26" t="s">
+      <c r="C12" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="E12" s="26" t="s">
+      <c r="E12" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="F12" s="27" t="s">
+      <c r="F12" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="G12" s="28"/>
+      <c r="G12" s="25"/>
     </row>
     <row r="13" ht="15.75" spans="1:7">
-      <c r="A13" s="24">
+      <c r="A13" s="22">
         <v>12</v>
       </c>
-      <c r="B13" s="25" t="s">
+      <c r="B13" s="23" t="s">
         <v>38</v>
       </c>
-      <c r="C13" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D13" s="26" t="s">
+      <c r="C13" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="E13" s="26" t="s">
+      <c r="E13" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="F13" s="27" t="s">
+      <c r="F13" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="G13" s="28"/>
+      <c r="G13" s="25"/>
     </row>
     <row r="14" ht="15.75" spans="1:7">
-      <c r="A14" s="24">
+      <c r="A14" s="22">
         <v>13</v>
       </c>
-      <c r="B14" s="25" t="s">
+      <c r="B14" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="C14" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D14" s="26" t="s">
+      <c r="C14" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="E14" s="26" t="s">
+      <c r="E14" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="F14" s="27" t="s">
+      <c r="F14" s="26" t="s">
         <v>41</v>
       </c>
-      <c r="G14" s="28"/>
+      <c r="G14" s="25"/>
     </row>
     <row r="15" ht="15.75" spans="1:7">
-      <c r="A15" s="24">
+      <c r="A15" s="22">
         <v>14</v>
       </c>
-      <c r="B15" s="25" t="s">
+      <c r="B15" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="C15" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D15" s="26" t="s">
+      <c r="C15" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D15" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="E15" s="26" t="s">
+      <c r="E15" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="F15" s="27" t="s">
+      <c r="F15" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="G15" s="28"/>
+      <c r="G15" s="25"/>
     </row>
     <row r="16" ht="31.5" spans="1:7">
-      <c r="A16" s="24">
+      <c r="A16" s="22">
         <v>15</v>
       </c>
-      <c r="B16" s="25" t="s">
+      <c r="B16" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="C16" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D16" s="26" t="s">
+      <c r="C16" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="E16" s="26" t="s">
+      <c r="E16" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="F16" s="27" t="s">
+      <c r="F16" s="26" t="s">
         <v>45</v>
       </c>
-      <c r="G16" s="28"/>
+      <c r="G16" s="25"/>
     </row>
     <row r="17" ht="15.75" spans="1:7">
-      <c r="A17" s="24">
+      <c r="A17" s="22">
         <v>16</v>
       </c>
-      <c r="B17" s="25" t="s">
+      <c r="B17" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="C17" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D17" s="26" t="s">
+      <c r="C17" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="E17" s="26" t="s">
+      <c r="E17" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="F17" s="27" t="s">
+      <c r="F17" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="G17" s="28"/>
+      <c r="G17" s="25"/>
     </row>
     <row r="18" ht="15.75" spans="1:7">
-      <c r="A18" s="24">
+      <c r="A18" s="22">
         <v>17</v>
       </c>
-      <c r="B18" s="25" t="s">
+      <c r="B18" s="23" t="s">
         <v>49</v>
       </c>
-      <c r="C18" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D18" s="26" t="s">
+      <c r="C18" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="E18" s="26" t="s">
+      <c r="E18" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="F18" s="27" t="s">
+      <c r="F18" s="26" t="s">
         <v>50</v>
       </c>
-      <c r="G18" s="28"/>
+      <c r="G18" s="25"/>
     </row>
     <row r="19" ht="15.75" spans="1:7">
-      <c r="A19" s="24">
+      <c r="A19" s="22">
         <v>18</v>
       </c>
-      <c r="B19" s="25" t="s">
+      <c r="B19" s="23" t="s">
         <v>51</v>
       </c>
-      <c r="C19" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D19" s="26" t="s">
+      <c r="C19" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="E19" s="34" t="s">
+      <c r="E19" s="31" t="s">
         <v>47</v>
       </c>
       <c r="F19" s="32" t="s">
         <v>52</v>
       </c>
-      <c r="G19" s="28"/>
+      <c r="G19" s="25"/>
     </row>
     <row r="20" ht="31.5" spans="1:7">
-      <c r="A20" s="24">
+      <c r="A20" s="22">
         <v>19</v>
       </c>
-      <c r="B20" s="25" t="s">
+      <c r="B20" s="23" t="s">
         <v>53</v>
       </c>
-      <c r="C20" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D20" s="26" t="s">
+      <c r="C20" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D20" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="E20" s="26" t="s">
+      <c r="E20" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="F20" s="27" t="s">
+      <c r="F20" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="G20" s="28"/>
+      <c r="G20" s="25"/>
     </row>
     <row r="21" ht="15.75" spans="1:7">
-      <c r="A21" s="24">
+      <c r="A21" s="22">
         <v>20</v>
       </c>
-      <c r="B21" s="25" t="s">
+      <c r="B21" s="23" t="s">
         <v>55</v>
       </c>
-      <c r="C21" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D21" s="26" t="s">
+      <c r="C21" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="E21" s="26" t="s">
+      <c r="E21" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="F21" s="27" t="s">
+      <c r="F21" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="G21" s="28"/>
+      <c r="G21" s="25"/>
     </row>
     <row r="22" ht="15.75" spans="1:7">
-      <c r="A22" s="24">
+      <c r="A22" s="22">
         <v>21</v>
       </c>
-      <c r="B22" s="25" t="s">
+      <c r="B22" s="23" t="s">
         <v>57</v>
       </c>
-      <c r="C22" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D22" s="26" t="s">
+      <c r="C22" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="E22" s="26" t="s">
+      <c r="E22" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="F22" s="27" t="s">
+      <c r="F22" s="26" t="s">
         <v>58</v>
       </c>
-      <c r="G22" s="28"/>
+      <c r="G22" s="25"/>
     </row>
     <row r="23" ht="15.75" spans="1:7">
-      <c r="A23" s="24">
+      <c r="A23" s="22">
         <v>22</v>
       </c>
-      <c r="B23" s="25" t="s">
+      <c r="B23" s="23" t="s">
         <v>59</v>
       </c>
-      <c r="C23" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D23" s="26" t="s">
+      <c r="C23" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D23" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="E23" s="26" t="s">
+      <c r="E23" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="F23" s="27" t="s">
+      <c r="F23" s="26" t="s">
         <v>60</v>
       </c>
-      <c r="G23" s="28"/>
+      <c r="G23" s="25"/>
     </row>
     <row r="24" ht="15.75" spans="1:7">
-      <c r="A24" s="24">
+      <c r="A24" s="22">
         <v>23</v>
       </c>
-      <c r="B24" s="25" t="s">
+      <c r="B24" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="C24" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D24" s="26" t="s">
+      <c r="C24" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="E24" s="26" t="s">
+      <c r="E24" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="F24" s="27" t="s">
+      <c r="F24" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="G24" s="28"/>
+      <c r="G24" s="25"/>
     </row>
     <row r="25" ht="15.75" spans="1:7">
-      <c r="A25" s="24">
+      <c r="A25" s="22">
         <v>24</v>
       </c>
-      <c r="B25" s="25" t="s">
+      <c r="B25" s="23" t="s">
         <v>63</v>
       </c>
-      <c r="C25" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D25" s="26" t="s">
+      <c r="C25" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D25" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="E25" s="26" t="s">
+      <c r="E25" s="22" t="s">
         <v>29</v>
       </c>
       <c r="F25" s="32" t="s">
         <v>64</v>
       </c>
-      <c r="G25" s="28"/>
+      <c r="G25" s="25"/>
     </row>
     <row r="26" ht="31.5" spans="1:7">
-      <c r="A26" s="24">
+      <c r="A26" s="22">
         <v>25</v>
       </c>
-      <c r="B26" s="25" t="s">
+      <c r="B26" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="C26" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D26" s="26" t="s">
+      <c r="C26" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="E26" s="26" t="s">
+      <c r="E26" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="F26" s="27" t="s">
+      <c r="F26" s="26" t="s">
         <v>66</v>
       </c>
-      <c r="G26" s="28"/>
+      <c r="G26" s="25"/>
     </row>
     <row r="27" ht="15.75" spans="1:7">
-      <c r="A27" s="24">
+      <c r="A27" s="22">
         <v>26</v>
       </c>
-      <c r="B27" s="25" t="s">
+      <c r="B27" s="23" t="s">
         <v>67</v>
       </c>
-      <c r="C27" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D27" s="26" t="s">
+      <c r="C27" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D27" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="E27" s="26" t="s">
+      <c r="E27" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="F27" s="27" t="s">
+      <c r="F27" s="26" t="s">
         <v>68</v>
       </c>
-      <c r="G27" s="28"/>
+      <c r="G27" s="25"/>
     </row>
     <row r="28" ht="15.75" spans="1:7">
-      <c r="A28" s="24">
+      <c r="A28" s="22">
         <v>27</v>
       </c>
-      <c r="B28" s="25" t="s">
+      <c r="B28" s="23" t="s">
         <v>69</v>
       </c>
-      <c r="C28" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D28" s="26" t="s">
+      <c r="C28" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D28" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="E28" s="26" t="s">
+      <c r="E28" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="F28" s="27" t="s">
+      <c r="F28" s="26" t="s">
         <v>70</v>
       </c>
-      <c r="G28" s="28"/>
+      <c r="G28" s="25"/>
     </row>
     <row r="29" ht="15.75" spans="1:7">
-      <c r="A29" s="24">
+      <c r="A29" s="22">
         <v>28</v>
       </c>
-      <c r="B29" s="25" t="s">
+      <c r="B29" s="23" t="s">
         <v>71</v>
       </c>
-      <c r="C29" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D29" s="26" t="s">
+      <c r="C29" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D29" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="E29" s="26" t="s">
+      <c r="E29" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="F29" s="27" t="s">
+      <c r="F29" s="26" t="s">
         <v>72</v>
       </c>
-      <c r="G29" s="28"/>
+      <c r="G29" s="25"/>
     </row>
     <row r="30" ht="15.75" spans="1:7">
-      <c r="A30" s="24">
+      <c r="A30" s="22">
         <v>29</v>
       </c>
-      <c r="B30" s="25" t="s">
+      <c r="B30" s="23" t="s">
         <v>73</v>
       </c>
-      <c r="C30" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D30" s="26" t="s">
+      <c r="C30" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D30" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="E30" s="26" t="s">
+      <c r="E30" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="F30" s="27" t="s">
+      <c r="F30" s="26" t="s">
         <v>74</v>
       </c>
-      <c r="G30" s="28"/>
+      <c r="G30" s="25"/>
     </row>
     <row r="31" ht="15.75" spans="1:7">
-      <c r="A31" s="24">
+      <c r="A31" s="22">
         <v>30</v>
       </c>
-      <c r="B31" s="25" t="s">
+      <c r="B31" s="23" t="s">
         <v>75</v>
       </c>
-      <c r="C31" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D31" s="26" t="s">
+      <c r="C31" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D31" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="E31" s="26" t="s">
+      <c r="E31" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="F31" s="27" t="s">
+      <c r="F31" s="26" t="s">
         <v>76</v>
       </c>
-      <c r="G31" s="28"/>
+      <c r="G31" s="25"/>
     </row>
     <row r="32" ht="15.75" spans="1:7">
-      <c r="A32" s="24">
+      <c r="A32" s="22">
         <v>31</v>
       </c>
-      <c r="B32" s="25" t="s">
+      <c r="B32" s="23" t="s">
         <v>77</v>
       </c>
-      <c r="C32" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D32" s="26" t="s">
+      <c r="C32" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D32" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="E32" s="26" t="s">
+      <c r="E32" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="F32" s="33" t="s">
+      <c r="F32" s="24" t="s">
         <v>78</v>
       </c>
-      <c r="G32" s="28"/>
+      <c r="G32" s="25"/>
     </row>
     <row r="33" ht="15.75" spans="1:7">
-      <c r="A33" s="24">
+      <c r="A33" s="22">
         <v>32</v>
       </c>
-      <c r="B33" s="25" t="s">
+      <c r="B33" s="23" t="s">
         <v>79</v>
       </c>
-      <c r="C33" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D33" s="26" t="s">
+      <c r="C33" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D33" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="E33" s="26" t="s">
+      <c r="E33" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="F33" s="27" t="s">
+      <c r="F33" s="26" t="s">
         <v>80</v>
       </c>
-      <c r="G33" s="28"/>
+      <c r="G33" s="25"/>
     </row>
     <row r="34" ht="15.75" spans="1:7">
-      <c r="A34" s="24">
+      <c r="A34" s="22">
         <v>33</v>
       </c>
-      <c r="B34" s="25" t="s">
+      <c r="B34" s="23" t="s">
         <v>81</v>
       </c>
-      <c r="C34" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D34" s="26" t="s">
+      <c r="C34" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D34" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="E34" s="26" t="s">
+      <c r="E34" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="F34" s="27" t="s">
+      <c r="F34" s="26" t="s">
         <v>82</v>
       </c>
-      <c r="G34" s="28"/>
+      <c r="G34" s="25"/>
     </row>
     <row r="35" ht="15.75" spans="1:7">
-      <c r="A35" s="24">
+      <c r="A35" s="22">
         <v>34</v>
       </c>
-      <c r="B35" s="25" t="s">
+      <c r="B35" s="23" t="s">
         <v>83</v>
       </c>
-      <c r="C35" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D35" s="26" t="s">
+      <c r="C35" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D35" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="E35" s="26" t="s">
+      <c r="E35" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="F35" s="27" t="s">
+      <c r="F35" s="26" t="s">
         <v>84</v>
       </c>
-      <c r="G35" s="28"/>
+      <c r="G35" s="25"/>
     </row>
     <row r="36" ht="15.75" spans="1:7">
-      <c r="A36" s="24">
+      <c r="A36" s="22">
         <v>35</v>
       </c>
-      <c r="B36" s="25" t="s">
+      <c r="B36" s="23" t="s">
         <v>85</v>
       </c>
-      <c r="C36" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D36" s="26" t="s">
+      <c r="C36" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D36" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="E36" s="26" t="s">
+      <c r="E36" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="F36" s="27" t="s">
+      <c r="F36" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="G36" s="28"/>
+      <c r="G36" s="25"/>
     </row>
     <row r="37" ht="15.75" spans="1:7">
-      <c r="A37" s="24">
+      <c r="A37" s="22">
         <v>36</v>
       </c>
-      <c r="B37" s="25" t="s">
+      <c r="B37" s="23" t="s">
         <v>87</v>
       </c>
-      <c r="C37" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D37" s="26" t="s">
+      <c r="C37" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D37" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="E37" s="26" t="s">
+      <c r="E37" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="F37" s="27" t="s">
+      <c r="F37" s="26" t="s">
         <v>88</v>
       </c>
       <c r="G37" s="51" t="s">
@@ -3197,43 +3206,43 @@
       </c>
     </row>
     <row r="38" ht="15.75" spans="1:7">
-      <c r="A38" s="24">
+      <c r="A38" s="22">
         <v>37</v>
       </c>
-      <c r="B38" s="25" t="s">
+      <c r="B38" s="23" t="s">
         <v>90</v>
       </c>
-      <c r="C38" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D38" s="26" t="s">
+      <c r="C38" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D38" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="E38" s="26" t="s">
+      <c r="E38" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="F38" s="27" t="s">
+      <c r="F38" s="26" t="s">
         <v>91</v>
       </c>
-      <c r="G38" s="28"/>
+      <c r="G38" s="25"/>
     </row>
     <row r="39" ht="15.75" spans="1:7">
-      <c r="A39" s="24">
+      <c r="A39" s="22">
         <v>38</v>
       </c>
-      <c r="B39" s="25" t="s">
+      <c r="B39" s="23" t="s">
         <v>92</v>
       </c>
-      <c r="C39" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D39" s="26" t="s">
+      <c r="C39" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D39" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="E39" s="26" t="s">
+      <c r="E39" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="F39" s="27" t="s">
+      <c r="F39" s="26" t="s">
         <v>93</v>
       </c>
       <c r="G39" s="50" t="s">
@@ -3241,295 +3250,295 @@
       </c>
     </row>
     <row r="40" ht="15.75" spans="1:7">
-      <c r="A40" s="24">
+      <c r="A40" s="22">
         <v>39</v>
       </c>
-      <c r="B40" s="25" t="s">
+      <c r="B40" s="23" t="s">
         <v>95</v>
       </c>
-      <c r="C40" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D40" s="26" t="s">
+      <c r="C40" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D40" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="E40" s="26" t="s">
+      <c r="E40" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="F40" s="27" t="s">
+      <c r="F40" s="26" t="s">
         <v>96</v>
       </c>
-      <c r="G40" s="28"/>
+      <c r="G40" s="25"/>
     </row>
     <row r="41" ht="15.75" spans="1:7">
-      <c r="A41" s="24">
+      <c r="A41" s="22">
         <v>40</v>
       </c>
-      <c r="B41" s="25" t="s">
+      <c r="B41" s="23" t="s">
         <v>97</v>
       </c>
-      <c r="C41" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D41" s="26" t="s">
+      <c r="C41" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D41" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="E41" s="26" t="s">
+      <c r="E41" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="F41" s="27" t="s">
+      <c r="F41" s="26" t="s">
         <v>98</v>
       </c>
-      <c r="G41" s="28"/>
+      <c r="G41" s="25"/>
     </row>
     <row r="42" ht="15.75" spans="1:7">
-      <c r="A42" s="24">
+      <c r="A42" s="22">
         <v>41</v>
       </c>
-      <c r="B42" s="25" t="s">
+      <c r="B42" s="23" t="s">
         <v>99</v>
       </c>
-      <c r="C42" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D42" s="26" t="s">
+      <c r="C42" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D42" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="E42" s="26" t="s">
+      <c r="E42" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="F42" s="27" t="s">
+      <c r="F42" s="26" t="s">
         <v>100</v>
       </c>
-      <c r="G42" s="28"/>
+      <c r="G42" s="25"/>
     </row>
     <row r="43" ht="15.75" spans="1:7">
-      <c r="A43" s="24">
+      <c r="A43" s="22">
         <v>42</v>
       </c>
-      <c r="B43" s="25" t="s">
+      <c r="B43" s="23" t="s">
         <v>101</v>
       </c>
-      <c r="C43" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D43" s="26" t="s">
+      <c r="C43" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D43" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="E43" s="26" t="s">
+      <c r="E43" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="F43" s="27" t="s">
+      <c r="F43" s="26" t="s">
         <v>102</v>
       </c>
-      <c r="G43" s="28"/>
+      <c r="G43" s="25"/>
     </row>
     <row r="44" ht="15.75" spans="1:7">
-      <c r="A44" s="24">
+      <c r="A44" s="22">
         <v>43</v>
       </c>
-      <c r="B44" s="25" t="s">
+      <c r="B44" s="23" t="s">
         <v>103</v>
       </c>
-      <c r="C44" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D44" s="26" t="s">
+      <c r="C44" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D44" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="E44" s="26" t="s">
+      <c r="E44" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="F44" s="27" t="s">
+      <c r="F44" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="G44" s="28"/>
+      <c r="G44" s="25"/>
     </row>
     <row r="45" ht="15.75" spans="1:7">
-      <c r="A45" s="24">
+      <c r="A45" s="22">
         <v>44</v>
       </c>
-      <c r="B45" s="25" t="s">
+      <c r="B45" s="23" t="s">
         <v>105</v>
       </c>
-      <c r="C45" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D45" s="26" t="s">
+      <c r="C45" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D45" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="E45" s="26" t="s">
+      <c r="E45" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="F45" s="27" t="s">
+      <c r="F45" s="26" t="s">
         <v>106</v>
       </c>
-      <c r="G45" s="28"/>
+      <c r="G45" s="25"/>
     </row>
     <row r="46" ht="15.75" spans="1:7">
-      <c r="A46" s="24">
+      <c r="A46" s="22">
         <v>45</v>
       </c>
-      <c r="B46" s="25" t="s">
+      <c r="B46" s="23" t="s">
         <v>107</v>
       </c>
-      <c r="C46" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D46" s="26" t="s">
+      <c r="C46" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D46" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="E46" s="26" t="s">
+      <c r="E46" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="F46" s="27" t="s">
+      <c r="F46" s="26" t="s">
         <v>108</v>
       </c>
-      <c r="G46" s="28"/>
+      <c r="G46" s="25"/>
     </row>
     <row r="47" ht="15.75" spans="1:7">
-      <c r="A47" s="24">
+      <c r="A47" s="22">
         <v>46</v>
       </c>
-      <c r="B47" s="25" t="s">
+      <c r="B47" s="23" t="s">
         <v>109</v>
       </c>
-      <c r="C47" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D47" s="26" t="s">
+      <c r="C47" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D47" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="E47" s="26" t="s">
+      <c r="E47" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="F47" s="27" t="s">
+      <c r="F47" s="26" t="s">
         <v>110</v>
       </c>
-      <c r="G47" s="28"/>
+      <c r="G47" s="25"/>
     </row>
     <row r="48" ht="15.75" spans="1:7">
-      <c r="A48" s="24">
+      <c r="A48" s="22">
         <v>47</v>
       </c>
-      <c r="B48" s="25" t="s">
+      <c r="B48" s="23" t="s">
         <v>111</v>
       </c>
-      <c r="C48" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D48" s="26" t="s">
+      <c r="C48" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D48" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="E48" s="26" t="s">
+      <c r="E48" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="F48" s="27" t="s">
+      <c r="F48" s="26" t="s">
         <v>112</v>
       </c>
-      <c r="G48" s="28"/>
+      <c r="G48" s="25"/>
     </row>
     <row r="49" ht="15.75" spans="1:7">
-      <c r="A49" s="24">
+      <c r="A49" s="22">
         <v>48</v>
       </c>
-      <c r="B49" s="25" t="s">
+      <c r="B49" s="23" t="s">
         <v>113</v>
       </c>
-      <c r="C49" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D49" s="26" t="s">
+      <c r="C49" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D49" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="E49" s="26" t="s">
+      <c r="E49" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="F49" s="27" t="s">
+      <c r="F49" s="26" t="s">
         <v>114</v>
       </c>
-      <c r="G49" s="28"/>
+      <c r="G49" s="25"/>
     </row>
     <row r="50" ht="15.75" spans="1:7">
-      <c r="A50" s="24">
+      <c r="A50" s="22">
         <v>49</v>
       </c>
-      <c r="B50" s="25" t="s">
+      <c r="B50" s="23" t="s">
         <v>115</v>
       </c>
-      <c r="C50" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D50" s="26" t="s">
+      <c r="C50" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D50" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="E50" s="26" t="s">
+      <c r="E50" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="F50" s="27" t="s">
+      <c r="F50" s="26" t="s">
         <v>116</v>
       </c>
-      <c r="G50" s="28"/>
+      <c r="G50" s="25"/>
     </row>
     <row r="51" ht="15.75" spans="1:7">
-      <c r="A51" s="24">
+      <c r="A51" s="22">
         <v>50</v>
       </c>
-      <c r="B51" s="25" t="s">
+      <c r="B51" s="23" t="s">
         <v>117</v>
       </c>
-      <c r="C51" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D51" s="26" t="s">
+      <c r="C51" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D51" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="E51" s="26" t="s">
+      <c r="E51" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="F51" s="27" t="s">
+      <c r="F51" s="26" t="s">
         <v>118</v>
       </c>
-      <c r="G51" s="28"/>
+      <c r="G51" s="25"/>
     </row>
     <row r="52" ht="15.75" spans="1:7">
-      <c r="A52" s="24">
+      <c r="A52" s="22">
         <v>51</v>
       </c>
-      <c r="B52" s="25" t="s">
+      <c r="B52" s="23" t="s">
         <v>119</v>
       </c>
-      <c r="C52" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D52" s="26" t="s">
+      <c r="C52" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D52" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="E52" s="26" t="s">
+      <c r="E52" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="F52" s="27" t="s">
+      <c r="F52" s="26" t="s">
         <v>120</v>
       </c>
-      <c r="G52" s="28"/>
+      <c r="G52" s="25"/>
     </row>
     <row r="53" ht="15.75" spans="1:7">
-      <c r="A53" s="24">
+      <c r="A53" s="22">
         <v>52</v>
       </c>
-      <c r="B53" s="25" t="s">
+      <c r="B53" s="23" t="s">
         <v>121</v>
       </c>
-      <c r="C53" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D53" s="26" t="s">
+      <c r="C53" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D53" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="E53" s="26" t="s">
+      <c r="E53" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="F53" s="27" t="s">
+      <c r="F53" s="26" t="s">
         <v>122</v>
       </c>
       <c r="G53" s="50" t="s">
@@ -3537,40 +3546,40 @@
       </c>
     </row>
     <row r="54" ht="15.75" spans="1:7">
-      <c r="A54" s="24">
+      <c r="A54" s="22">
         <v>53</v>
       </c>
-      <c r="B54" s="25" t="s">
+      <c r="B54" s="23" t="s">
         <v>124</v>
       </c>
-      <c r="C54" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D54" s="26" t="s">
+      <c r="C54" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D54" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="E54" s="26" t="s">
+      <c r="E54" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="F54" s="27" t="s">
+      <c r="F54" s="26" t="s">
         <v>125</v>
       </c>
-      <c r="G54" s="28"/>
+      <c r="G54" s="25"/>
     </row>
     <row r="55" ht="15.75" spans="1:7">
-      <c r="A55" s="24">
+      <c r="A55" s="22">
         <v>54</v>
       </c>
-      <c r="B55" s="25" t="s">
+      <c r="B55" s="23" t="s">
         <v>126</v>
       </c>
-      <c r="C55" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D55" s="30" t="s">
+      <c r="C55" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D55" s="28" t="s">
         <v>127</v>
       </c>
-      <c r="E55" s="26" t="s">
+      <c r="E55" s="22" t="s">
         <v>128</v>
       </c>
       <c r="F55" s="32" t="s">
@@ -3581,215 +3590,215 @@
       </c>
     </row>
     <row r="56" ht="15.75" spans="1:7">
-      <c r="A56" s="24">
+      <c r="A56" s="22">
         <v>55</v>
       </c>
-      <c r="B56" s="25" t="s">
+      <c r="B56" s="23" t="s">
         <v>131</v>
       </c>
-      <c r="C56" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D56" s="30" t="s">
+      <c r="C56" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D56" s="28" t="s">
         <v>127</v>
       </c>
-      <c r="E56" s="35"/>
-      <c r="F56" s="27" t="s">
+      <c r="E56" s="33"/>
+      <c r="F56" s="26" t="s">
         <v>132</v>
       </c>
-      <c r="G56" s="28" t="s">
+      <c r="G56" s="25" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="57" ht="15.75" spans="1:7">
-      <c r="A57" s="24">
+      <c r="A57" s="22">
         <v>56</v>
       </c>
-      <c r="B57" s="25" t="s">
+      <c r="B57" s="23" t="s">
         <v>134</v>
       </c>
-      <c r="C57" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D57" s="30" t="s">
+      <c r="C57" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D57" s="28" t="s">
         <v>127</v>
       </c>
-      <c r="E57" s="31"/>
-      <c r="F57" s="36"/>
-      <c r="G57" s="28"/>
+      <c r="E57" s="29"/>
+      <c r="F57" s="34"/>
+      <c r="G57" s="25"/>
     </row>
     <row r="58" ht="15.75" spans="1:7">
-      <c r="A58" s="24">
+      <c r="A58" s="22">
         <v>57</v>
       </c>
-      <c r="B58" s="25" t="s">
+      <c r="B58" s="23" t="s">
         <v>135</v>
       </c>
-      <c r="C58" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D58" s="30" t="s">
+      <c r="C58" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D58" s="28" t="s">
         <v>127</v>
       </c>
-      <c r="E58" s="30" t="s">
+      <c r="E58" s="28" t="s">
         <v>136</v>
       </c>
       <c r="F58" s="32" t="s">
         <v>137</v>
       </c>
-      <c r="G58" s="28" t="s">
+      <c r="G58" s="25" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="59" ht="15.75" spans="1:7">
-      <c r="A59" s="24">
+      <c r="A59" s="22">
         <v>58</v>
       </c>
-      <c r="B59" s="25" t="s">
+      <c r="B59" s="23" t="s">
         <v>139</v>
       </c>
-      <c r="C59" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D59" s="30" t="s">
+      <c r="C59" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D59" s="28" t="s">
         <v>127</v>
       </c>
-      <c r="E59" s="30" t="s">
+      <c r="E59" s="28" t="s">
         <v>140</v>
       </c>
       <c r="F59" s="32" t="s">
         <v>141</v>
       </c>
-      <c r="G59" s="28" t="s">
+      <c r="G59" s="25" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="60" ht="15.75" spans="1:7">
-      <c r="A60" s="24">
+      <c r="A60" s="22">
         <v>59</v>
       </c>
-      <c r="B60" s="25" t="s">
+      <c r="B60" s="23" t="s">
         <v>143</v>
       </c>
-      <c r="C60" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D60" s="26" t="s">
+      <c r="C60" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D60" s="22" t="s">
         <v>127</v>
       </c>
-      <c r="E60" s="26" t="s">
+      <c r="E60" s="22" t="s">
         <v>140</v>
       </c>
       <c r="F60" s="32" t="s">
         <v>144</v>
       </c>
-      <c r="G60" s="28" t="s">
+      <c r="G60" s="25" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="61" ht="15.75" spans="1:7">
-      <c r="A61" s="24">
+      <c r="A61" s="22">
         <v>60</v>
       </c>
-      <c r="B61" s="25" t="s">
+      <c r="B61" s="23" t="s">
         <v>146</v>
       </c>
-      <c r="C61" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D61" s="26" t="s">
+      <c r="C61" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D61" s="22" t="s">
         <v>127</v>
       </c>
-      <c r="E61" s="37" t="s">
+      <c r="E61" s="35" t="s">
         <v>136</v>
       </c>
       <c r="F61" s="32" t="s">
         <v>147</v>
       </c>
-      <c r="G61" s="28" t="s">
+      <c r="G61" s="25" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="62" ht="15.75" spans="1:7">
-      <c r="A62" s="24">
+      <c r="A62" s="22">
         <v>61</v>
       </c>
-      <c r="B62" s="25" t="s">
+      <c r="B62" s="23" t="s">
         <v>149</v>
       </c>
-      <c r="C62" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D62" s="38" t="s">
+      <c r="C62" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D62" s="36" t="s">
         <v>127</v>
       </c>
-      <c r="E62" s="39"/>
+      <c r="E62" s="37"/>
       <c r="F62" s="32" t="s">
         <v>150</v>
       </c>
-      <c r="G62" s="40" t="s">
+      <c r="G62" s="38" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="63" ht="31.5" spans="1:7">
-      <c r="A63" s="24">
+      <c r="A63" s="22">
         <v>62</v>
       </c>
-      <c r="B63" s="25" t="s">
+      <c r="B63" s="23" t="s">
         <v>152</v>
       </c>
-      <c r="C63" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D63" s="30" t="s">
+      <c r="C63" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D63" s="28" t="s">
         <v>127</v>
       </c>
-      <c r="E63" s="31"/>
-      <c r="F63" s="41" t="s">
+      <c r="E63" s="29"/>
+      <c r="F63" s="39" t="s">
         <v>153</v>
       </c>
-      <c r="G63" s="28" t="s">
+      <c r="G63" s="25" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="64" ht="15.75" spans="1:7">
-      <c r="A64" s="24">
+      <c r="A64" s="22">
         <v>63</v>
       </c>
-      <c r="B64" s="25" t="s">
+      <c r="B64" s="23" t="s">
         <v>155</v>
       </c>
-      <c r="C64" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D64" s="26" t="s">
+      <c r="C64" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D64" s="22" t="s">
         <v>127</v>
       </c>
-      <c r="E64" s="37"/>
+      <c r="E64" s="35"/>
       <c r="F64" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="G64" s="28" t="s">
+      <c r="G64" s="25" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="65" ht="15.75" spans="1:7">
-      <c r="A65" s="24">
+      <c r="A65" s="22">
         <v>64</v>
       </c>
-      <c r="B65" s="25" t="s">
+      <c r="B65" s="23" t="s">
         <v>158</v>
       </c>
-      <c r="C65" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D65" s="42" t="s">
+      <c r="C65" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D65" s="40" t="s">
         <v>127</v>
       </c>
-      <c r="E65" s="42" t="s">
+      <c r="E65" s="40" t="s">
         <v>136</v>
       </c>
-      <c r="F65" s="43" t="s">
+      <c r="F65" s="41" t="s">
         <v>159</v>
       </c>
       <c r="G65" s="50" t="s">
@@ -3797,62 +3806,62 @@
       </c>
     </row>
     <row r="66" ht="31.5" spans="1:7">
-      <c r="A66" s="24">
+      <c r="A66" s="22">
         <v>65</v>
       </c>
-      <c r="B66" s="25" t="s">
+      <c r="B66" s="23" t="s">
         <v>161</v>
       </c>
-      <c r="C66" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D66" s="26" t="s">
+      <c r="C66" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D66" s="22" t="s">
         <v>127</v>
       </c>
-      <c r="E66" s="34"/>
+      <c r="E66" s="31"/>
       <c r="F66" s="32" t="s">
         <v>162</v>
       </c>
-      <c r="G66" s="28" t="s">
+      <c r="G66" s="25" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="67" ht="15.75" spans="1:7">
-      <c r="A67" s="24">
+      <c r="A67" s="22">
         <v>66</v>
       </c>
-      <c r="B67" s="25" t="s">
+      <c r="B67" s="23" t="s">
         <v>164</v>
       </c>
-      <c r="C67" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D67" s="26" t="s">
+      <c r="C67" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D67" s="22" t="s">
         <v>127</v>
       </c>
-      <c r="E67" s="37"/>
-      <c r="F67" s="44" t="s">
+      <c r="E67" s="35"/>
+      <c r="F67" s="42" t="s">
         <v>165</v>
       </c>
-      <c r="G67" s="28" t="s">
+      <c r="G67" s="25" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="68" ht="15.75" spans="1:7">
-      <c r="A68" s="24">
+      <c r="A68" s="22">
         <v>67</v>
       </c>
-      <c r="B68" s="25" t="s">
+      <c r="B68" s="23" t="s">
         <v>167</v>
       </c>
-      <c r="C68" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D68" s="26" t="s">
+      <c r="C68" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D68" s="22" t="s">
         <v>127</v>
       </c>
-      <c r="E68" s="34"/>
-      <c r="F68" s="33" t="s">
+      <c r="E68" s="31"/>
+      <c r="F68" s="24" t="s">
         <v>168</v>
       </c>
       <c r="G68" s="51" t="s">
@@ -3860,42 +3869,42 @@
       </c>
     </row>
     <row r="69" ht="15.75" spans="1:7">
-      <c r="A69" s="24">
+      <c r="A69" s="22">
         <v>68</v>
       </c>
-      <c r="B69" s="25" t="s">
+      <c r="B69" s="23" t="s">
         <v>170</v>
       </c>
-      <c r="C69" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D69" s="26" t="s">
+      <c r="C69" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D69" s="22" t="s">
         <v>127</v>
       </c>
-      <c r="E69" s="26" t="s">
+      <c r="E69" s="22" t="s">
         <v>136</v>
       </c>
       <c r="F69" s="32" t="s">
         <v>171</v>
       </c>
-      <c r="G69" s="28" t="s">
+      <c r="G69" s="25" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="70" ht="15.75" spans="1:7">
-      <c r="A70" s="24">
+      <c r="A70" s="22">
         <v>69</v>
       </c>
-      <c r="B70" s="25" t="s">
+      <c r="B70" s="23" t="s">
         <v>173</v>
       </c>
-      <c r="C70" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D70" s="26" t="s">
+      <c r="C70" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D70" s="22" t="s">
         <v>127</v>
       </c>
-      <c r="E70" s="26"/>
+      <c r="E70" s="22"/>
       <c r="F70" s="32" t="s">
         <v>174</v>
       </c>
@@ -3904,19 +3913,19 @@
       </c>
     </row>
     <row r="71" ht="15.75" spans="1:7">
-      <c r="A71" s="24">
+      <c r="A71" s="22">
         <v>70</v>
       </c>
-      <c r="B71" s="25" t="s">
+      <c r="B71" s="23" t="s">
         <v>176</v>
       </c>
-      <c r="C71" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D71" s="26" t="s">
+      <c r="C71" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D71" s="22" t="s">
         <v>127</v>
       </c>
-      <c r="E71" s="26"/>
+      <c r="E71" s="22"/>
       <c r="F71" s="32" t="s">
         <v>177</v>
       </c>
@@ -3925,20 +3934,20 @@
       </c>
     </row>
     <row r="72" ht="31.5" spans="1:7">
-      <c r="A72" s="24">
+      <c r="A72" s="22">
         <v>71</v>
       </c>
-      <c r="B72" s="25" t="s">
+      <c r="B72" s="23" t="s">
         <v>179</v>
       </c>
-      <c r="C72" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D72" s="30" t="s">
+      <c r="C72" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D72" s="28" t="s">
         <v>127</v>
       </c>
-      <c r="E72" s="26"/>
-      <c r="F72" s="41" t="s">
+      <c r="E72" s="22"/>
+      <c r="F72" s="39" t="s">
         <v>180</v>
       </c>
       <c r="G72" s="50" t="s">
@@ -3946,20 +3955,20 @@
       </c>
     </row>
     <row r="73" ht="15.75" spans="1:7">
-      <c r="A73" s="24">
+      <c r="A73" s="22">
         <v>72</v>
       </c>
-      <c r="B73" s="25" t="s">
+      <c r="B73" s="23" t="s">
         <v>182</v>
       </c>
-      <c r="C73" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D73" s="26" t="s">
+      <c r="C73" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D73" s="22" t="s">
         <v>127</v>
       </c>
-      <c r="E73" s="26"/>
-      <c r="F73" s="27" t="s">
+      <c r="E73" s="22"/>
+      <c r="F73" s="26" t="s">
         <v>183</v>
       </c>
       <c r="G73" s="50" t="s">
@@ -3967,22 +3976,22 @@
       </c>
     </row>
     <row r="74" ht="15.75" spans="1:7">
-      <c r="A74" s="24">
+      <c r="A74" s="22">
         <v>73</v>
       </c>
-      <c r="B74" s="25" t="s">
+      <c r="B74" s="23" t="s">
         <v>185</v>
       </c>
-      <c r="C74" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D74" s="26" t="s">
+      <c r="C74" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D74" s="22" t="s">
         <v>127</v>
       </c>
-      <c r="E74" s="26" t="s">
+      <c r="E74" s="22" t="s">
         <v>136</v>
       </c>
-      <c r="F74" s="27" t="s">
+      <c r="F74" s="26" t="s">
         <v>186</v>
       </c>
       <c r="G74" s="50" t="s">
@@ -3990,63 +3999,63 @@
       </c>
     </row>
     <row r="75" ht="15.75" spans="1:7">
-      <c r="A75" s="24">
+      <c r="A75" s="22">
         <v>74</v>
       </c>
-      <c r="B75" s="25" t="s">
+      <c r="B75" s="23" t="s">
         <v>188</v>
       </c>
-      <c r="C75" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D75" s="26" t="s">
+      <c r="C75" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D75" s="22" t="s">
         <v>127</v>
       </c>
-      <c r="E75" s="26"/>
+      <c r="E75" s="22"/>
       <c r="F75" s="32" t="s">
         <v>189</v>
       </c>
-      <c r="G75" s="28" t="s">
+      <c r="G75" s="25" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="76" ht="15.75" spans="1:7">
-      <c r="A76" s="24">
+      <c r="A76" s="22">
         <v>75</v>
       </c>
-      <c r="B76" s="25" t="s">
+      <c r="B76" s="23" t="s">
         <v>191</v>
       </c>
-      <c r="C76" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D76" s="26" t="s">
+      <c r="C76" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D76" s="22" t="s">
         <v>127</v>
       </c>
-      <c r="E76" s="26" t="s">
+      <c r="E76" s="22" t="s">
         <v>136</v>
       </c>
       <c r="F76" s="32" t="s">
         <v>192</v>
       </c>
-      <c r="G76" s="28" t="s">
+      <c r="G76" s="25" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="77" ht="15.75" spans="1:7">
-      <c r="A77" s="24">
+      <c r="A77" s="22">
         <v>76</v>
       </c>
-      <c r="B77" s="25" t="s">
+      <c r="B77" s="23" t="s">
         <v>194</v>
       </c>
-      <c r="C77" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D77" s="26" t="s">
+      <c r="C77" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D77" s="22" t="s">
         <v>127</v>
       </c>
-      <c r="E77" s="26"/>
+      <c r="E77" s="22"/>
       <c r="F77" s="32" t="s">
         <v>195</v>
       </c>
@@ -4055,61 +4064,61 @@
       </c>
     </row>
     <row r="78" ht="31.5" spans="1:7">
-      <c r="A78" s="24">
+      <c r="A78" s="22">
         <v>77</v>
       </c>
-      <c r="B78" s="25" t="s">
+      <c r="B78" s="23" t="s">
         <v>197</v>
       </c>
-      <c r="C78" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D78" s="26" t="s">
+      <c r="C78" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D78" s="22" t="s">
         <v>127</v>
       </c>
-      <c r="E78" s="26" t="s">
+      <c r="E78" s="22" t="s">
         <v>128</v>
       </c>
       <c r="F78" s="32" t="s">
         <v>198</v>
       </c>
-      <c r="G78" s="28" t="s">
+      <c r="G78" s="25" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="79" ht="15.75" spans="1:7">
-      <c r="A79" s="24">
+      <c r="A79" s="22">
         <v>78</v>
       </c>
-      <c r="B79" s="25" t="s">
+      <c r="B79" s="23" t="s">
         <v>200</v>
       </c>
-      <c r="C79" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D79" s="26" t="s">
+      <c r="C79" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D79" s="22" t="s">
         <v>127</v>
       </c>
-      <c r="E79" s="26"/>
+      <c r="E79" s="22"/>
       <c r="F79" s="32" t="s">
         <v>201</v>
       </c>
-      <c r="G79" s="28"/>
+      <c r="G79" s="25"/>
     </row>
     <row r="80" ht="15.75" spans="1:7">
-      <c r="A80" s="24">
+      <c r="A80" s="22">
         <v>79</v>
       </c>
-      <c r="B80" s="25" t="s">
+      <c r="B80" s="23" t="s">
         <v>202</v>
       </c>
-      <c r="C80" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D80" s="26" t="s">
+      <c r="C80" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D80" s="22" t="s">
         <v>127</v>
       </c>
-      <c r="E80" s="26" t="s">
+      <c r="E80" s="22" t="s">
         <v>128</v>
       </c>
       <c r="F80" s="32" t="s">
@@ -4120,210 +4129,210 @@
       </c>
     </row>
     <row r="81" ht="15.75" spans="1:7">
-      <c r="A81" s="24">
+      <c r="A81" s="22">
         <v>80</v>
       </c>
-      <c r="B81" s="25" t="s">
+      <c r="B81" s="23" t="s">
         <v>205</v>
       </c>
-      <c r="C81" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D81" s="26" t="s">
+      <c r="C81" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D81" s="22" t="s">
         <v>127</v>
       </c>
-      <c r="E81" s="26" t="s">
+      <c r="E81" s="22" t="s">
         <v>136</v>
       </c>
       <c r="F81" s="32" t="s">
         <v>206</v>
       </c>
-      <c r="G81" s="28" t="s">
+      <c r="G81" s="25" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="82" ht="15.75" spans="1:7">
-      <c r="A82" s="24">
+      <c r="A82" s="22">
         <v>81</v>
       </c>
-      <c r="B82" s="25" t="s">
+      <c r="B82" s="23" t="s">
         <v>208</v>
       </c>
-      <c r="C82" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D82" s="26" t="s">
+      <c r="C82" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D82" s="22" t="s">
         <v>127</v>
       </c>
-      <c r="E82" s="26" t="s">
+      <c r="E82" s="22" t="s">
         <v>140</v>
       </c>
       <c r="F82" s="32" t="s">
         <v>209</v>
       </c>
-      <c r="G82" s="28"/>
+      <c r="G82" s="25"/>
     </row>
     <row r="83" ht="15.75" spans="1:7">
-      <c r="A83" s="24">
+      <c r="A83" s="22">
         <v>82</v>
       </c>
-      <c r="B83" s="25" t="s">
+      <c r="B83" s="23" t="s">
         <v>210</v>
       </c>
-      <c r="C83" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D83" s="26" t="s">
+      <c r="C83" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D83" s="22" t="s">
         <v>127</v>
       </c>
-      <c r="E83" s="26"/>
-      <c r="F83" s="33" t="s">
+      <c r="E83" s="22"/>
+      <c r="F83" s="24" t="s">
         <v>211</v>
       </c>
-      <c r="G83" s="28" t="s">
+      <c r="G83" s="25" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="84" ht="15.75" spans="1:7">
-      <c r="A84" s="24">
+      <c r="A84" s="22">
         <v>83</v>
       </c>
-      <c r="B84" s="25" t="s">
+      <c r="B84" s="23" t="s">
         <v>213</v>
       </c>
-      <c r="C84" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D84" s="26" t="s">
+      <c r="C84" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D84" s="22" t="s">
         <v>127</v>
       </c>
-      <c r="E84" s="26" t="s">
+      <c r="E84" s="22" t="s">
         <v>128</v>
       </c>
       <c r="F84" s="32" t="s">
         <v>214</v>
       </c>
-      <c r="G84" s="28" t="s">
+      <c r="G84" s="25" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="85" ht="15.75" spans="1:7">
-      <c r="A85" s="24">
+      <c r="A85" s="22">
         <v>84</v>
       </c>
-      <c r="B85" s="25" t="s">
+      <c r="B85" s="23" t="s">
         <v>216</v>
       </c>
-      <c r="C85" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D85" s="26" t="s">
+      <c r="C85" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D85" s="22" t="s">
         <v>127</v>
       </c>
-      <c r="E85" s="34"/>
+      <c r="E85" s="31"/>
       <c r="F85" s="32" t="s">
         <v>217</v>
       </c>
-      <c r="G85" s="28"/>
+      <c r="G85" s="25"/>
     </row>
     <row r="86" ht="15.75" spans="1:7">
-      <c r="A86" s="24">
+      <c r="A86" s="22">
         <v>85</v>
       </c>
-      <c r="B86" s="25" t="s">
+      <c r="B86" s="23" t="s">
         <v>218</v>
       </c>
-      <c r="C86" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D86" s="26" t="s">
+      <c r="C86" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D86" s="22" t="s">
         <v>127</v>
       </c>
-      <c r="E86" s="34" t="s">
+      <c r="E86" s="31" t="s">
         <v>140</v>
       </c>
-      <c r="F86" s="45" t="s">
+      <c r="F86" s="43" t="s">
         <v>219</v>
       </c>
-      <c r="G86" s="28" t="s">
+      <c r="G86" s="25" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="87" ht="15.75" spans="1:7">
-      <c r="A87" s="24">
+      <c r="A87" s="22">
         <v>86</v>
       </c>
-      <c r="B87" s="25" t="s">
+      <c r="B87" s="23" t="s">
         <v>221</v>
       </c>
-      <c r="C87" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D87" s="30" t="s">
+      <c r="C87" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D87" s="28" t="s">
         <v>127</v>
       </c>
-      <c r="E87" s="34"/>
+      <c r="E87" s="31"/>
       <c r="F87" s="32" t="s">
         <v>222</v>
       </c>
-      <c r="G87" s="28"/>
+      <c r="G87" s="25"/>
     </row>
     <row r="88" ht="15.75" spans="1:7">
-      <c r="A88" s="24">
+      <c r="A88" s="22">
         <v>87</v>
       </c>
-      <c r="B88" s="25" t="s">
+      <c r="B88" s="23" t="s">
         <v>223</v>
       </c>
-      <c r="C88" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D88" s="26" t="s">
+      <c r="C88" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D88" s="22" t="s">
         <v>127</v>
       </c>
-      <c r="E88" s="34"/>
+      <c r="E88" s="31"/>
       <c r="F88" s="32" t="s">
         <v>224</v>
       </c>
-      <c r="G88" s="28" t="s">
+      <c r="G88" s="25" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="89" ht="15.75" spans="1:7">
-      <c r="A89" s="24">
+      <c r="A89" s="22">
         <v>88</v>
       </c>
-      <c r="B89" s="25" t="s">
+      <c r="B89" s="23" t="s">
         <v>226</v>
       </c>
-      <c r="C89" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D89" s="26" t="s">
+      <c r="C89" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D89" s="22" t="s">
         <v>127</v>
       </c>
-      <c r="E89" s="37"/>
+      <c r="E89" s="35"/>
       <c r="F89" s="32" t="s">
         <v>227</v>
       </c>
-      <c r="G89" s="28" t="s">
+      <c r="G89" s="25" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="90" ht="15.75" spans="1:7">
-      <c r="A90" s="24">
+      <c r="A90" s="22">
         <v>89</v>
       </c>
-      <c r="B90" s="25" t="s">
+      <c r="B90" s="23" t="s">
         <v>229</v>
       </c>
-      <c r="C90" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D90" s="26" t="s">
+      <c r="C90" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D90" s="22" t="s">
         <v>127</v>
       </c>
-      <c r="E90" s="26"/>
+      <c r="E90" s="22"/>
       <c r="F90" s="32" t="s">
         <v>230</v>
       </c>
@@ -4332,42 +4341,42 @@
       </c>
     </row>
     <row r="91" ht="15.75" spans="1:7">
-      <c r="A91" s="24">
+      <c r="A91" s="22">
         <v>90</v>
       </c>
-      <c r="B91" s="25" t="s">
+      <c r="B91" s="23" t="s">
         <v>232</v>
       </c>
-      <c r="C91" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D91" s="26" t="s">
+      <c r="C91" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D91" s="22" t="s">
         <v>127</v>
       </c>
-      <c r="E91" s="26" t="s">
+      <c r="E91" s="22" t="s">
         <v>140</v>
       </c>
       <c r="F91" s="32" t="s">
         <v>233</v>
       </c>
-      <c r="G91" s="28" t="s">
+      <c r="G91" s="25" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="92" ht="15.75" spans="1:7">
-      <c r="A92" s="24">
+      <c r="A92" s="22">
         <v>91</v>
       </c>
-      <c r="B92" s="25" t="s">
+      <c r="B92" s="23" t="s">
         <v>235</v>
       </c>
-      <c r="C92" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D92" s="26" t="s">
+      <c r="C92" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D92" s="22" t="s">
         <v>127</v>
       </c>
-      <c r="E92" s="26"/>
+      <c r="E92" s="22"/>
       <c r="F92" s="32" t="s">
         <v>236</v>
       </c>
@@ -4376,19 +4385,19 @@
       </c>
     </row>
     <row r="93" ht="15.75" spans="1:7">
-      <c r="A93" s="24">
+      <c r="A93" s="22">
         <v>92</v>
       </c>
-      <c r="B93" s="25" t="s">
+      <c r="B93" s="23" t="s">
         <v>238</v>
       </c>
-      <c r="C93" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D93" s="26" t="s">
+      <c r="C93" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D93" s="22" t="s">
         <v>127</v>
       </c>
-      <c r="E93" s="26" t="s">
+      <c r="E93" s="22" t="s">
         <v>239</v>
       </c>
       <c r="F93" s="32" t="s">
@@ -4399,43 +4408,43 @@
       </c>
     </row>
     <row r="94" ht="15.75" spans="1:7">
-      <c r="A94" s="24">
+      <c r="A94" s="22">
         <v>93</v>
       </c>
-      <c r="B94" s="25" t="s">
+      <c r="B94" s="23" t="s">
         <v>242</v>
       </c>
-      <c r="C94" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D94" s="26" t="s">
+      <c r="C94" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D94" s="22" t="s">
         <v>127</v>
       </c>
-      <c r="E94" s="26"/>
+      <c r="E94" s="22"/>
       <c r="F94" s="32" t="s">
         <v>243</v>
       </c>
-      <c r="G94" s="28" t="s">
+      <c r="G94" s="25" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="95" ht="15.75" spans="1:7">
-      <c r="A95" s="24">
+      <c r="A95" s="22">
         <v>94</v>
       </c>
-      <c r="B95" s="25" t="s">
+      <c r="B95" s="23" t="s">
         <v>245</v>
       </c>
-      <c r="C95" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D95" s="26" t="s">
+      <c r="C95" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D95" s="22" t="s">
         <v>127</v>
       </c>
-      <c r="E95" s="26" t="s">
+      <c r="E95" s="22" t="s">
         <v>136</v>
       </c>
-      <c r="F95" s="45" t="s">
+      <c r="F95" s="43" t="s">
         <v>246</v>
       </c>
       <c r="G95" s="50" t="s">
@@ -4443,231 +4452,231 @@
       </c>
     </row>
     <row r="96" ht="15.75" spans="1:7">
-      <c r="A96" s="24">
+      <c r="A96" s="22">
         <v>95</v>
       </c>
-      <c r="B96" s="25" t="s">
+      <c r="B96" s="23" t="s">
         <v>248</v>
       </c>
-      <c r="C96" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D96" s="26" t="s">
+      <c r="C96" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D96" s="22" t="s">
         <v>127</v>
       </c>
-      <c r="E96" s="26"/>
+      <c r="E96" s="22"/>
       <c r="F96" s="32" t="s">
         <v>249</v>
       </c>
-      <c r="G96" s="28" t="s">
+      <c r="G96" s="25" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="97" ht="31.5" spans="1:7">
-      <c r="A97" s="24">
+      <c r="A97" s="22">
         <v>96</v>
       </c>
-      <c r="B97" s="25" t="s">
+      <c r="B97" s="23" t="s">
         <v>251</v>
       </c>
-      <c r="C97" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D97" s="30" t="s">
+      <c r="C97" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D97" s="28" t="s">
         <v>127</v>
       </c>
-      <c r="E97" s="26" t="s">
+      <c r="E97" s="22" t="s">
         <v>252</v>
       </c>
       <c r="F97" s="32" t="s">
         <v>253</v>
       </c>
-      <c r="G97" s="28" t="s">
+      <c r="G97" s="25" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="98" ht="15.75" spans="1:7">
-      <c r="A98" s="24">
+      <c r="A98" s="22">
         <v>97</v>
       </c>
-      <c r="B98" s="25" t="s">
+      <c r="B98" s="23" t="s">
         <v>255</v>
       </c>
-      <c r="C98" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D98" s="26" t="s">
+      <c r="C98" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D98" s="22" t="s">
         <v>127</v>
       </c>
-      <c r="E98" s="26" t="s">
+      <c r="E98" s="22" t="s">
         <v>140</v>
       </c>
       <c r="F98" s="32" t="s">
         <v>256</v>
       </c>
-      <c r="G98" s="28" t="s">
+      <c r="G98" s="25" t="s">
         <v>257</v>
       </c>
     </row>
     <row r="99" ht="15.75" spans="1:7">
-      <c r="A99" s="24">
+      <c r="A99" s="22">
         <v>98</v>
       </c>
-      <c r="B99" s="25" t="s">
+      <c r="B99" s="23" t="s">
         <v>258</v>
       </c>
-      <c r="C99" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D99" s="26" t="s">
+      <c r="C99" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D99" s="22" t="s">
         <v>127</v>
       </c>
-      <c r="E99" s="26" t="s">
+      <c r="E99" s="22" t="s">
         <v>136</v>
       </c>
       <c r="F99" s="32" t="s">
         <v>259</v>
       </c>
-      <c r="G99" s="28" t="s">
+      <c r="G99" s="25" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="100" ht="15.75" spans="1:7">
-      <c r="A100" s="24">
+      <c r="A100" s="22">
         <v>99</v>
       </c>
-      <c r="B100" s="25" t="s">
+      <c r="B100" s="23" t="s">
         <v>261</v>
       </c>
-      <c r="C100" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D100" s="26" t="s">
+      <c r="C100" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D100" s="22" t="s">
         <v>127</v>
       </c>
-      <c r="E100" s="26"/>
+      <c r="E100" s="22"/>
       <c r="F100" s="32"/>
-      <c r="G100" s="28"/>
+      <c r="G100" s="25"/>
     </row>
     <row r="101" ht="15.75" spans="1:7">
-      <c r="A101" s="24">
+      <c r="A101" s="22">
         <v>100</v>
       </c>
-      <c r="B101" s="25" t="s">
+      <c r="B101" s="23" t="s">
         <v>262</v>
       </c>
-      <c r="C101" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D101" s="26" t="s">
+      <c r="C101" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D101" s="22" t="s">
         <v>127</v>
       </c>
-      <c r="E101" s="37"/>
-      <c r="F101" s="27" t="s">
+      <c r="E101" s="35"/>
+      <c r="F101" s="26" t="s">
         <v>263</v>
       </c>
-      <c r="G101" s="28" t="s">
+      <c r="G101" s="25" t="s">
         <v>264</v>
       </c>
     </row>
     <row r="102" ht="15.75" spans="1:7">
-      <c r="A102" s="24">
+      <c r="A102" s="22">
         <v>101</v>
       </c>
-      <c r="B102" s="25" t="s">
+      <c r="B102" s="23" t="s">
         <v>265</v>
       </c>
-      <c r="C102" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D102" s="26" t="s">
+      <c r="C102" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D102" s="22" t="s">
         <v>127</v>
       </c>
-      <c r="E102" s="34"/>
-      <c r="F102" s="27" t="s">
+      <c r="E102" s="31"/>
+      <c r="F102" s="26" t="s">
         <v>266</v>
       </c>
-      <c r="G102" s="28"/>
+      <c r="G102" s="25"/>
     </row>
     <row r="103" ht="15.75" spans="1:7">
-      <c r="A103" s="24">
+      <c r="A103" s="22">
         <v>102</v>
       </c>
-      <c r="B103" s="25" t="s">
+      <c r="B103" s="23" t="s">
         <v>267</v>
       </c>
-      <c r="C103" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D103" s="26" t="s">
+      <c r="C103" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D103" s="22" t="s">
         <v>127</v>
       </c>
-      <c r="E103" s="37"/>
+      <c r="E103" s="35"/>
       <c r="F103" s="32" t="s">
         <v>268</v>
       </c>
-      <c r="G103" s="28" t="s">
+      <c r="G103" s="25" t="s">
         <v>269</v>
       </c>
     </row>
     <row r="104" ht="15.75" spans="1:7">
-      <c r="A104" s="24">
+      <c r="A104" s="22">
         <v>103</v>
       </c>
-      <c r="B104" s="25" t="s">
+      <c r="B104" s="23" t="s">
         <v>270</v>
       </c>
-      <c r="C104" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D104" s="26" t="s">
+      <c r="C104" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D104" s="22" t="s">
         <v>127</v>
       </c>
-      <c r="E104" s="26" t="s">
+      <c r="E104" s="22" t="s">
         <v>136</v>
       </c>
       <c r="F104" s="32" t="s">
         <v>271</v>
       </c>
-      <c r="G104" s="28" t="s">
+      <c r="G104" s="25" t="s">
         <v>272</v>
       </c>
     </row>
     <row r="105" ht="15.75" spans="1:7">
-      <c r="A105" s="24">
+      <c r="A105" s="22">
         <v>104</v>
       </c>
-      <c r="B105" s="25" t="s">
+      <c r="B105" s="23" t="s">
         <v>273</v>
       </c>
-      <c r="C105" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D105" s="26" t="s">
+      <c r="C105" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D105" s="22" t="s">
         <v>127</v>
       </c>
-      <c r="E105" s="37"/>
+      <c r="E105" s="35"/>
       <c r="F105" s="32" t="s">
         <v>274</v>
       </c>
-      <c r="G105" s="28" t="s">
+      <c r="G105" s="25" t="s">
         <v>275</v>
       </c>
     </row>
     <row r="106" ht="15.75" spans="1:7">
-      <c r="A106" s="24">
+      <c r="A106" s="22">
         <v>105</v>
       </c>
-      <c r="B106" s="25" t="s">
+      <c r="B106" s="23" t="s">
         <v>276</v>
       </c>
-      <c r="C106" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D106" s="26" t="s">
+      <c r="C106" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D106" s="22" t="s">
         <v>127</v>
       </c>
-      <c r="E106" s="26" t="s">
+      <c r="E106" s="22" t="s">
         <v>140</v>
       </c>
       <c r="F106" s="32" t="s">
@@ -4678,4604 +4687,4623 @@
       </c>
     </row>
     <row r="107" ht="15.75" spans="1:7">
-      <c r="A107" s="24">
+      <c r="A107" s="22">
         <v>106</v>
       </c>
-      <c r="B107" s="25" t="s">
+      <c r="B107" s="23" t="s">
         <v>279</v>
       </c>
-      <c r="C107" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D107" s="26" t="s">
+      <c r="C107" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D107" s="22" t="s">
         <v>127</v>
       </c>
-      <c r="E107" s="26" t="s">
+      <c r="E107" s="22" t="s">
         <v>280</v>
       </c>
       <c r="F107" s="32" t="s">
         <v>281</v>
       </c>
-      <c r="G107" s="28"/>
+      <c r="G107" s="25"/>
     </row>
     <row r="108" ht="15.75" spans="1:7">
-      <c r="A108" s="24">
+      <c r="A108" s="22">
         <v>107</v>
       </c>
-      <c r="B108" s="25" t="s">
+      <c r="B108" s="23" t="s">
         <v>282</v>
       </c>
-      <c r="C108" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D108" s="46" t="s">
+      <c r="C108" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D108" s="44" t="s">
         <v>127</v>
       </c>
-      <c r="E108" s="47"/>
-      <c r="F108" s="48" t="s">
+      <c r="E108" s="45"/>
+      <c r="F108" s="46" t="s">
         <v>283</v>
       </c>
-      <c r="G108" s="29"/>
+      <c r="G108" s="27"/>
     </row>
     <row r="109" ht="15.75" spans="1:7">
-      <c r="A109" s="24">
+      <c r="A109" s="22">
         <v>108</v>
       </c>
-      <c r="B109" s="25" t="s">
+      <c r="B109" s="23" t="s">
         <v>284</v>
       </c>
-      <c r="C109" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D109" s="46" t="s">
+      <c r="C109" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D109" s="44" t="s">
         <v>127</v>
       </c>
-      <c r="E109" s="47"/>
-      <c r="F109" s="48" t="s">
+      <c r="E109" s="45"/>
+      <c r="F109" s="46" t="s">
         <v>285</v>
       </c>
-      <c r="G109" s="29"/>
+      <c r="G109" s="27"/>
     </row>
     <row r="110" ht="31.5" spans="1:7">
-      <c r="A110" s="24">
+      <c r="A110" s="22">
         <v>109</v>
       </c>
-      <c r="B110" s="25" t="s">
+      <c r="B110" s="23" t="s">
         <v>286</v>
       </c>
-      <c r="C110" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D110" s="46" t="s">
+      <c r="C110" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D110" s="44" t="s">
         <v>127</v>
       </c>
-      <c r="E110" s="47"/>
-      <c r="F110" s="48" t="s">
+      <c r="E110" s="45"/>
+      <c r="F110" s="46" t="s">
         <v>287</v>
       </c>
-      <c r="G110" s="29"/>
+      <c r="G110" s="27"/>
     </row>
     <row r="111" ht="15.75" spans="1:7">
-      <c r="A111" s="24">
+      <c r="A111" s="22">
         <v>110</v>
       </c>
-      <c r="B111" s="25" t="s">
+      <c r="B111" s="23" t="s">
         <v>288</v>
       </c>
-      <c r="C111" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D111" s="46" t="s">
+      <c r="C111" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D111" s="44" t="s">
         <v>127</v>
       </c>
-      <c r="E111" s="47"/>
-      <c r="F111" s="48" t="s">
+      <c r="E111" s="45"/>
+      <c r="F111" s="46" t="s">
         <v>289</v>
       </c>
-      <c r="G111" s="29"/>
+      <c r="G111" s="27"/>
     </row>
     <row r="112" ht="31.5" spans="1:7">
-      <c r="A112" s="24">
+      <c r="A112" s="22">
         <v>111</v>
       </c>
-      <c r="B112" s="25" t="s">
+      <c r="B112" s="23" t="s">
         <v>290</v>
       </c>
-      <c r="C112" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D112" s="46" t="s">
+      <c r="C112" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D112" s="44" t="s">
         <v>127</v>
       </c>
-      <c r="E112" s="47"/>
-      <c r="F112" s="48" t="s">
+      <c r="E112" s="45"/>
+      <c r="F112" s="46" t="s">
         <v>291</v>
       </c>
-      <c r="G112" s="29"/>
+      <c r="G112" s="27"/>
     </row>
     <row r="113" ht="15.75" spans="1:7">
-      <c r="A113" s="24">
+      <c r="A113" s="22">
         <v>112</v>
       </c>
-      <c r="B113" s="25" t="s">
+      <c r="B113" s="23" t="s">
         <v>292</v>
       </c>
-      <c r="C113" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D113" s="46" t="s">
+      <c r="C113" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D113" s="44" t="s">
         <v>127</v>
       </c>
-      <c r="E113" s="47"/>
-      <c r="F113" s="48" t="s">
+      <c r="E113" s="45"/>
+      <c r="F113" s="46" t="s">
         <v>293</v>
       </c>
-      <c r="G113" s="29"/>
+      <c r="G113" s="27"/>
     </row>
     <row r="114" ht="15.75" spans="1:7">
-      <c r="A114" s="24">
+      <c r="A114" s="22">
         <v>113</v>
       </c>
-      <c r="B114" s="25" t="s">
+      <c r="B114" s="23" t="s">
         <v>294</v>
       </c>
-      <c r="C114" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D114" s="46" t="s">
+      <c r="C114" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D114" s="44" t="s">
         <v>127</v>
       </c>
-      <c r="E114" s="47"/>
-      <c r="F114" s="48" t="s">
+      <c r="E114" s="45"/>
+      <c r="F114" s="46" t="s">
         <v>277</v>
       </c>
-      <c r="G114" s="29"/>
+      <c r="G114" s="27"/>
     </row>
     <row r="115" s="15" customFormat="1" ht="15.75" spans="1:7">
-      <c r="A115" s="24">
+      <c r="A115" s="22">
         <v>114</v>
       </c>
-      <c r="B115" s="25" t="s">
+      <c r="B115" s="23" t="s">
         <v>295</v>
       </c>
-      <c r="C115" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D115" s="46" t="s">
+      <c r="C115" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D115" s="44" t="s">
         <v>127</v>
       </c>
-      <c r="E115" s="47"/>
-      <c r="F115" s="48" t="s">
+      <c r="E115" s="45"/>
+      <c r="F115" s="46" t="s">
         <v>296</v>
       </c>
-      <c r="G115" s="29"/>
+      <c r="G115" s="27"/>
     </row>
     <row r="116" ht="15.75" spans="1:7">
-      <c r="A116" s="24">
+      <c r="A116" s="22">
         <v>115</v>
       </c>
-      <c r="B116" s="25" t="s">
+      <c r="B116" s="23" t="s">
         <v>297</v>
       </c>
-      <c r="C116" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D116" s="46" t="s">
+      <c r="C116" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D116" s="44" t="s">
         <v>127</v>
       </c>
-      <c r="E116" s="46" t="s">
+      <c r="E116" s="44" t="s">
         <v>140</v>
       </c>
-      <c r="F116" s="48" t="s">
+      <c r="F116" s="46" t="s">
         <v>298</v>
       </c>
-      <c r="G116" s="29"/>
+      <c r="G116" s="27"/>
     </row>
     <row r="117" ht="15.75" spans="1:7">
-      <c r="A117" s="24">
+      <c r="A117" s="22">
         <v>116</v>
       </c>
-      <c r="B117" s="25" t="s">
+      <c r="B117" s="23" t="s">
         <v>299</v>
       </c>
-      <c r="C117" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D117" s="46" t="s">
+      <c r="C117" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D117" s="44" t="s">
         <v>127</v>
       </c>
-      <c r="E117" s="47"/>
-      <c r="F117" s="48" t="s">
+      <c r="E117" s="45"/>
+      <c r="F117" s="46" t="s">
         <v>300</v>
       </c>
-      <c r="G117" s="29"/>
+      <c r="G117" s="27"/>
     </row>
     <row r="118" ht="15.75" spans="1:7">
-      <c r="A118" s="24">
+      <c r="A118" s="22">
         <v>117</v>
       </c>
-      <c r="B118" s="25" t="s">
+      <c r="B118" s="23" t="s">
         <v>301</v>
       </c>
-      <c r="C118" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D118" s="46" t="s">
+      <c r="C118" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D118" s="44" t="s">
         <v>127</v>
       </c>
-      <c r="E118" s="47"/>
-      <c r="F118" s="48" t="s">
+      <c r="E118" s="45"/>
+      <c r="F118" s="46" t="s">
         <v>302</v>
       </c>
-      <c r="G118" s="29"/>
+      <c r="G118" s="27"/>
     </row>
     <row r="119" ht="15.75" spans="1:7">
-      <c r="A119" s="24">
+      <c r="A119" s="22">
         <v>118</v>
       </c>
-      <c r="B119" s="25" t="s">
+      <c r="B119" s="23" t="s">
         <v>303</v>
       </c>
-      <c r="C119" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D119" s="46" t="s">
+      <c r="C119" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D119" s="44" t="s">
         <v>127</v>
       </c>
-      <c r="E119" s="47"/>
-      <c r="F119" s="48" t="s">
+      <c r="E119" s="45"/>
+      <c r="F119" s="46" t="s">
         <v>304</v>
       </c>
-      <c r="G119" s="29"/>
+      <c r="G119" s="27"/>
     </row>
     <row r="120" ht="15.75" spans="1:7">
-      <c r="A120" s="24">
+      <c r="A120" s="22">
         <v>119</v>
       </c>
-      <c r="B120" s="25" t="s">
+      <c r="B120" s="23" t="s">
         <v>305</v>
       </c>
-      <c r="C120" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D120" s="46" t="s">
+      <c r="C120" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D120" s="44" t="s">
         <v>127</v>
       </c>
-      <c r="E120" s="47"/>
-      <c r="F120" s="48" t="s">
+      <c r="E120" s="45"/>
+      <c r="F120" s="46" t="s">
         <v>306</v>
       </c>
-      <c r="G120" s="29"/>
+      <c r="G120" s="27"/>
     </row>
     <row r="121" ht="15.75" spans="1:7">
-      <c r="A121" s="24">
+      <c r="A121" s="22">
         <v>120</v>
       </c>
-      <c r="B121" s="25" t="s">
+      <c r="B121" s="23" t="s">
         <v>307</v>
       </c>
-      <c r="C121" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D121" s="46" t="s">
+      <c r="C121" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D121" s="44" t="s">
         <v>127</v>
       </c>
-      <c r="E121" s="47"/>
-      <c r="F121" s="48" t="s">
+      <c r="E121" s="45"/>
+      <c r="F121" s="46" t="s">
         <v>308</v>
       </c>
-      <c r="G121" s="29"/>
+      <c r="G121" s="27"/>
     </row>
     <row r="122" ht="15.75" spans="1:7">
-      <c r="A122" s="24">
+      <c r="A122" s="22">
         <v>121</v>
       </c>
-      <c r="B122" s="25" t="s">
+      <c r="B122" s="23" t="s">
         <v>309</v>
       </c>
-      <c r="C122" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D122" s="46" t="s">
+      <c r="C122" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D122" s="44" t="s">
         <v>127</v>
       </c>
-      <c r="E122" s="47"/>
-      <c r="F122" s="48" t="s">
+      <c r="E122" s="45"/>
+      <c r="F122" s="46" t="s">
         <v>310</v>
       </c>
-      <c r="G122" s="29"/>
+      <c r="G122" s="27"/>
     </row>
     <row r="123" ht="15.75" spans="1:7">
-      <c r="A123" s="24">
+      <c r="A123" s="22">
         <v>122</v>
       </c>
-      <c r="B123" s="25" t="s">
+      <c r="B123" s="23" t="s">
         <v>311</v>
       </c>
-      <c r="C123" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D123" s="46" t="s">
+      <c r="C123" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D123" s="44" t="s">
         <v>127</v>
       </c>
-      <c r="E123" s="47"/>
-      <c r="F123" s="48" t="s">
+      <c r="E123" s="45"/>
+      <c r="F123" s="46" t="s">
         <v>312</v>
       </c>
-      <c r="G123" s="49"/>
+      <c r="G123" s="47"/>
     </row>
     <row r="124" ht="15.75" spans="1:7">
-      <c r="A124" s="24">
+      <c r="A124" s="22">
         <v>123</v>
       </c>
-      <c r="B124" s="25" t="s">
+      <c r="B124" s="23" t="s">
         <v>313</v>
       </c>
-      <c r="C124" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D124" s="46" t="s">
+      <c r="C124" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D124" s="44" t="s">
         <v>127</v>
       </c>
-      <c r="E124" s="47"/>
-      <c r="F124" s="48" t="s">
+      <c r="E124" s="45"/>
+      <c r="F124" s="46" t="s">
         <v>314</v>
       </c>
-      <c r="G124" s="29"/>
+      <c r="G124" s="27"/>
     </row>
     <row r="125" ht="15.75" spans="1:7">
-      <c r="A125" s="24">
+      <c r="A125" s="22">
         <v>124</v>
       </c>
-      <c r="B125" s="25" t="s">
+      <c r="B125" s="23" t="s">
         <v>315</v>
       </c>
-      <c r="C125" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D125" s="46" t="s">
+      <c r="C125" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D125" s="44" t="s">
         <v>316</v>
       </c>
-      <c r="E125" s="46" t="s">
+      <c r="E125" s="44" t="s">
         <v>10</v>
       </c>
-      <c r="F125" s="48" t="s">
+      <c r="F125" s="46" t="s">
         <v>317</v>
       </c>
-      <c r="G125" s="29"/>
+      <c r="G125" s="27"/>
     </row>
     <row r="126" ht="31.5" spans="1:7">
-      <c r="A126" s="24">
+      <c r="A126" s="22">
         <v>125</v>
       </c>
-      <c r="B126" s="25" t="s">
+      <c r="B126" s="23" t="s">
         <v>318</v>
       </c>
-      <c r="C126" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D126" s="46" t="s">
+      <c r="C126" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D126" s="44" t="s">
         <v>319</v>
       </c>
-      <c r="E126" s="46" t="s">
+      <c r="E126" s="44" t="s">
         <v>29</v>
       </c>
-      <c r="F126" s="48" t="s">
+      <c r="F126" s="46" t="s">
         <v>320</v>
       </c>
-      <c r="G126" s="29"/>
+      <c r="G126" s="27"/>
     </row>
     <row r="127" ht="15.75" spans="1:7">
-      <c r="A127" s="24">
+      <c r="A127" s="22">
         <v>126</v>
       </c>
-      <c r="B127" s="25" t="s">
+      <c r="B127" s="23" t="s">
         <v>321</v>
       </c>
-      <c r="C127" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D127" s="46" t="s">
+      <c r="C127" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D127" s="44" t="s">
         <v>127</v>
       </c>
-      <c r="E127" s="47"/>
-      <c r="F127" s="48" t="s">
+      <c r="E127" s="45"/>
+      <c r="F127" s="46" t="s">
         <v>322</v>
       </c>
-      <c r="G127" s="29"/>
+      <c r="G127" s="27"/>
     </row>
     <row r="128" ht="31.5" spans="1:7">
-      <c r="A128" s="24">
+      <c r="A128" s="22">
         <v>127</v>
       </c>
-      <c r="B128" s="25" t="s">
+      <c r="B128" s="23" t="s">
         <v>323</v>
       </c>
-      <c r="C128" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D128" s="46" t="s">
+      <c r="C128" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D128" s="44" t="s">
         <v>324</v>
       </c>
-      <c r="E128" s="47" t="s">
+      <c r="E128" s="45" t="s">
         <v>29</v>
       </c>
-      <c r="F128" s="48" t="s">
+      <c r="F128" s="46" t="s">
         <v>325</v>
       </c>
-      <c r="G128" s="29"/>
+      <c r="G128" s="27"/>
     </row>
     <row r="129" ht="31.5" spans="1:7">
-      <c r="A129" s="24">
+      <c r="A129" s="22">
         <v>128</v>
       </c>
-      <c r="B129" s="25" t="s">
+      <c r="B129" s="23" t="s">
         <v>326</v>
       </c>
-      <c r="C129" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D129" s="46" t="s">
+      <c r="C129" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D129" s="44" t="s">
         <v>324</v>
       </c>
-      <c r="E129" s="47" t="s">
+      <c r="E129" s="45" t="s">
         <v>29</v>
       </c>
-      <c r="F129" s="48" t="s">
+      <c r="F129" s="46" t="s">
         <v>327</v>
       </c>
-      <c r="G129" s="29"/>
-    </row>
-    <row r="130" spans="1:7">
-      <c r="A130" s="19"/>
-      <c r="D130" s="17"/>
+      <c r="G129" s="27"/>
+    </row>
+    <row r="130" ht="31.5" spans="1:7">
+      <c r="A130" s="22">
+        <v>129</v>
+      </c>
+      <c r="B130" s="23" t="s">
+        <v>328</v>
+      </c>
+      <c r="C130" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D130" s="44" t="s">
+        <v>324</v>
+      </c>
+      <c r="E130" s="45" t="s">
+        <v>10</v>
+      </c>
+      <c r="F130" s="48" t="s">
+        <v>329</v>
+      </c>
+      <c r="G130" s="50" t="s">
+        <v>330</v>
+      </c>
     </row>
     <row r="131" spans="1:7">
-      <c r="A131" s="19"/>
+      <c r="A131" s="49"/>
       <c r="D131" s="17"/>
     </row>
     <row r="132" spans="1:7">
-      <c r="A132" s="19"/>
+      <c r="A132" s="49"/>
       <c r="D132" s="17"/>
     </row>
     <row r="133" spans="1:7">
-      <c r="A133" s="19"/>
+      <c r="A133" s="49"/>
       <c r="D133" s="17"/>
     </row>
     <row r="134" spans="1:7">
-      <c r="A134" s="19"/>
+      <c r="A134" s="49"/>
       <c r="D134" s="17"/>
     </row>
     <row r="135" spans="1:7">
-      <c r="A135" s="19"/>
+      <c r="A135" s="49"/>
       <c r="D135" s="17"/>
     </row>
     <row r="136" spans="1:7">
-      <c r="A136" s="19"/>
+      <c r="A136" s="49"/>
       <c r="D136" s="17"/>
     </row>
     <row r="137" spans="1:7">
-      <c r="A137" s="19"/>
+      <c r="A137" s="49"/>
       <c r="D137" s="17"/>
     </row>
     <row r="138" spans="1:7">
-      <c r="A138" s="19"/>
+      <c r="A138" s="49"/>
       <c r="D138" s="17"/>
     </row>
     <row r="139" spans="1:7">
-      <c r="A139" s="19"/>
+      <c r="A139" s="49"/>
       <c r="D139" s="17"/>
     </row>
     <row r="140" spans="1:7">
-      <c r="A140" s="19"/>
+      <c r="A140" s="49"/>
       <c r="D140" s="17"/>
     </row>
     <row r="141" spans="1:7">
-      <c r="A141" s="19"/>
+      <c r="A141" s="49"/>
       <c r="D141" s="17"/>
     </row>
     <row r="142" spans="1:7">
-      <c r="A142" s="19"/>
+      <c r="A142" s="49"/>
       <c r="D142" s="17"/>
     </row>
     <row r="143" spans="1:7">
-      <c r="A143" s="19"/>
+      <c r="A143" s="49"/>
       <c r="D143" s="17"/>
     </row>
     <row r="144" spans="1:7">
-      <c r="A144" s="19"/>
+      <c r="A144" s="49"/>
       <c r="D144" s="17"/>
     </row>
     <row r="145" spans="1:4">
-      <c r="A145" s="19"/>
+      <c r="A145" s="49"/>
       <c r="D145" s="17"/>
     </row>
     <row r="146" spans="1:4">
-      <c r="A146" s="19"/>
+      <c r="A146" s="49"/>
       <c r="D146" s="17"/>
     </row>
     <row r="147" spans="1:4">
-      <c r="A147" s="19"/>
+      <c r="A147" s="49"/>
       <c r="D147" s="17"/>
     </row>
     <row r="148" spans="1:4">
-      <c r="A148" s="19"/>
+      <c r="A148" s="49"/>
       <c r="D148" s="17"/>
     </row>
     <row r="149" spans="1:4">
-      <c r="A149" s="19"/>
+      <c r="A149" s="49"/>
       <c r="D149" s="17"/>
     </row>
     <row r="150" spans="1:4">
-      <c r="A150" s="19"/>
+      <c r="A150" s="49"/>
       <c r="D150" s="17"/>
     </row>
     <row r="151" spans="1:4">
-      <c r="A151" s="19"/>
+      <c r="A151" s="49"/>
       <c r="D151" s="17"/>
     </row>
     <row r="152" spans="1:4">
-      <c r="A152" s="19"/>
+      <c r="A152" s="49"/>
       <c r="D152" s="17"/>
     </row>
     <row r="153" spans="1:4">
-      <c r="A153" s="19"/>
+      <c r="A153" s="49"/>
       <c r="D153" s="17"/>
     </row>
     <row r="154" spans="1:4">
-      <c r="A154" s="19"/>
+      <c r="A154" s="49"/>
       <c r="D154" s="17"/>
     </row>
     <row r="155" spans="1:4">
-      <c r="A155" s="19"/>
+      <c r="A155" s="49"/>
       <c r="D155" s="17"/>
     </row>
     <row r="156" spans="1:4">
-      <c r="A156" s="19"/>
+      <c r="A156" s="49"/>
       <c r="D156" s="17"/>
     </row>
     <row r="157" spans="1:4">
-      <c r="A157" s="19"/>
+      <c r="A157" s="49"/>
       <c r="D157" s="17"/>
     </row>
     <row r="158" spans="1:4">
-      <c r="A158" s="19"/>
+      <c r="A158" s="49"/>
       <c r="D158" s="17"/>
     </row>
     <row r="159" spans="1:4">
-      <c r="A159" s="19"/>
+      <c r="A159" s="49"/>
       <c r="D159" s="17"/>
     </row>
     <row r="160" spans="1:4">
-      <c r="A160" s="19"/>
+      <c r="A160" s="49"/>
       <c r="D160" s="17"/>
     </row>
     <row r="161" spans="1:4">
-      <c r="A161" s="19"/>
+      <c r="A161" s="49"/>
       <c r="D161" s="17"/>
     </row>
     <row r="162" spans="1:4">
-      <c r="A162" s="19"/>
+      <c r="A162" s="49"/>
       <c r="D162" s="17"/>
     </row>
     <row r="163" spans="1:4">
-      <c r="A163" s="19"/>
+      <c r="A163" s="49"/>
       <c r="D163" s="17"/>
     </row>
     <row r="164" spans="1:4">
-      <c r="A164" s="19"/>
+      <c r="A164" s="49"/>
       <c r="D164" s="17"/>
     </row>
     <row r="165" spans="1:4">
-      <c r="A165" s="19"/>
+      <c r="A165" s="49"/>
       <c r="D165" s="17"/>
     </row>
     <row r="166" spans="1:4">
-      <c r="A166" s="19"/>
+      <c r="A166" s="49"/>
       <c r="D166" s="17"/>
     </row>
     <row r="167" spans="1:4">
-      <c r="A167" s="19"/>
+      <c r="A167" s="49"/>
       <c r="D167" s="17"/>
     </row>
     <row r="168" spans="1:4">
-      <c r="A168" s="19"/>
+      <c r="A168" s="49"/>
       <c r="D168" s="17"/>
     </row>
     <row r="169" spans="1:4">
-      <c r="A169" s="19"/>
+      <c r="A169" s="49"/>
       <c r="D169" s="17"/>
     </row>
     <row r="170" spans="1:4">
-      <c r="A170" s="19"/>
+      <c r="A170" s="49"/>
       <c r="D170" s="17"/>
     </row>
     <row r="171" spans="1:4">
-      <c r="A171" s="19"/>
+      <c r="A171" s="49"/>
       <c r="D171" s="17"/>
     </row>
     <row r="172" spans="1:4">
-      <c r="A172" s="19"/>
+      <c r="A172" s="49"/>
       <c r="D172" s="17"/>
     </row>
     <row r="173" spans="1:4">
-      <c r="A173" s="19"/>
+      <c r="A173" s="49"/>
       <c r="D173" s="17"/>
     </row>
     <row r="174" spans="1:4">
-      <c r="A174" s="19"/>
+      <c r="A174" s="49"/>
       <c r="D174" s="17"/>
     </row>
     <row r="175" spans="1:4">
-      <c r="A175" s="19"/>
+      <c r="A175" s="49"/>
       <c r="D175" s="17"/>
     </row>
     <row r="176" spans="1:4">
-      <c r="A176" s="19"/>
+      <c r="A176" s="49"/>
       <c r="D176" s="17"/>
     </row>
     <row r="177" spans="1:4">
-      <c r="A177" s="19"/>
+      <c r="A177" s="49"/>
       <c r="D177" s="17"/>
     </row>
     <row r="178" spans="1:4">
-      <c r="A178" s="19"/>
+      <c r="A178" s="49"/>
       <c r="D178" s="17"/>
     </row>
     <row r="179" spans="1:4">
-      <c r="A179" s="19"/>
+      <c r="A179" s="49"/>
       <c r="D179" s="17"/>
     </row>
     <row r="180" spans="1:4">
-      <c r="A180" s="19"/>
+      <c r="A180" s="49"/>
       <c r="D180" s="17"/>
     </row>
     <row r="181" spans="1:4">
-      <c r="A181" s="19"/>
+      <c r="A181" s="49"/>
       <c r="D181" s="17"/>
     </row>
     <row r="182" spans="1:4">
-      <c r="A182" s="19"/>
+      <c r="A182" s="49"/>
       <c r="D182" s="17"/>
     </row>
     <row r="183" spans="1:4">
-      <c r="A183" s="19"/>
+      <c r="A183" s="49"/>
       <c r="D183" s="17"/>
     </row>
     <row r="184" spans="1:4">
-      <c r="A184" s="19"/>
+      <c r="A184" s="49"/>
       <c r="D184" s="17"/>
     </row>
     <row r="185" spans="1:4">
-      <c r="A185" s="19"/>
+      <c r="A185" s="49"/>
       <c r="D185" s="17"/>
     </row>
     <row r="186" spans="1:4">
-      <c r="A186" s="19"/>
+      <c r="A186" s="49"/>
       <c r="D186" s="17"/>
     </row>
     <row r="187" spans="1:4">
-      <c r="A187" s="19"/>
+      <c r="A187" s="49"/>
       <c r="D187" s="17"/>
     </row>
     <row r="188" spans="1:4">
-      <c r="A188" s="19"/>
+      <c r="A188" s="49"/>
       <c r="D188" s="17"/>
     </row>
     <row r="189" spans="1:4">
-      <c r="A189" s="19"/>
+      <c r="A189" s="49"/>
       <c r="D189" s="17"/>
     </row>
     <row r="190" spans="1:4">
-      <c r="A190" s="19"/>
+      <c r="A190" s="49"/>
       <c r="D190" s="17"/>
     </row>
     <row r="191" spans="1:4">
-      <c r="A191" s="19"/>
+      <c r="A191" s="49"/>
       <c r="D191" s="17"/>
     </row>
     <row r="192" spans="1:4">
-      <c r="A192" s="19"/>
+      <c r="A192" s="49"/>
       <c r="D192" s="17"/>
     </row>
     <row r="193" spans="1:4">
-      <c r="A193" s="19"/>
+      <c r="A193" s="49"/>
       <c r="D193" s="17"/>
     </row>
     <row r="194" spans="1:4">
-      <c r="A194" s="19"/>
+      <c r="A194" s="49"/>
       <c r="D194" s="17"/>
     </row>
     <row r="195" spans="1:4">
-      <c r="A195" s="19"/>
+      <c r="A195" s="49"/>
       <c r="D195" s="17"/>
     </row>
     <row r="196" spans="1:4">
-      <c r="A196" s="19"/>
+      <c r="A196" s="49"/>
       <c r="D196" s="17"/>
     </row>
     <row r="197" spans="1:4">
-      <c r="A197" s="19"/>
+      <c r="A197" s="49"/>
       <c r="D197" s="17"/>
     </row>
     <row r="198" spans="1:4">
-      <c r="A198" s="19"/>
+      <c r="A198" s="49"/>
       <c r="D198" s="17"/>
     </row>
     <row r="199" spans="1:4">
-      <c r="A199" s="19"/>
+      <c r="A199" s="49"/>
       <c r="D199" s="17"/>
     </row>
     <row r="200" spans="1:4">
-      <c r="A200" s="19"/>
+      <c r="A200" s="49"/>
       <c r="D200" s="17"/>
     </row>
     <row r="201" spans="1:4">
-      <c r="A201" s="19"/>
+      <c r="A201" s="49"/>
       <c r="D201" s="17"/>
     </row>
     <row r="202" spans="1:4">
-      <c r="A202" s="19"/>
+      <c r="A202" s="49"/>
       <c r="D202" s="17"/>
     </row>
     <row r="203" spans="1:4">
-      <c r="A203" s="19"/>
+      <c r="A203" s="49"/>
       <c r="D203" s="17"/>
     </row>
     <row r="204" spans="1:4">
-      <c r="A204" s="19"/>
+      <c r="A204" s="49"/>
       <c r="D204" s="17"/>
     </row>
     <row r="205" spans="1:4">
-      <c r="A205" s="19"/>
+      <c r="A205" s="49"/>
       <c r="D205" s="17"/>
     </row>
     <row r="206" spans="1:4">
-      <c r="A206" s="19"/>
+      <c r="A206" s="49"/>
       <c r="D206" s="17"/>
     </row>
     <row r="207" spans="1:4">
-      <c r="A207" s="19"/>
+      <c r="A207" s="49"/>
       <c r="D207" s="17"/>
     </row>
     <row r="208" spans="1:4">
-      <c r="A208" s="19"/>
+      <c r="A208" s="49"/>
       <c r="D208" s="17"/>
     </row>
     <row r="209" spans="1:4">
-      <c r="A209" s="19"/>
+      <c r="A209" s="49"/>
       <c r="D209" s="17"/>
     </row>
     <row r="210" spans="1:4">
-      <c r="A210" s="19"/>
+      <c r="A210" s="49"/>
       <c r="D210" s="17"/>
     </row>
     <row r="211" spans="1:4">
-      <c r="A211" s="19"/>
+      <c r="A211" s="49"/>
       <c r="D211" s="17"/>
     </row>
     <row r="212" spans="1:4">
-      <c r="A212" s="19"/>
+      <c r="A212" s="49"/>
       <c r="D212" s="17"/>
     </row>
     <row r="213" spans="1:4">
-      <c r="A213" s="19"/>
+      <c r="A213" s="49"/>
       <c r="D213" s="17"/>
     </row>
     <row r="214" spans="1:4">
-      <c r="A214" s="19"/>
+      <c r="A214" s="49"/>
       <c r="D214" s="17"/>
     </row>
     <row r="215" spans="1:4">
-      <c r="A215" s="19"/>
+      <c r="A215" s="49"/>
       <c r="D215" s="17"/>
     </row>
     <row r="216" spans="1:4">
-      <c r="A216" s="19"/>
+      <c r="A216" s="49"/>
       <c r="D216" s="17"/>
     </row>
     <row r="217" spans="1:4">
-      <c r="A217" s="19"/>
+      <c r="A217" s="49"/>
       <c r="D217" s="17"/>
     </row>
     <row r="218" spans="1:4">
-      <c r="A218" s="19"/>
+      <c r="A218" s="49"/>
       <c r="D218" s="17"/>
     </row>
     <row r="219" spans="1:4">
-      <c r="A219" s="19"/>
+      <c r="A219" s="49"/>
       <c r="D219" s="17"/>
     </row>
     <row r="220" spans="1:4">
-      <c r="A220" s="19"/>
+      <c r="A220" s="49"/>
       <c r="D220" s="17"/>
     </row>
     <row r="221" spans="1:4">
-      <c r="A221" s="19"/>
+      <c r="A221" s="49"/>
       <c r="D221" s="17"/>
     </row>
     <row r="222" spans="1:4">
-      <c r="A222" s="19"/>
+      <c r="A222" s="49"/>
       <c r="D222" s="17"/>
     </row>
     <row r="223" spans="1:4">
-      <c r="A223" s="19"/>
+      <c r="A223" s="49"/>
       <c r="D223" s="17"/>
     </row>
     <row r="224" spans="1:4">
-      <c r="A224" s="19"/>
+      <c r="A224" s="49"/>
       <c r="D224" s="17"/>
     </row>
     <row r="225" spans="1:4">
-      <c r="A225" s="19"/>
+      <c r="A225" s="49"/>
       <c r="D225" s="17"/>
     </row>
     <row r="226" spans="1:4">
-      <c r="A226" s="19"/>
+      <c r="A226" s="49"/>
       <c r="D226" s="17"/>
     </row>
     <row r="227" spans="1:4">
-      <c r="A227" s="19"/>
+      <c r="A227" s="49"/>
       <c r="D227" s="17"/>
     </row>
     <row r="228" spans="1:4">
-      <c r="A228" s="19"/>
+      <c r="A228" s="49"/>
       <c r="D228" s="17"/>
     </row>
     <row r="229" spans="1:4">
-      <c r="A229" s="19"/>
+      <c r="A229" s="49"/>
       <c r="D229" s="17"/>
     </row>
     <row r="230" spans="1:4">
-      <c r="A230" s="19"/>
+      <c r="A230" s="49"/>
       <c r="D230" s="17"/>
     </row>
     <row r="231" spans="1:4">
-      <c r="A231" s="19"/>
+      <c r="A231" s="49"/>
       <c r="D231" s="17"/>
     </row>
     <row r="232" spans="1:4">
-      <c r="A232" s="19"/>
+      <c r="A232" s="49"/>
       <c r="D232" s="17"/>
     </row>
     <row r="233" spans="1:4">
-      <c r="A233" s="19"/>
+      <c r="A233" s="49"/>
       <c r="D233" s="17"/>
     </row>
     <row r="234" spans="1:4">
-      <c r="A234" s="19"/>
+      <c r="A234" s="49"/>
       <c r="D234" s="17"/>
     </row>
     <row r="235" spans="1:4">
-      <c r="A235" s="19"/>
+      <c r="A235" s="49"/>
       <c r="D235" s="17"/>
     </row>
     <row r="236" spans="1:4">
-      <c r="A236" s="19"/>
+      <c r="A236" s="49"/>
       <c r="D236" s="17"/>
     </row>
     <row r="237" spans="1:4">
-      <c r="A237" s="19"/>
+      <c r="A237" s="49"/>
       <c r="D237" s="17"/>
     </row>
     <row r="238" spans="1:4">
-      <c r="A238" s="19"/>
+      <c r="A238" s="49"/>
       <c r="D238" s="17"/>
     </row>
     <row r="239" spans="1:4">
-      <c r="A239" s="19"/>
+      <c r="A239" s="49"/>
       <c r="D239" s="17"/>
     </row>
     <row r="240" spans="1:4">
-      <c r="A240" s="19"/>
+      <c r="A240" s="49"/>
       <c r="D240" s="17"/>
     </row>
     <row r="241" spans="1:4">
-      <c r="A241" s="19"/>
+      <c r="A241" s="49"/>
       <c r="D241" s="17"/>
     </row>
     <row r="242" spans="1:4">
-      <c r="A242" s="19"/>
+      <c r="A242" s="49"/>
       <c r="D242" s="17"/>
     </row>
     <row r="243" spans="1:4">
-      <c r="A243" s="19"/>
+      <c r="A243" s="49"/>
       <c r="D243" s="17"/>
     </row>
     <row r="244" spans="1:4">
-      <c r="A244" s="19"/>
+      <c r="A244" s="49"/>
       <c r="D244" s="17"/>
     </row>
     <row r="245" spans="1:4">
-      <c r="A245" s="19"/>
+      <c r="A245" s="49"/>
       <c r="D245" s="17"/>
     </row>
     <row r="246" spans="1:4">
-      <c r="A246" s="19"/>
+      <c r="A246" s="49"/>
       <c r="D246" s="17"/>
     </row>
     <row r="247" spans="1:4">
-      <c r="A247" s="19"/>
+      <c r="A247" s="49"/>
       <c r="D247" s="17"/>
     </row>
     <row r="248" spans="1:4">
-      <c r="A248" s="19"/>
+      <c r="A248" s="49"/>
       <c r="D248" s="17"/>
     </row>
     <row r="249" spans="1:4">
-      <c r="A249" s="19"/>
+      <c r="A249" s="49"/>
       <c r="D249" s="17"/>
     </row>
     <row r="250" spans="1:4">
-      <c r="A250" s="19"/>
+      <c r="A250" s="49"/>
       <c r="D250" s="17"/>
     </row>
     <row r="251" spans="1:4">
-      <c r="A251" s="19"/>
+      <c r="A251" s="49"/>
       <c r="D251" s="17"/>
     </row>
     <row r="252" spans="1:4">
-      <c r="A252" s="19"/>
+      <c r="A252" s="49"/>
       <c r="D252" s="17"/>
     </row>
     <row r="253" spans="1:4">
-      <c r="A253" s="19"/>
+      <c r="A253" s="49"/>
       <c r="D253" s="17"/>
     </row>
     <row r="254" spans="1:4">
-      <c r="A254" s="19"/>
+      <c r="A254" s="49"/>
       <c r="D254" s="17"/>
     </row>
     <row r="255" spans="1:4">
-      <c r="A255" s="19"/>
+      <c r="A255" s="49"/>
       <c r="D255" s="17"/>
     </row>
     <row r="256" spans="1:4">
-      <c r="A256" s="19"/>
+      <c r="A256" s="49"/>
       <c r="D256" s="17"/>
     </row>
     <row r="257" spans="1:4">
-      <c r="A257" s="19"/>
+      <c r="A257" s="49"/>
       <c r="D257" s="17"/>
     </row>
     <row r="258" spans="1:4">
-      <c r="A258" s="19"/>
+      <c r="A258" s="49"/>
       <c r="D258" s="17"/>
     </row>
     <row r="259" spans="1:4">
-      <c r="A259" s="19"/>
+      <c r="A259" s="49"/>
       <c r="D259" s="17"/>
     </row>
     <row r="260" spans="1:4">
-      <c r="A260" s="19"/>
+      <c r="A260" s="49"/>
       <c r="D260" s="17"/>
     </row>
     <row r="261" spans="1:4">
-      <c r="A261" s="19"/>
+      <c r="A261" s="49"/>
       <c r="D261" s="17"/>
     </row>
     <row r="262" spans="1:4">
-      <c r="A262" s="19"/>
+      <c r="A262" s="49"/>
       <c r="D262" s="17"/>
     </row>
     <row r="263" spans="1:4">
-      <c r="A263" s="19"/>
+      <c r="A263" s="49"/>
       <c r="D263" s="17"/>
     </row>
     <row r="264" spans="1:4">
-      <c r="A264" s="19"/>
+      <c r="A264" s="49"/>
       <c r="D264" s="17"/>
     </row>
     <row r="265" spans="1:4">
-      <c r="A265" s="19"/>
+      <c r="A265" s="49"/>
       <c r="D265" s="17"/>
     </row>
     <row r="266" spans="1:4">
-      <c r="A266" s="19"/>
+      <c r="A266" s="49"/>
       <c r="D266" s="17"/>
     </row>
     <row r="267" spans="1:4">
-      <c r="A267" s="19"/>
+      <c r="A267" s="49"/>
       <c r="D267" s="17"/>
     </row>
     <row r="268" spans="1:4">
-      <c r="A268" s="19"/>
+      <c r="A268" s="49"/>
       <c r="D268" s="17"/>
     </row>
     <row r="269" spans="1:4">
-      <c r="A269" s="19"/>
+      <c r="A269" s="49"/>
       <c r="D269" s="17"/>
     </row>
     <row r="270" spans="1:4">
-      <c r="A270" s="19"/>
+      <c r="A270" s="49"/>
       <c r="D270" s="17"/>
     </row>
     <row r="271" spans="1:4">
-      <c r="A271" s="19"/>
+      <c r="A271" s="49"/>
       <c r="D271" s="17"/>
     </row>
     <row r="272" spans="1:4">
-      <c r="A272" s="19"/>
+      <c r="A272" s="49"/>
       <c r="D272" s="17"/>
     </row>
     <row r="273" spans="1:4">
-      <c r="A273" s="19"/>
+      <c r="A273" s="49"/>
       <c r="D273" s="17"/>
     </row>
     <row r="274" spans="1:4">
-      <c r="A274" s="19"/>
+      <c r="A274" s="49"/>
       <c r="D274" s="17"/>
     </row>
     <row r="275" spans="1:4">
-      <c r="A275" s="19"/>
+      <c r="A275" s="49"/>
       <c r="D275" s="17"/>
     </row>
     <row r="276" spans="1:4">
-      <c r="A276" s="19"/>
+      <c r="A276" s="49"/>
       <c r="D276" s="17"/>
     </row>
     <row r="277" spans="1:4">
-      <c r="A277" s="19"/>
+      <c r="A277" s="49"/>
       <c r="D277" s="17"/>
     </row>
     <row r="278" spans="1:4">
-      <c r="A278" s="19"/>
+      <c r="A278" s="49"/>
       <c r="D278" s="17"/>
     </row>
     <row r="279" spans="1:4">
-      <c r="A279" s="19"/>
+      <c r="A279" s="49"/>
       <c r="D279" s="17"/>
     </row>
     <row r="280" spans="1:4">
-      <c r="A280" s="19"/>
+      <c r="A280" s="49"/>
       <c r="D280" s="17"/>
     </row>
     <row r="281" spans="1:4">
-      <c r="A281" s="19"/>
+      <c r="A281" s="49"/>
       <c r="D281" s="17"/>
     </row>
     <row r="282" spans="1:4">
-      <c r="A282" s="19"/>
+      <c r="A282" s="49"/>
       <c r="D282" s="17"/>
     </row>
     <row r="283" spans="1:4">
-      <c r="A283" s="19"/>
+      <c r="A283" s="49"/>
       <c r="D283" s="17"/>
     </row>
     <row r="284" spans="1:4">
-      <c r="A284" s="19"/>
+      <c r="A284" s="49"/>
       <c r="D284" s="17"/>
     </row>
     <row r="285" spans="1:4">
-      <c r="A285" s="19"/>
+      <c r="A285" s="49"/>
       <c r="D285" s="17"/>
     </row>
     <row r="286" spans="1:4">
-      <c r="A286" s="19"/>
+      <c r="A286" s="49"/>
       <c r="D286" s="17"/>
     </row>
     <row r="287" spans="1:4">
-      <c r="A287" s="19"/>
+      <c r="A287" s="49"/>
       <c r="D287" s="17"/>
     </row>
     <row r="288" spans="1:4">
-      <c r="A288" s="19"/>
+      <c r="A288" s="49"/>
       <c r="D288" s="17"/>
     </row>
     <row r="289" spans="1:4">
-      <c r="A289" s="19"/>
+      <c r="A289" s="49"/>
       <c r="D289" s="17"/>
     </row>
     <row r="290" spans="1:4">
-      <c r="A290" s="19"/>
+      <c r="A290" s="49"/>
       <c r="D290" s="17"/>
     </row>
     <row r="291" spans="1:4">
-      <c r="A291" s="19"/>
+      <c r="A291" s="49"/>
       <c r="D291" s="17"/>
     </row>
     <row r="292" spans="1:4">
-      <c r="A292" s="19"/>
+      <c r="A292" s="49"/>
       <c r="D292" s="17"/>
     </row>
     <row r="293" spans="1:4">
-      <c r="A293" s="19"/>
+      <c r="A293" s="49"/>
       <c r="D293" s="17"/>
     </row>
     <row r="294" spans="1:4">
-      <c r="A294" s="19"/>
+      <c r="A294" s="49"/>
       <c r="D294" s="17"/>
     </row>
     <row r="295" spans="1:4">
-      <c r="A295" s="19"/>
+      <c r="A295" s="49"/>
       <c r="D295" s="17"/>
     </row>
     <row r="296" spans="1:4">
-      <c r="A296" s="19"/>
+      <c r="A296" s="49"/>
       <c r="D296" s="17"/>
     </row>
     <row r="297" spans="1:4">
-      <c r="A297" s="19"/>
+      <c r="A297" s="49"/>
       <c r="D297" s="17"/>
     </row>
     <row r="298" spans="1:4">
-      <c r="A298" s="19"/>
+      <c r="A298" s="49"/>
       <c r="D298" s="17"/>
     </row>
     <row r="299" spans="1:4">
-      <c r="A299" s="19"/>
+      <c r="A299" s="49"/>
       <c r="D299" s="17"/>
     </row>
     <row r="300" spans="1:4">
-      <c r="A300" s="19"/>
+      <c r="A300" s="49"/>
       <c r="D300" s="17"/>
     </row>
     <row r="301" spans="1:4">
-      <c r="A301" s="19"/>
+      <c r="A301" s="49"/>
       <c r="D301" s="17"/>
     </row>
     <row r="302" spans="1:4">
-      <c r="A302" s="19"/>
+      <c r="A302" s="49"/>
       <c r="D302" s="17"/>
     </row>
     <row r="303" spans="1:4">
-      <c r="A303" s="19"/>
+      <c r="A303" s="49"/>
       <c r="D303" s="17"/>
     </row>
     <row r="304" spans="1:4">
-      <c r="A304" s="19"/>
+      <c r="A304" s="49"/>
       <c r="D304" s="17"/>
     </row>
     <row r="305" spans="1:4">
-      <c r="A305" s="19"/>
+      <c r="A305" s="49"/>
       <c r="D305" s="17"/>
     </row>
     <row r="306" spans="1:4">
-      <c r="A306" s="19"/>
+      <c r="A306" s="49"/>
       <c r="D306" s="17"/>
     </row>
     <row r="307" spans="1:4">
-      <c r="A307" s="19"/>
+      <c r="A307" s="49"/>
       <c r="D307" s="17"/>
     </row>
     <row r="308" spans="1:4">
-      <c r="A308" s="19"/>
+      <c r="A308" s="49"/>
       <c r="D308" s="17"/>
     </row>
     <row r="309" spans="1:4">
-      <c r="A309" s="19"/>
+      <c r="A309" s="49"/>
       <c r="D309" s="17"/>
     </row>
     <row r="310" spans="1:4">
-      <c r="A310" s="19"/>
+      <c r="A310" s="49"/>
       <c r="D310" s="17"/>
     </row>
     <row r="311" spans="1:4">
-      <c r="A311" s="19"/>
+      <c r="A311" s="49"/>
       <c r="D311" s="17"/>
     </row>
     <row r="312" spans="1:4">
-      <c r="A312" s="19"/>
+      <c r="A312" s="49"/>
       <c r="D312" s="17"/>
     </row>
     <row r="313" spans="1:4">
-      <c r="A313" s="19"/>
+      <c r="A313" s="49"/>
       <c r="D313" s="17"/>
     </row>
     <row r="314" spans="1:4">
-      <c r="A314" s="19"/>
+      <c r="A314" s="49"/>
       <c r="D314" s="17"/>
     </row>
     <row r="315" spans="1:4">
-      <c r="A315" s="19"/>
+      <c r="A315" s="49"/>
       <c r="D315" s="17"/>
     </row>
     <row r="316" spans="1:4">
-      <c r="A316" s="19"/>
+      <c r="A316" s="49"/>
       <c r="D316" s="17"/>
     </row>
     <row r="317" spans="1:4">
-      <c r="A317" s="19"/>
+      <c r="A317" s="49"/>
       <c r="D317" s="17"/>
     </row>
     <row r="318" spans="1:4">
-      <c r="A318" s="19"/>
+      <c r="A318" s="49"/>
       <c r="D318" s="17"/>
     </row>
     <row r="319" spans="1:4">
-      <c r="A319" s="19"/>
+      <c r="A319" s="49"/>
       <c r="D319" s="17"/>
     </row>
     <row r="320" spans="1:4">
-      <c r="A320" s="19"/>
+      <c r="A320" s="49"/>
       <c r="D320" s="17"/>
     </row>
     <row r="321" spans="1:4">
-      <c r="A321" s="19"/>
+      <c r="A321" s="49"/>
       <c r="D321" s="17"/>
     </row>
     <row r="322" spans="1:4">
-      <c r="A322" s="19"/>
+      <c r="A322" s="49"/>
       <c r="D322" s="17"/>
     </row>
     <row r="323" spans="1:4">
-      <c r="A323" s="19"/>
+      <c r="A323" s="49"/>
       <c r="D323" s="17"/>
     </row>
     <row r="324" spans="1:4">
-      <c r="A324" s="19"/>
+      <c r="A324" s="49"/>
       <c r="D324" s="17"/>
     </row>
     <row r="325" spans="1:4">
-      <c r="A325" s="19"/>
+      <c r="A325" s="49"/>
       <c r="D325" s="17"/>
     </row>
     <row r="326" spans="1:4">
-      <c r="A326" s="19"/>
+      <c r="A326" s="49"/>
       <c r="D326" s="17"/>
     </row>
     <row r="327" spans="1:4">
-      <c r="A327" s="19"/>
+      <c r="A327" s="49"/>
       <c r="D327" s="17"/>
     </row>
     <row r="328" spans="1:4">
-      <c r="A328" s="19"/>
+      <c r="A328" s="49"/>
       <c r="D328" s="17"/>
     </row>
     <row r="329" spans="1:4">
-      <c r="A329" s="19"/>
+      <c r="A329" s="49"/>
       <c r="D329" s="17"/>
     </row>
     <row r="330" spans="1:4">
-      <c r="A330" s="19"/>
+      <c r="A330" s="49"/>
       <c r="D330" s="17"/>
     </row>
     <row r="331" spans="1:4">
-      <c r="A331" s="19"/>
+      <c r="A331" s="49"/>
       <c r="D331" s="17"/>
     </row>
     <row r="332" spans="1:4">
-      <c r="A332" s="19"/>
+      <c r="A332" s="49"/>
       <c r="D332" s="17"/>
     </row>
     <row r="333" spans="1:4">
-      <c r="A333" s="19"/>
+      <c r="A333" s="49"/>
       <c r="D333" s="17"/>
     </row>
     <row r="334" spans="1:4">
-      <c r="A334" s="19"/>
+      <c r="A334" s="49"/>
       <c r="D334" s="17"/>
     </row>
     <row r="335" spans="1:4">
-      <c r="A335" s="19"/>
+      <c r="A335" s="49"/>
       <c r="D335" s="17"/>
     </row>
     <row r="336" spans="1:4">
-      <c r="A336" s="19"/>
+      <c r="A336" s="49"/>
       <c r="D336" s="17"/>
     </row>
     <row r="337" spans="1:4">
-      <c r="A337" s="19"/>
+      <c r="A337" s="49"/>
       <c r="D337" s="17"/>
     </row>
     <row r="338" spans="1:4">
-      <c r="A338" s="19"/>
+      <c r="A338" s="49"/>
       <c r="D338" s="17"/>
     </row>
     <row r="339" spans="1:4">
-      <c r="A339" s="19"/>
+      <c r="A339" s="49"/>
       <c r="D339" s="17"/>
     </row>
     <row r="340" spans="1:4">
-      <c r="A340" s="19"/>
+      <c r="A340" s="49"/>
       <c r="D340" s="17"/>
     </row>
     <row r="341" spans="1:4">
-      <c r="A341" s="19"/>
+      <c r="A341" s="49"/>
       <c r="D341" s="17"/>
     </row>
     <row r="342" spans="1:4">
-      <c r="A342" s="19"/>
+      <c r="A342" s="49"/>
       <c r="D342" s="17"/>
     </row>
     <row r="343" spans="1:4">
-      <c r="A343" s="19"/>
+      <c r="A343" s="49"/>
       <c r="D343" s="17"/>
     </row>
     <row r="344" spans="1:4">
-      <c r="A344" s="19"/>
+      <c r="A344" s="49"/>
       <c r="D344" s="17"/>
     </row>
     <row r="345" spans="1:4">
-      <c r="A345" s="19"/>
+      <c r="A345" s="49"/>
       <c r="D345" s="17"/>
     </row>
     <row r="346" spans="1:4">
-      <c r="A346" s="19"/>
+      <c r="A346" s="49"/>
       <c r="D346" s="17"/>
     </row>
     <row r="347" spans="1:4">
-      <c r="A347" s="19"/>
+      <c r="A347" s="49"/>
       <c r="D347" s="17"/>
     </row>
     <row r="348" spans="1:4">
-      <c r="A348" s="19"/>
+      <c r="A348" s="49"/>
       <c r="D348" s="17"/>
     </row>
     <row r="349" spans="1:4">
-      <c r="A349" s="19"/>
+      <c r="A349" s="49"/>
       <c r="D349" s="17"/>
     </row>
     <row r="350" spans="1:4">
-      <c r="A350" s="19"/>
+      <c r="A350" s="49"/>
       <c r="D350" s="17"/>
     </row>
     <row r="351" spans="1:4">
-      <c r="A351" s="19"/>
+      <c r="A351" s="49"/>
       <c r="D351" s="17"/>
     </row>
     <row r="352" spans="1:4">
-      <c r="A352" s="19"/>
+      <c r="A352" s="49"/>
       <c r="D352" s="17"/>
     </row>
     <row r="353" spans="1:4">
-      <c r="A353" s="19"/>
+      <c r="A353" s="49"/>
       <c r="D353" s="17"/>
     </row>
     <row r="354" spans="1:4">
-      <c r="A354" s="19"/>
+      <c r="A354" s="49"/>
       <c r="D354" s="17"/>
     </row>
     <row r="355" spans="1:4">
-      <c r="A355" s="19"/>
+      <c r="A355" s="49"/>
       <c r="D355" s="17"/>
     </row>
     <row r="356" spans="1:4">
-      <c r="A356" s="19"/>
+      <c r="A356" s="49"/>
       <c r="D356" s="17"/>
     </row>
     <row r="357" spans="1:4">
-      <c r="A357" s="19"/>
+      <c r="A357" s="49"/>
       <c r="D357" s="17"/>
     </row>
     <row r="358" spans="1:4">
-      <c r="A358" s="19"/>
+      <c r="A358" s="49"/>
       <c r="D358" s="17"/>
     </row>
     <row r="359" spans="1:4">
-      <c r="A359" s="19"/>
+      <c r="A359" s="49"/>
       <c r="D359" s="17"/>
     </row>
     <row r="360" spans="1:4">
-      <c r="A360" s="19"/>
+      <c r="A360" s="49"/>
       <c r="D360" s="17"/>
     </row>
     <row r="361" spans="1:4">
-      <c r="A361" s="19"/>
+      <c r="A361" s="49"/>
       <c r="D361" s="17"/>
     </row>
     <row r="362" spans="1:4">
-      <c r="A362" s="19"/>
+      <c r="A362" s="49"/>
       <c r="D362" s="17"/>
     </row>
     <row r="363" spans="1:4">
-      <c r="A363" s="19"/>
+      <c r="A363" s="49"/>
       <c r="D363" s="17"/>
     </row>
     <row r="364" spans="1:4">
-      <c r="A364" s="19"/>
+      <c r="A364" s="49"/>
       <c r="D364" s="17"/>
     </row>
     <row r="365" spans="1:4">
-      <c r="A365" s="19"/>
+      <c r="A365" s="49"/>
       <c r="D365" s="17"/>
     </row>
     <row r="366" spans="1:4">
-      <c r="A366" s="19"/>
+      <c r="A366" s="49"/>
       <c r="D366" s="17"/>
     </row>
     <row r="367" spans="1:4">
-      <c r="A367" s="19"/>
+      <c r="A367" s="49"/>
       <c r="D367" s="17"/>
     </row>
     <row r="368" spans="1:4">
-      <c r="A368" s="19"/>
+      <c r="A368" s="49"/>
       <c r="D368" s="17"/>
     </row>
     <row r="369" spans="1:4">
-      <c r="A369" s="19"/>
+      <c r="A369" s="49"/>
       <c r="D369" s="17"/>
     </row>
     <row r="370" spans="1:4">
-      <c r="A370" s="19"/>
+      <c r="A370" s="49"/>
       <c r="D370" s="17"/>
     </row>
     <row r="371" spans="1:4">
-      <c r="A371" s="19"/>
+      <c r="A371" s="49"/>
       <c r="D371" s="17"/>
     </row>
     <row r="372" spans="1:4">
-      <c r="A372" s="19"/>
+      <c r="A372" s="49"/>
       <c r="D372" s="17"/>
     </row>
     <row r="373" spans="1:4">
-      <c r="A373" s="19"/>
+      <c r="A373" s="49"/>
       <c r="D373" s="17"/>
     </row>
     <row r="374" spans="1:4">
-      <c r="A374" s="19"/>
+      <c r="A374" s="49"/>
       <c r="D374" s="17"/>
     </row>
     <row r="375" spans="1:4">
-      <c r="A375" s="19"/>
+      <c r="A375" s="49"/>
       <c r="D375" s="17"/>
     </row>
     <row r="376" spans="1:4">
-      <c r="A376" s="19"/>
+      <c r="A376" s="49"/>
       <c r="D376" s="17"/>
     </row>
     <row r="377" spans="1:4">
-      <c r="A377" s="19"/>
+      <c r="A377" s="49"/>
       <c r="D377" s="17"/>
     </row>
     <row r="378" spans="1:4">
-      <c r="A378" s="19"/>
+      <c r="A378" s="49"/>
       <c r="D378" s="17"/>
     </row>
     <row r="379" spans="1:4">
-      <c r="A379" s="19"/>
+      <c r="A379" s="49"/>
       <c r="D379" s="17"/>
     </row>
     <row r="380" spans="1:4">
-      <c r="A380" s="19"/>
+      <c r="A380" s="49"/>
       <c r="D380" s="17"/>
     </row>
     <row r="381" spans="1:4">
-      <c r="A381" s="19"/>
+      <c r="A381" s="49"/>
       <c r="D381" s="17"/>
     </row>
     <row r="382" spans="1:4">
-      <c r="A382" s="19"/>
+      <c r="A382" s="49"/>
       <c r="D382" s="17"/>
     </row>
     <row r="383" spans="1:4">
-      <c r="A383" s="19"/>
+      <c r="A383" s="49"/>
       <c r="D383" s="17"/>
     </row>
     <row r="384" spans="1:4">
-      <c r="A384" s="19"/>
+      <c r="A384" s="49"/>
       <c r="D384" s="17"/>
     </row>
     <row r="385" spans="1:4">
-      <c r="A385" s="19"/>
+      <c r="A385" s="49"/>
       <c r="D385" s="17"/>
     </row>
     <row r="386" spans="1:4">
-      <c r="A386" s="19"/>
+      <c r="A386" s="49"/>
       <c r="D386" s="17"/>
     </row>
     <row r="387" spans="1:4">
-      <c r="A387" s="19"/>
+      <c r="A387" s="49"/>
       <c r="D387" s="17"/>
     </row>
     <row r="388" spans="1:4">
-      <c r="A388" s="19"/>
+      <c r="A388" s="49"/>
       <c r="D388" s="17"/>
     </row>
     <row r="389" spans="1:4">
-      <c r="A389" s="19"/>
+      <c r="A389" s="49"/>
       <c r="D389" s="17"/>
     </row>
     <row r="390" spans="1:4">
-      <c r="A390" s="19"/>
+      <c r="A390" s="49"/>
       <c r="D390" s="17"/>
     </row>
     <row r="391" spans="1:4">
-      <c r="A391" s="19"/>
+      <c r="A391" s="49"/>
       <c r="D391" s="17"/>
     </row>
     <row r="392" spans="1:4">
-      <c r="A392" s="19"/>
+      <c r="A392" s="49"/>
       <c r="D392" s="17"/>
     </row>
     <row r="393" spans="1:4">
-      <c r="A393" s="19"/>
+      <c r="A393" s="49"/>
       <c r="D393" s="17"/>
     </row>
     <row r="394" spans="1:4">
-      <c r="A394" s="19"/>
+      <c r="A394" s="49"/>
       <c r="D394" s="17"/>
     </row>
     <row r="395" spans="1:4">
-      <c r="A395" s="19"/>
+      <c r="A395" s="49"/>
       <c r="D395" s="17"/>
     </row>
     <row r="396" spans="1:4">
-      <c r="A396" s="19"/>
+      <c r="A396" s="49"/>
       <c r="D396" s="17"/>
     </row>
     <row r="397" spans="1:4">
-      <c r="A397" s="19"/>
+      <c r="A397" s="49"/>
       <c r="D397" s="17"/>
     </row>
     <row r="398" spans="1:4">
-      <c r="A398" s="19"/>
+      <c r="A398" s="49"/>
       <c r="D398" s="17"/>
     </row>
     <row r="399" spans="1:4">
-      <c r="A399" s="19"/>
+      <c r="A399" s="49"/>
       <c r="D399" s="17"/>
     </row>
     <row r="400" spans="1:4">
-      <c r="A400" s="19"/>
+      <c r="A400" s="49"/>
       <c r="D400" s="17"/>
     </row>
     <row r="401" spans="1:4">
-      <c r="A401" s="19"/>
+      <c r="A401" s="49"/>
       <c r="D401" s="17"/>
     </row>
     <row r="402" spans="1:4">
-      <c r="A402" s="19"/>
+      <c r="A402" s="49"/>
       <c r="D402" s="17"/>
     </row>
     <row r="403" spans="1:4">
-      <c r="A403" s="19"/>
+      <c r="A403" s="49"/>
       <c r="D403" s="17"/>
     </row>
     <row r="404" spans="1:4">
-      <c r="A404" s="19"/>
+      <c r="A404" s="49"/>
       <c r="D404" s="17"/>
     </row>
     <row r="405" spans="1:4">
-      <c r="A405" s="19"/>
+      <c r="A405" s="49"/>
       <c r="D405" s="17"/>
     </row>
     <row r="406" spans="1:4">
-      <c r="A406" s="19"/>
+      <c r="A406" s="49"/>
       <c r="D406" s="17"/>
     </row>
     <row r="407" spans="1:4">
-      <c r="A407" s="19"/>
+      <c r="A407" s="49"/>
       <c r="D407" s="17"/>
     </row>
     <row r="408" spans="1:4">
-      <c r="A408" s="19"/>
+      <c r="A408" s="49"/>
       <c r="D408" s="17"/>
     </row>
     <row r="409" spans="1:4">
-      <c r="A409" s="19"/>
+      <c r="A409" s="49"/>
       <c r="D409" s="17"/>
     </row>
     <row r="410" spans="1:4">
-      <c r="A410" s="19"/>
+      <c r="A410" s="49"/>
       <c r="D410" s="17"/>
     </row>
     <row r="411" spans="1:4">
-      <c r="A411" s="19"/>
+      <c r="A411" s="49"/>
       <c r="D411" s="17"/>
     </row>
     <row r="412" spans="1:4">
-      <c r="A412" s="19"/>
+      <c r="A412" s="49"/>
       <c r="D412" s="17"/>
     </row>
     <row r="413" spans="1:4">
-      <c r="A413" s="19"/>
+      <c r="A413" s="49"/>
       <c r="D413" s="17"/>
     </row>
     <row r="414" spans="1:4">
-      <c r="A414" s="19"/>
+      <c r="A414" s="49"/>
       <c r="D414" s="17"/>
     </row>
     <row r="415" spans="1:4">
-      <c r="A415" s="19"/>
+      <c r="A415" s="49"/>
       <c r="D415" s="17"/>
     </row>
     <row r="416" spans="1:4">
-      <c r="A416" s="19"/>
+      <c r="A416" s="49"/>
       <c r="D416" s="17"/>
     </row>
     <row r="417" spans="1:4">
-      <c r="A417" s="19"/>
+      <c r="A417" s="49"/>
       <c r="D417" s="17"/>
     </row>
     <row r="418" spans="1:4">
-      <c r="A418" s="19"/>
+      <c r="A418" s="49"/>
       <c r="D418" s="17"/>
     </row>
     <row r="419" spans="1:4">
-      <c r="A419" s="19"/>
+      <c r="A419" s="49"/>
       <c r="D419" s="17"/>
     </row>
     <row r="420" spans="1:4">
-      <c r="A420" s="19"/>
+      <c r="A420" s="49"/>
       <c r="D420" s="17"/>
     </row>
     <row r="421" spans="1:4">
-      <c r="A421" s="19"/>
+      <c r="A421" s="49"/>
       <c r="D421" s="17"/>
     </row>
     <row r="422" spans="1:4">
-      <c r="A422" s="19"/>
+      <c r="A422" s="49"/>
       <c r="D422" s="17"/>
     </row>
     <row r="423" spans="1:4">
-      <c r="A423" s="19"/>
+      <c r="A423" s="49"/>
       <c r="D423" s="17"/>
     </row>
     <row r="424" spans="1:4">
-      <c r="A424" s="19"/>
+      <c r="A424" s="49"/>
       <c r="D424" s="17"/>
     </row>
     <row r="425" spans="1:4">
-      <c r="A425" s="19"/>
+      <c r="A425" s="49"/>
       <c r="D425" s="17"/>
     </row>
     <row r="426" spans="1:4">
-      <c r="A426" s="19"/>
+      <c r="A426" s="49"/>
       <c r="D426" s="17"/>
     </row>
     <row r="427" spans="1:4">
-      <c r="A427" s="19"/>
+      <c r="A427" s="49"/>
       <c r="D427" s="17"/>
     </row>
     <row r="428" spans="1:4">
-      <c r="A428" s="19"/>
+      <c r="A428" s="49"/>
       <c r="D428" s="17"/>
     </row>
     <row r="429" spans="1:4">
-      <c r="A429" s="19"/>
+      <c r="A429" s="49"/>
       <c r="D429" s="17"/>
     </row>
     <row r="430" spans="1:4">
-      <c r="A430" s="19"/>
+      <c r="A430" s="49"/>
       <c r="D430" s="17"/>
     </row>
     <row r="431" spans="1:4">
-      <c r="A431" s="19"/>
+      <c r="A431" s="49"/>
       <c r="D431" s="17"/>
     </row>
     <row r="432" spans="1:4">
-      <c r="A432" s="19"/>
+      <c r="A432" s="49"/>
       <c r="D432" s="17"/>
     </row>
     <row r="433" spans="1:4">
-      <c r="A433" s="19"/>
+      <c r="A433" s="49"/>
       <c r="D433" s="17"/>
     </row>
     <row r="434" spans="1:4">
-      <c r="A434" s="19"/>
+      <c r="A434" s="49"/>
       <c r="D434" s="17"/>
     </row>
     <row r="435" spans="1:4">
-      <c r="A435" s="19"/>
+      <c r="A435" s="49"/>
       <c r="D435" s="17"/>
     </row>
     <row r="436" spans="1:4">
-      <c r="A436" s="19"/>
+      <c r="A436" s="49"/>
       <c r="D436" s="17"/>
     </row>
     <row r="437" spans="1:4">
-      <c r="A437" s="19"/>
+      <c r="A437" s="49"/>
       <c r="D437" s="17"/>
     </row>
     <row r="438" spans="1:4">
-      <c r="A438" s="19"/>
+      <c r="A438" s="49"/>
       <c r="D438" s="17"/>
     </row>
     <row r="439" spans="1:4">
-      <c r="A439" s="19"/>
+      <c r="A439" s="49"/>
       <c r="D439" s="17"/>
     </row>
     <row r="440" spans="1:4">
-      <c r="A440" s="19"/>
+      <c r="A440" s="49"/>
       <c r="D440" s="17"/>
     </row>
     <row r="441" spans="1:4">
-      <c r="A441" s="19"/>
+      <c r="A441" s="49"/>
       <c r="D441" s="17"/>
     </row>
     <row r="442" spans="1:4">
-      <c r="A442" s="19"/>
+      <c r="A442" s="49"/>
       <c r="D442" s="17"/>
     </row>
     <row r="443" spans="1:4">
-      <c r="A443" s="19"/>
+      <c r="A443" s="49"/>
       <c r="D443" s="17"/>
     </row>
     <row r="444" spans="1:4">
-      <c r="A444" s="19"/>
+      <c r="A444" s="49"/>
       <c r="D444" s="17"/>
     </row>
     <row r="445" spans="1:4">
-      <c r="A445" s="19"/>
+      <c r="A445" s="49"/>
       <c r="D445" s="17"/>
     </row>
     <row r="446" spans="1:4">
-      <c r="A446" s="19"/>
+      <c r="A446" s="49"/>
       <c r="D446" s="17"/>
     </row>
     <row r="447" spans="1:4">
-      <c r="A447" s="19"/>
+      <c r="A447" s="49"/>
       <c r="D447" s="17"/>
     </row>
     <row r="448" spans="1:4">
-      <c r="A448" s="19"/>
+      <c r="A448" s="49"/>
       <c r="D448" s="17"/>
     </row>
     <row r="449" spans="1:4">
-      <c r="A449" s="19"/>
+      <c r="A449" s="49"/>
       <c r="D449" s="17"/>
     </row>
     <row r="450" spans="1:4">
-      <c r="A450" s="19"/>
+      <c r="A450" s="49"/>
       <c r="D450" s="17"/>
     </row>
     <row r="451" spans="1:4">
-      <c r="A451" s="19"/>
+      <c r="A451" s="49"/>
       <c r="D451" s="17"/>
     </row>
     <row r="452" spans="1:4">
-      <c r="A452" s="19"/>
+      <c r="A452" s="49"/>
       <c r="D452" s="17"/>
     </row>
     <row r="453" spans="1:4">
-      <c r="A453" s="19"/>
+      <c r="A453" s="49"/>
       <c r="D453" s="17"/>
     </row>
     <row r="454" spans="1:4">
-      <c r="A454" s="19"/>
+      <c r="A454" s="49"/>
       <c r="D454" s="17"/>
     </row>
     <row r="455" spans="1:4">
-      <c r="A455" s="19"/>
+      <c r="A455" s="49"/>
       <c r="D455" s="17"/>
     </row>
     <row r="456" spans="1:4">
-      <c r="A456" s="19"/>
+      <c r="A456" s="49"/>
       <c r="D456" s="17"/>
     </row>
     <row r="457" spans="1:4">
-      <c r="A457" s="19"/>
+      <c r="A457" s="49"/>
       <c r="D457" s="17"/>
     </row>
     <row r="458" spans="1:4">
-      <c r="A458" s="19"/>
+      <c r="A458" s="49"/>
       <c r="D458" s="17"/>
     </row>
     <row r="459" spans="1:4">
-      <c r="A459" s="19"/>
+      <c r="A459" s="49"/>
       <c r="D459" s="17"/>
     </row>
     <row r="460" spans="1:4">
-      <c r="A460" s="19"/>
+      <c r="A460" s="49"/>
       <c r="D460" s="17"/>
     </row>
     <row r="461" spans="1:4">
-      <c r="A461" s="19"/>
+      <c r="A461" s="49"/>
       <c r="D461" s="17"/>
     </row>
     <row r="462" spans="1:4">
-      <c r="A462" s="19"/>
+      <c r="A462" s="49"/>
       <c r="D462" s="17"/>
     </row>
     <row r="463" spans="1:4">
-      <c r="A463" s="19"/>
+      <c r="A463" s="49"/>
       <c r="D463" s="17"/>
     </row>
     <row r="464" spans="1:4">
-      <c r="A464" s="19"/>
+      <c r="A464" s="49"/>
       <c r="D464" s="17"/>
     </row>
     <row r="465" spans="1:4">
-      <c r="A465" s="19"/>
+      <c r="A465" s="49"/>
       <c r="D465" s="17"/>
     </row>
     <row r="466" spans="1:4">
-      <c r="A466" s="19"/>
+      <c r="A466" s="49"/>
       <c r="D466" s="17"/>
     </row>
     <row r="467" spans="1:4">
-      <c r="A467" s="19"/>
+      <c r="A467" s="49"/>
       <c r="D467" s="17"/>
     </row>
     <row r="468" spans="1:4">
-      <c r="A468" s="19"/>
+      <c r="A468" s="49"/>
       <c r="D468" s="17"/>
     </row>
     <row r="469" spans="1:4">
-      <c r="A469" s="19"/>
+      <c r="A469" s="49"/>
       <c r="D469" s="17"/>
     </row>
     <row r="470" spans="1:4">
-      <c r="A470" s="19"/>
+      <c r="A470" s="49"/>
       <c r="D470" s="17"/>
     </row>
     <row r="471" spans="1:4">
-      <c r="A471" s="19"/>
+      <c r="A471" s="49"/>
       <c r="D471" s="17"/>
     </row>
     <row r="472" spans="1:4">
-      <c r="A472" s="19"/>
+      <c r="A472" s="49"/>
       <c r="D472" s="17"/>
     </row>
     <row r="473" spans="1:4">
-      <c r="A473" s="19"/>
+      <c r="A473" s="49"/>
       <c r="D473" s="17"/>
     </row>
     <row r="474" spans="1:4">
-      <c r="A474" s="19"/>
+      <c r="A474" s="49"/>
       <c r="D474" s="17"/>
     </row>
     <row r="475" spans="1:4">
-      <c r="A475" s="19"/>
+      <c r="A475" s="49"/>
       <c r="D475" s="17"/>
     </row>
     <row r="476" spans="1:4">
-      <c r="A476" s="19"/>
+      <c r="A476" s="49"/>
       <c r="D476" s="17"/>
     </row>
     <row r="477" spans="1:4">
-      <c r="A477" s="19"/>
+      <c r="A477" s="49"/>
       <c r="D477" s="17"/>
     </row>
     <row r="478" spans="1:4">
-      <c r="A478" s="19"/>
+      <c r="A478" s="49"/>
       <c r="D478" s="17"/>
     </row>
     <row r="479" spans="1:4">
-      <c r="A479" s="19"/>
+      <c r="A479" s="49"/>
       <c r="D479" s="17"/>
     </row>
     <row r="480" spans="1:4">
-      <c r="A480" s="19"/>
+      <c r="A480" s="49"/>
       <c r="D480" s="17"/>
     </row>
     <row r="481" spans="1:4">
-      <c r="A481" s="19"/>
+      <c r="A481" s="49"/>
       <c r="D481" s="17"/>
     </row>
     <row r="482" spans="1:4">
-      <c r="A482" s="19"/>
+      <c r="A482" s="49"/>
       <c r="D482" s="17"/>
     </row>
     <row r="483" spans="1:4">
-      <c r="A483" s="19"/>
+      <c r="A483" s="49"/>
       <c r="D483" s="17"/>
     </row>
     <row r="484" spans="1:4">
-      <c r="A484" s="19"/>
+      <c r="A484" s="49"/>
       <c r="D484" s="17"/>
     </row>
     <row r="485" spans="1:4">
-      <c r="A485" s="19"/>
+      <c r="A485" s="49"/>
       <c r="D485" s="17"/>
     </row>
     <row r="486" spans="1:4">
-      <c r="A486" s="19"/>
+      <c r="A486" s="49"/>
       <c r="D486" s="17"/>
     </row>
     <row r="487" spans="1:4">
-      <c r="A487" s="19"/>
+      <c r="A487" s="49"/>
       <c r="D487" s="17"/>
     </row>
     <row r="488" spans="1:4">
-      <c r="A488" s="19"/>
+      <c r="A488" s="49"/>
       <c r="D488" s="17"/>
     </row>
     <row r="489" spans="1:4">
-      <c r="A489" s="19"/>
+      <c r="A489" s="49"/>
       <c r="D489" s="17"/>
     </row>
     <row r="490" spans="1:4">
-      <c r="A490" s="19"/>
+      <c r="A490" s="49"/>
       <c r="D490" s="17"/>
     </row>
     <row r="491" spans="1:4">
-      <c r="A491" s="19"/>
+      <c r="A491" s="49"/>
       <c r="D491" s="17"/>
     </row>
     <row r="492" spans="1:4">
-      <c r="A492" s="19"/>
+      <c r="A492" s="49"/>
       <c r="D492" s="17"/>
     </row>
     <row r="493" spans="1:4">
-      <c r="A493" s="19"/>
+      <c r="A493" s="49"/>
       <c r="D493" s="17"/>
     </row>
     <row r="494" spans="1:4">
-      <c r="A494" s="19"/>
+      <c r="A494" s="49"/>
       <c r="D494" s="17"/>
     </row>
     <row r="495" spans="1:4">
-      <c r="A495" s="19"/>
+      <c r="A495" s="49"/>
       <c r="D495" s="17"/>
     </row>
     <row r="496" spans="1:4">
-      <c r="A496" s="19"/>
+      <c r="A496" s="49"/>
       <c r="D496" s="17"/>
     </row>
     <row r="497" spans="1:4">
-      <c r="A497" s="19"/>
+      <c r="A497" s="49"/>
       <c r="D497" s="17"/>
     </row>
     <row r="498" spans="1:4">
-      <c r="A498" s="19"/>
+      <c r="A498" s="49"/>
       <c r="D498" s="17"/>
     </row>
     <row r="499" spans="1:4">
-      <c r="A499" s="19"/>
+      <c r="A499" s="49"/>
       <c r="D499" s="17"/>
     </row>
     <row r="500" spans="1:4">
-      <c r="A500" s="19"/>
+      <c r="A500" s="49"/>
       <c r="D500" s="17"/>
     </row>
     <row r="501" spans="1:4">
-      <c r="A501" s="19"/>
+      <c r="A501" s="49"/>
       <c r="D501" s="17"/>
     </row>
     <row r="502" spans="1:4">
-      <c r="A502" s="19"/>
+      <c r="A502" s="49"/>
       <c r="D502" s="17"/>
     </row>
     <row r="503" spans="1:4">
-      <c r="A503" s="19"/>
+      <c r="A503" s="49"/>
       <c r="D503" s="17"/>
     </row>
     <row r="504" spans="1:4">
-      <c r="A504" s="19"/>
+      <c r="A504" s="49"/>
       <c r="D504" s="17"/>
     </row>
     <row r="505" spans="1:4">
-      <c r="A505" s="19"/>
+      <c r="A505" s="49"/>
       <c r="D505" s="17"/>
     </row>
     <row r="506" spans="1:4">
-      <c r="A506" s="19"/>
+      <c r="A506" s="49"/>
       <c r="D506" s="17"/>
     </row>
     <row r="507" spans="1:4">
-      <c r="A507" s="19"/>
+      <c r="A507" s="49"/>
       <c r="D507" s="17"/>
     </row>
     <row r="508" spans="1:4">
-      <c r="A508" s="19"/>
+      <c r="A508" s="49"/>
       <c r="D508" s="17"/>
     </row>
     <row r="509" spans="1:4">
-      <c r="A509" s="19"/>
+      <c r="A509" s="49"/>
       <c r="D509" s="17"/>
     </row>
     <row r="510" spans="1:4">
-      <c r="A510" s="19"/>
+      <c r="A510" s="49"/>
       <c r="D510" s="17"/>
     </row>
     <row r="511" spans="1:4">
-      <c r="A511" s="19"/>
+      <c r="A511" s="49"/>
       <c r="D511" s="17"/>
     </row>
     <row r="512" spans="1:4">
-      <c r="A512" s="19"/>
+      <c r="A512" s="49"/>
       <c r="D512" s="17"/>
     </row>
     <row r="513" spans="1:4">
-      <c r="A513" s="19"/>
+      <c r="A513" s="49"/>
       <c r="D513" s="17"/>
     </row>
     <row r="514" spans="1:4">
-      <c r="A514" s="19"/>
+      <c r="A514" s="49"/>
       <c r="D514" s="17"/>
     </row>
     <row r="515" spans="1:4">
-      <c r="A515" s="19"/>
+      <c r="A515" s="49"/>
       <c r="D515" s="17"/>
     </row>
     <row r="516" spans="1:4">
-      <c r="A516" s="19"/>
+      <c r="A516" s="49"/>
       <c r="D516" s="17"/>
     </row>
     <row r="517" spans="1:4">
-      <c r="A517" s="19"/>
+      <c r="A517" s="49"/>
       <c r="D517" s="17"/>
     </row>
     <row r="518" spans="1:4">
-      <c r="A518" s="19"/>
+      <c r="A518" s="49"/>
       <c r="D518" s="17"/>
     </row>
     <row r="519" spans="1:4">
-      <c r="A519" s="19"/>
+      <c r="A519" s="49"/>
       <c r="D519" s="17"/>
     </row>
     <row r="520" spans="1:4">
-      <c r="A520" s="19"/>
+      <c r="A520" s="49"/>
       <c r="D520" s="17"/>
     </row>
     <row r="521" spans="1:4">
-      <c r="A521" s="19"/>
+      <c r="A521" s="49"/>
       <c r="D521" s="17"/>
     </row>
     <row r="522" spans="1:4">
-      <c r="A522" s="19"/>
+      <c r="A522" s="49"/>
       <c r="D522" s="17"/>
     </row>
     <row r="523" spans="1:4">
-      <c r="A523" s="19"/>
+      <c r="A523" s="49"/>
       <c r="D523" s="17"/>
     </row>
     <row r="524" spans="1:4">
-      <c r="A524" s="19"/>
+      <c r="A524" s="49"/>
       <c r="D524" s="17"/>
     </row>
     <row r="525" spans="1:4">
-      <c r="A525" s="19"/>
+      <c r="A525" s="49"/>
       <c r="D525" s="17"/>
     </row>
     <row r="526" spans="1:4">
-      <c r="A526" s="19"/>
+      <c r="A526" s="49"/>
       <c r="D526" s="17"/>
     </row>
     <row r="527" spans="1:4">
-      <c r="A527" s="19"/>
+      <c r="A527" s="49"/>
       <c r="D527" s="17"/>
     </row>
     <row r="528" spans="1:4">
-      <c r="A528" s="19"/>
+      <c r="A528" s="49"/>
       <c r="D528" s="17"/>
     </row>
     <row r="529" spans="1:4">
-      <c r="A529" s="19"/>
+      <c r="A529" s="49"/>
       <c r="D529" s="17"/>
     </row>
     <row r="530" spans="1:4">
-      <c r="A530" s="19"/>
+      <c r="A530" s="49"/>
       <c r="D530" s="17"/>
     </row>
     <row r="531" spans="1:4">
-      <c r="A531" s="19"/>
+      <c r="A531" s="49"/>
       <c r="D531" s="17"/>
     </row>
     <row r="532" spans="1:4">
-      <c r="A532" s="19"/>
+      <c r="A532" s="49"/>
       <c r="D532" s="17"/>
     </row>
     <row r="533" spans="1:4">
-      <c r="A533" s="19"/>
+      <c r="A533" s="49"/>
       <c r="D533" s="17"/>
     </row>
     <row r="534" spans="1:4">
-      <c r="A534" s="19"/>
+      <c r="A534" s="49"/>
       <c r="D534" s="17"/>
     </row>
     <row r="535" spans="1:4">
-      <c r="A535" s="19"/>
+      <c r="A535" s="49"/>
       <c r="D535" s="17"/>
     </row>
     <row r="536" spans="1:4">
-      <c r="A536" s="19"/>
+      <c r="A536" s="49"/>
       <c r="D536" s="17"/>
     </row>
     <row r="537" spans="1:4">
-      <c r="A537" s="19"/>
+      <c r="A537" s="49"/>
       <c r="D537" s="17"/>
     </row>
     <row r="538" spans="1:4">
-      <c r="A538" s="19"/>
+      <c r="A538" s="49"/>
       <c r="D538" s="17"/>
     </row>
     <row r="539" spans="1:4">
-      <c r="A539" s="19"/>
+      <c r="A539" s="49"/>
       <c r="D539" s="17"/>
     </row>
     <row r="540" spans="1:4">
-      <c r="A540" s="19"/>
+      <c r="A540" s="49"/>
       <c r="D540" s="17"/>
     </row>
     <row r="541" spans="1:4">
-      <c r="A541" s="19"/>
+      <c r="A541" s="49"/>
       <c r="D541" s="17"/>
     </row>
     <row r="542" spans="1:4">
-      <c r="A542" s="19"/>
+      <c r="A542" s="49"/>
       <c r="D542" s="17"/>
     </row>
     <row r="543" spans="1:4">
-      <c r="A543" s="19"/>
+      <c r="A543" s="49"/>
       <c r="D543" s="17"/>
     </row>
     <row r="544" spans="1:4">
-      <c r="A544" s="19"/>
+      <c r="A544" s="49"/>
       <c r="D544" s="17"/>
     </row>
     <row r="545" spans="1:4">
-      <c r="A545" s="19"/>
+      <c r="A545" s="49"/>
       <c r="D545" s="17"/>
     </row>
     <row r="546" spans="1:4">
-      <c r="A546" s="19"/>
+      <c r="A546" s="49"/>
       <c r="D546" s="17"/>
     </row>
     <row r="547" spans="1:4">
-      <c r="A547" s="19"/>
+      <c r="A547" s="49"/>
       <c r="D547" s="17"/>
     </row>
     <row r="548" spans="1:4">
-      <c r="A548" s="19"/>
+      <c r="A548" s="49"/>
       <c r="D548" s="17"/>
     </row>
     <row r="549" spans="1:4">
-      <c r="A549" s="19"/>
+      <c r="A549" s="49"/>
       <c r="D549" s="17"/>
     </row>
     <row r="550" spans="1:4">
-      <c r="A550" s="19"/>
+      <c r="A550" s="49"/>
       <c r="D550" s="17"/>
     </row>
     <row r="551" spans="1:4">
-      <c r="A551" s="19"/>
+      <c r="A551" s="49"/>
       <c r="D551" s="17"/>
     </row>
     <row r="552" spans="1:4">
-      <c r="A552" s="19"/>
+      <c r="A552" s="49"/>
       <c r="D552" s="17"/>
     </row>
     <row r="553" spans="1:4">
-      <c r="A553" s="19"/>
+      <c r="A553" s="49"/>
       <c r="D553" s="17"/>
     </row>
     <row r="554" spans="1:4">
-      <c r="A554" s="19"/>
+      <c r="A554" s="49"/>
       <c r="D554" s="17"/>
     </row>
     <row r="555" spans="1:4">
-      <c r="A555" s="19"/>
+      <c r="A555" s="49"/>
       <c r="D555" s="17"/>
     </row>
     <row r="556" spans="1:4">
-      <c r="A556" s="19"/>
+      <c r="A556" s="49"/>
       <c r="D556" s="17"/>
     </row>
     <row r="557" spans="1:4">
-      <c r="A557" s="19"/>
+      <c r="A557" s="49"/>
       <c r="D557" s="17"/>
     </row>
     <row r="558" spans="1:4">
-      <c r="A558" s="19"/>
+      <c r="A558" s="49"/>
       <c r="D558" s="17"/>
     </row>
     <row r="559" spans="1:4">
-      <c r="A559" s="19"/>
+      <c r="A559" s="49"/>
       <c r="D559" s="17"/>
     </row>
     <row r="560" spans="1:4">
-      <c r="A560" s="19"/>
+      <c r="A560" s="49"/>
       <c r="D560" s="17"/>
     </row>
     <row r="561" spans="1:4">
-      <c r="A561" s="19"/>
+      <c r="A561" s="49"/>
       <c r="D561" s="17"/>
     </row>
     <row r="562" spans="1:4">
-      <c r="A562" s="19"/>
+      <c r="A562" s="49"/>
       <c r="D562" s="17"/>
     </row>
     <row r="563" spans="1:4">
-      <c r="A563" s="19"/>
+      <c r="A563" s="49"/>
       <c r="D563" s="17"/>
     </row>
     <row r="564" spans="1:4">
-      <c r="A564" s="19"/>
+      <c r="A564" s="49"/>
       <c r="D564" s="17"/>
     </row>
     <row r="565" spans="1:4">
-      <c r="A565" s="19"/>
+      <c r="A565" s="49"/>
       <c r="D565" s="17"/>
     </row>
     <row r="566" spans="1:4">
-      <c r="A566" s="19"/>
+      <c r="A566" s="49"/>
       <c r="D566" s="17"/>
     </row>
     <row r="567" spans="1:4">
-      <c r="A567" s="19"/>
+      <c r="A567" s="49"/>
       <c r="D567" s="17"/>
     </row>
     <row r="568" spans="1:4">
-      <c r="A568" s="19"/>
+      <c r="A568" s="49"/>
       <c r="D568" s="17"/>
     </row>
     <row r="569" spans="1:4">
-      <c r="A569" s="19"/>
+      <c r="A569" s="49"/>
       <c r="D569" s="17"/>
     </row>
     <row r="570" spans="1:4">
-      <c r="A570" s="19"/>
+      <c r="A570" s="49"/>
       <c r="D570" s="17"/>
     </row>
     <row r="571" spans="1:4">
-      <c r="A571" s="19"/>
+      <c r="A571" s="49"/>
       <c r="D571" s="17"/>
     </row>
     <row r="572" spans="1:4">
-      <c r="A572" s="19"/>
+      <c r="A572" s="49"/>
       <c r="D572" s="17"/>
     </row>
     <row r="573" spans="1:4">
-      <c r="A573" s="19"/>
+      <c r="A573" s="49"/>
       <c r="D573" s="17"/>
     </row>
     <row r="574" spans="1:4">
-      <c r="A574" s="19"/>
+      <c r="A574" s="49"/>
       <c r="D574" s="17"/>
     </row>
     <row r="575" spans="1:4">
-      <c r="A575" s="19"/>
+      <c r="A575" s="49"/>
       <c r="D575" s="17"/>
     </row>
     <row r="576" spans="1:4">
-      <c r="A576" s="19"/>
+      <c r="A576" s="49"/>
       <c r="D576" s="17"/>
     </row>
     <row r="577" spans="1:4">
-      <c r="A577" s="19"/>
+      <c r="A577" s="49"/>
       <c r="D577" s="17"/>
     </row>
     <row r="578" spans="1:4">
-      <c r="A578" s="19"/>
+      <c r="A578" s="49"/>
       <c r="D578" s="17"/>
     </row>
     <row r="579" spans="1:4">
-      <c r="A579" s="19"/>
+      <c r="A579" s="49"/>
       <c r="D579" s="17"/>
     </row>
     <row r="580" spans="1:4">
-      <c r="A580" s="19"/>
+      <c r="A580" s="49"/>
       <c r="D580" s="17"/>
     </row>
     <row r="581" spans="1:4">
-      <c r="A581" s="19"/>
+      <c r="A581" s="49"/>
       <c r="D581" s="17"/>
     </row>
     <row r="582" spans="1:4">
-      <c r="A582" s="19"/>
+      <c r="A582" s="49"/>
       <c r="D582" s="17"/>
     </row>
     <row r="583" spans="1:4">
-      <c r="A583" s="19"/>
+      <c r="A583" s="49"/>
       <c r="D583" s="17"/>
     </row>
     <row r="584" spans="1:4">
-      <c r="A584" s="19"/>
+      <c r="A584" s="49"/>
       <c r="D584" s="17"/>
     </row>
     <row r="585" spans="1:4">
-      <c r="A585" s="19"/>
+      <c r="A585" s="49"/>
       <c r="D585" s="17"/>
     </row>
     <row r="586" spans="1:4">
-      <c r="A586" s="19"/>
+      <c r="A586" s="49"/>
       <c r="D586" s="17"/>
     </row>
     <row r="587" spans="1:4">
-      <c r="A587" s="19"/>
+      <c r="A587" s="49"/>
       <c r="D587" s="17"/>
     </row>
     <row r="588" spans="1:4">
-      <c r="A588" s="19"/>
+      <c r="A588" s="49"/>
       <c r="D588" s="17"/>
     </row>
     <row r="589" spans="1:4">
-      <c r="A589" s="19"/>
+      <c r="A589" s="49"/>
       <c r="D589" s="17"/>
     </row>
     <row r="590" spans="1:4">
-      <c r="A590" s="19"/>
+      <c r="A590" s="49"/>
       <c r="D590" s="17"/>
     </row>
     <row r="591" spans="1:4">
-      <c r="A591" s="19"/>
+      <c r="A591" s="49"/>
       <c r="D591" s="17"/>
     </row>
     <row r="592" spans="1:4">
-      <c r="A592" s="19"/>
+      <c r="A592" s="49"/>
       <c r="D592" s="17"/>
     </row>
     <row r="593" spans="1:4">
-      <c r="A593" s="19"/>
+      <c r="A593" s="49"/>
       <c r="D593" s="17"/>
     </row>
     <row r="594" spans="1:4">
-      <c r="A594" s="19"/>
+      <c r="A594" s="49"/>
       <c r="D594" s="17"/>
     </row>
     <row r="595" spans="1:4">
-      <c r="A595" s="19"/>
+      <c r="A595" s="49"/>
       <c r="D595" s="17"/>
     </row>
     <row r="596" spans="1:4">
-      <c r="A596" s="19"/>
+      <c r="A596" s="49"/>
       <c r="D596" s="17"/>
     </row>
     <row r="597" spans="1:4">
-      <c r="A597" s="19"/>
+      <c r="A597" s="49"/>
       <c r="D597" s="17"/>
     </row>
     <row r="598" spans="1:4">
-      <c r="A598" s="19"/>
+      <c r="A598" s="49"/>
       <c r="D598" s="17"/>
     </row>
     <row r="599" spans="1:4">
-      <c r="A599" s="19"/>
+      <c r="A599" s="49"/>
       <c r="D599" s="17"/>
     </row>
     <row r="600" spans="1:4">
-      <c r="A600" s="19"/>
+      <c r="A600" s="49"/>
       <c r="D600" s="17"/>
     </row>
     <row r="601" spans="1:4">
-      <c r="A601" s="19"/>
+      <c r="A601" s="49"/>
       <c r="D601" s="17"/>
     </row>
     <row r="602" spans="1:4">
-      <c r="A602" s="19"/>
+      <c r="A602" s="49"/>
       <c r="D602" s="17"/>
     </row>
     <row r="603" spans="1:4">
-      <c r="A603" s="19"/>
+      <c r="A603" s="49"/>
       <c r="D603" s="17"/>
     </row>
     <row r="604" spans="1:4">
-      <c r="A604" s="19"/>
+      <c r="A604" s="49"/>
       <c r="D604" s="17"/>
     </row>
     <row r="605" spans="1:4">
-      <c r="A605" s="19"/>
+      <c r="A605" s="49"/>
       <c r="D605" s="17"/>
     </row>
     <row r="606" spans="1:4">
-      <c r="A606" s="19"/>
+      <c r="A606" s="49"/>
       <c r="D606" s="17"/>
     </row>
     <row r="607" spans="1:4">
-      <c r="A607" s="19"/>
+      <c r="A607" s="49"/>
       <c r="D607" s="17"/>
     </row>
     <row r="608" spans="1:4">
-      <c r="A608" s="19"/>
+      <c r="A608" s="49"/>
       <c r="D608" s="17"/>
     </row>
     <row r="609" spans="1:4">
-      <c r="A609" s="19"/>
+      <c r="A609" s="49"/>
       <c r="D609" s="17"/>
     </row>
     <row r="610" spans="1:4">
-      <c r="A610" s="19"/>
+      <c r="A610" s="49"/>
       <c r="D610" s="17"/>
     </row>
     <row r="611" spans="1:4">
-      <c r="A611" s="19"/>
+      <c r="A611" s="49"/>
       <c r="D611" s="17"/>
     </row>
     <row r="612" spans="1:4">
-      <c r="A612" s="19"/>
+      <c r="A612" s="49"/>
       <c r="D612" s="17"/>
     </row>
     <row r="613" spans="1:4">
-      <c r="A613" s="19"/>
+      <c r="A613" s="49"/>
       <c r="D613" s="17"/>
     </row>
     <row r="614" spans="1:4">
-      <c r="A614" s="19"/>
+      <c r="A614" s="49"/>
       <c r="D614" s="17"/>
     </row>
     <row r="615" spans="1:4">
-      <c r="A615" s="19"/>
+      <c r="A615" s="49"/>
       <c r="D615" s="17"/>
     </row>
     <row r="616" spans="1:4">
-      <c r="A616" s="19"/>
+      <c r="A616" s="49"/>
       <c r="D616" s="17"/>
     </row>
     <row r="617" spans="1:4">
-      <c r="A617" s="19"/>
+      <c r="A617" s="49"/>
       <c r="D617" s="17"/>
     </row>
     <row r="618" spans="1:4">
-      <c r="A618" s="19"/>
+      <c r="A618" s="49"/>
       <c r="D618" s="17"/>
     </row>
     <row r="619" spans="1:4">
-      <c r="A619" s="19"/>
+      <c r="A619" s="49"/>
       <c r="D619" s="17"/>
     </row>
     <row r="620" spans="1:4">
-      <c r="A620" s="19"/>
+      <c r="A620" s="49"/>
       <c r="D620" s="17"/>
     </row>
     <row r="621" spans="1:4">
-      <c r="A621" s="19"/>
+      <c r="A621" s="49"/>
       <c r="D621" s="17"/>
     </row>
     <row r="622" spans="1:4">
-      <c r="A622" s="19"/>
+      <c r="A622" s="49"/>
       <c r="D622" s="17"/>
     </row>
     <row r="623" spans="1:4">
-      <c r="A623" s="19"/>
+      <c r="A623" s="49"/>
       <c r="D623" s="17"/>
     </row>
     <row r="624" spans="1:4">
-      <c r="A624" s="19"/>
+      <c r="A624" s="49"/>
       <c r="D624" s="17"/>
     </row>
     <row r="625" spans="1:4">
-      <c r="A625" s="19"/>
+      <c r="A625" s="49"/>
       <c r="D625" s="17"/>
     </row>
     <row r="626" spans="1:4">
-      <c r="A626" s="19"/>
+      <c r="A626" s="49"/>
       <c r="D626" s="17"/>
     </row>
     <row r="627" spans="1:4">
-      <c r="A627" s="19"/>
+      <c r="A627" s="49"/>
       <c r="D627" s="17"/>
     </row>
     <row r="628" spans="1:4">
-      <c r="A628" s="19"/>
+      <c r="A628" s="49"/>
       <c r="D628" s="17"/>
     </row>
     <row r="629" spans="1:4">
-      <c r="A629" s="19"/>
+      <c r="A629" s="49"/>
       <c r="D629" s="17"/>
     </row>
     <row r="630" spans="1:4">
-      <c r="A630" s="19"/>
+      <c r="A630" s="49"/>
       <c r="D630" s="17"/>
     </row>
     <row r="631" spans="1:4">
-      <c r="A631" s="19"/>
+      <c r="A631" s="49"/>
       <c r="D631" s="17"/>
     </row>
     <row r="632" spans="1:4">
-      <c r="A632" s="19"/>
+      <c r="A632" s="49"/>
       <c r="D632" s="17"/>
     </row>
     <row r="633" spans="1:4">
-      <c r="A633" s="19"/>
+      <c r="A633" s="49"/>
       <c r="D633" s="17"/>
     </row>
     <row r="634" spans="1:4">
-      <c r="A634" s="19"/>
+      <c r="A634" s="49"/>
       <c r="D634" s="17"/>
     </row>
     <row r="635" spans="1:4">
-      <c r="A635" s="19"/>
+      <c r="A635" s="49"/>
       <c r="D635" s="17"/>
     </row>
     <row r="636" spans="1:4">
-      <c r="A636" s="19"/>
+      <c r="A636" s="49"/>
       <c r="D636" s="17"/>
     </row>
     <row r="637" spans="1:4">
-      <c r="A637" s="19"/>
+      <c r="A637" s="49"/>
       <c r="D637" s="17"/>
     </row>
     <row r="638" spans="1:4">
-      <c r="A638" s="19"/>
+      <c r="A638" s="49"/>
       <c r="D638" s="17"/>
     </row>
     <row r="639" spans="1:4">
-      <c r="A639" s="19"/>
+      <c r="A639" s="49"/>
       <c r="D639" s="17"/>
     </row>
     <row r="640" spans="1:4">
-      <c r="A640" s="19"/>
+      <c r="A640" s="49"/>
       <c r="D640" s="17"/>
     </row>
     <row r="641" spans="1:4">
-      <c r="A641" s="19"/>
+      <c r="A641" s="49"/>
       <c r="D641" s="17"/>
     </row>
     <row r="642" spans="1:4">
-      <c r="A642" s="19"/>
+      <c r="A642" s="49"/>
       <c r="D642" s="17"/>
     </row>
     <row r="643" spans="1:4">
-      <c r="A643" s="19"/>
+      <c r="A643" s="49"/>
       <c r="D643" s="17"/>
     </row>
     <row r="644" spans="1:4">
-      <c r="A644" s="19"/>
+      <c r="A644" s="49"/>
       <c r="D644" s="17"/>
     </row>
     <row r="645" spans="1:4">
-      <c r="A645" s="19"/>
+      <c r="A645" s="49"/>
       <c r="D645" s="17"/>
     </row>
     <row r="646" spans="1:4">
-      <c r="A646" s="19"/>
+      <c r="A646" s="49"/>
       <c r="D646" s="17"/>
     </row>
     <row r="647" spans="1:4">
-      <c r="A647" s="19"/>
+      <c r="A647" s="49"/>
       <c r="D647" s="17"/>
     </row>
     <row r="648" spans="1:4">
-      <c r="A648" s="19"/>
+      <c r="A648" s="49"/>
       <c r="D648" s="17"/>
     </row>
     <row r="649" spans="1:4">
-      <c r="A649" s="19"/>
+      <c r="A649" s="49"/>
       <c r="D649" s="17"/>
     </row>
     <row r="650" spans="1:4">
-      <c r="A650" s="19"/>
+      <c r="A650" s="49"/>
       <c r="D650" s="17"/>
     </row>
     <row r="651" spans="1:4">
-      <c r="A651" s="19"/>
+      <c r="A651" s="49"/>
       <c r="D651" s="17"/>
     </row>
     <row r="652" spans="1:4">
-      <c r="A652" s="19"/>
+      <c r="A652" s="49"/>
       <c r="D652" s="17"/>
     </row>
     <row r="653" spans="1:4">
-      <c r="A653" s="19"/>
+      <c r="A653" s="49"/>
       <c r="D653" s="17"/>
     </row>
     <row r="654" spans="1:4">
-      <c r="A654" s="19"/>
+      <c r="A654" s="49"/>
       <c r="D654" s="17"/>
     </row>
     <row r="655" spans="1:4">
-      <c r="A655" s="19"/>
+      <c r="A655" s="49"/>
       <c r="D655" s="17"/>
     </row>
     <row r="656" spans="1:4">
-      <c r="A656" s="19"/>
+      <c r="A656" s="49"/>
       <c r="D656" s="17"/>
     </row>
     <row r="657" spans="1:4">
-      <c r="A657" s="19"/>
+      <c r="A657" s="49"/>
       <c r="D657" s="17"/>
     </row>
     <row r="658" spans="1:4">
-      <c r="A658" s="19"/>
+      <c r="A658" s="49"/>
       <c r="D658" s="17"/>
     </row>
     <row r="659" spans="1:4">
-      <c r="A659" s="19"/>
+      <c r="A659" s="49"/>
       <c r="D659" s="17"/>
     </row>
     <row r="660" spans="1:4">
-      <c r="A660" s="19"/>
+      <c r="A660" s="49"/>
       <c r="D660" s="17"/>
     </row>
     <row r="661" spans="1:4">
-      <c r="A661" s="19"/>
+      <c r="A661" s="49"/>
       <c r="D661" s="17"/>
     </row>
     <row r="662" spans="1:4">
-      <c r="A662" s="19"/>
+      <c r="A662" s="49"/>
       <c r="D662" s="17"/>
     </row>
     <row r="663" spans="1:4">
-      <c r="A663" s="19"/>
+      <c r="A663" s="49"/>
       <c r="D663" s="17"/>
     </row>
     <row r="664" spans="1:4">
-      <c r="A664" s="19"/>
+      <c r="A664" s="49"/>
       <c r="D664" s="17"/>
     </row>
     <row r="665" spans="1:4">
-      <c r="A665" s="19"/>
+      <c r="A665" s="49"/>
       <c r="D665" s="17"/>
     </row>
     <row r="666" spans="1:4">
-      <c r="A666" s="19"/>
+      <c r="A666" s="49"/>
       <c r="D666" s="17"/>
     </row>
     <row r="667" spans="1:4">
-      <c r="A667" s="19"/>
+      <c r="A667" s="49"/>
       <c r="D667" s="17"/>
     </row>
     <row r="668" spans="1:4">
-      <c r="A668" s="19"/>
+      <c r="A668" s="49"/>
       <c r="D668" s="17"/>
     </row>
     <row r="669" spans="1:4">
-      <c r="A669" s="19"/>
+      <c r="A669" s="49"/>
       <c r="D669" s="17"/>
     </row>
     <row r="670" spans="1:4">
-      <c r="A670" s="19"/>
+      <c r="A670" s="49"/>
       <c r="D670" s="17"/>
     </row>
     <row r="671" spans="1:4">
-      <c r="A671" s="19"/>
+      <c r="A671" s="49"/>
       <c r="D671" s="17"/>
     </row>
     <row r="672" spans="1:4">
-      <c r="A672" s="19"/>
+      <c r="A672" s="49"/>
       <c r="D672" s="17"/>
     </row>
     <row r="673" spans="1:4">
-      <c r="A673" s="19"/>
+      <c r="A673" s="49"/>
       <c r="D673" s="17"/>
     </row>
     <row r="674" spans="1:4">
-      <c r="A674" s="19"/>
+      <c r="A674" s="49"/>
       <c r="D674" s="17"/>
     </row>
     <row r="675" spans="1:4">
-      <c r="A675" s="19"/>
+      <c r="A675" s="49"/>
       <c r="D675" s="17"/>
     </row>
     <row r="676" spans="1:4">
-      <c r="A676" s="19"/>
+      <c r="A676" s="49"/>
       <c r="D676" s="17"/>
     </row>
     <row r="677" spans="1:4">
-      <c r="A677" s="19"/>
+      <c r="A677" s="49"/>
       <c r="D677" s="17"/>
     </row>
     <row r="678" spans="1:4">
-      <c r="A678" s="19"/>
+      <c r="A678" s="49"/>
       <c r="D678" s="17"/>
     </row>
     <row r="679" spans="1:4">
-      <c r="A679" s="19"/>
+      <c r="A679" s="49"/>
       <c r="D679" s="17"/>
     </row>
     <row r="680" spans="1:4">
-      <c r="A680" s="19"/>
+      <c r="A680" s="49"/>
       <c r="D680" s="17"/>
     </row>
     <row r="681" spans="1:4">
-      <c r="A681" s="19"/>
+      <c r="A681" s="49"/>
       <c r="D681" s="17"/>
     </row>
     <row r="682" spans="1:4">
-      <c r="A682" s="19"/>
+      <c r="A682" s="49"/>
       <c r="D682" s="17"/>
     </row>
     <row r="683" spans="1:4">
-      <c r="A683" s="19"/>
+      <c r="A683" s="49"/>
       <c r="D683" s="17"/>
     </row>
     <row r="684" spans="1:4">
-      <c r="A684" s="19"/>
+      <c r="A684" s="49"/>
       <c r="D684" s="17"/>
     </row>
     <row r="685" spans="1:4">
-      <c r="A685" s="19"/>
+      <c r="A685" s="49"/>
       <c r="D685" s="17"/>
     </row>
     <row r="686" spans="1:4">
-      <c r="A686" s="19"/>
+      <c r="A686" s="49"/>
       <c r="D686" s="17"/>
     </row>
     <row r="687" spans="1:4">
-      <c r="A687" s="19"/>
+      <c r="A687" s="49"/>
       <c r="D687" s="17"/>
     </row>
     <row r="688" spans="1:4">
-      <c r="A688" s="19"/>
+      <c r="A688" s="49"/>
       <c r="D688" s="17"/>
     </row>
     <row r="689" spans="1:4">
-      <c r="A689" s="19"/>
+      <c r="A689" s="49"/>
       <c r="D689" s="17"/>
     </row>
     <row r="690" spans="1:4">
-      <c r="A690" s="19"/>
+      <c r="A690" s="49"/>
       <c r="D690" s="17"/>
     </row>
     <row r="691" spans="1:4">
-      <c r="A691" s="19"/>
+      <c r="A691" s="49"/>
       <c r="D691" s="17"/>
     </row>
     <row r="692" spans="1:4">
-      <c r="A692" s="19"/>
+      <c r="A692" s="49"/>
       <c r="D692" s="17"/>
     </row>
     <row r="693" spans="1:4">
-      <c r="A693" s="19"/>
+      <c r="A693" s="49"/>
       <c r="D693" s="17"/>
     </row>
     <row r="694" spans="1:4">
-      <c r="A694" s="19"/>
+      <c r="A694" s="49"/>
       <c r="D694" s="17"/>
     </row>
     <row r="695" spans="1:4">
-      <c r="A695" s="19"/>
+      <c r="A695" s="49"/>
       <c r="D695" s="17"/>
     </row>
     <row r="696" spans="1:4">
-      <c r="A696" s="19"/>
+      <c r="A696" s="49"/>
       <c r="D696" s="17"/>
     </row>
     <row r="697" spans="1:4">
-      <c r="A697" s="19"/>
+      <c r="A697" s="49"/>
       <c r="D697" s="17"/>
     </row>
     <row r="698" spans="1:4">
-      <c r="A698" s="19"/>
+      <c r="A698" s="49"/>
       <c r="D698" s="17"/>
     </row>
     <row r="699" spans="1:4">
-      <c r="A699" s="19"/>
+      <c r="A699" s="49"/>
       <c r="D699" s="17"/>
     </row>
     <row r="700" spans="1:4">
-      <c r="A700" s="19"/>
+      <c r="A700" s="49"/>
       <c r="D700" s="17"/>
     </row>
     <row r="701" spans="1:4">
-      <c r="A701" s="19"/>
+      <c r="A701" s="49"/>
       <c r="D701" s="17"/>
     </row>
     <row r="702" spans="1:4">
-      <c r="A702" s="19"/>
+      <c r="A702" s="49"/>
       <c r="D702" s="17"/>
     </row>
     <row r="703" spans="1:4">
-      <c r="A703" s="19"/>
+      <c r="A703" s="49"/>
       <c r="D703" s="17"/>
     </row>
     <row r="704" spans="1:4">
-      <c r="A704" s="19"/>
+      <c r="A704" s="49"/>
       <c r="D704" s="17"/>
     </row>
     <row r="705" spans="1:4">
-      <c r="A705" s="19"/>
+      <c r="A705" s="49"/>
       <c r="D705" s="17"/>
     </row>
     <row r="706" spans="1:4">
-      <c r="A706" s="19"/>
+      <c r="A706" s="49"/>
       <c r="D706" s="17"/>
     </row>
     <row r="707" spans="1:4">
-      <c r="A707" s="19"/>
+      <c r="A707" s="49"/>
       <c r="D707" s="17"/>
     </row>
     <row r="708" spans="1:4">
-      <c r="A708" s="19"/>
+      <c r="A708" s="49"/>
       <c r="D708" s="17"/>
     </row>
     <row r="709" spans="1:4">
-      <c r="A709" s="19"/>
+      <c r="A709" s="49"/>
       <c r="D709" s="17"/>
     </row>
     <row r="710" spans="1:4">
-      <c r="A710" s="19"/>
+      <c r="A710" s="49"/>
       <c r="D710" s="17"/>
     </row>
     <row r="711" spans="1:4">
-      <c r="A711" s="19"/>
+      <c r="A711" s="49"/>
       <c r="D711" s="17"/>
     </row>
     <row r="712" spans="1:4">
-      <c r="A712" s="19"/>
+      <c r="A712" s="49"/>
       <c r="D712" s="17"/>
     </row>
     <row r="713" spans="1:4">
-      <c r="A713" s="19"/>
+      <c r="A713" s="49"/>
       <c r="D713" s="17"/>
     </row>
     <row r="714" spans="1:4">
-      <c r="A714" s="19"/>
+      <c r="A714" s="49"/>
       <c r="D714" s="17"/>
     </row>
     <row r="715" spans="1:4">
-      <c r="A715" s="19"/>
+      <c r="A715" s="49"/>
       <c r="D715" s="17"/>
     </row>
     <row r="716" spans="1:4">
-      <c r="A716" s="19"/>
+      <c r="A716" s="49"/>
       <c r="D716" s="17"/>
     </row>
     <row r="717" spans="1:4">
-      <c r="A717" s="19"/>
+      <c r="A717" s="49"/>
       <c r="D717" s="17"/>
     </row>
     <row r="718" spans="1:4">
-      <c r="A718" s="19"/>
+      <c r="A718" s="49"/>
       <c r="D718" s="17"/>
     </row>
     <row r="719" spans="1:4">
-      <c r="A719" s="19"/>
+      <c r="A719" s="49"/>
       <c r="D719" s="17"/>
     </row>
     <row r="720" spans="1:4">
-      <c r="A720" s="19"/>
+      <c r="A720" s="49"/>
       <c r="D720" s="17"/>
     </row>
     <row r="721" spans="1:4">
-      <c r="A721" s="19"/>
+      <c r="A721" s="49"/>
       <c r="D721" s="17"/>
     </row>
     <row r="722" spans="1:4">
-      <c r="A722" s="19"/>
+      <c r="A722" s="49"/>
       <c r="D722" s="17"/>
     </row>
     <row r="723" spans="1:4">
-      <c r="A723" s="19"/>
+      <c r="A723" s="49"/>
       <c r="D723" s="17"/>
     </row>
     <row r="724" spans="1:4">
-      <c r="A724" s="19"/>
+      <c r="A724" s="49"/>
       <c r="D724" s="17"/>
     </row>
     <row r="725" spans="1:4">
-      <c r="A725" s="19"/>
+      <c r="A725" s="49"/>
       <c r="D725" s="17"/>
     </row>
     <row r="726" spans="1:4">
-      <c r="A726" s="19"/>
+      <c r="A726" s="49"/>
       <c r="D726" s="17"/>
     </row>
     <row r="727" spans="1:4">
-      <c r="A727" s="19"/>
+      <c r="A727" s="49"/>
       <c r="D727" s="17"/>
     </row>
     <row r="728" spans="1:4">
-      <c r="A728" s="19"/>
+      <c r="A728" s="49"/>
       <c r="D728" s="17"/>
     </row>
     <row r="729" spans="1:4">
-      <c r="A729" s="19"/>
+      <c r="A729" s="49"/>
       <c r="D729" s="17"/>
     </row>
     <row r="730" spans="1:4">
-      <c r="A730" s="19"/>
+      <c r="A730" s="49"/>
       <c r="D730" s="17"/>
     </row>
     <row r="731" spans="1:4">
-      <c r="A731" s="19"/>
+      <c r="A731" s="49"/>
       <c r="D731" s="17"/>
     </row>
     <row r="732" spans="1:4">
-      <c r="A732" s="19"/>
+      <c r="A732" s="49"/>
       <c r="D732" s="17"/>
     </row>
     <row r="733" spans="1:4">
-      <c r="A733" s="19"/>
+      <c r="A733" s="49"/>
       <c r="D733" s="17"/>
     </row>
     <row r="734" spans="1:4">
-      <c r="A734" s="19"/>
+      <c r="A734" s="49"/>
       <c r="D734" s="17"/>
     </row>
     <row r="735" spans="1:4">
-      <c r="A735" s="19"/>
+      <c r="A735" s="49"/>
       <c r="D735" s="17"/>
     </row>
     <row r="736" spans="1:4">
-      <c r="A736" s="19"/>
+      <c r="A736" s="49"/>
       <c r="D736" s="17"/>
     </row>
     <row r="737" spans="1:4">
-      <c r="A737" s="19"/>
+      <c r="A737" s="49"/>
       <c r="D737" s="17"/>
     </row>
     <row r="738" spans="1:4">
-      <c r="A738" s="19"/>
+      <c r="A738" s="49"/>
       <c r="D738" s="17"/>
     </row>
     <row r="739" spans="1:4">
-      <c r="A739" s="19"/>
+      <c r="A739" s="49"/>
       <c r="D739" s="17"/>
     </row>
     <row r="740" spans="1:4">
-      <c r="A740" s="19"/>
+      <c r="A740" s="49"/>
       <c r="D740" s="17"/>
     </row>
     <row r="741" spans="1:4">
-      <c r="A741" s="19"/>
+      <c r="A741" s="49"/>
       <c r="D741" s="17"/>
     </row>
     <row r="742" spans="1:4">
-      <c r="A742" s="19"/>
+      <c r="A742" s="49"/>
       <c r="D742" s="17"/>
     </row>
     <row r="743" spans="1:4">
-      <c r="A743" s="19"/>
+      <c r="A743" s="49"/>
       <c r="D743" s="17"/>
     </row>
     <row r="744" spans="1:4">
-      <c r="A744" s="19"/>
+      <c r="A744" s="49"/>
       <c r="D744" s="17"/>
     </row>
     <row r="745" spans="1:4">
-      <c r="A745" s="19"/>
+      <c r="A745" s="49"/>
       <c r="D745" s="17"/>
     </row>
     <row r="746" spans="1:4">
-      <c r="A746" s="19"/>
+      <c r="A746" s="49"/>
       <c r="D746" s="17"/>
     </row>
     <row r="747" spans="1:4">
-      <c r="A747" s="19"/>
+      <c r="A747" s="49"/>
       <c r="D747" s="17"/>
     </row>
     <row r="748" spans="1:4">
-      <c r="A748" s="19"/>
+      <c r="A748" s="49"/>
       <c r="D748" s="17"/>
     </row>
     <row r="749" spans="1:4">
-      <c r="A749" s="19"/>
+      <c r="A749" s="49"/>
       <c r="D749" s="17"/>
     </row>
     <row r="750" spans="1:4">
-      <c r="A750" s="19"/>
+      <c r="A750" s="49"/>
       <c r="D750" s="17"/>
     </row>
     <row r="751" spans="1:4">
-      <c r="A751" s="19"/>
+      <c r="A751" s="49"/>
       <c r="D751" s="17"/>
     </row>
     <row r="752" spans="1:4">
-      <c r="A752" s="19"/>
+      <c r="A752" s="49"/>
       <c r="D752" s="17"/>
     </row>
     <row r="753" spans="1:4">
-      <c r="A753" s="19"/>
+      <c r="A753" s="49"/>
       <c r="D753" s="17"/>
     </row>
     <row r="754" spans="1:4">
-      <c r="A754" s="19"/>
+      <c r="A754" s="49"/>
       <c r="D754" s="17"/>
     </row>
     <row r="755" spans="1:4">
-      <c r="A755" s="19"/>
+      <c r="A755" s="49"/>
       <c r="D755" s="17"/>
     </row>
     <row r="756" spans="1:4">
-      <c r="A756" s="19"/>
+      <c r="A756" s="49"/>
       <c r="D756" s="17"/>
     </row>
     <row r="757" spans="1:4">
-      <c r="A757" s="19"/>
+      <c r="A757" s="49"/>
       <c r="D757" s="17"/>
     </row>
     <row r="758" spans="1:4">
-      <c r="A758" s="19"/>
+      <c r="A758" s="49"/>
       <c r="D758" s="17"/>
     </row>
     <row r="759" spans="1:4">
-      <c r="A759" s="19"/>
+      <c r="A759" s="49"/>
       <c r="D759" s="17"/>
     </row>
     <row r="760" spans="1:4">
-      <c r="A760" s="19"/>
+      <c r="A760" s="49"/>
       <c r="D760" s="17"/>
     </row>
     <row r="761" spans="1:4">
-      <c r="A761" s="19"/>
+      <c r="A761" s="49"/>
       <c r="D761" s="17"/>
     </row>
     <row r="762" spans="1:4">
-      <c r="A762" s="19"/>
+      <c r="A762" s="49"/>
       <c r="D762" s="17"/>
     </row>
     <row r="763" spans="1:4">
-      <c r="A763" s="19"/>
+      <c r="A763" s="49"/>
       <c r="D763" s="17"/>
     </row>
     <row r="764" spans="1:4">
-      <c r="A764" s="19"/>
+      <c r="A764" s="49"/>
       <c r="D764" s="17"/>
     </row>
     <row r="765" spans="1:4">
-      <c r="A765" s="19"/>
+      <c r="A765" s="49"/>
       <c r="D765" s="17"/>
     </row>
     <row r="766" spans="1:4">
-      <c r="A766" s="19"/>
+      <c r="A766" s="49"/>
       <c r="D766" s="17"/>
     </row>
     <row r="767" spans="1:4">
-      <c r="A767" s="19"/>
+      <c r="A767" s="49"/>
       <c r="D767" s="17"/>
     </row>
     <row r="768" spans="1:4">
-      <c r="A768" s="19"/>
+      <c r="A768" s="49"/>
       <c r="D768" s="17"/>
     </row>
     <row r="769" spans="1:4">
-      <c r="A769" s="19"/>
+      <c r="A769" s="49"/>
       <c r="D769" s="17"/>
     </row>
     <row r="770" spans="1:4">
-      <c r="A770" s="19"/>
+      <c r="A770" s="49"/>
       <c r="D770" s="17"/>
     </row>
     <row r="771" spans="1:4">
-      <c r="A771" s="19"/>
+      <c r="A771" s="49"/>
       <c r="D771" s="17"/>
     </row>
     <row r="772" spans="1:4">
-      <c r="A772" s="19"/>
+      <c r="A772" s="49"/>
       <c r="D772" s="17"/>
     </row>
     <row r="773" spans="1:4">
-      <c r="A773" s="19"/>
+      <c r="A773" s="49"/>
       <c r="D773" s="17"/>
     </row>
     <row r="774" spans="1:4">
-      <c r="A774" s="19"/>
+      <c r="A774" s="49"/>
       <c r="D774" s="17"/>
     </row>
     <row r="775" spans="1:4">
-      <c r="A775" s="19"/>
+      <c r="A775" s="49"/>
       <c r="D775" s="17"/>
     </row>
     <row r="776" spans="1:4">
-      <c r="A776" s="19"/>
+      <c r="A776" s="49"/>
       <c r="D776" s="17"/>
     </row>
     <row r="777" spans="1:4">
-      <c r="A777" s="19"/>
+      <c r="A777" s="49"/>
       <c r="D777" s="17"/>
     </row>
     <row r="778" spans="1:4">
-      <c r="A778" s="19"/>
+      <c r="A778" s="49"/>
       <c r="D778" s="17"/>
     </row>
     <row r="779" spans="1:4">
-      <c r="A779" s="19"/>
+      <c r="A779" s="49"/>
       <c r="D779" s="17"/>
     </row>
     <row r="780" spans="1:4">
-      <c r="A780" s="19"/>
+      <c r="A780" s="49"/>
       <c r="D780" s="17"/>
     </row>
     <row r="781" spans="1:4">
-      <c r="A781" s="19"/>
+      <c r="A781" s="49"/>
       <c r="D781" s="17"/>
     </row>
     <row r="782" spans="1:4">
-      <c r="A782" s="19"/>
+      <c r="A782" s="49"/>
       <c r="D782" s="17"/>
     </row>
     <row r="783" spans="1:4">
-      <c r="A783" s="19"/>
+      <c r="A783" s="49"/>
       <c r="D783" s="17"/>
     </row>
     <row r="784" spans="1:4">
-      <c r="A784" s="19"/>
+      <c r="A784" s="49"/>
       <c r="D784" s="17"/>
     </row>
     <row r="785" spans="1:4">
-      <c r="A785" s="19"/>
+      <c r="A785" s="49"/>
       <c r="D785" s="17"/>
     </row>
     <row r="786" spans="1:4">
-      <c r="A786" s="19"/>
+      <c r="A786" s="49"/>
       <c r="D786" s="17"/>
     </row>
     <row r="787" spans="1:4">
-      <c r="A787" s="19"/>
+      <c r="A787" s="49"/>
       <c r="D787" s="17"/>
     </row>
     <row r="788" spans="1:4">
-      <c r="A788" s="19"/>
+      <c r="A788" s="49"/>
       <c r="D788" s="17"/>
     </row>
     <row r="789" spans="1:4">
-      <c r="A789" s="19"/>
+      <c r="A789" s="49"/>
       <c r="D789" s="17"/>
     </row>
     <row r="790" spans="1:4">
-      <c r="A790" s="19"/>
+      <c r="A790" s="49"/>
       <c r="D790" s="17"/>
     </row>
     <row r="791" spans="1:4">
-      <c r="A791" s="19"/>
+      <c r="A791" s="49"/>
       <c r="D791" s="17"/>
     </row>
     <row r="792" spans="1:4">
-      <c r="A792" s="19"/>
+      <c r="A792" s="49"/>
       <c r="D792" s="17"/>
     </row>
     <row r="793" spans="1:4">
-      <c r="A793" s="19"/>
+      <c r="A793" s="49"/>
       <c r="D793" s="17"/>
     </row>
     <row r="794" spans="1:4">
-      <c r="A794" s="19"/>
+      <c r="A794" s="49"/>
       <c r="D794" s="17"/>
     </row>
     <row r="795" spans="1:4">
-      <c r="A795" s="19"/>
+      <c r="A795" s="49"/>
       <c r="D795" s="17"/>
     </row>
     <row r="796" spans="1:4">
-      <c r="A796" s="19"/>
+      <c r="A796" s="49"/>
       <c r="D796" s="17"/>
     </row>
     <row r="797" spans="1:4">
-      <c r="A797" s="19"/>
+      <c r="A797" s="49"/>
       <c r="D797" s="17"/>
     </row>
     <row r="798" spans="1:4">
-      <c r="A798" s="19"/>
+      <c r="A798" s="49"/>
       <c r="D798" s="17"/>
     </row>
     <row r="799" spans="1:4">
-      <c r="A799" s="19"/>
+      <c r="A799" s="49"/>
       <c r="D799" s="17"/>
     </row>
     <row r="800" spans="1:4">
-      <c r="A800" s="19"/>
+      <c r="A800" s="49"/>
       <c r="D800" s="17"/>
     </row>
     <row r="801" spans="1:4">
-      <c r="A801" s="19"/>
+      <c r="A801" s="49"/>
       <c r="D801" s="17"/>
     </row>
     <row r="802" spans="1:4">
-      <c r="A802" s="19"/>
+      <c r="A802" s="49"/>
       <c r="D802" s="17"/>
     </row>
     <row r="803" spans="1:4">
-      <c r="A803" s="19"/>
+      <c r="A803" s="49"/>
       <c r="D803" s="17"/>
     </row>
     <row r="804" spans="1:4">
-      <c r="A804" s="19"/>
+      <c r="A804" s="49"/>
       <c r="D804" s="17"/>
     </row>
     <row r="805" spans="1:4">
-      <c r="A805" s="19"/>
+      <c r="A805" s="49"/>
       <c r="D805" s="17"/>
     </row>
     <row r="806" spans="1:4">
-      <c r="A806" s="19"/>
+      <c r="A806" s="49"/>
       <c r="D806" s="17"/>
     </row>
     <row r="807" spans="1:4">
-      <c r="A807" s="19"/>
+      <c r="A807" s="49"/>
       <c r="D807" s="17"/>
     </row>
     <row r="808" spans="1:4">
-      <c r="A808" s="19"/>
+      <c r="A808" s="49"/>
       <c r="D808" s="17"/>
     </row>
     <row r="809" spans="1:4">
-      <c r="A809" s="19"/>
+      <c r="A809" s="49"/>
       <c r="D809" s="17"/>
     </row>
     <row r="810" spans="1:4">
-      <c r="A810" s="19"/>
+      <c r="A810" s="49"/>
       <c r="D810" s="17"/>
     </row>
     <row r="811" spans="1:4">
-      <c r="A811" s="19"/>
+      <c r="A811" s="49"/>
       <c r="D811" s="17"/>
     </row>
     <row r="812" spans="1:4">
-      <c r="A812" s="19"/>
+      <c r="A812" s="49"/>
       <c r="D812" s="17"/>
     </row>
     <row r="813" spans="1:4">
-      <c r="A813" s="19"/>
+      <c r="A813" s="49"/>
       <c r="D813" s="17"/>
     </row>
     <row r="814" spans="1:4">
-      <c r="A814" s="19"/>
+      <c r="A814" s="49"/>
       <c r="D814" s="17"/>
     </row>
     <row r="815" spans="1:4">
-      <c r="A815" s="19"/>
+      <c r="A815" s="49"/>
       <c r="D815" s="17"/>
     </row>
     <row r="816" spans="1:4">
-      <c r="A816" s="19"/>
+      <c r="A816" s="49"/>
       <c r="D816" s="17"/>
     </row>
     <row r="817" spans="1:4">
-      <c r="A817" s="19"/>
+      <c r="A817" s="49"/>
       <c r="D817" s="17"/>
     </row>
     <row r="818" spans="1:4">
-      <c r="A818" s="19"/>
+      <c r="A818" s="49"/>
       <c r="D818" s="17"/>
     </row>
     <row r="819" spans="1:4">
-      <c r="A819" s="19"/>
+      <c r="A819" s="49"/>
       <c r="D819" s="17"/>
     </row>
     <row r="820" spans="1:4">
-      <c r="A820" s="19"/>
+      <c r="A820" s="49"/>
       <c r="D820" s="17"/>
     </row>
     <row r="821" spans="1:4">
-      <c r="A821" s="19"/>
+      <c r="A821" s="49"/>
       <c r="D821" s="17"/>
     </row>
     <row r="822" spans="1:4">
-      <c r="A822" s="19"/>
+      <c r="A822" s="49"/>
       <c r="D822" s="17"/>
     </row>
     <row r="823" spans="1:4">
-      <c r="A823" s="19"/>
+      <c r="A823" s="49"/>
       <c r="D823" s="17"/>
     </row>
     <row r="824" spans="1:4">
-      <c r="A824" s="19"/>
+      <c r="A824" s="49"/>
       <c r="D824" s="17"/>
     </row>
     <row r="825" spans="1:4">
-      <c r="A825" s="19"/>
+      <c r="A825" s="49"/>
       <c r="D825" s="17"/>
     </row>
     <row r="826" spans="1:4">
-      <c r="A826" s="19"/>
+      <c r="A826" s="49"/>
       <c r="D826" s="17"/>
     </row>
     <row r="827" spans="1:4">
-      <c r="A827" s="19"/>
+      <c r="A827" s="49"/>
       <c r="D827" s="17"/>
     </row>
     <row r="828" spans="1:4">
-      <c r="A828" s="19"/>
+      <c r="A828" s="49"/>
       <c r="D828" s="17"/>
     </row>
     <row r="829" spans="1:4">
-      <c r="A829" s="19"/>
+      <c r="A829" s="49"/>
       <c r="D829" s="17"/>
     </row>
     <row r="830" spans="1:4">
-      <c r="A830" s="19"/>
+      <c r="A830" s="49"/>
       <c r="D830" s="17"/>
     </row>
     <row r="831" spans="1:4">
-      <c r="A831" s="19"/>
+      <c r="A831" s="49"/>
       <c r="D831" s="17"/>
     </row>
     <row r="832" spans="1:4">
-      <c r="A832" s="19"/>
+      <c r="A832" s="49"/>
       <c r="D832" s="17"/>
     </row>
     <row r="833" spans="1:4">
-      <c r="A833" s="19"/>
+      <c r="A833" s="49"/>
       <c r="D833" s="17"/>
     </row>
     <row r="834" spans="1:4">
-      <c r="A834" s="19"/>
+      <c r="A834" s="49"/>
       <c r="D834" s="17"/>
     </row>
     <row r="835" spans="1:4">
-      <c r="A835" s="19"/>
+      <c r="A835" s="49"/>
       <c r="D835" s="17"/>
     </row>
     <row r="836" spans="1:4">
-      <c r="A836" s="19"/>
+      <c r="A836" s="49"/>
       <c r="D836" s="17"/>
     </row>
     <row r="837" spans="1:4">
-      <c r="A837" s="19"/>
+      <c r="A837" s="49"/>
       <c r="D837" s="17"/>
     </row>
     <row r="838" spans="1:4">
-      <c r="A838" s="19"/>
+      <c r="A838" s="49"/>
       <c r="D838" s="17"/>
     </row>
     <row r="839" spans="1:4">
-      <c r="A839" s="19"/>
+      <c r="A839" s="49"/>
       <c r="D839" s="17"/>
     </row>
     <row r="840" spans="1:4">
-      <c r="A840" s="19"/>
+      <c r="A840" s="49"/>
       <c r="D840" s="17"/>
     </row>
     <row r="841" spans="1:4">
-      <c r="A841" s="19"/>
+      <c r="A841" s="49"/>
       <c r="D841" s="17"/>
     </row>
     <row r="842" spans="1:4">
-      <c r="A842" s="19"/>
+      <c r="A842" s="49"/>
       <c r="D842" s="17"/>
     </row>
     <row r="843" spans="1:4">
-      <c r="A843" s="19"/>
+      <c r="A843" s="49"/>
       <c r="D843" s="17"/>
     </row>
     <row r="844" spans="1:4">
-      <c r="A844" s="19"/>
+      <c r="A844" s="49"/>
       <c r="D844" s="17"/>
     </row>
     <row r="845" spans="1:4">
-      <c r="A845" s="19"/>
+      <c r="A845" s="49"/>
       <c r="D845" s="17"/>
     </row>
     <row r="846" spans="1:4">
-      <c r="A846" s="19"/>
+      <c r="A846" s="49"/>
       <c r="D846" s="17"/>
     </row>
     <row r="847" spans="1:4">
-      <c r="A847" s="19"/>
+      <c r="A847" s="49"/>
       <c r="D847" s="17"/>
     </row>
     <row r="848" spans="1:4">
-      <c r="A848" s="19"/>
+      <c r="A848" s="49"/>
       <c r="D848" s="17"/>
     </row>
     <row r="849" spans="1:4">
-      <c r="A849" s="19"/>
+      <c r="A849" s="49"/>
       <c r="D849" s="17"/>
     </row>
     <row r="850" spans="1:4">
-      <c r="A850" s="19"/>
+      <c r="A850" s="49"/>
       <c r="D850" s="17"/>
     </row>
     <row r="851" spans="1:4">
-      <c r="A851" s="19"/>
+      <c r="A851" s="49"/>
       <c r="D851" s="17"/>
     </row>
     <row r="852" spans="1:4">
-      <c r="A852" s="19"/>
+      <c r="A852" s="49"/>
       <c r="D852" s="17"/>
     </row>
     <row r="853" spans="1:4">
-      <c r="A853" s="19"/>
+      <c r="A853" s="49"/>
       <c r="D853" s="17"/>
     </row>
     <row r="854" spans="1:4">
-      <c r="A854" s="19"/>
+      <c r="A854" s="49"/>
       <c r="D854" s="17"/>
     </row>
     <row r="855" spans="1:4">
-      <c r="A855" s="19"/>
+      <c r="A855" s="49"/>
       <c r="D855" s="17"/>
     </row>
     <row r="856" spans="1:4">
-      <c r="A856" s="19"/>
+      <c r="A856" s="49"/>
       <c r="D856" s="17"/>
     </row>
     <row r="857" spans="1:4">
-      <c r="A857" s="19"/>
+      <c r="A857" s="49"/>
       <c r="D857" s="17"/>
     </row>
     <row r="858" spans="1:4">
-      <c r="A858" s="19"/>
+      <c r="A858" s="49"/>
       <c r="D858" s="17"/>
     </row>
     <row r="859" spans="1:4">
-      <c r="A859" s="19"/>
+      <c r="A859" s="49"/>
       <c r="D859" s="17"/>
     </row>
     <row r="860" spans="1:4">
-      <c r="A860" s="19"/>
+      <c r="A860" s="49"/>
       <c r="D860" s="17"/>
     </row>
     <row r="861" spans="1:4">
-      <c r="A861" s="19"/>
+      <c r="A861" s="49"/>
       <c r="D861" s="17"/>
     </row>
     <row r="862" spans="1:4">
-      <c r="A862" s="19"/>
+      <c r="A862" s="49"/>
       <c r="D862" s="17"/>
     </row>
     <row r="863" spans="1:4">
-      <c r="A863" s="19"/>
+      <c r="A863" s="49"/>
       <c r="D863" s="17"/>
     </row>
     <row r="864" spans="1:4">
-      <c r="A864" s="19"/>
+      <c r="A864" s="49"/>
       <c r="D864" s="17"/>
     </row>
     <row r="865" spans="1:4">
-      <c r="A865" s="19"/>
+      <c r="A865" s="49"/>
       <c r="D865" s="17"/>
     </row>
     <row r="866" spans="1:4">
-      <c r="A866" s="19"/>
+      <c r="A866" s="49"/>
       <c r="D866" s="17"/>
     </row>
     <row r="867" spans="1:4">
-      <c r="A867" s="19"/>
+      <c r="A867" s="49"/>
       <c r="D867" s="17"/>
     </row>
     <row r="868" spans="1:4">
-      <c r="A868" s="19"/>
+      <c r="A868" s="49"/>
       <c r="D868" s="17"/>
     </row>
     <row r="869" spans="1:4">
-      <c r="A869" s="19"/>
+      <c r="A869" s="49"/>
       <c r="D869" s="17"/>
     </row>
     <row r="870" spans="1:4">
-      <c r="A870" s="19"/>
+      <c r="A870" s="49"/>
       <c r="D870" s="17"/>
     </row>
     <row r="871" spans="1:4">
-      <c r="A871" s="19"/>
+      <c r="A871" s="49"/>
       <c r="D871" s="17"/>
     </row>
     <row r="872" spans="1:4">
-      <c r="A872" s="19"/>
+      <c r="A872" s="49"/>
       <c r="D872" s="17"/>
     </row>
     <row r="873" spans="1:4">
-      <c r="A873" s="19"/>
+      <c r="A873" s="49"/>
       <c r="D873" s="17"/>
     </row>
     <row r="874" spans="1:4">
-      <c r="A874" s="19"/>
+      <c r="A874" s="49"/>
       <c r="D874" s="17"/>
     </row>
     <row r="875" spans="1:4">
-      <c r="A875" s="19"/>
+      <c r="A875" s="49"/>
       <c r="D875" s="17"/>
     </row>
     <row r="876" spans="1:4">
-      <c r="A876" s="19"/>
+      <c r="A876" s="49"/>
       <c r="D876" s="17"/>
     </row>
     <row r="877" spans="1:4">
-      <c r="A877" s="19"/>
+      <c r="A877" s="49"/>
       <c r="D877" s="17"/>
     </row>
     <row r="878" spans="1:4">
-      <c r="A878" s="19"/>
+      <c r="A878" s="49"/>
       <c r="D878" s="17"/>
     </row>
     <row r="879" spans="1:4">
-      <c r="A879" s="19"/>
+      <c r="A879" s="49"/>
       <c r="D879" s="17"/>
     </row>
     <row r="880" spans="1:4">
-      <c r="A880" s="19"/>
+      <c r="A880" s="49"/>
       <c r="D880" s="17"/>
     </row>
     <row r="881" spans="1:4">
-      <c r="A881" s="19"/>
+      <c r="A881" s="49"/>
       <c r="D881" s="17"/>
     </row>
     <row r="882" spans="1:4">
-      <c r="A882" s="19"/>
+      <c r="A882" s="49"/>
       <c r="D882" s="17"/>
     </row>
     <row r="883" spans="1:4">
-      <c r="A883" s="19"/>
+      <c r="A883" s="49"/>
       <c r="D883" s="17"/>
     </row>
     <row r="884" spans="1:4">
-      <c r="A884" s="19"/>
+      <c r="A884" s="49"/>
       <c r="D884" s="17"/>
     </row>
     <row r="885" spans="1:4">
-      <c r="A885" s="19"/>
+      <c r="A885" s="49"/>
       <c r="D885" s="17"/>
     </row>
     <row r="886" spans="1:4">
-      <c r="A886" s="19"/>
+      <c r="A886" s="49"/>
       <c r="D886" s="17"/>
     </row>
     <row r="887" spans="1:4">
-      <c r="A887" s="19"/>
+      <c r="A887" s="49"/>
       <c r="D887" s="17"/>
     </row>
     <row r="888" spans="1:4">
-      <c r="A888" s="19"/>
+      <c r="A888" s="49"/>
       <c r="D888" s="17"/>
     </row>
     <row r="889" spans="1:4">
-      <c r="A889" s="19"/>
+      <c r="A889" s="49"/>
       <c r="D889" s="17"/>
     </row>
     <row r="890" spans="1:4">
-      <c r="A890" s="19"/>
+      <c r="A890" s="49"/>
       <c r="D890" s="17"/>
     </row>
     <row r="891" spans="1:4">
-      <c r="A891" s="19"/>
+      <c r="A891" s="49"/>
       <c r="D891" s="17"/>
     </row>
     <row r="892" spans="1:4">
-      <c r="A892" s="19"/>
+      <c r="A892" s="49"/>
       <c r="D892" s="17"/>
     </row>
     <row r="893" spans="1:4">
-      <c r="A893" s="19"/>
+      <c r="A893" s="49"/>
       <c r="D893" s="17"/>
     </row>
     <row r="894" spans="1:4">
-      <c r="A894" s="19"/>
+      <c r="A894" s="49"/>
       <c r="D894" s="17"/>
     </row>
     <row r="895" spans="1:4">
-      <c r="A895" s="19"/>
+      <c r="A895" s="49"/>
       <c r="D895" s="17"/>
     </row>
     <row r="896" spans="1:4">
-      <c r="A896" s="19"/>
+      <c r="A896" s="49"/>
       <c r="D896" s="17"/>
     </row>
     <row r="897" spans="1:4">
-      <c r="A897" s="19"/>
+      <c r="A897" s="49"/>
       <c r="D897" s="17"/>
     </row>
     <row r="898" spans="1:4">
-      <c r="A898" s="19"/>
+      <c r="A898" s="49"/>
       <c r="D898" s="17"/>
     </row>
     <row r="899" spans="1:4">
-      <c r="A899" s="19"/>
+      <c r="A899" s="49"/>
       <c r="D899" s="17"/>
     </row>
     <row r="900" spans="1:4">
-      <c r="A900" s="19"/>
+      <c r="A900" s="49"/>
       <c r="D900" s="17"/>
     </row>
     <row r="901" spans="1:4">
-      <c r="A901" s="19"/>
+      <c r="A901" s="49"/>
       <c r="D901" s="17"/>
     </row>
     <row r="902" spans="1:4">
-      <c r="A902" s="19"/>
+      <c r="A902" s="49"/>
       <c r="D902" s="17"/>
     </row>
     <row r="903" spans="1:4">
-      <c r="A903" s="19"/>
+      <c r="A903" s="49"/>
       <c r="D903" s="17"/>
     </row>
     <row r="904" spans="1:4">
-      <c r="A904" s="19"/>
+      <c r="A904" s="49"/>
       <c r="D904" s="17"/>
     </row>
     <row r="905" spans="1:4">
-      <c r="A905" s="19"/>
+      <c r="A905" s="49"/>
       <c r="D905" s="17"/>
     </row>
     <row r="906" spans="1:4">
-      <c r="A906" s="19"/>
+      <c r="A906" s="49"/>
       <c r="D906" s="17"/>
     </row>
     <row r="907" spans="1:4">
-      <c r="A907" s="19"/>
+      <c r="A907" s="49"/>
       <c r="D907" s="17"/>
     </row>
     <row r="908" spans="1:4">
-      <c r="A908" s="19"/>
+      <c r="A908" s="49"/>
       <c r="D908" s="17"/>
     </row>
     <row r="909" spans="1:4">
-      <c r="A909" s="19"/>
+      <c r="A909" s="49"/>
       <c r="D909" s="17"/>
     </row>
     <row r="910" spans="1:4">
-      <c r="A910" s="19"/>
+      <c r="A910" s="49"/>
       <c r="D910" s="17"/>
     </row>
     <row r="911" spans="1:4">
-      <c r="A911" s="19"/>
+      <c r="A911" s="49"/>
       <c r="D911" s="17"/>
     </row>
     <row r="912" spans="1:4">
-      <c r="A912" s="19"/>
+      <c r="A912" s="49"/>
       <c r="D912" s="17"/>
     </row>
     <row r="913" spans="1:4">
-      <c r="A913" s="19"/>
+      <c r="A913" s="49"/>
       <c r="D913" s="17"/>
     </row>
     <row r="914" spans="1:4">
-      <c r="A914" s="19"/>
+      <c r="A914" s="49"/>
       <c r="D914" s="17"/>
     </row>
     <row r="915" spans="1:4">
-      <c r="A915" s="19"/>
+      <c r="A915" s="49"/>
       <c r="D915" s="17"/>
     </row>
     <row r="916" spans="1:4">
-      <c r="A916" s="19"/>
+      <c r="A916" s="49"/>
       <c r="D916" s="17"/>
     </row>
     <row r="917" spans="1:4">
-      <c r="A917" s="19"/>
+      <c r="A917" s="49"/>
       <c r="D917" s="17"/>
     </row>
     <row r="918" spans="1:4">
-      <c r="A918" s="19"/>
+      <c r="A918" s="49"/>
       <c r="D918" s="17"/>
     </row>
     <row r="919" spans="1:4">
-      <c r="A919" s="19"/>
+      <c r="A919" s="49"/>
       <c r="D919" s="17"/>
     </row>
     <row r="920" spans="1:4">
-      <c r="A920" s="19"/>
+      <c r="A920" s="49"/>
       <c r="D920" s="17"/>
     </row>
     <row r="921" spans="1:4">
-      <c r="A921" s="19"/>
+      <c r="A921" s="49"/>
       <c r="D921" s="17"/>
     </row>
     <row r="922" spans="1:4">
-      <c r="A922" s="19"/>
+      <c r="A922" s="49"/>
       <c r="D922" s="17"/>
     </row>
     <row r="923" spans="1:4">
-      <c r="A923" s="19"/>
+      <c r="A923" s="49"/>
       <c r="D923" s="17"/>
     </row>
     <row r="924" spans="1:4">
-      <c r="A924" s="19"/>
+      <c r="A924" s="49"/>
       <c r="D924" s="17"/>
     </row>
     <row r="925" spans="1:4">
-      <c r="A925" s="19"/>
+      <c r="A925" s="49"/>
       <c r="D925" s="17"/>
     </row>
     <row r="926" spans="1:4">
-      <c r="A926" s="19"/>
+      <c r="A926" s="49"/>
       <c r="D926" s="17"/>
     </row>
     <row r="927" spans="1:4">
-      <c r="A927" s="19"/>
+      <c r="A927" s="49"/>
       <c r="D927" s="17"/>
     </row>
     <row r="928" spans="1:4">
-      <c r="A928" s="19"/>
+      <c r="A928" s="49"/>
       <c r="D928" s="17"/>
     </row>
     <row r="929" spans="1:4">
-      <c r="A929" s="19"/>
+      <c r="A929" s="49"/>
       <c r="D929" s="17"/>
     </row>
     <row r="930" spans="1:4">
-      <c r="A930" s="19"/>
+      <c r="A930" s="49"/>
       <c r="D930" s="17"/>
     </row>
     <row r="931" spans="1:4">
-      <c r="A931" s="19"/>
+      <c r="A931" s="49"/>
       <c r="D931" s="17"/>
     </row>
     <row r="932" spans="1:4">
-      <c r="A932" s="19"/>
+      <c r="A932" s="49"/>
       <c r="D932" s="17"/>
     </row>
     <row r="933" spans="1:4">
-      <c r="A933" s="19"/>
+      <c r="A933" s="49"/>
       <c r="D933" s="17"/>
     </row>
     <row r="934" spans="1:4">
-      <c r="A934" s="19"/>
+      <c r="A934" s="49"/>
       <c r="D934" s="17"/>
     </row>
     <row r="935" spans="1:4">
-      <c r="A935" s="19"/>
+      <c r="A935" s="49"/>
       <c r="D935" s="17"/>
     </row>
     <row r="936" spans="1:4">
-      <c r="A936" s="19"/>
+      <c r="A936" s="49"/>
       <c r="D936" s="17"/>
     </row>
     <row r="937" spans="1:4">
-      <c r="A937" s="19"/>
+      <c r="A937" s="49"/>
       <c r="D937" s="17"/>
     </row>
     <row r="938" spans="1:4">
-      <c r="A938" s="19"/>
+      <c r="A938" s="49"/>
       <c r="D938" s="17"/>
     </row>
     <row r="939" spans="1:4">
-      <c r="A939" s="19"/>
+      <c r="A939" s="49"/>
       <c r="D939" s="17"/>
     </row>
     <row r="940" spans="1:4">
-      <c r="A940" s="19"/>
+      <c r="A940" s="49"/>
       <c r="D940" s="17"/>
     </row>
     <row r="941" spans="1:4">
-      <c r="A941" s="19"/>
+      <c r="A941" s="49"/>
       <c r="D941" s="17"/>
     </row>
     <row r="942" spans="1:4">
-      <c r="A942" s="19"/>
+      <c r="A942" s="49"/>
       <c r="D942" s="17"/>
     </row>
     <row r="943" spans="1:4">
-      <c r="A943" s="19"/>
+      <c r="A943" s="49"/>
       <c r="D943" s="17"/>
     </row>
     <row r="944" spans="1:4">
-      <c r="A944" s="19"/>
+      <c r="A944" s="49"/>
       <c r="D944" s="17"/>
     </row>
     <row r="945" spans="1:4">
-      <c r="A945" s="19"/>
+      <c r="A945" s="49"/>
       <c r="D945" s="17"/>
     </row>
     <row r="946" spans="1:4">
-      <c r="A946" s="19"/>
+      <c r="A946" s="49"/>
       <c r="D946" s="17"/>
     </row>
     <row r="947" spans="1:4">
-      <c r="A947" s="19"/>
+      <c r="A947" s="49"/>
       <c r="D947" s="17"/>
     </row>
     <row r="948" spans="1:4">
-      <c r="A948" s="19"/>
+      <c r="A948" s="49"/>
       <c r="D948" s="17"/>
     </row>
     <row r="949" spans="1:4">
-      <c r="A949" s="19"/>
+      <c r="A949" s="49"/>
       <c r="D949" s="17"/>
     </row>
     <row r="950" spans="1:4">
-      <c r="A950" s="19"/>
+      <c r="A950" s="49"/>
       <c r="D950" s="17"/>
     </row>
     <row r="951" spans="1:4">
-      <c r="A951" s="19"/>
+      <c r="A951" s="49"/>
       <c r="D951" s="17"/>
     </row>
     <row r="952" spans="1:4">
-      <c r="A952" s="19"/>
+      <c r="A952" s="49"/>
       <c r="D952" s="17"/>
     </row>
     <row r="953" spans="1:4">
-      <c r="A953" s="19"/>
+      <c r="A953" s="49"/>
       <c r="D953" s="17"/>
     </row>
     <row r="954" spans="1:4">
-      <c r="A954" s="19"/>
+      <c r="A954" s="49"/>
       <c r="D954" s="17"/>
     </row>
     <row r="955" spans="1:4">
-      <c r="A955" s="19"/>
+      <c r="A955" s="49"/>
       <c r="D955" s="17"/>
     </row>
     <row r="956" spans="1:4">
-      <c r="A956" s="19"/>
+      <c r="A956" s="49"/>
       <c r="D956" s="17"/>
     </row>
     <row r="957" spans="1:4">
-      <c r="A957" s="19"/>
+      <c r="A957" s="49"/>
       <c r="D957" s="17"/>
     </row>
     <row r="958" spans="1:4">
-      <c r="A958" s="19"/>
+      <c r="A958" s="49"/>
       <c r="D958" s="17"/>
     </row>
     <row r="959" spans="1:4">
-      <c r="A959" s="19"/>
+      <c r="A959" s="49"/>
       <c r="D959" s="17"/>
     </row>
     <row r="960" spans="1:4">
-      <c r="A960" s="19"/>
+      <c r="A960" s="49"/>
       <c r="D960" s="17"/>
     </row>
     <row r="961" spans="1:4">
-      <c r="A961" s="19"/>
+      <c r="A961" s="49"/>
       <c r="D961" s="17"/>
     </row>
     <row r="962" spans="1:4">
-      <c r="A962" s="19"/>
+      <c r="A962" s="49"/>
       <c r="D962" s="17"/>
     </row>
     <row r="963" spans="1:4">
-      <c r="A963" s="19"/>
+      <c r="A963" s="49"/>
       <c r="D963" s="17"/>
     </row>
     <row r="964" spans="1:4">
-      <c r="A964" s="19"/>
+      <c r="A964" s="49"/>
       <c r="D964" s="17"/>
     </row>
     <row r="965" spans="1:4">
-      <c r="A965" s="19"/>
+      <c r="A965" s="49"/>
       <c r="D965" s="17"/>
     </row>
     <row r="966" spans="1:4">
-      <c r="A966" s="19"/>
+      <c r="A966" s="49"/>
       <c r="D966" s="17"/>
     </row>
     <row r="967" spans="1:4">
-      <c r="A967" s="19"/>
+      <c r="A967" s="49"/>
       <c r="D967" s="17"/>
     </row>
     <row r="968" spans="1:4">
-      <c r="A968" s="19"/>
+      <c r="A968" s="49"/>
       <c r="D968" s="17"/>
     </row>
     <row r="969" spans="1:4">
-      <c r="A969" s="19"/>
+      <c r="A969" s="49"/>
       <c r="D969" s="17"/>
     </row>
     <row r="970" spans="1:4">
-      <c r="A970" s="19"/>
+      <c r="A970" s="49"/>
       <c r="D970" s="17"/>
     </row>
     <row r="971" spans="1:4">
-      <c r="A971" s="19"/>
+      <c r="A971" s="49"/>
       <c r="D971" s="17"/>
     </row>
     <row r="972" spans="1:4">
-      <c r="A972" s="19"/>
+      <c r="A972" s="49"/>
       <c r="D972" s="17"/>
     </row>
     <row r="973" spans="1:4">
-      <c r="A973" s="19"/>
+      <c r="A973" s="49"/>
       <c r="D973" s="17"/>
     </row>
     <row r="974" spans="1:4">
-      <c r="A974" s="19"/>
+      <c r="A974" s="49"/>
       <c r="D974" s="17"/>
     </row>
     <row r="975" spans="1:4">
-      <c r="A975" s="19"/>
+      <c r="A975" s="49"/>
       <c r="D975" s="17"/>
     </row>
     <row r="976" spans="1:4">
-      <c r="A976" s="19"/>
+      <c r="A976" s="49"/>
       <c r="D976" s="17"/>
     </row>
     <row r="977" spans="1:4">
-      <c r="A977" s="19"/>
+      <c r="A977" s="49"/>
       <c r="D977" s="17"/>
     </row>
     <row r="978" spans="1:4">
-      <c r="A978" s="19"/>
+      <c r="A978" s="49"/>
       <c r="D978" s="17"/>
     </row>
     <row r="979" spans="1:4">
-      <c r="A979" s="19"/>
+      <c r="A979" s="49"/>
       <c r="D979" s="17"/>
     </row>
     <row r="980" spans="1:4">
-      <c r="A980" s="19"/>
+      <c r="A980" s="49"/>
       <c r="D980" s="17"/>
     </row>
     <row r="981" spans="1:4">
-      <c r="A981" s="19"/>
+      <c r="A981" s="49"/>
       <c r="D981" s="17"/>
     </row>
     <row r="982" spans="1:4">
-      <c r="A982" s="19"/>
+      <c r="A982" s="49"/>
       <c r="D982" s="17"/>
     </row>
     <row r="983" spans="1:4">
-      <c r="A983" s="19"/>
+      <c r="A983" s="49"/>
       <c r="D983" s="17"/>
     </row>
     <row r="984" spans="1:4">
-      <c r="A984" s="19"/>
+      <c r="A984" s="49"/>
       <c r="D984" s="17"/>
     </row>
     <row r="985" spans="1:4">
-      <c r="A985" s="19"/>
+      <c r="A985" s="49"/>
       <c r="D985" s="17"/>
     </row>
     <row r="986" spans="1:4">
-      <c r="A986" s="19"/>
+      <c r="A986" s="49"/>
       <c r="D986" s="17"/>
     </row>
     <row r="987" spans="1:4">
-      <c r="A987" s="19"/>
+      <c r="A987" s="49"/>
       <c r="D987" s="17"/>
     </row>
     <row r="988" spans="1:4">
-      <c r="A988" s="19"/>
+      <c r="A988" s="49"/>
       <c r="D988" s="17"/>
     </row>
     <row r="989" spans="1:4">
-      <c r="A989" s="19"/>
+      <c r="A989" s="49"/>
       <c r="D989" s="17"/>
     </row>
     <row r="990" spans="1:4">
-      <c r="A990" s="19"/>
+      <c r="A990" s="49"/>
       <c r="D990" s="17"/>
     </row>
     <row r="991" spans="1:4">
-      <c r="A991" s="19"/>
+      <c r="A991" s="49"/>
       <c r="D991" s="17"/>
     </row>
     <row r="992" spans="1:4">
-      <c r="A992" s="19"/>
+      <c r="A992" s="49"/>
       <c r="D992" s="17"/>
     </row>
     <row r="993" spans="1:4">
-      <c r="A993" s="19"/>
+      <c r="A993" s="49"/>
       <c r="D993" s="17"/>
     </row>
     <row r="994" spans="1:4">
-      <c r="A994" s="19"/>
+      <c r="A994" s="49"/>
       <c r="D994" s="17"/>
     </row>
     <row r="995" spans="1:4">
-      <c r="A995" s="19"/>
+      <c r="A995" s="49"/>
       <c r="D995" s="17"/>
     </row>
     <row r="996" spans="1:4">
-      <c r="A996" s="19"/>
+      <c r="A996" s="49"/>
       <c r="D996" s="17"/>
     </row>
     <row r="997" spans="1:4">
-      <c r="A997" s="19"/>
+      <c r="A997" s="49"/>
       <c r="D997" s="17"/>
     </row>
     <row r="998" spans="1:4">
-      <c r="A998" s="19"/>
+      <c r="A998" s="49"/>
       <c r="D998" s="17"/>
     </row>
     <row r="999" spans="1:4">
-      <c r="A999" s="19"/>
+      <c r="A999" s="49"/>
       <c r="D999" s="17"/>
     </row>
     <row r="1000" spans="1:4">
-      <c r="A1000" s="19"/>
+      <c r="A1000" s="49"/>
       <c r="D1000" s="17"/>
     </row>
     <row r="1001" spans="1:4">
-      <c r="A1001" s="19"/>
+      <c r="A1001" s="49"/>
       <c r="D1001" s="17"/>
     </row>
     <row r="1002" spans="1:4">
-      <c r="A1002" s="19"/>
+      <c r="A1002" s="49"/>
       <c r="D1002" s="17"/>
     </row>
     <row r="1003" spans="1:4">
-      <c r="A1003" s="19"/>
+      <c r="A1003" s="49"/>
       <c r="D1003" s="17"/>
     </row>
     <row r="1004" spans="1:4">
-      <c r="A1004" s="19"/>
+      <c r="A1004" s="49"/>
       <c r="D1004" s="17"/>
     </row>
     <row r="1005" spans="1:4">
-      <c r="A1005" s="19"/>
+      <c r="A1005" s="49"/>
       <c r="D1005" s="17"/>
     </row>
     <row r="1006" spans="1:4">
-      <c r="A1006" s="19"/>
+      <c r="A1006" s="49"/>
       <c r="D1006" s="17"/>
     </row>
     <row r="1007" spans="1:4">
-      <c r="A1007" s="19"/>
+      <c r="A1007" s="49"/>
       <c r="D1007" s="17"/>
     </row>
     <row r="1008" spans="1:4">
-      <c r="A1008" s="19"/>
+      <c r="A1008" s="49"/>
       <c r="D1008" s="17"/>
     </row>
     <row r="1009" spans="1:4">
-      <c r="A1009" s="19"/>
+      <c r="A1009" s="49"/>
       <c r="D1009" s="17"/>
     </row>
     <row r="1010" spans="1:4">
-      <c r="A1010" s="19"/>
+      <c r="A1010" s="49"/>
       <c r="D1010" s="17"/>
     </row>
     <row r="1011" spans="1:4">
-      <c r="A1011" s="19"/>
+      <c r="A1011" s="49"/>
       <c r="D1011" s="17"/>
     </row>
     <row r="1012" spans="1:4">
-      <c r="A1012" s="19"/>
+      <c r="A1012" s="49"/>
       <c r="D1012" s="17"/>
     </row>
     <row r="1013" spans="1:4">
-      <c r="A1013" s="19"/>
+      <c r="A1013" s="49"/>
       <c r="D1013" s="17"/>
     </row>
     <row r="1014" spans="1:4">
-      <c r="A1014" s="19"/>
+      <c r="A1014" s="49"/>
       <c r="D1014" s="17"/>
     </row>
     <row r="1015" spans="1:4">
-      <c r="A1015" s="19"/>
+      <c r="A1015" s="49"/>
       <c r="D1015" s="17"/>
     </row>
     <row r="1016" spans="1:4">
-      <c r="A1016" s="19"/>
+      <c r="A1016" s="49"/>
       <c r="D1016" s="17"/>
     </row>
     <row r="1017" spans="1:4">
-      <c r="A1017" s="19"/>
+      <c r="A1017" s="49"/>
       <c r="D1017" s="17"/>
     </row>
     <row r="1018" spans="1:4">
-      <c r="A1018" s="19"/>
+      <c r="A1018" s="49"/>
       <c r="D1018" s="17"/>
     </row>
     <row r="1019" spans="1:4">
-      <c r="A1019" s="19"/>
+      <c r="A1019" s="49"/>
       <c r="D1019" s="17"/>
     </row>
     <row r="1020" spans="1:4">
-      <c r="A1020" s="19"/>
+      <c r="A1020" s="49"/>
       <c r="D1020" s="17"/>
     </row>
     <row r="1021" spans="1:4">
-      <c r="A1021" s="19"/>
+      <c r="A1021" s="49"/>
       <c r="D1021" s="17"/>
     </row>
     <row r="1022" spans="1:4">
-      <c r="A1022" s="19"/>
+      <c r="A1022" s="49"/>
       <c r="D1022" s="17"/>
     </row>
     <row r="1023" spans="1:4">
-      <c r="A1023" s="19"/>
+      <c r="A1023" s="49"/>
       <c r="D1023" s="17"/>
     </row>
     <row r="1024" spans="1:4">
-      <c r="A1024" s="19"/>
+      <c r="A1024" s="49"/>
       <c r="D1024" s="17"/>
     </row>
     <row r="1025" spans="1:4">
-      <c r="A1025" s="19"/>
+      <c r="A1025" s="49"/>
       <c r="D1025" s="17"/>
     </row>
     <row r="1026" spans="1:4">
-      <c r="A1026" s="19"/>
+      <c r="A1026" s="49"/>
       <c r="D1026" s="17"/>
     </row>
     <row r="1027" spans="1:4">
-      <c r="A1027" s="19"/>
+      <c r="A1027" s="49"/>
       <c r="D1027" s="17"/>
     </row>
     <row r="1028" spans="1:4">
-      <c r="A1028" s="19"/>
+      <c r="A1028" s="49"/>
       <c r="D1028" s="17"/>
     </row>
     <row r="1029" spans="1:4">
-      <c r="A1029" s="19"/>
+      <c r="A1029" s="49"/>
       <c r="D1029" s="17"/>
     </row>
     <row r="1030" spans="1:4">
-      <c r="A1030" s="19"/>
+      <c r="A1030" s="49"/>
       <c r="D1030" s="17"/>
     </row>
     <row r="1031" spans="1:4">
-      <c r="A1031" s="19"/>
+      <c r="A1031" s="49"/>
       <c r="D1031" s="17"/>
     </row>
     <row r="1032" spans="1:4">
-      <c r="A1032" s="19"/>
+      <c r="A1032" s="49"/>
       <c r="D1032" s="17"/>
     </row>
     <row r="1033" spans="1:4">
-      <c r="A1033" s="19"/>
+      <c r="A1033" s="49"/>
       <c r="D1033" s="17"/>
     </row>
     <row r="1034" spans="1:4">
-      <c r="A1034" s="19"/>
+      <c r="A1034" s="49"/>
       <c r="D1034" s="17"/>
     </row>
     <row r="1035" spans="1:4">
-      <c r="A1035" s="19"/>
+      <c r="A1035" s="49"/>
       <c r="D1035" s="17"/>
     </row>
     <row r="1036" spans="1:4">
-      <c r="A1036" s="19"/>
+      <c r="A1036" s="49"/>
       <c r="D1036" s="17"/>
     </row>
     <row r="1037" spans="1:4">
-      <c r="A1037" s="19"/>
+      <c r="A1037" s="49"/>
       <c r="D1037" s="17"/>
     </row>
     <row r="1038" spans="1:4">
-      <c r="A1038" s="19"/>
+      <c r="A1038" s="49"/>
       <c r="D1038" s="17"/>
     </row>
     <row r="1039" spans="1:4">
-      <c r="A1039" s="19"/>
+      <c r="A1039" s="49"/>
       <c r="D1039" s="17"/>
     </row>
     <row r="1040" spans="1:4">
-      <c r="A1040" s="19"/>
+      <c r="A1040" s="49"/>
       <c r="D1040" s="17"/>
     </row>
     <row r="1041" spans="1:4">
-      <c r="A1041" s="19"/>
+      <c r="A1041" s="49"/>
       <c r="D1041" s="17"/>
     </row>
     <row r="1042" spans="1:4">
-      <c r="A1042" s="19"/>
+      <c r="A1042" s="49"/>
       <c r="D1042" s="17"/>
     </row>
     <row r="1043" spans="1:4">
-      <c r="A1043" s="19"/>
+      <c r="A1043" s="49"/>
       <c r="D1043" s="17"/>
     </row>
     <row r="1044" spans="1:4">
-      <c r="A1044" s="19"/>
+      <c r="A1044" s="49"/>
       <c r="D1044" s="17"/>
     </row>
     <row r="1045" spans="1:4">
-      <c r="A1045" s="19"/>
+      <c r="A1045" s="49"/>
       <c r="D1045" s="17"/>
     </row>
     <row r="1046" spans="1:4">
-      <c r="A1046" s="19"/>
+      <c r="A1046" s="49"/>
       <c r="D1046" s="17"/>
     </row>
     <row r="1047" spans="1:4">
-      <c r="A1047" s="19"/>
+      <c r="A1047" s="49"/>
       <c r="D1047" s="17"/>
     </row>
     <row r="1048" spans="1:4">
-      <c r="A1048" s="19"/>
+      <c r="A1048" s="49"/>
       <c r="D1048" s="17"/>
     </row>
     <row r="1049" spans="1:4">
-      <c r="A1049" s="19"/>
+      <c r="A1049" s="49"/>
       <c r="D1049" s="17"/>
     </row>
     <row r="1050" spans="1:4">
-      <c r="A1050" s="19"/>
+      <c r="A1050" s="49"/>
       <c r="D1050" s="17"/>
     </row>
     <row r="1051" spans="1:4">
-      <c r="A1051" s="19"/>
+      <c r="A1051" s="49"/>
       <c r="D1051" s="17"/>
     </row>
     <row r="1052" spans="1:4">
-      <c r="A1052" s="19"/>
+      <c r="A1052" s="49"/>
       <c r="D1052" s="17"/>
     </row>
     <row r="1053" spans="1:4">
-      <c r="A1053" s="19"/>
+      <c r="A1053" s="49"/>
       <c r="D1053" s="17"/>
     </row>
     <row r="1054" spans="1:4">
-      <c r="A1054" s="19"/>
+      <c r="A1054" s="49"/>
       <c r="D1054" s="17"/>
     </row>
     <row r="1055" spans="1:4">
-      <c r="A1055" s="19"/>
+      <c r="A1055" s="49"/>
       <c r="D1055" s="17"/>
     </row>
     <row r="1056" spans="1:4">
-      <c r="A1056" s="19"/>
+      <c r="A1056" s="49"/>
       <c r="D1056" s="17"/>
     </row>
     <row r="1057" spans="1:4">
-      <c r="A1057" s="19"/>
+      <c r="A1057" s="49"/>
       <c r="D1057" s="17"/>
     </row>
     <row r="1058" spans="1:4">
-      <c r="A1058" s="19"/>
+      <c r="A1058" s="49"/>
       <c r="D1058" s="17"/>
     </row>
     <row r="1059" spans="1:4">
-      <c r="A1059" s="19"/>
+      <c r="A1059" s="49"/>
       <c r="D1059" s="17"/>
     </row>
     <row r="1060" spans="1:4">
-      <c r="A1060" s="19"/>
+      <c r="A1060" s="49"/>
       <c r="D1060" s="17"/>
     </row>
     <row r="1061" spans="1:4">
-      <c r="A1061" s="19"/>
+      <c r="A1061" s="49"/>
       <c r="D1061" s="17"/>
     </row>
     <row r="1062" spans="1:4">
-      <c r="A1062" s="19"/>
+      <c r="A1062" s="49"/>
       <c r="D1062" s="17"/>
     </row>
     <row r="1063" spans="1:4">
-      <c r="A1063" s="19"/>
+      <c r="A1063" s="49"/>
       <c r="D1063" s="17"/>
     </row>
     <row r="1064" spans="1:4">
-      <c r="A1064" s="19"/>
+      <c r="A1064" s="49"/>
       <c r="D1064" s="17"/>
     </row>
     <row r="1065" spans="1:4">
-      <c r="A1065" s="19"/>
+      <c r="A1065" s="49"/>
       <c r="D1065" s="17"/>
     </row>
     <row r="1066" spans="1:4">
-      <c r="A1066" s="19"/>
+      <c r="A1066" s="49"/>
       <c r="D1066" s="17"/>
     </row>
     <row r="1067" spans="1:4">
-      <c r="A1067" s="19"/>
+      <c r="A1067" s="49"/>
       <c r="D1067" s="17"/>
     </row>
     <row r="1068" spans="1:4">
-      <c r="A1068" s="19"/>
+      <c r="A1068" s="49"/>
       <c r="D1068" s="17"/>
     </row>
     <row r="1069" spans="1:4">
-      <c r="A1069" s="19"/>
+      <c r="A1069" s="49"/>
       <c r="D1069" s="17"/>
     </row>
     <row r="1070" spans="1:4">
-      <c r="A1070" s="19"/>
+      <c r="A1070" s="49"/>
       <c r="D1070" s="17"/>
     </row>
     <row r="1071" spans="1:4">
-      <c r="A1071" s="19"/>
+      <c r="A1071" s="49"/>
       <c r="D1071" s="17"/>
     </row>
     <row r="1072" spans="1:4">
-      <c r="A1072" s="19"/>
+      <c r="A1072" s="49"/>
       <c r="D1072" s="17"/>
     </row>
     <row r="1073" spans="1:4">
-      <c r="A1073" s="19"/>
+      <c r="A1073" s="49"/>
       <c r="D1073" s="17"/>
     </row>
     <row r="1074" spans="1:4">
-      <c r="A1074" s="19"/>
+      <c r="A1074" s="49"/>
       <c r="D1074" s="17"/>
     </row>
     <row r="1075" spans="1:4">
-      <c r="A1075" s="19"/>
+      <c r="A1075" s="49"/>
       <c r="D1075" s="17"/>
     </row>
     <row r="1076" spans="1:4">
-      <c r="A1076" s="19"/>
+      <c r="A1076" s="49"/>
       <c r="D1076" s="17"/>
     </row>
     <row r="1077" spans="1:4">
-      <c r="A1077" s="19"/>
+      <c r="A1077" s="49"/>
       <c r="D1077" s="17"/>
     </row>
     <row r="1078" spans="1:4">
-      <c r="A1078" s="19"/>
+      <c r="A1078" s="49"/>
       <c r="D1078" s="17"/>
     </row>
     <row r="1079" spans="1:4">
-      <c r="A1079" s="19"/>
+      <c r="A1079" s="49"/>
       <c r="D1079" s="17"/>
     </row>
     <row r="1080" spans="1:4">
-      <c r="A1080" s="19"/>
+      <c r="A1080" s="49"/>
       <c r="D1080" s="17"/>
     </row>
     <row r="1081" spans="1:4">
-      <c r="A1081" s="19"/>
+      <c r="A1081" s="49"/>
       <c r="D1081" s="17"/>
     </row>
     <row r="1082" spans="1:4">
-      <c r="A1082" s="19"/>
+      <c r="A1082" s="49"/>
       <c r="D1082" s="17"/>
     </row>
     <row r="1083" spans="1:4">
-      <c r="A1083" s="19"/>
+      <c r="A1083" s="49"/>
       <c r="D1083" s="17"/>
     </row>
     <row r="1084" spans="1:4">
-      <c r="A1084" s="19"/>
+      <c r="A1084" s="49"/>
       <c r="D1084" s="17"/>
     </row>
     <row r="1085" spans="1:4">
-      <c r="A1085" s="19"/>
+      <c r="A1085" s="49"/>
       <c r="D1085" s="17"/>
     </row>
     <row r="1086" spans="1:4">
-      <c r="A1086" s="19"/>
+      <c r="A1086" s="49"/>
       <c r="D1086" s="17"/>
     </row>
     <row r="1087" spans="1:4">
-      <c r="A1087" s="19"/>
+      <c r="A1087" s="49"/>
       <c r="D1087" s="17"/>
     </row>
     <row r="1088" spans="1:4">
-      <c r="A1088" s="19"/>
+      <c r="A1088" s="49"/>
       <c r="D1088" s="17"/>
     </row>
     <row r="1089" spans="1:4">
-      <c r="A1089" s="19"/>
+      <c r="A1089" s="49"/>
       <c r="D1089" s="17"/>
     </row>
     <row r="1090" spans="1:4">
-      <c r="A1090" s="19"/>
+      <c r="A1090" s="49"/>
       <c r="D1090" s="17"/>
     </row>
     <row r="1091" spans="1:4">
-      <c r="A1091" s="19"/>
+      <c r="A1091" s="49"/>
       <c r="D1091" s="17"/>
     </row>
     <row r="1092" spans="1:4">
-      <c r="A1092" s="19"/>
+      <c r="A1092" s="49"/>
       <c r="D1092" s="17"/>
     </row>
     <row r="1093" spans="1:4">
-      <c r="A1093" s="19"/>
+      <c r="A1093" s="49"/>
       <c r="D1093" s="17"/>
     </row>
     <row r="1094" spans="1:4">
-      <c r="A1094" s="19"/>
+      <c r="A1094" s="49"/>
       <c r="D1094" s="17"/>
     </row>
     <row r="1095" spans="1:4">
-      <c r="A1095" s="19"/>
+      <c r="A1095" s="49"/>
       <c r="D1095" s="17"/>
     </row>
     <row r="1096" spans="1:4">
-      <c r="A1096" s="19"/>
+      <c r="A1096" s="49"/>
       <c r="D1096" s="17"/>
     </row>
     <row r="1097" spans="1:4">
-      <c r="A1097" s="19"/>
+      <c r="A1097" s="49"/>
       <c r="D1097" s="17"/>
     </row>
     <row r="1098" spans="1:4">
-      <c r="A1098" s="19"/>
+      <c r="A1098" s="49"/>
       <c r="D1098" s="17"/>
     </row>
     <row r="1099" spans="1:4">
-      <c r="A1099" s="19"/>
+      <c r="A1099" s="49"/>
       <c r="D1099" s="17"/>
     </row>
     <row r="1100" spans="1:4">
-      <c r="A1100" s="19"/>
+      <c r="A1100" s="49"/>
       <c r="D1100" s="17"/>
     </row>
     <row r="1101" spans="1:4">
-      <c r="A1101" s="19"/>
+      <c r="A1101" s="49"/>
       <c r="D1101" s="17"/>
     </row>
     <row r="1102" spans="1:4">
-      <c r="A1102" s="19"/>
+      <c r="A1102" s="49"/>
       <c r="D1102" s="17"/>
     </row>
     <row r="1103" spans="1:4">
-      <c r="A1103" s="19"/>
+      <c r="A1103" s="49"/>
       <c r="D1103" s="17"/>
     </row>
     <row r="1104" spans="1:4">
-      <c r="A1104" s="19"/>
+      <c r="A1104" s="49"/>
       <c r="D1104" s="17"/>
     </row>
     <row r="1105" spans="1:4">
-      <c r="A1105" s="19"/>
+      <c r="A1105" s="49"/>
       <c r="D1105" s="17"/>
     </row>
     <row r="1106" spans="1:4">
-      <c r="A1106" s="19"/>
+      <c r="A1106" s="49"/>
       <c r="D1106" s="17"/>
     </row>
     <row r="1107" spans="1:4">
-      <c r="A1107" s="19"/>
+      <c r="A1107" s="49"/>
       <c r="D1107" s="17"/>
     </row>
     <row r="1108" spans="1:4">
-      <c r="A1108" s="19"/>
+      <c r="A1108" s="49"/>
       <c r="D1108" s="17"/>
     </row>
     <row r="1109" spans="1:4">
-      <c r="A1109" s="19"/>
+      <c r="A1109" s="49"/>
       <c r="D1109" s="17"/>
     </row>
     <row r="1110" spans="1:4">
-      <c r="A1110" s="19"/>
+      <c r="A1110" s="49"/>
       <c r="D1110" s="17"/>
     </row>
     <row r="1111" spans="1:4">
-      <c r="A1111" s="19"/>
+      <c r="A1111" s="49"/>
       <c r="D1111" s="17"/>
     </row>
     <row r="1112" spans="1:4">
-      <c r="A1112" s="19"/>
+      <c r="A1112" s="49"/>
       <c r="D1112" s="17"/>
     </row>
     <row r="1113" spans="1:4">
-      <c r="A1113" s="19"/>
+      <c r="A1113" s="49"/>
       <c r="D1113" s="17"/>
     </row>
     <row r="1114" spans="1:4">
-      <c r="A1114" s="19"/>
+      <c r="A1114" s="49"/>
       <c r="D1114" s="17"/>
     </row>
     <row r="1115" spans="1:4">
-      <c r="A1115" s="19"/>
+      <c r="A1115" s="49"/>
       <c r="D1115" s="17"/>
     </row>
     <row r="1116" spans="1:4">
-      <c r="A1116" s="19"/>
+      <c r="A1116" s="49"/>
       <c r="D1116" s="17"/>
     </row>
     <row r="1117" spans="1:4">
-      <c r="A1117" s="19"/>
+      <c r="A1117" s="49"/>
       <c r="D1117" s="17"/>
     </row>
     <row r="1118" spans="1:4">
-      <c r="A1118" s="19"/>
+      <c r="A1118" s="49"/>
       <c r="D1118" s="17"/>
     </row>
     <row r="1119" spans="1:4">
-      <c r="A1119" s="19"/>
+      <c r="A1119" s="49"/>
       <c r="D1119" s="17"/>
     </row>
     <row r="1120" spans="1:4">
-      <c r="A1120" s="19"/>
+      <c r="A1120" s="49"/>
       <c r="D1120" s="17"/>
     </row>
     <row r="1121" spans="1:4">
-      <c r="A1121" s="19"/>
+      <c r="A1121" s="49"/>
       <c r="D1121" s="17"/>
     </row>
     <row r="1122" spans="1:4">
-      <c r="A1122" s="19"/>
+      <c r="A1122" s="49"/>
       <c r="D1122" s="17"/>
     </row>
     <row r="1123" spans="1:4">
-      <c r="A1123" s="19"/>
+      <c r="A1123" s="49"/>
       <c r="D1123" s="17"/>
     </row>
     <row r="1124" spans="1:4">
-      <c r="A1124" s="19"/>
+      <c r="A1124" s="49"/>
       <c r="D1124" s="17"/>
     </row>
     <row r="1125" spans="1:4">
-      <c r="A1125" s="19"/>
+      <c r="A1125" s="49"/>
       <c r="D1125" s="17"/>
     </row>
     <row r="1126" spans="1:4">
-      <c r="A1126" s="19"/>
+      <c r="A1126" s="49"/>
       <c r="D1126" s="17"/>
     </row>
     <row r="1127" spans="1:4">
-      <c r="A1127" s="19"/>
+      <c r="A1127" s="49"/>
       <c r="D1127" s="17"/>
     </row>
     <row r="1128" spans="1:4">
-      <c r="A1128" s="19"/>
+      <c r="A1128" s="49"/>
       <c r="D1128" s="17"/>
     </row>
     <row r="1129" spans="1:4">
-      <c r="A1129" s="19"/>
+      <c r="A1129" s="49"/>
       <c r="D1129" s="17"/>
     </row>
     <row r="1130" spans="1:4">
-      <c r="A1130" s="19"/>
+      <c r="A1130" s="49"/>
       <c r="D1130" s="17"/>
     </row>
     <row r="1131" spans="1:4">
-      <c r="A1131" s="19"/>
+      <c r="A1131" s="49"/>
       <c r="D1131" s="17"/>
     </row>
     <row r="1132" spans="1:4">
-      <c r="A1132" s="19"/>
+      <c r="A1132" s="49"/>
       <c r="D1132" s="17"/>
     </row>
     <row r="1133" spans="1:4">
-      <c r="A1133" s="19"/>
+      <c r="A1133" s="49"/>
       <c r="D1133" s="17"/>
     </row>
     <row r="1134" spans="1:4">
-      <c r="A1134" s="19"/>
+      <c r="A1134" s="49"/>
       <c r="D1134" s="17"/>
     </row>
     <row r="1135" spans="1:4">
-      <c r="A1135" s="19"/>
+      <c r="A1135" s="49"/>
       <c r="D1135" s="17"/>
     </row>
     <row r="1136" spans="1:4">
-      <c r="A1136" s="19"/>
+      <c r="A1136" s="49"/>
       <c r="D1136" s="17"/>
     </row>
     <row r="1137" spans="1:4">
-      <c r="A1137" s="19"/>
+      <c r="A1137" s="49"/>
       <c r="D1137" s="17"/>
     </row>
     <row r="1138" spans="1:4">
-      <c r="A1138" s="19"/>
+      <c r="A1138" s="49"/>
       <c r="D1138" s="17"/>
     </row>
     <row r="1139" spans="1:4">
-      <c r="A1139" s="19"/>
+      <c r="A1139" s="49"/>
       <c r="D1139" s="17"/>
     </row>
     <row r="1140" spans="1:4">
-      <c r="A1140" s="19"/>
+      <c r="A1140" s="49"/>
       <c r="D1140" s="17"/>
     </row>
     <row r="1141" spans="1:4">
-      <c r="A1141" s="19"/>
+      <c r="A1141" s="49"/>
       <c r="D1141" s="17"/>
     </row>
     <row r="1142" spans="1:4">
-      <c r="A1142" s="19"/>
+      <c r="A1142" s="49"/>
       <c r="D1142" s="17"/>
     </row>
     <row r="1143" spans="1:4">
-      <c r="A1143" s="19"/>
+      <c r="A1143" s="49"/>
       <c r="D1143" s="17"/>
     </row>
     <row r="1144" spans="1:4">
-      <c r="A1144" s="19"/>
+      <c r="A1144" s="49"/>
       <c r="D1144" s="17"/>
     </row>
     <row r="1145" spans="1:4">
-      <c r="A1145" s="19"/>
+      <c r="A1145" s="49"/>
       <c r="D1145" s="17"/>
     </row>
     <row r="1146" spans="1:4">
-      <c r="A1146" s="19"/>
+      <c r="A1146" s="49"/>
       <c r="D1146" s="17"/>
     </row>
     <row r="1147" spans="1:4">
-      <c r="A1147" s="19"/>
+      <c r="A1147" s="49"/>
       <c r="D1147" s="17"/>
     </row>
     <row r="1148" spans="1:4">
-      <c r="A1148" s="19"/>
+      <c r="A1148" s="49"/>
       <c r="D1148" s="17"/>
     </row>
     <row r="1149" spans="1:4">
-      <c r="A1149" s="19"/>
+      <c r="A1149" s="49"/>
       <c r="D1149" s="17"/>
     </row>
     <row r="1150" spans="1:4">
-      <c r="A1150" s="19"/>
+      <c r="A1150" s="49"/>
       <c r="D1150" s="17"/>
     </row>
     <row r="1151" spans="1:4">
-      <c r="A1151" s="19"/>
+      <c r="A1151" s="49"/>
       <c r="D1151" s="17"/>
     </row>
     <row r="1152" spans="1:4">
-      <c r="A1152" s="19"/>
+      <c r="A1152" s="49"/>
       <c r="D1152" s="17"/>
     </row>
     <row r="1153" spans="1:4">
-      <c r="A1153" s="19"/>
+      <c r="A1153" s="49"/>
       <c r="D1153" s="17"/>
     </row>
     <row r="1154" spans="1:4">
-      <c r="A1154" s="19"/>
+      <c r="A1154" s="49"/>
       <c r="D1154" s="17"/>
     </row>
     <row r="1155" spans="1:4">
-      <c r="A1155" s="19"/>
+      <c r="A1155" s="49"/>
       <c r="D1155" s="17"/>
     </row>
     <row r="1156" spans="1:4">
-      <c r="A1156" s="19"/>
+      <c r="A1156" s="49"/>
       <c r="D1156" s="17"/>
     </row>
     <row r="1157" spans="1:4">
-      <c r="A1157" s="19"/>
+      <c r="A1157" s="49"/>
       <c r="D1157" s="17"/>
     </row>
     <row r="1158" spans="1:4">
-      <c r="A1158" s="19"/>
+      <c r="A1158" s="49"/>
       <c r="D1158" s="17"/>
     </row>
     <row r="1159" spans="1:4">
-      <c r="A1159" s="19"/>
+      <c r="A1159" s="49"/>
       <c r="D1159" s="17"/>
     </row>
     <row r="1160" spans="1:4">
-      <c r="A1160" s="19"/>
+      <c r="A1160" s="49"/>
       <c r="D1160" s="17"/>
     </row>
     <row r="1161" spans="1:4">
-      <c r="A1161" s="19"/>
+      <c r="A1161" s="49"/>
       <c r="D1161" s="17"/>
     </row>
     <row r="1162" spans="1:4">
-      <c r="A1162" s="19"/>
+      <c r="A1162" s="49"/>
       <c r="D1162" s="17"/>
     </row>
     <row r="1163" spans="1:4">
-      <c r="A1163" s="19"/>
+      <c r="A1163" s="49"/>
       <c r="D1163" s="17"/>
     </row>
     <row r="1164" spans="1:4">
-      <c r="A1164" s="19"/>
+      <c r="A1164" s="49"/>
       <c r="D1164" s="17"/>
     </row>
     <row r="1165" spans="1:4">
-      <c r="A1165" s="19"/>
+      <c r="A1165" s="49"/>
       <c r="D1165" s="17"/>
     </row>
     <row r="1166" spans="1:4">
-      <c r="A1166" s="19"/>
+      <c r="A1166" s="49"/>
       <c r="D1166" s="17"/>
     </row>
     <row r="1167" spans="1:4">
-      <c r="A1167" s="19"/>
+      <c r="A1167" s="49"/>
       <c r="D1167" s="17"/>
     </row>
   </sheetData>
@@ -9304,7 +9332,7 @@
     <hyperlink ref="F84" r:id="rId19" display="protoboy9999@gmail.com"/>
     <hyperlink ref="F118" r:id="rId20" display="khadidjafezazi90@gmail"/>
     <hyperlink ref="F78" r:id="rId21" display="elghodasseabdelmadjid@gmail.com"/>
-    <hyperlink ref="F75" r:id="rId22" display="Lamia_du22@hotmail.com"/>
+    <hyperlink ref="F75" r:id="rId22" display="Lamia_du22@hotmail.com" tooltip="mailto:Lamia_du22@hotmail.com"/>
     <hyperlink ref="F70" r:id="rId23" display="douaaboularaf@gmail.com"/>
     <hyperlink ref="F114" r:id="rId24" display="berhenen@yahoo.fr"/>
     <hyperlink ref="F64" r:id="rId25" display="rawnakritedj@gmail.com" tooltip="mailto:rawnakritedj@gmail.com"/>
@@ -9324,6 +9352,12 @@
     <hyperlink ref="F83" r:id="rId39" display="ahmed.hadji22@yahoo.com"/>
     <hyperlink ref="F106" r:id="rId40" display="berhenen@yahoo.fr"/>
     <hyperlink ref="F32" r:id="rId41" display="khatir.mohamed1977@gmail.com"/>
+    <hyperlink ref="F2" r:id="rId42" display="irecom_abid@yahoo.fr"/>
+    <hyperlink ref="F7" r:id="rId43" display="karis483@hotmail.fr"/>
+    <hyperlink ref="F8" r:id="rId44" display="bahlilmounir@yahoo.fr"/>
+    <hyperlink ref="F10" r:id="rId45" display="beddadboucif@gmail.com"/>
+    <hyperlink ref="F9" r:id="rId46" display="seyfeddine.electrotechnique@gmail.com"/>
+    <hyperlink ref="F130" r:id="rId47" display="milouaf@yahoo.fr" tooltip="mailto:milouaf@yahoo.fr"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
@@ -9346,202 +9380,202 @@
   <sheetData>
     <row r="1" ht="15.75" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="2" ht="15.75" spans="1:4">
       <c r="A2" s="4" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="3" ht="15.75" spans="1:4">
       <c r="A3" s="8"/>
       <c r="B3" s="5" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="4" ht="15.75" spans="1:4">
       <c r="A4" s="8"/>
       <c r="B4" s="5" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="5" ht="15.75" spans="1:4">
       <c r="A5" s="8"/>
       <c r="B5" s="5" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="6" ht="15.75" spans="1:4">
       <c r="A6" s="8"/>
       <c r="B6" s="5" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="7" ht="15.75" spans="1:4">
       <c r="A7" s="9" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="8" ht="15.75" spans="1:4">
       <c r="A8" s="8"/>
       <c r="B8" s="10" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="9" ht="15.75" spans="1:4">
       <c r="A9" s="11" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="10" ht="15.75" spans="1:4">
       <c r="A10" s="8"/>
       <c r="B10" s="13" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="11" ht="15.75" spans="1:4">
       <c r="A11" s="8"/>
       <c r="B11" s="13" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="12" ht="15.75" spans="1:4">
       <c r="A12" s="8"/>
       <c r="B12" s="13" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="13" ht="15.75" spans="1:4">
       <c r="A13" s="8"/>
       <c r="B13" s="13" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="14" ht="15.75" spans="1:4">
       <c r="A14" s="8"/>
       <c r="B14" s="13" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="15" ht="15.75" spans="1:4">
       <c r="A15" s="8"/>
       <c r="B15" s="13" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="16" ht="15.75" spans="1:4">
       <c r="A16" s="8"/>
       <c r="B16" s="13" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
     </row>
     <row r="656" ht="15.75"/>
